--- a/orcamento/Orcamento_JURIDICO_2026.xlsx
+++ b/orcamento/Orcamento_JURIDICO_2026.xlsx
@@ -17,8 +17,8 @@
     <sheet name="Como usar" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Comparativo'!$A$5:$N$15</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Planejado'!$A$4:$T$14</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Comparativo'!$A$5:$N$14</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Planejado'!$A$4:$T$13</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -1115,15 +1115,15 @@
         </is>
       </c>
       <c r="C6" s="8">
-        <f>SUMIFS(Planejado!$T$5:$T$14,Planejado!$B$5:$B$14,"Jurídico",Planejado!$C$5:$C$14,"Equipe")</f>
+        <f>SUMIFS(Planejado!$T$5:$T$13,Planejado!$B$5:$B$13,"Jurídico",Planejado!$C$5:$C$13,"Equipe")</f>
         <v/>
       </c>
       <c r="D6" s="8">
-        <f>SUMIFS(Comparativo!$I$6:$I$15,Comparativo!$B$6:$B$15,"Jurídico",Comparativo!$C$6:$C$15,"Equipe")</f>
+        <f>SUMIFS(Comparativo!$I$6:$I$14,Comparativo!$B$6:$B$14,"Jurídico",Comparativo!$C$6:$C$14,"Equipe")</f>
         <v/>
       </c>
       <c r="E6" s="8">
-        <f>SUMIFS(Comparativo!$J$6:$J$15,Comparativo!$B$6:$B$15,"Jurídico",Comparativo!$C$6:$C$15,"Equipe")</f>
+        <f>SUMIFS(Comparativo!$J$6:$J$14,Comparativo!$B$6:$B$14,"Jurídico",Comparativo!$C$6:$C$14,"Equipe")</f>
         <v/>
       </c>
       <c r="F6" s="8">
@@ -1139,7 +1139,7 @@
         <v/>
       </c>
       <c r="I6" s="10">
-        <f>COUNTIFS(Comparativo!$P$6:$P$15,"&gt;0",Comparativo!$B$6:$B$15,"Jurídico",Comparativo!$C$6:$C$15,"Equipe")&amp;" de "&amp;COUNTIFS(Comparativo!$A$6:$A$15,"?*",Comparativo!$B$6:$B$15,"Jurídico",Comparativo!$C$6:$C$15,"Equipe")</f>
+        <f>COUNTIFS(Comparativo!$P$6:$P$14,"&gt;0",Comparativo!$B$6:$B$14,"Jurídico",Comparativo!$C$6:$C$14,"Equipe")&amp;" de "&amp;COUNTIFS(Comparativo!$A$6:$A$14,"?*",Comparativo!$B$6:$B$14,"Jurídico",Comparativo!$C$6:$C$14,"Equipe")</f>
         <v/>
       </c>
     </row>
@@ -1155,15 +1155,15 @@
         </is>
       </c>
       <c r="C7" s="8">
-        <f>SUMIFS(Planejado!$T$5:$T$14,Planejado!$B$5:$B$14,"Jurídico",Planejado!$C$5:$C$14,"Despesas")</f>
+        <f>SUMIFS(Planejado!$T$5:$T$13,Planejado!$B$5:$B$13,"Jurídico",Planejado!$C$5:$C$13,"Despesas")</f>
         <v/>
       </c>
       <c r="D7" s="8">
-        <f>SUMIFS(Comparativo!$I$6:$I$15,Comparativo!$B$6:$B$15,"Jurídico",Comparativo!$C$6:$C$15,"Despesas")</f>
+        <f>SUMIFS(Comparativo!$I$6:$I$14,Comparativo!$B$6:$B$14,"Jurídico",Comparativo!$C$6:$C$14,"Despesas")</f>
         <v/>
       </c>
       <c r="E7" s="8">
-        <f>SUMIFS(Comparativo!$J$6:$J$15,Comparativo!$B$6:$B$15,"Jurídico",Comparativo!$C$6:$C$15,"Despesas")</f>
+        <f>SUMIFS(Comparativo!$J$6:$J$14,Comparativo!$B$6:$B$14,"Jurídico",Comparativo!$C$6:$C$14,"Despesas")</f>
         <v/>
       </c>
       <c r="F7" s="8">
@@ -1179,7 +1179,7 @@
         <v/>
       </c>
       <c r="I7" s="10">
-        <f>COUNTIFS(Comparativo!$P$6:$P$15,"&gt;0",Comparativo!$B$6:$B$15,"Jurídico",Comparativo!$C$6:$C$15,"Despesas")&amp;" de "&amp;COUNTIFS(Comparativo!$A$6:$A$15,"?*",Comparativo!$B$6:$B$15,"Jurídico",Comparativo!$C$6:$C$15,"Despesas")</f>
+        <f>COUNTIFS(Comparativo!$P$6:$P$14,"&gt;0",Comparativo!$B$6:$B$14,"Jurídico",Comparativo!$C$6:$C$14,"Despesas")&amp;" de "&amp;COUNTIFS(Comparativo!$A$6:$A$14,"?*",Comparativo!$B$6:$B$14,"Jurídico",Comparativo!$C$6:$C$14,"Despesas")</f>
         <v/>
       </c>
     </row>
@@ -1195,15 +1195,15 @@
         </is>
       </c>
       <c r="C8" s="12">
-        <f>SUMIFS(Planejado!$T$5:$T$14,Planejado!$B$5:$B$14,"Jurídico")</f>
+        <f>SUMIFS(Planejado!$T$5:$T$13,Planejado!$B$5:$B$13,"Jurídico")</f>
         <v/>
       </c>
       <c r="D8" s="12">
-        <f>SUMIFS(Comparativo!$I$6:$I$15,Comparativo!$B$6:$B$15,"Jurídico")</f>
+        <f>SUMIFS(Comparativo!$I$6:$I$14,Comparativo!$B$6:$B$14,"Jurídico")</f>
         <v/>
       </c>
       <c r="E8" s="12">
-        <f>SUMIFS(Comparativo!$J$6:$J$15,Comparativo!$B$6:$B$15,"Jurídico")</f>
+        <f>SUMIFS(Comparativo!$J$6:$J$14,Comparativo!$B$6:$B$14,"Jurídico")</f>
         <v/>
       </c>
       <c r="F8" s="12">
@@ -1219,7 +1219,7 @@
         <v/>
       </c>
       <c r="I8" s="14">
-        <f>COUNTIFS(Comparativo!$P$6:$P$15,"&gt;0",Comparativo!$B$6:$B$15,"Jurídico")&amp;" de "&amp;COUNTIFS(Comparativo!$A$6:$A$15,"?*",Comparativo!$B$6:$B$15,"Jurídico")</f>
+        <f>COUNTIFS(Comparativo!$P$6:$P$14,"&gt;0",Comparativo!$B$6:$B$14,"Jurídico")&amp;" de "&amp;COUNTIFS(Comparativo!$A$6:$A$14,"?*",Comparativo!$B$6:$B$14,"Jurídico")</f>
         <v/>
       </c>
     </row>
@@ -1273,23 +1273,23 @@
         <v>1</v>
       </c>
       <c r="B13" s="17">
-        <f>IFERROR(INDEX(Comparativo!$D$6:$D$15,MATCH(LARGE(Comparativo!$O$6:$O$15,A13),Comparativo!$O$6:$O$15,0)),"")</f>
+        <f>IFERROR(INDEX(Comparativo!$D$6:$D$14,MATCH(LARGE(Comparativo!$O$6:$O$14,A13),Comparativo!$O$6:$O$14,0)),"")</f>
         <v/>
       </c>
       <c r="C13" s="17">
-        <f>IFERROR(INDEX(Comparativo!$B$6:$B$15,MATCH(LARGE(Comparativo!$O$6:$O$15,A13),Comparativo!$O$6:$O$15,0)),"")</f>
+        <f>IFERROR(INDEX(Comparativo!$B$6:$B$14,MATCH(LARGE(Comparativo!$O$6:$O$14,A13),Comparativo!$O$6:$O$14,0)),"")</f>
         <v/>
       </c>
       <c r="D13" s="18">
-        <f>IFERROR(INDEX(Comparativo!$I$6:$I$15,MATCH(LARGE(Comparativo!$O$6:$O$15,A13),Comparativo!$O$6:$O$15,0)),"")</f>
+        <f>IFERROR(INDEX(Comparativo!$I$6:$I$14,MATCH(LARGE(Comparativo!$O$6:$O$14,A13),Comparativo!$O$6:$O$14,0)),"")</f>
         <v/>
       </c>
       <c r="E13" s="18">
-        <f>IFERROR(INDEX(Comparativo!$J$6:$J$15,MATCH(LARGE(Comparativo!$O$6:$O$15,A13),Comparativo!$O$6:$O$15,0)),"")</f>
+        <f>IFERROR(INDEX(Comparativo!$J$6:$J$14,MATCH(LARGE(Comparativo!$O$6:$O$14,A13),Comparativo!$O$6:$O$14,0)),"")</f>
         <v/>
       </c>
       <c r="F13" s="18">
-        <f>IFERROR(INDEX(Comparativo!$K$6:$K$15,MATCH(LARGE(Comparativo!$O$6:$O$15,A13),Comparativo!$O$6:$O$15,0)),"")</f>
+        <f>IFERROR(INDEX(Comparativo!$K$6:$K$14,MATCH(LARGE(Comparativo!$O$6:$O$14,A13),Comparativo!$O$6:$O$14,0)),"")</f>
         <v/>
       </c>
       <c r="G13" s="19">
@@ -1302,23 +1302,23 @@
         <v>2</v>
       </c>
       <c r="B14" s="17">
-        <f>IFERROR(INDEX(Comparativo!$D$6:$D$15,MATCH(LARGE(Comparativo!$O$6:$O$15,A14),Comparativo!$O$6:$O$15,0)),"")</f>
+        <f>IFERROR(INDEX(Comparativo!$D$6:$D$14,MATCH(LARGE(Comparativo!$O$6:$O$14,A14),Comparativo!$O$6:$O$14,0)),"")</f>
         <v/>
       </c>
       <c r="C14" s="17">
-        <f>IFERROR(INDEX(Comparativo!$B$6:$B$15,MATCH(LARGE(Comparativo!$O$6:$O$15,A14),Comparativo!$O$6:$O$15,0)),"")</f>
+        <f>IFERROR(INDEX(Comparativo!$B$6:$B$14,MATCH(LARGE(Comparativo!$O$6:$O$14,A14),Comparativo!$O$6:$O$14,0)),"")</f>
         <v/>
       </c>
       <c r="D14" s="18">
-        <f>IFERROR(INDEX(Comparativo!$I$6:$I$15,MATCH(LARGE(Comparativo!$O$6:$O$15,A14),Comparativo!$O$6:$O$15,0)),"")</f>
+        <f>IFERROR(INDEX(Comparativo!$I$6:$I$14,MATCH(LARGE(Comparativo!$O$6:$O$14,A14),Comparativo!$O$6:$O$14,0)),"")</f>
         <v/>
       </c>
       <c r="E14" s="18">
-        <f>IFERROR(INDEX(Comparativo!$J$6:$J$15,MATCH(LARGE(Comparativo!$O$6:$O$15,A14),Comparativo!$O$6:$O$15,0)),"")</f>
+        <f>IFERROR(INDEX(Comparativo!$J$6:$J$14,MATCH(LARGE(Comparativo!$O$6:$O$14,A14),Comparativo!$O$6:$O$14,0)),"")</f>
         <v/>
       </c>
       <c r="F14" s="18">
-        <f>IFERROR(INDEX(Comparativo!$K$6:$K$15,MATCH(LARGE(Comparativo!$O$6:$O$15,A14),Comparativo!$O$6:$O$15,0)),"")</f>
+        <f>IFERROR(INDEX(Comparativo!$K$6:$K$14,MATCH(LARGE(Comparativo!$O$6:$O$14,A14),Comparativo!$O$6:$O$14,0)),"")</f>
         <v/>
       </c>
       <c r="G14" s="19">
@@ -1331,23 +1331,23 @@
         <v>3</v>
       </c>
       <c r="B15" s="17">
-        <f>IFERROR(INDEX(Comparativo!$D$6:$D$15,MATCH(LARGE(Comparativo!$O$6:$O$15,A15),Comparativo!$O$6:$O$15,0)),"")</f>
+        <f>IFERROR(INDEX(Comparativo!$D$6:$D$14,MATCH(LARGE(Comparativo!$O$6:$O$14,A15),Comparativo!$O$6:$O$14,0)),"")</f>
         <v/>
       </c>
       <c r="C15" s="17">
-        <f>IFERROR(INDEX(Comparativo!$B$6:$B$15,MATCH(LARGE(Comparativo!$O$6:$O$15,A15),Comparativo!$O$6:$O$15,0)),"")</f>
+        <f>IFERROR(INDEX(Comparativo!$B$6:$B$14,MATCH(LARGE(Comparativo!$O$6:$O$14,A15),Comparativo!$O$6:$O$14,0)),"")</f>
         <v/>
       </c>
       <c r="D15" s="18">
-        <f>IFERROR(INDEX(Comparativo!$I$6:$I$15,MATCH(LARGE(Comparativo!$O$6:$O$15,A15),Comparativo!$O$6:$O$15,0)),"")</f>
+        <f>IFERROR(INDEX(Comparativo!$I$6:$I$14,MATCH(LARGE(Comparativo!$O$6:$O$14,A15),Comparativo!$O$6:$O$14,0)),"")</f>
         <v/>
       </c>
       <c r="E15" s="18">
-        <f>IFERROR(INDEX(Comparativo!$J$6:$J$15,MATCH(LARGE(Comparativo!$O$6:$O$15,A15),Comparativo!$O$6:$O$15,0)),"")</f>
+        <f>IFERROR(INDEX(Comparativo!$J$6:$J$14,MATCH(LARGE(Comparativo!$O$6:$O$14,A15),Comparativo!$O$6:$O$14,0)),"")</f>
         <v/>
       </c>
       <c r="F15" s="18">
-        <f>IFERROR(INDEX(Comparativo!$K$6:$K$15,MATCH(LARGE(Comparativo!$O$6:$O$15,A15),Comparativo!$O$6:$O$15,0)),"")</f>
+        <f>IFERROR(INDEX(Comparativo!$K$6:$K$14,MATCH(LARGE(Comparativo!$O$6:$O$14,A15),Comparativo!$O$6:$O$14,0)),"")</f>
         <v/>
       </c>
       <c r="G15" s="19">
@@ -1360,23 +1360,23 @@
         <v>4</v>
       </c>
       <c r="B16" s="17">
-        <f>IFERROR(INDEX(Comparativo!$D$6:$D$15,MATCH(LARGE(Comparativo!$O$6:$O$15,A16),Comparativo!$O$6:$O$15,0)),"")</f>
+        <f>IFERROR(INDEX(Comparativo!$D$6:$D$14,MATCH(LARGE(Comparativo!$O$6:$O$14,A16),Comparativo!$O$6:$O$14,0)),"")</f>
         <v/>
       </c>
       <c r="C16" s="17">
-        <f>IFERROR(INDEX(Comparativo!$B$6:$B$15,MATCH(LARGE(Comparativo!$O$6:$O$15,A16),Comparativo!$O$6:$O$15,0)),"")</f>
+        <f>IFERROR(INDEX(Comparativo!$B$6:$B$14,MATCH(LARGE(Comparativo!$O$6:$O$14,A16),Comparativo!$O$6:$O$14,0)),"")</f>
         <v/>
       </c>
       <c r="D16" s="18">
-        <f>IFERROR(INDEX(Comparativo!$I$6:$I$15,MATCH(LARGE(Comparativo!$O$6:$O$15,A16),Comparativo!$O$6:$O$15,0)),"")</f>
+        <f>IFERROR(INDEX(Comparativo!$I$6:$I$14,MATCH(LARGE(Comparativo!$O$6:$O$14,A16),Comparativo!$O$6:$O$14,0)),"")</f>
         <v/>
       </c>
       <c r="E16" s="18">
-        <f>IFERROR(INDEX(Comparativo!$J$6:$J$15,MATCH(LARGE(Comparativo!$O$6:$O$15,A16),Comparativo!$O$6:$O$15,0)),"")</f>
+        <f>IFERROR(INDEX(Comparativo!$J$6:$J$14,MATCH(LARGE(Comparativo!$O$6:$O$14,A16),Comparativo!$O$6:$O$14,0)),"")</f>
         <v/>
       </c>
       <c r="F16" s="18">
-        <f>IFERROR(INDEX(Comparativo!$K$6:$K$15,MATCH(LARGE(Comparativo!$O$6:$O$15,A16),Comparativo!$O$6:$O$15,0)),"")</f>
+        <f>IFERROR(INDEX(Comparativo!$K$6:$K$14,MATCH(LARGE(Comparativo!$O$6:$O$14,A16),Comparativo!$O$6:$O$14,0)),"")</f>
         <v/>
       </c>
       <c r="G16" s="19">
@@ -1389,23 +1389,23 @@
         <v>5</v>
       </c>
       <c r="B17" s="17">
-        <f>IFERROR(INDEX(Comparativo!$D$6:$D$15,MATCH(LARGE(Comparativo!$O$6:$O$15,A17),Comparativo!$O$6:$O$15,0)),"")</f>
+        <f>IFERROR(INDEX(Comparativo!$D$6:$D$14,MATCH(LARGE(Comparativo!$O$6:$O$14,A17),Comparativo!$O$6:$O$14,0)),"")</f>
         <v/>
       </c>
       <c r="C17" s="17">
-        <f>IFERROR(INDEX(Comparativo!$B$6:$B$15,MATCH(LARGE(Comparativo!$O$6:$O$15,A17),Comparativo!$O$6:$O$15,0)),"")</f>
+        <f>IFERROR(INDEX(Comparativo!$B$6:$B$14,MATCH(LARGE(Comparativo!$O$6:$O$14,A17),Comparativo!$O$6:$O$14,0)),"")</f>
         <v/>
       </c>
       <c r="D17" s="18">
-        <f>IFERROR(INDEX(Comparativo!$I$6:$I$15,MATCH(LARGE(Comparativo!$O$6:$O$15,A17),Comparativo!$O$6:$O$15,0)),"")</f>
+        <f>IFERROR(INDEX(Comparativo!$I$6:$I$14,MATCH(LARGE(Comparativo!$O$6:$O$14,A17),Comparativo!$O$6:$O$14,0)),"")</f>
         <v/>
       </c>
       <c r="E17" s="18">
-        <f>IFERROR(INDEX(Comparativo!$J$6:$J$15,MATCH(LARGE(Comparativo!$O$6:$O$15,A17),Comparativo!$O$6:$O$15,0)),"")</f>
+        <f>IFERROR(INDEX(Comparativo!$J$6:$J$14,MATCH(LARGE(Comparativo!$O$6:$O$14,A17),Comparativo!$O$6:$O$14,0)),"")</f>
         <v/>
       </c>
       <c r="F17" s="18">
-        <f>IFERROR(INDEX(Comparativo!$K$6:$K$15,MATCH(LARGE(Comparativo!$O$6:$O$15,A17),Comparativo!$O$6:$O$15,0)),"")</f>
+        <f>IFERROR(INDEX(Comparativo!$K$6:$K$14,MATCH(LARGE(Comparativo!$O$6:$O$14,A17),Comparativo!$O$6:$O$14,0)),"")</f>
         <v/>
       </c>
       <c r="G17" s="19">
@@ -1429,7 +1429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P29"/>
+  <dimension ref="A1:P27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -2161,123 +2161,57 @@
         <v/>
       </c>
     </row>
-    <row r="15" ht="24" customHeight="1">
-      <c r="A15" s="24">
-        <f>Planejado!A14</f>
-        <v/>
-      </c>
-      <c r="B15" s="24">
-        <f>Planejado!B14</f>
-        <v/>
-      </c>
-      <c r="C15" s="24">
-        <f>Planejado!C14</f>
-        <v/>
-      </c>
-      <c r="D15" s="25">
-        <f>Planejado!D14</f>
-        <v/>
-      </c>
-      <c r="E15" s="24">
-        <f>Planejado!G14</f>
-        <v/>
-      </c>
-      <c r="F15" s="26">
-        <f>INDEX(Planejado!$H14:$S14,$D$3)</f>
-        <v/>
-      </c>
-      <c r="G15" s="26">
-        <f>INDEX(Realizado!$H14:$S14,$D$3)</f>
-        <v/>
-      </c>
-      <c r="H15" s="26">
-        <f>G15-F15</f>
-        <v/>
-      </c>
-      <c r="I15" s="26">
-        <f>SUMPRODUCT((COLUMN(Planejado!$H$4:$S$4)-COLUMN(Planejado!$H$4)+1&lt;=$D$3)*Planejado!$H14:$S14)</f>
-        <v/>
-      </c>
-      <c r="J15" s="26">
-        <f>SUMPRODUCT((COLUMN(Realizado!$H$4:$S$4)-COLUMN(Realizado!$H$4)+1&lt;=$D$3)*Realizado!$H14:$S14)</f>
-        <v/>
-      </c>
-      <c r="K15" s="26">
-        <f>J15-I15</f>
-        <v/>
-      </c>
-      <c r="L15" s="27">
-        <f>IFERROR(K15/I15,"")</f>
-        <v/>
-      </c>
-      <c r="M15" s="27">
-        <f>IFERROR(J15/I15,"")</f>
-        <v/>
-      </c>
-      <c r="N15" s="28">
-        <f>IF(P15=0,"Sem lançamento",IF(AND(I15=0,J15=0),"—",IF(I15=0,"Não orçado",IF(K15&gt;0.05*I15,"Acima do orçado",IF(K15&lt;-0.05*I15,"Abaixo do orçado","Dentro do orçado")))))</f>
-        <v/>
-      </c>
-      <c r="O15" s="23">
-        <f>IF(K15&gt;1,K15+ROW()/1000000,"")</f>
-        <v/>
-      </c>
-      <c r="P15" s="29">
-        <f>SUMPRODUCT((COLUMN(Realizado!$H$4:$S$4)-COLUMN(Realizado!$H$4)+1&lt;=$D$3)*(Realizado!$H14:$S14&lt;&gt;""))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="30" t="inlineStr">
+    <row r="27">
+      <c r="A27" s="30" t="inlineStr">
         <is>
           <t>TOTAL GERAL</t>
         </is>
       </c>
-      <c r="B29" s="30" t="n"/>
-      <c r="C29" s="30" t="n"/>
-      <c r="D29" s="30" t="n"/>
-      <c r="E29" s="30" t="n"/>
-      <c r="F29" s="31">
-        <f>SUM(F6:F15)</f>
-        <v/>
-      </c>
-      <c r="G29" s="31">
-        <f>SUM(G6:G15)</f>
-        <v/>
-      </c>
-      <c r="H29" s="31">
-        <f>SUM(H6:H15)</f>
-        <v/>
-      </c>
-      <c r="I29" s="31">
-        <f>SUM(I6:I15)</f>
-        <v/>
-      </c>
-      <c r="J29" s="31">
-        <f>SUM(J6:J15)</f>
-        <v/>
-      </c>
-      <c r="K29" s="31">
-        <f>SUM(K6:K15)</f>
-        <v/>
-      </c>
-      <c r="L29" s="32">
-        <f>IFERROR(K29/I29,"")</f>
-        <v/>
-      </c>
-      <c r="M29" s="32">
-        <f>IFERROR(J29/I29,"")</f>
-        <v/>
-      </c>
-      <c r="N29" s="30" t="n"/>
+      <c r="B27" s="30" t="n"/>
+      <c r="C27" s="30" t="n"/>
+      <c r="D27" s="30" t="n"/>
+      <c r="E27" s="30" t="n"/>
+      <c r="F27" s="31">
+        <f>SUM(F6:F14)</f>
+        <v/>
+      </c>
+      <c r="G27" s="31">
+        <f>SUM(G6:G14)</f>
+        <v/>
+      </c>
+      <c r="H27" s="31">
+        <f>SUM(H6:H14)</f>
+        <v/>
+      </c>
+      <c r="I27" s="31">
+        <f>SUM(I6:I14)</f>
+        <v/>
+      </c>
+      <c r="J27" s="31">
+        <f>SUM(J6:J14)</f>
+        <v/>
+      </c>
+      <c r="K27" s="31">
+        <f>SUM(K6:K14)</f>
+        <v/>
+      </c>
+      <c r="L27" s="32">
+        <f>IFERROR(K27/I27,"")</f>
+        <v/>
+      </c>
+      <c r="M27" s="32">
+        <f>IFERROR(J27/I27,"")</f>
+        <v/>
+      </c>
+      <c r="N27" s="30" t="n"/>
     </row>
   </sheetData>
-  <autoFilter ref="A5:N15"/>
+  <autoFilter ref="A5:N14"/>
   <mergeCells count="2">
     <mergeCell ref="A2:N2"/>
     <mergeCell ref="A1:N1"/>
   </mergeCells>
-  <conditionalFormatting sqref="H6:H15">
+  <conditionalFormatting sqref="H6:H14">
     <cfRule type="cellIs" priority="1" operator="greaterThan" dxfId="0">
       <formula>0</formula>
     </cfRule>
@@ -2285,7 +2219,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K6:K15">
+  <conditionalFormatting sqref="K6:K14">
     <cfRule type="cellIs" priority="3" operator="greaterThan" dxfId="0">
       <formula>0</formula>
     </cfRule>
@@ -2308,7 +2242,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T15"/>
+  <dimension ref="A1:T14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -2544,12 +2478,12 @@
       </c>
       <c r="D6" s="25" t="inlineStr">
         <is>
-          <t>Geovanna — salário bruto</t>
+          <t>Geovanna</t>
         </is>
       </c>
       <c r="E6" s="25" t="inlineStr">
         <is>
-          <t>Analista Administrativo</t>
+          <t>Analista Administrativo — orçada pelo custo total (encargos de folha + benefícios). Salário bruto informado: R$ 2.886,91/mês</t>
         </is>
       </c>
       <c r="F6" s="24" t="inlineStr">
@@ -2563,40 +2497,40 @@
         </is>
       </c>
       <c r="H6" s="26" t="n">
-        <v>2886.91</v>
+        <v>4825.515</v>
       </c>
       <c r="I6" s="26" t="n">
-        <v>2886.91</v>
+        <v>4825.515</v>
       </c>
       <c r="J6" s="26" t="n">
-        <v>2886.91</v>
+        <v>4825.515</v>
       </c>
       <c r="K6" s="26" t="n">
-        <v>2886.91</v>
+        <v>4825.515</v>
       </c>
       <c r="L6" s="26" t="n">
-        <v>2886.91</v>
+        <v>4825.515</v>
       </c>
       <c r="M6" s="26" t="n">
-        <v>2886.91</v>
+        <v>4825.515</v>
       </c>
       <c r="N6" s="26" t="n">
-        <v>2886.91</v>
+        <v>4825.515</v>
       </c>
       <c r="O6" s="26" t="n">
-        <v>2886.91</v>
+        <v>4825.515</v>
       </c>
       <c r="P6" s="26" t="n">
-        <v>2886.91</v>
+        <v>4825.515</v>
       </c>
       <c r="Q6" s="26" t="n">
-        <v>2886.91</v>
+        <v>4825.515</v>
       </c>
       <c r="R6" s="26" t="n">
-        <v>2886.91</v>
+        <v>4825.515</v>
       </c>
       <c r="S6" s="26" t="n">
-        <v>2886.91</v>
+        <v>4825.515</v>
       </c>
       <c r="T6" s="33">
         <f>SUM(H6:S6)</f>
@@ -2606,7 +2540,7 @@
     <row r="7" ht="26" customHeight="1">
       <c r="A7" s="24" t="inlineStr">
         <is>
-          <t>JUR-E02B</t>
+          <t>JUR-E03</t>
         </is>
       </c>
       <c r="B7" s="24" t="inlineStr">
@@ -2621,59 +2555,59 @@
       </c>
       <c r="D7" s="25" t="inlineStr">
         <is>
-          <t>Geovanna — encargos e benefícios</t>
+          <t>Thamar Victória</t>
         </is>
       </c>
       <c r="E7" s="25" t="inlineStr">
         <is>
-          <t>INSS patronal, FGTS, provisões de 13º e férias, benefícios — PREENCHER</t>
+          <t>Advogada — reajuste permanente de R$ 5.000 para R$ 5.500 (revisado a partir de out/26)</t>
         </is>
       </c>
       <c r="F7" s="24" t="inlineStr">
         <is>
-          <t>CLT</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="G7" s="24" t="inlineStr">
         <is>
-          <t>Encargos e Benefícios - CLT</t>
+          <t>Pessoal - PJ</t>
         </is>
       </c>
       <c r="H7" s="26" t="n">
-        <v>1938.605</v>
+        <v>5000</v>
       </c>
       <c r="I7" s="26" t="n">
-        <v>1938.605</v>
+        <v>5000</v>
       </c>
       <c r="J7" s="26" t="n">
-        <v>1938.605</v>
+        <v>5000</v>
       </c>
       <c r="K7" s="26" t="n">
-        <v>1938.605</v>
+        <v>5000</v>
       </c>
       <c r="L7" s="26" t="n">
-        <v>1938.605</v>
+        <v>5000</v>
       </c>
       <c r="M7" s="26" t="n">
-        <v>1938.605</v>
+        <v>5000</v>
       </c>
       <c r="N7" s="26" t="n">
-        <v>1938.605</v>
+        <v>5000</v>
       </c>
       <c r="O7" s="26" t="n">
-        <v>1938.605</v>
+        <v>5000</v>
       </c>
       <c r="P7" s="26" t="n">
-        <v>1938.605</v>
+        <v>5000</v>
       </c>
       <c r="Q7" s="26" t="n">
-        <v>1938.605</v>
+        <v>5500</v>
       </c>
       <c r="R7" s="26" t="n">
-        <v>1938.605</v>
+        <v>5500</v>
       </c>
       <c r="S7" s="26" t="n">
-        <v>1938.605</v>
+        <v>5500</v>
       </c>
       <c r="T7" s="33">
         <f>SUM(H7:S7)</f>
@@ -2683,7 +2617,7 @@
     <row r="8" ht="26" customHeight="1">
       <c r="A8" s="24" t="inlineStr">
         <is>
-          <t>JUR-E03</t>
+          <t>JUR-D01</t>
         </is>
       </c>
       <c r="B8" s="24" t="inlineStr">
@@ -2693,64 +2627,60 @@
       </c>
       <c r="C8" s="24" t="inlineStr">
         <is>
-          <t>Equipe</t>
+          <t>Despesas</t>
         </is>
       </c>
       <c r="D8" s="25" t="inlineStr">
         <is>
-          <t>Thamar Victória</t>
+          <t>JUSFY</t>
         </is>
       </c>
       <c r="E8" s="25" t="inlineStr">
         <is>
-          <t>Advogada — reajuste permanente de R$ 5.000 para R$ 5.500 (revisado a partir de out/26)</t>
-        </is>
-      </c>
-      <c r="F8" s="24" t="inlineStr">
-        <is>
-          <t>PJ</t>
-        </is>
-      </c>
+          <t>Fase de teste com objetivo de eliminar o Astrea</t>
+        </is>
+      </c>
+      <c r="F8" s="24" t="inlineStr"/>
       <c r="G8" s="24" t="inlineStr">
         <is>
-          <t>Pessoal - PJ</t>
+          <t>Licenças de Softwares</t>
         </is>
       </c>
       <c r="H8" s="26" t="n">
-        <v>5000</v>
+        <v>100</v>
       </c>
       <c r="I8" s="26" t="n">
-        <v>5000</v>
+        <v>100</v>
       </c>
       <c r="J8" s="26" t="n">
-        <v>5000</v>
+        <v>100</v>
       </c>
       <c r="K8" s="26" t="n">
-        <v>5000</v>
+        <v>100</v>
       </c>
       <c r="L8" s="26" t="n">
-        <v>5000</v>
+        <v>100</v>
       </c>
       <c r="M8" s="26" t="n">
-        <v>5000</v>
+        <v>100</v>
       </c>
       <c r="N8" s="26" t="n">
-        <v>5000</v>
+        <v>100</v>
       </c>
       <c r="O8" s="26" t="n">
-        <v>5000</v>
+        <v>100</v>
       </c>
       <c r="P8" s="26" t="n">
-        <v>5000</v>
+        <v>100</v>
       </c>
       <c r="Q8" s="26" t="n">
-        <v>5500</v>
+        <v>100</v>
       </c>
       <c r="R8" s="26" t="n">
-        <v>5500</v>
+        <v>100</v>
       </c>
       <c r="S8" s="26" t="n">
-        <v>5500</v>
+        <v>100</v>
       </c>
       <c r="T8" s="33">
         <f>SUM(H8:S8)</f>
@@ -2760,7 +2690,7 @@
     <row r="9" ht="26" customHeight="1">
       <c r="A9" s="24" t="inlineStr">
         <is>
-          <t>JUR-D01</t>
+          <t>JUR-D02</t>
         </is>
       </c>
       <c r="B9" s="24" t="inlineStr">
@@ -2775,14 +2705,10 @@
       </c>
       <c r="D9" s="25" t="inlineStr">
         <is>
-          <t>JUSFY</t>
-        </is>
-      </c>
-      <c r="E9" s="25" t="inlineStr">
-        <is>
-          <t>Fase de teste com objetivo de eliminar o Astrea</t>
-        </is>
-      </c>
+          <t>JUSBRASIL</t>
+        </is>
+      </c>
+      <c r="E9" s="25" t="inlineStr"/>
       <c r="F9" s="24" t="inlineStr"/>
       <c r="G9" s="24" t="inlineStr">
         <is>
@@ -2790,40 +2716,40 @@
         </is>
       </c>
       <c r="H9" s="26" t="n">
-        <v>100</v>
+        <v>104.9</v>
       </c>
       <c r="I9" s="26" t="n">
-        <v>100</v>
+        <v>104.9</v>
       </c>
       <c r="J9" s="26" t="n">
-        <v>100</v>
+        <v>104.9</v>
       </c>
       <c r="K9" s="26" t="n">
-        <v>100</v>
+        <v>104.9</v>
       </c>
       <c r="L9" s="26" t="n">
-        <v>100</v>
+        <v>104.9</v>
       </c>
       <c r="M9" s="26" t="n">
-        <v>100</v>
+        <v>104.9</v>
       </c>
       <c r="N9" s="26" t="n">
-        <v>100</v>
+        <v>104.9</v>
       </c>
       <c r="O9" s="26" t="n">
-        <v>100</v>
+        <v>104.9</v>
       </c>
       <c r="P9" s="26" t="n">
-        <v>100</v>
+        <v>104.9</v>
       </c>
       <c r="Q9" s="26" t="n">
-        <v>100</v>
+        <v>104.9</v>
       </c>
       <c r="R9" s="26" t="n">
-        <v>100</v>
+        <v>104.9</v>
       </c>
       <c r="S9" s="26" t="n">
-        <v>100</v>
+        <v>104.9</v>
       </c>
       <c r="T9" s="33">
         <f>SUM(H9:S9)</f>
@@ -2833,7 +2759,7 @@
     <row r="10" ht="26" customHeight="1">
       <c r="A10" s="24" t="inlineStr">
         <is>
-          <t>JUR-D02</t>
+          <t>JUR-D03</t>
         </is>
       </c>
       <c r="B10" s="24" t="inlineStr">
@@ -2848,10 +2774,14 @@
       </c>
       <c r="D10" s="25" t="inlineStr">
         <is>
-          <t>JUSBRASIL</t>
-        </is>
-      </c>
-      <c r="E10" s="25" t="inlineStr"/>
+          <t>ASTREA</t>
+        </is>
+      </c>
+      <c r="E10" s="25" t="inlineStr">
+        <is>
+          <t>Cancelado — realizado zerado desde mai/26</t>
+        </is>
+      </c>
       <c r="F10" s="24" t="inlineStr"/>
       <c r="G10" s="24" t="inlineStr">
         <is>
@@ -2859,40 +2789,40 @@
         </is>
       </c>
       <c r="H10" s="26" t="n">
-        <v>104.9</v>
+        <v>112.07</v>
       </c>
       <c r="I10" s="26" t="n">
-        <v>104.9</v>
+        <v>112.07</v>
       </c>
       <c r="J10" s="26" t="n">
-        <v>104.9</v>
+        <v>112.07</v>
       </c>
       <c r="K10" s="26" t="n">
-        <v>104.9</v>
+        <v>112.07</v>
       </c>
       <c r="L10" s="26" t="n">
-        <v>104.9</v>
+        <v>112.07</v>
       </c>
       <c r="M10" s="26" t="n">
-        <v>104.9</v>
+        <v>112.07</v>
       </c>
       <c r="N10" s="26" t="n">
-        <v>104.9</v>
+        <v>112.07</v>
       </c>
       <c r="O10" s="26" t="n">
-        <v>104.9</v>
+        <v>112.07</v>
       </c>
       <c r="P10" s="26" t="n">
-        <v>104.9</v>
+        <v>112.07</v>
       </c>
       <c r="Q10" s="26" t="n">
-        <v>104.9</v>
+        <v>112.07</v>
       </c>
       <c r="R10" s="26" t="n">
-        <v>104.9</v>
+        <v>112.07</v>
       </c>
       <c r="S10" s="26" t="n">
-        <v>104.9</v>
+        <v>112.07</v>
       </c>
       <c r="T10" s="33">
         <f>SUM(H10:S10)</f>
@@ -2902,7 +2832,7 @@
     <row r="11" ht="26" customHeight="1">
       <c r="A11" s="24" t="inlineStr">
         <is>
-          <t>JUR-D03</t>
+          <t>JUR-D04</t>
         </is>
       </c>
       <c r="B11" s="24" t="inlineStr">
@@ -2917,14 +2847,10 @@
       </c>
       <c r="D11" s="25" t="inlineStr">
         <is>
-          <t>ASTREA</t>
-        </is>
-      </c>
-      <c r="E11" s="25" t="inlineStr">
-        <is>
-          <t>Cancelado — realizado zerado desde mai/26</t>
-        </is>
-      </c>
+          <t>LEME</t>
+        </is>
+      </c>
+      <c r="E11" s="25" t="inlineStr"/>
       <c r="F11" s="24" t="inlineStr"/>
       <c r="G11" s="24" t="inlineStr">
         <is>
@@ -2932,40 +2858,40 @@
         </is>
       </c>
       <c r="H11" s="26" t="n">
-        <v>112.07</v>
+        <v>1030</v>
       </c>
       <c r="I11" s="26" t="n">
-        <v>112.07</v>
+        <v>1030</v>
       </c>
       <c r="J11" s="26" t="n">
-        <v>112.07</v>
+        <v>1030</v>
       </c>
       <c r="K11" s="26" t="n">
-        <v>112.07</v>
+        <v>1030</v>
       </c>
       <c r="L11" s="26" t="n">
-        <v>112.07</v>
+        <v>1030</v>
       </c>
       <c r="M11" s="26" t="n">
-        <v>112.07</v>
+        <v>1030</v>
       </c>
       <c r="N11" s="26" t="n">
-        <v>112.07</v>
+        <v>1030</v>
       </c>
       <c r="O11" s="26" t="n">
-        <v>112.07</v>
+        <v>1030</v>
       </c>
       <c r="P11" s="26" t="n">
-        <v>112.07</v>
+        <v>1030</v>
       </c>
       <c r="Q11" s="26" t="n">
-        <v>112.07</v>
+        <v>1030</v>
       </c>
       <c r="R11" s="26" t="n">
-        <v>112.07</v>
+        <v>1030</v>
       </c>
       <c r="S11" s="26" t="n">
-        <v>112.07</v>
+        <v>1030</v>
       </c>
       <c r="T11" s="33">
         <f>SUM(H11:S11)</f>
@@ -2975,7 +2901,7 @@
     <row r="12" ht="26" customHeight="1">
       <c r="A12" s="24" t="inlineStr">
         <is>
-          <t>JUR-D04</t>
+          <t>JUR-D05</t>
         </is>
       </c>
       <c r="B12" s="24" t="inlineStr">
@@ -2990,51 +2916,51 @@
       </c>
       <c r="D12" s="25" t="inlineStr">
         <is>
-          <t>LEME</t>
+          <t>Cursos / Eventos / Network</t>
         </is>
       </c>
       <c r="E12" s="25" t="inlineStr"/>
       <c r="F12" s="24" t="inlineStr"/>
       <c r="G12" s="24" t="inlineStr">
         <is>
-          <t>Licenças de Softwares</t>
+          <t>Custeio de Treinamento</t>
         </is>
       </c>
       <c r="H12" s="26" t="n">
-        <v>1030</v>
+        <v>1000</v>
       </c>
       <c r="I12" s="26" t="n">
-        <v>1030</v>
+        <v>1000</v>
       </c>
       <c r="J12" s="26" t="n">
-        <v>1030</v>
+        <v>1000</v>
       </c>
       <c r="K12" s="26" t="n">
-        <v>1030</v>
+        <v>1000</v>
       </c>
       <c r="L12" s="26" t="n">
-        <v>1030</v>
+        <v>1000</v>
       </c>
       <c r="M12" s="26" t="n">
-        <v>1030</v>
+        <v>1000</v>
       </c>
       <c r="N12" s="26" t="n">
-        <v>1030</v>
+        <v>1000</v>
       </c>
       <c r="O12" s="26" t="n">
-        <v>1030</v>
+        <v>1000</v>
       </c>
       <c r="P12" s="26" t="n">
-        <v>1030</v>
+        <v>1000</v>
       </c>
       <c r="Q12" s="26" t="n">
-        <v>1030</v>
+        <v>1000</v>
       </c>
       <c r="R12" s="26" t="n">
-        <v>1030</v>
+        <v>1000</v>
       </c>
       <c r="S12" s="26" t="n">
-        <v>1030</v>
+        <v>1000</v>
       </c>
       <c r="T12" s="33">
         <f>SUM(H12:S12)</f>
@@ -3044,7 +2970,7 @@
     <row r="13" ht="26" customHeight="1">
       <c r="A13" s="24" t="inlineStr">
         <is>
-          <t>JUR-D05</t>
+          <t>JUR-D06</t>
         </is>
       </c>
       <c r="B13" s="24" t="inlineStr">
@@ -3059,197 +2985,128 @@
       </c>
       <c r="D13" s="25" t="inlineStr">
         <is>
-          <t>Cursos / Eventos / Network</t>
-        </is>
-      </c>
-      <c r="E13" s="25" t="inlineStr"/>
+          <t>Bonificações trimestrais/semestrais do time</t>
+        </is>
+      </c>
+      <c r="E13" s="25" t="inlineStr">
+        <is>
+          <t>Participação em projetos e atingimento de resultados — CONFIRMAR se houve parcela no 1º quadrimestre</t>
+        </is>
+      </c>
       <c r="F13" s="24" t="inlineStr"/>
       <c r="G13" s="24" t="inlineStr">
         <is>
-          <t>Custeio de Treinamento</t>
+          <t>Prêmios</t>
         </is>
       </c>
       <c r="H13" s="26" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="I13" s="26" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="J13" s="26" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="K13" s="26" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="L13" s="26" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="M13" s="26" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="N13" s="26" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="O13" s="26" t="n">
-        <v>1000</v>
+        <v>10293.6</v>
       </c>
       <c r="P13" s="26" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="Q13" s="26" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="R13" s="26" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="S13" s="26" t="n">
-        <v>1000</v>
+        <v>12867</v>
       </c>
       <c r="T13" s="33">
         <f>SUM(H13:S13)</f>
         <v/>
       </c>
     </row>
-    <row r="14" ht="26" customHeight="1">
-      <c r="A14" s="24" t="inlineStr">
-        <is>
-          <t>JUR-D06</t>
-        </is>
-      </c>
-      <c r="B14" s="24" t="inlineStr">
-        <is>
-          <t>Jurídico</t>
-        </is>
-      </c>
-      <c r="C14" s="24" t="inlineStr">
-        <is>
-          <t>Despesas</t>
-        </is>
-      </c>
-      <c r="D14" s="25" t="inlineStr">
-        <is>
-          <t>Bonificações trimestrais/semestrais do time</t>
-        </is>
-      </c>
-      <c r="E14" s="25" t="inlineStr">
-        <is>
-          <t>Participação em projetos e atingimento de resultados — CONFIRMAR se houve parcela no 1º quadrimestre</t>
-        </is>
-      </c>
-      <c r="F14" s="24" t="inlineStr"/>
-      <c r="G14" s="24" t="inlineStr">
-        <is>
-          <t>Prêmios</t>
-        </is>
-      </c>
-      <c r="H14" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="I14" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="J14" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="K14" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="L14" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="M14" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="N14" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="O14" s="26" t="n">
-        <v>10293.6</v>
-      </c>
-      <c r="P14" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q14" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="R14" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="S14" s="26" t="n">
-        <v>12867</v>
-      </c>
-      <c r="T14" s="33">
-        <f>SUM(H14:S14)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="30" t="inlineStr">
+    <row r="14">
+      <c r="A14" s="30" t="inlineStr">
         <is>
           <t>TOTAL GERAL</t>
         </is>
       </c>
-      <c r="B15" s="30" t="n"/>
-      <c r="C15" s="30" t="n"/>
-      <c r="D15" s="30" t="n"/>
-      <c r="E15" s="30" t="n"/>
-      <c r="F15" s="30" t="n"/>
-      <c r="G15" s="30" t="n"/>
-      <c r="H15" s="31">
-        <f>SUM(H5:H14)</f>
-        <v/>
-      </c>
-      <c r="I15" s="31">
-        <f>SUM(I5:I14)</f>
-        <v/>
-      </c>
-      <c r="J15" s="31">
-        <f>SUM(J5:J14)</f>
-        <v/>
-      </c>
-      <c r="K15" s="31">
-        <f>SUM(K5:K14)</f>
-        <v/>
-      </c>
-      <c r="L15" s="31">
-        <f>SUM(L5:L14)</f>
-        <v/>
-      </c>
-      <c r="M15" s="31">
-        <f>SUM(M5:M14)</f>
-        <v/>
-      </c>
-      <c r="N15" s="31">
-        <f>SUM(N5:N14)</f>
-        <v/>
-      </c>
-      <c r="O15" s="31">
-        <f>SUM(O5:O14)</f>
-        <v/>
-      </c>
-      <c r="P15" s="31">
-        <f>SUM(P5:P14)</f>
-        <v/>
-      </c>
-      <c r="Q15" s="31">
-        <f>SUM(Q5:Q14)</f>
-        <v/>
-      </c>
-      <c r="R15" s="31">
-        <f>SUM(R5:R14)</f>
-        <v/>
-      </c>
-      <c r="S15" s="31">
-        <f>SUM(S5:S14)</f>
-        <v/>
-      </c>
-      <c r="T15" s="31">
-        <f>SUM(T5:T14)</f>
+      <c r="B14" s="30" t="n"/>
+      <c r="C14" s="30" t="n"/>
+      <c r="D14" s="30" t="n"/>
+      <c r="E14" s="30" t="n"/>
+      <c r="F14" s="30" t="n"/>
+      <c r="G14" s="30" t="n"/>
+      <c r="H14" s="31">
+        <f>SUM(H5:H13)</f>
+        <v/>
+      </c>
+      <c r="I14" s="31">
+        <f>SUM(I5:I13)</f>
+        <v/>
+      </c>
+      <c r="J14" s="31">
+        <f>SUM(J5:J13)</f>
+        <v/>
+      </c>
+      <c r="K14" s="31">
+        <f>SUM(K5:K13)</f>
+        <v/>
+      </c>
+      <c r="L14" s="31">
+        <f>SUM(L5:L13)</f>
+        <v/>
+      </c>
+      <c r="M14" s="31">
+        <f>SUM(M5:M13)</f>
+        <v/>
+      </c>
+      <c r="N14" s="31">
+        <f>SUM(N5:N13)</f>
+        <v/>
+      </c>
+      <c r="O14" s="31">
+        <f>SUM(O5:O13)</f>
+        <v/>
+      </c>
+      <c r="P14" s="31">
+        <f>SUM(P5:P13)</f>
+        <v/>
+      </c>
+      <c r="Q14" s="31">
+        <f>SUM(Q5:Q13)</f>
+        <v/>
+      </c>
+      <c r="R14" s="31">
+        <f>SUM(R5:R13)</f>
+        <v/>
+      </c>
+      <c r="S14" s="31">
+        <f>SUM(S5:S13)</f>
+        <v/>
+      </c>
+      <c r="T14" s="31">
+        <f>SUM(T5:T13)</f>
         <v/>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:T14"/>
+  <autoFilter ref="A4:T13"/>
   <mergeCells count="2">
     <mergeCell ref="A1:T1"/>
     <mergeCell ref="A2:T2"/>
@@ -3264,7 +3121,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V15"/>
+  <dimension ref="A1:V14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -3508,28 +3365,18 @@
       <c r="I6" s="37" t="n"/>
       <c r="J6" s="37" t="n"/>
       <c r="K6" s="37" t="n"/>
-      <c r="L6" s="37" t="n">
-        <v>2886.91</v>
-      </c>
-      <c r="M6" s="37" t="n">
-        <v>2886.91</v>
-      </c>
-      <c r="N6" s="37" t="n">
-        <v>2886.91</v>
-      </c>
+      <c r="L6" s="37" t="n"/>
+      <c r="M6" s="37" t="n"/>
+      <c r="N6" s="37" t="n"/>
       <c r="O6" s="37" t="n"/>
       <c r="T6" s="33">
         <f>SUM(H6:S6)</f>
         <v/>
       </c>
-      <c r="U6" s="38" t="inlineStr">
-        <is>
-          <t>Gestora, 05/08/26</t>
-        </is>
-      </c>
+      <c r="U6" s="38" t="n"/>
       <c r="V6" s="38" t="inlineStr">
         <is>
-          <t>Salário bruto</t>
+          <t>PREENCHER com o CUSTO TOTAL. Bruto informado: R$ 2.886,91/mês — faltam encargos e benefícios</t>
         </is>
       </c>
     </row>
@@ -3566,18 +3413,28 @@
       <c r="I7" s="37" t="n"/>
       <c r="J7" s="37" t="n"/>
       <c r="K7" s="37" t="n"/>
-      <c r="L7" s="37" t="n"/>
-      <c r="M7" s="37" t="n"/>
-      <c r="N7" s="37" t="n"/>
+      <c r="L7" s="37" t="n">
+        <v>5500</v>
+      </c>
+      <c r="M7" s="37" t="n">
+        <v>5500</v>
+      </c>
+      <c r="N7" s="37" t="n">
+        <v>5500</v>
+      </c>
       <c r="O7" s="37" t="n"/>
       <c r="T7" s="33">
         <f>SUM(H7:S7)</f>
         <v/>
       </c>
-      <c r="U7" s="38" t="n"/>
+      <c r="U7" s="38" t="inlineStr">
+        <is>
+          <t>Gestora, 05/08/26</t>
+        </is>
+      </c>
       <c r="V7" s="38" t="inlineStr">
         <is>
-          <t>PREENCHER — encargos e benefícios sobre o bruto</t>
+          <t>Reajuste permanente aplicado desde mai/26</t>
         </is>
       </c>
     </row>
@@ -3615,13 +3472,13 @@
       <c r="J8" s="37" t="n"/>
       <c r="K8" s="37" t="n"/>
       <c r="L8" s="37" t="n">
-        <v>5500</v>
+        <v>0</v>
       </c>
       <c r="M8" s="37" t="n">
-        <v>5500</v>
+        <v>0</v>
       </c>
       <c r="N8" s="37" t="n">
-        <v>5500</v>
+        <v>0</v>
       </c>
       <c r="O8" s="37" t="n"/>
       <c r="T8" s="33">
@@ -3635,7 +3492,7 @@
       </c>
       <c r="V8" s="38" t="inlineStr">
         <is>
-          <t>Reajuste permanente aplicado desde mai/26</t>
+          <t>Ainda não iniciado — sem cobrança</t>
         </is>
       </c>
     </row>
@@ -3673,13 +3530,13 @@
       <c r="J9" s="37" t="n"/>
       <c r="K9" s="37" t="n"/>
       <c r="L9" s="37" t="n">
-        <v>0</v>
+        <v>136</v>
       </c>
       <c r="M9" s="37" t="n">
-        <v>0</v>
+        <v>136</v>
       </c>
       <c r="N9" s="37" t="n">
-        <v>0</v>
+        <v>136</v>
       </c>
       <c r="O9" s="37" t="n"/>
       <c r="T9" s="33">
@@ -3693,7 +3550,7 @@
       </c>
       <c r="V9" s="38" t="inlineStr">
         <is>
-          <t>Ainda não iniciado — sem cobrança</t>
+          <t>Acima do orçado (R$ 104,90) — conferir contrato</t>
         </is>
       </c>
     </row>
@@ -3731,13 +3588,13 @@
       <c r="J10" s="37" t="n"/>
       <c r="K10" s="37" t="n"/>
       <c r="L10" s="37" t="n">
-        <v>136</v>
+        <v>0</v>
       </c>
       <c r="M10" s="37" t="n">
-        <v>136</v>
+        <v>0</v>
       </c>
       <c r="N10" s="37" t="n">
-        <v>136</v>
+        <v>0</v>
       </c>
       <c r="O10" s="37" t="n"/>
       <c r="T10" s="33">
@@ -3751,7 +3608,7 @@
       </c>
       <c r="V10" s="38" t="inlineStr">
         <is>
-          <t>Acima do orçado (R$ 104,90) — conferir contrato</t>
+          <t>Cancelado — sem cobrança</t>
         </is>
       </c>
     </row>
@@ -3789,13 +3646,13 @@
       <c r="J11" s="37" t="n"/>
       <c r="K11" s="37" t="n"/>
       <c r="L11" s="37" t="n">
-        <v>0</v>
+        <v>970</v>
       </c>
       <c r="M11" s="37" t="n">
-        <v>0</v>
+        <v>970</v>
       </c>
       <c r="N11" s="37" t="n">
-        <v>0</v>
+        <v>970</v>
       </c>
       <c r="O11" s="37" t="n"/>
       <c r="T11" s="33">
@@ -3807,11 +3664,7 @@
           <t>Gestora, 05/08/26</t>
         </is>
       </c>
-      <c r="V11" s="38" t="inlineStr">
-        <is>
-          <t>Cancelado — sem cobrança</t>
-        </is>
-      </c>
+      <c r="V11" s="38" t="n"/>
     </row>
     <row r="12" ht="26" customHeight="1">
       <c r="A12" s="35">
@@ -3847,13 +3700,13 @@
       <c r="J12" s="37" t="n"/>
       <c r="K12" s="37" t="n"/>
       <c r="L12" s="37" t="n">
-        <v>970</v>
+        <v>0</v>
       </c>
       <c r="M12" s="37" t="n">
-        <v>970</v>
+        <v>0</v>
       </c>
       <c r="N12" s="37" t="n">
-        <v>970</v>
+        <v>0</v>
       </c>
       <c r="O12" s="37" t="n"/>
       <c r="T12" s="33">
@@ -3865,7 +3718,11 @@
           <t>Gestora, 05/08/26</t>
         </is>
       </c>
-      <c r="V12" s="38" t="n"/>
+      <c r="V12" s="38" t="inlineStr">
+        <is>
+          <t>Sem gasto no período</t>
+        </is>
+      </c>
     </row>
     <row r="13" ht="26" customHeight="1">
       <c r="A13" s="35">
@@ -3900,145 +3757,87 @@
       <c r="I13" s="37" t="n"/>
       <c r="J13" s="37" t="n"/>
       <c r="K13" s="37" t="n"/>
-      <c r="L13" s="37" t="n">
-        <v>0</v>
-      </c>
-      <c r="M13" s="37" t="n">
-        <v>0</v>
-      </c>
-      <c r="N13" s="37" t="n">
-        <v>0</v>
-      </c>
+      <c r="L13" s="37" t="n"/>
+      <c r="M13" s="37" t="n"/>
+      <c r="N13" s="37" t="n"/>
       <c r="O13" s="37" t="n"/>
       <c r="T13" s="33">
         <f>SUM(H13:S13)</f>
         <v/>
       </c>
-      <c r="U13" s="38" t="inlineStr">
-        <is>
-          <t>Gestora, 05/08/26</t>
-        </is>
-      </c>
+      <c r="U13" s="38" t="n"/>
       <c r="V13" s="38" t="inlineStr">
         <is>
-          <t>Sem gasto no período</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="26" customHeight="1">
-      <c r="A14" s="35">
-        <f>Planejado!A14</f>
-        <v/>
-      </c>
-      <c r="B14" s="35">
-        <f>Planejado!B14</f>
-        <v/>
-      </c>
-      <c r="C14" s="35">
-        <f>Planejado!C14</f>
-        <v/>
-      </c>
-      <c r="D14" s="36">
-        <f>Planejado!D14</f>
-        <v/>
-      </c>
-      <c r="E14" s="36">
-        <f>Planejado!E14</f>
-        <v/>
-      </c>
-      <c r="F14" s="35">
-        <f>Planejado!F14</f>
-        <v/>
-      </c>
-      <c r="G14" s="35">
-        <f>Planejado!G14</f>
-        <v/>
-      </c>
-      <c r="H14" s="37" t="n"/>
-      <c r="I14" s="37" t="n"/>
-      <c r="J14" s="37" t="n"/>
-      <c r="K14" s="37" t="n"/>
-      <c r="L14" s="37" t="n"/>
-      <c r="M14" s="37" t="n"/>
-      <c r="N14" s="37" t="n"/>
-      <c r="O14" s="37" t="n"/>
-      <c r="T14" s="33">
-        <f>SUM(H14:S14)</f>
-        <v/>
-      </c>
-      <c r="U14" s="38" t="n"/>
-      <c r="V14" s="38" t="inlineStr">
-        <is>
           <t>Bonificação de ago/26 a confirmar</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="39" t="inlineStr">
+    <row r="14">
+      <c r="A14" s="39" t="inlineStr">
         <is>
           <t>TOTAL GERAL</t>
         </is>
       </c>
-      <c r="B15" s="39" t="n"/>
-      <c r="C15" s="39" t="n"/>
-      <c r="D15" s="39" t="n"/>
-      <c r="E15" s="39" t="n"/>
-      <c r="F15" s="39" t="n"/>
-      <c r="G15" s="39" t="n"/>
-      <c r="H15" s="40">
-        <f>SUM(H5:H14)</f>
-        <v/>
-      </c>
-      <c r="I15" s="40">
-        <f>SUM(I5:I14)</f>
-        <v/>
-      </c>
-      <c r="J15" s="40">
-        <f>SUM(J5:J14)</f>
-        <v/>
-      </c>
-      <c r="K15" s="40">
-        <f>SUM(K5:K14)</f>
-        <v/>
-      </c>
-      <c r="L15" s="40">
-        <f>SUM(L5:L14)</f>
-        <v/>
-      </c>
-      <c r="M15" s="40">
-        <f>SUM(M5:M14)</f>
-        <v/>
-      </c>
-      <c r="N15" s="40">
-        <f>SUM(N5:N14)</f>
-        <v/>
-      </c>
-      <c r="O15" s="40">
-        <f>SUM(O5:O14)</f>
-        <v/>
-      </c>
-      <c r="P15" s="40">
-        <f>SUM(P5:P14)</f>
-        <v/>
-      </c>
-      <c r="Q15" s="40">
-        <f>SUM(Q5:Q14)</f>
-        <v/>
-      </c>
-      <c r="R15" s="40">
-        <f>SUM(R5:R14)</f>
-        <v/>
-      </c>
-      <c r="S15" s="40">
-        <f>SUM(S5:S14)</f>
-        <v/>
-      </c>
-      <c r="T15" s="40">
-        <f>SUM(T5:T14)</f>
-        <v/>
-      </c>
-      <c r="U15" s="39" t="n"/>
-      <c r="V15" s="39" t="n"/>
+      <c r="B14" s="39" t="n"/>
+      <c r="C14" s="39" t="n"/>
+      <c r="D14" s="39" t="n"/>
+      <c r="E14" s="39" t="n"/>
+      <c r="F14" s="39" t="n"/>
+      <c r="G14" s="39" t="n"/>
+      <c r="H14" s="40">
+        <f>SUM(H5:H13)</f>
+        <v/>
+      </c>
+      <c r="I14" s="40">
+        <f>SUM(I5:I13)</f>
+        <v/>
+      </c>
+      <c r="J14" s="40">
+        <f>SUM(J5:J13)</f>
+        <v/>
+      </c>
+      <c r="K14" s="40">
+        <f>SUM(K5:K13)</f>
+        <v/>
+      </c>
+      <c r="L14" s="40">
+        <f>SUM(L5:L13)</f>
+        <v/>
+      </c>
+      <c r="M14" s="40">
+        <f>SUM(M5:M13)</f>
+        <v/>
+      </c>
+      <c r="N14" s="40">
+        <f>SUM(N5:N13)</f>
+        <v/>
+      </c>
+      <c r="O14" s="40">
+        <f>SUM(O5:O13)</f>
+        <v/>
+      </c>
+      <c r="P14" s="40">
+        <f>SUM(P5:P13)</f>
+        <v/>
+      </c>
+      <c r="Q14" s="40">
+        <f>SUM(Q5:Q13)</f>
+        <v/>
+      </c>
+      <c r="R14" s="40">
+        <f>SUM(R5:R13)</f>
+        <v/>
+      </c>
+      <c r="S14" s="40">
+        <f>SUM(S5:S13)</f>
+        <v/>
+      </c>
+      <c r="T14" s="40">
+        <f>SUM(T5:T13)</f>
+        <v/>
+      </c>
+      <c r="U14" s="39" t="n"/>
+      <c r="V14" s="39" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -4131,11 +3930,11 @@
         </is>
       </c>
       <c r="B5" s="26">
-        <f>SUMIFS(Planejado!$H$5:$H$14,Planejado!$B$5:$B$14,"Jurídico")</f>
+        <f>SUMIFS(Planejado!$H$5:$H$13,Planejado!$B$5:$B$13,"Jurídico")</f>
         <v/>
       </c>
       <c r="C5" s="26">
-        <f>SUMIFS(Realizado!$H$5:$H$14,Realizado!$B$5:$B$14,"Jurídico")</f>
+        <f>SUMIFS(Realizado!$H$5:$H$13,Realizado!$B$5:$B$13,"Jurídico")</f>
         <v/>
       </c>
       <c r="D5" s="26">
@@ -4166,11 +3965,11 @@
         </is>
       </c>
       <c r="B6" s="43">
-        <f>SUMIFS(Planejado!$I$5:$I$14,Planejado!$B$5:$B$14,"Jurídico")</f>
+        <f>SUMIFS(Planejado!$I$5:$I$13,Planejado!$B$5:$B$13,"Jurídico")</f>
         <v/>
       </c>
       <c r="C6" s="43">
-        <f>SUMIFS(Realizado!$I$5:$I$14,Realizado!$B$5:$B$14,"Jurídico")</f>
+        <f>SUMIFS(Realizado!$I$5:$I$13,Realizado!$B$5:$B$13,"Jurídico")</f>
         <v/>
       </c>
       <c r="D6" s="43">
@@ -4201,11 +4000,11 @@
         </is>
       </c>
       <c r="B7" s="26">
-        <f>SUMIFS(Planejado!$J$5:$J$14,Planejado!$B$5:$B$14,"Jurídico")</f>
+        <f>SUMIFS(Planejado!$J$5:$J$13,Planejado!$B$5:$B$13,"Jurídico")</f>
         <v/>
       </c>
       <c r="C7" s="26">
-        <f>SUMIFS(Realizado!$J$5:$J$14,Realizado!$B$5:$B$14,"Jurídico")</f>
+        <f>SUMIFS(Realizado!$J$5:$J$13,Realizado!$B$5:$B$13,"Jurídico")</f>
         <v/>
       </c>
       <c r="D7" s="26">
@@ -4236,11 +4035,11 @@
         </is>
       </c>
       <c r="B8" s="43">
-        <f>SUMIFS(Planejado!$K$5:$K$14,Planejado!$B$5:$B$14,"Jurídico")</f>
+        <f>SUMIFS(Planejado!$K$5:$K$13,Planejado!$B$5:$B$13,"Jurídico")</f>
         <v/>
       </c>
       <c r="C8" s="43">
-        <f>SUMIFS(Realizado!$K$5:$K$14,Realizado!$B$5:$B$14,"Jurídico")</f>
+        <f>SUMIFS(Realizado!$K$5:$K$13,Realizado!$B$5:$B$13,"Jurídico")</f>
         <v/>
       </c>
       <c r="D8" s="43">
@@ -4271,11 +4070,11 @@
         </is>
       </c>
       <c r="B9" s="26">
-        <f>SUMIFS(Planejado!$L$5:$L$14,Planejado!$B$5:$B$14,"Jurídico")</f>
+        <f>SUMIFS(Planejado!$L$5:$L$13,Planejado!$B$5:$B$13,"Jurídico")</f>
         <v/>
       </c>
       <c r="C9" s="26">
-        <f>SUMIFS(Realizado!$L$5:$L$14,Realizado!$B$5:$B$14,"Jurídico")</f>
+        <f>SUMIFS(Realizado!$L$5:$L$13,Realizado!$B$5:$B$13,"Jurídico")</f>
         <v/>
       </c>
       <c r="D9" s="26">
@@ -4306,11 +4105,11 @@
         </is>
       </c>
       <c r="B10" s="43">
-        <f>SUMIFS(Planejado!$M$5:$M$14,Planejado!$B$5:$B$14,"Jurídico")</f>
+        <f>SUMIFS(Planejado!$M$5:$M$13,Planejado!$B$5:$B$13,"Jurídico")</f>
         <v/>
       </c>
       <c r="C10" s="43">
-        <f>SUMIFS(Realizado!$M$5:$M$14,Realizado!$B$5:$B$14,"Jurídico")</f>
+        <f>SUMIFS(Realizado!$M$5:$M$13,Realizado!$B$5:$B$13,"Jurídico")</f>
         <v/>
       </c>
       <c r="D10" s="43">
@@ -4341,11 +4140,11 @@
         </is>
       </c>
       <c r="B11" s="26">
-        <f>SUMIFS(Planejado!$N$5:$N$14,Planejado!$B$5:$B$14,"Jurídico")</f>
+        <f>SUMIFS(Planejado!$N$5:$N$13,Planejado!$B$5:$B$13,"Jurídico")</f>
         <v/>
       </c>
       <c r="C11" s="26">
-        <f>SUMIFS(Realizado!$N$5:$N$14,Realizado!$B$5:$B$14,"Jurídico")</f>
+        <f>SUMIFS(Realizado!$N$5:$N$13,Realizado!$B$5:$B$13,"Jurídico")</f>
         <v/>
       </c>
       <c r="D11" s="26">
@@ -4376,11 +4175,11 @@
         </is>
       </c>
       <c r="B12" s="43">
-        <f>SUMIFS(Planejado!$O$5:$O$14,Planejado!$B$5:$B$14,"Jurídico")</f>
+        <f>SUMIFS(Planejado!$O$5:$O$13,Planejado!$B$5:$B$13,"Jurídico")</f>
         <v/>
       </c>
       <c r="C12" s="43">
-        <f>SUMIFS(Realizado!$O$5:$O$14,Realizado!$B$5:$B$14,"Jurídico")</f>
+        <f>SUMIFS(Realizado!$O$5:$O$13,Realizado!$B$5:$B$13,"Jurídico")</f>
         <v/>
       </c>
       <c r="D12" s="43">
@@ -4411,11 +4210,11 @@
         </is>
       </c>
       <c r="B13" s="26">
-        <f>SUMIFS(Planejado!$P$5:$P$14,Planejado!$B$5:$B$14,"Jurídico")</f>
+        <f>SUMIFS(Planejado!$P$5:$P$13,Planejado!$B$5:$B$13,"Jurídico")</f>
         <v/>
       </c>
       <c r="C13" s="26">
-        <f>SUMIFS(Realizado!$P$5:$P$14,Realizado!$B$5:$B$14,"Jurídico")</f>
+        <f>SUMIFS(Realizado!$P$5:$P$13,Realizado!$B$5:$B$13,"Jurídico")</f>
         <v/>
       </c>
       <c r="D13" s="26">
@@ -4446,11 +4245,11 @@
         </is>
       </c>
       <c r="B14" s="43">
-        <f>SUMIFS(Planejado!$Q$5:$Q$14,Planejado!$B$5:$B$14,"Jurídico")</f>
+        <f>SUMIFS(Planejado!$Q$5:$Q$13,Planejado!$B$5:$B$13,"Jurídico")</f>
         <v/>
       </c>
       <c r="C14" s="43">
-        <f>SUMIFS(Realizado!$Q$5:$Q$14,Realizado!$B$5:$B$14,"Jurídico")</f>
+        <f>SUMIFS(Realizado!$Q$5:$Q$13,Realizado!$B$5:$B$13,"Jurídico")</f>
         <v/>
       </c>
       <c r="D14" s="43">
@@ -4481,11 +4280,11 @@
         </is>
       </c>
       <c r="B15" s="26">
-        <f>SUMIFS(Planejado!$R$5:$R$14,Planejado!$B$5:$B$14,"Jurídico")</f>
+        <f>SUMIFS(Planejado!$R$5:$R$13,Planejado!$B$5:$B$13,"Jurídico")</f>
         <v/>
       </c>
       <c r="C15" s="26">
-        <f>SUMIFS(Realizado!$R$5:$R$14,Realizado!$B$5:$B$14,"Jurídico")</f>
+        <f>SUMIFS(Realizado!$R$5:$R$13,Realizado!$B$5:$B$13,"Jurídico")</f>
         <v/>
       </c>
       <c r="D15" s="26">
@@ -4516,11 +4315,11 @@
         </is>
       </c>
       <c r="B16" s="43">
-        <f>SUMIFS(Planejado!$S$5:$S$14,Planejado!$B$5:$B$14,"Jurídico")</f>
+        <f>SUMIFS(Planejado!$S$5:$S$13,Planejado!$B$5:$B$13,"Jurídico")</f>
         <v/>
       </c>
       <c r="C16" s="43">
-        <f>SUMIFS(Realizado!$S$5:$S$14,Realizado!$B$5:$B$14,"Jurídico")</f>
+        <f>SUMIFS(Realizado!$S$5:$S$13,Realizado!$B$5:$B$13,"Jurídico")</f>
         <v/>
       </c>
       <c r="D16" s="43">
@@ -4597,7 +4396,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H11"/>
+  <dimension ref="A1:H10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -4673,11 +4472,11 @@
         </is>
       </c>
       <c r="B5" s="26">
-        <f>SUMIFS(Comparativo!$I$6:$I$15,Comparativo!$E$6:$E$15,$A5,Comparativo!$B$6:$B$15,"Jurídico")</f>
+        <f>SUMIFS(Comparativo!$I$6:$I$14,Comparativo!$E$6:$E$14,$A5,Comparativo!$B$6:$B$14,"Jurídico")</f>
         <v/>
       </c>
       <c r="C5" s="26">
-        <f>SUMIFS(Comparativo!$J$6:$J$15,Comparativo!$E$6:$E$15,$A5,Comparativo!$B$6:$B$15,"Jurídico")</f>
+        <f>SUMIFS(Comparativo!$J$6:$J$14,Comparativo!$E$6:$E$14,$A5,Comparativo!$B$6:$B$14,"Jurídico")</f>
         <v/>
       </c>
       <c r="D5" s="26">
@@ -4697,22 +4496,22 @@
         <v/>
       </c>
       <c r="H5" s="26">
-        <f>SUMIFS(Planejado!$T$5:$T$14,Planejado!$G$5:$G$14,$A5)</f>
+        <f>SUMIFS(Planejado!$T$5:$T$13,Planejado!$G$5:$G$13,$A5)</f>
         <v/>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1">
       <c r="A6" s="46" t="inlineStr">
         <is>
-          <t>Encargos e Benefícios - CLT</t>
+          <t>Pessoal - PJ</t>
         </is>
       </c>
       <c r="B6" s="43">
-        <f>SUMIFS(Comparativo!$I$6:$I$15,Comparativo!$E$6:$E$15,$A6,Comparativo!$B$6:$B$15,"Jurídico")</f>
+        <f>SUMIFS(Comparativo!$I$6:$I$14,Comparativo!$E$6:$E$14,$A6,Comparativo!$B$6:$B$14,"Jurídico")</f>
         <v/>
       </c>
       <c r="C6" s="43">
-        <f>SUMIFS(Comparativo!$J$6:$J$15,Comparativo!$E$6:$E$15,$A6,Comparativo!$B$6:$B$15,"Jurídico")</f>
+        <f>SUMIFS(Comparativo!$J$6:$J$14,Comparativo!$E$6:$E$14,$A6,Comparativo!$B$6:$B$14,"Jurídico")</f>
         <v/>
       </c>
       <c r="D6" s="43">
@@ -4732,22 +4531,22 @@
         <v/>
       </c>
       <c r="H6" s="43">
-        <f>SUMIFS(Planejado!$T$5:$T$14,Planejado!$G$5:$G$14,$A6)</f>
+        <f>SUMIFS(Planejado!$T$5:$T$13,Planejado!$G$5:$G$13,$A6)</f>
         <v/>
       </c>
     </row>
     <row r="7" ht="20" customHeight="1">
       <c r="A7" s="44" t="inlineStr">
         <is>
-          <t>Pessoal - PJ</t>
+          <t>Licenças de Softwares</t>
         </is>
       </c>
       <c r="B7" s="26">
-        <f>SUMIFS(Comparativo!$I$6:$I$15,Comparativo!$E$6:$E$15,$A7,Comparativo!$B$6:$B$15,"Jurídico")</f>
+        <f>SUMIFS(Comparativo!$I$6:$I$14,Comparativo!$E$6:$E$14,$A7,Comparativo!$B$6:$B$14,"Jurídico")</f>
         <v/>
       </c>
       <c r="C7" s="26">
-        <f>SUMIFS(Comparativo!$J$6:$J$15,Comparativo!$E$6:$E$15,$A7,Comparativo!$B$6:$B$15,"Jurídico")</f>
+        <f>SUMIFS(Comparativo!$J$6:$J$14,Comparativo!$E$6:$E$14,$A7,Comparativo!$B$6:$B$14,"Jurídico")</f>
         <v/>
       </c>
       <c r="D7" s="26">
@@ -4767,22 +4566,22 @@
         <v/>
       </c>
       <c r="H7" s="26">
-        <f>SUMIFS(Planejado!$T$5:$T$14,Planejado!$G$5:$G$14,$A7)</f>
+        <f>SUMIFS(Planejado!$T$5:$T$13,Planejado!$G$5:$G$13,$A7)</f>
         <v/>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1">
       <c r="A8" s="46" t="inlineStr">
         <is>
-          <t>Licenças de Softwares</t>
+          <t>Custeio de Treinamento</t>
         </is>
       </c>
       <c r="B8" s="43">
-        <f>SUMIFS(Comparativo!$I$6:$I$15,Comparativo!$E$6:$E$15,$A8,Comparativo!$B$6:$B$15,"Jurídico")</f>
+        <f>SUMIFS(Comparativo!$I$6:$I$14,Comparativo!$E$6:$E$14,$A8,Comparativo!$B$6:$B$14,"Jurídico")</f>
         <v/>
       </c>
       <c r="C8" s="43">
-        <f>SUMIFS(Comparativo!$J$6:$J$15,Comparativo!$E$6:$E$15,$A8,Comparativo!$B$6:$B$15,"Jurídico")</f>
+        <f>SUMIFS(Comparativo!$J$6:$J$14,Comparativo!$E$6:$E$14,$A8,Comparativo!$B$6:$B$14,"Jurídico")</f>
         <v/>
       </c>
       <c r="D8" s="43">
@@ -4802,22 +4601,22 @@
         <v/>
       </c>
       <c r="H8" s="43">
-        <f>SUMIFS(Planejado!$T$5:$T$14,Planejado!$G$5:$G$14,$A8)</f>
+        <f>SUMIFS(Planejado!$T$5:$T$13,Planejado!$G$5:$G$13,$A8)</f>
         <v/>
       </c>
     </row>
     <row r="9" ht="20" customHeight="1">
       <c r="A9" s="44" t="inlineStr">
         <is>
-          <t>Custeio de Treinamento</t>
+          <t>Prêmios</t>
         </is>
       </c>
       <c r="B9" s="26">
-        <f>SUMIFS(Comparativo!$I$6:$I$15,Comparativo!$E$6:$E$15,$A9,Comparativo!$B$6:$B$15,"Jurídico")</f>
+        <f>SUMIFS(Comparativo!$I$6:$I$14,Comparativo!$E$6:$E$14,$A9,Comparativo!$B$6:$B$14,"Jurídico")</f>
         <v/>
       </c>
       <c r="C9" s="26">
-        <f>SUMIFS(Comparativo!$J$6:$J$15,Comparativo!$E$6:$E$15,$A9,Comparativo!$B$6:$B$15,"Jurídico")</f>
+        <f>SUMIFS(Comparativo!$J$6:$J$14,Comparativo!$E$6:$E$14,$A9,Comparativo!$B$6:$B$14,"Jurídico")</f>
         <v/>
       </c>
       <c r="D9" s="26">
@@ -4837,77 +4636,42 @@
         <v/>
       </c>
       <c r="H9" s="26">
-        <f>SUMIFS(Planejado!$T$5:$T$14,Planejado!$G$5:$G$14,$A9)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="10" ht="20" customHeight="1">
-      <c r="A10" s="46" t="inlineStr">
-        <is>
-          <t>Prêmios</t>
-        </is>
-      </c>
-      <c r="B10" s="43">
-        <f>SUMIFS(Comparativo!$I$6:$I$15,Comparativo!$E$6:$E$15,$A10,Comparativo!$B$6:$B$15,"Jurídico")</f>
-        <v/>
-      </c>
-      <c r="C10" s="43">
-        <f>SUMIFS(Comparativo!$J$6:$J$15,Comparativo!$E$6:$E$15,$A10,Comparativo!$B$6:$B$15,"Jurídico")</f>
-        <v/>
-      </c>
-      <c r="D10" s="43">
-        <f>B10</f>
-        <v/>
-      </c>
-      <c r="E10" s="43">
-        <f>C10</f>
-        <v/>
-      </c>
-      <c r="F10" s="43">
-        <f>E10-D10</f>
-        <v/>
-      </c>
-      <c r="G10" s="47">
+        <f>SUMIFS(Planejado!$T$5:$T$13,Planejado!$G$5:$G$13,$A9)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="30" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="B10" s="31">
+        <f>SUM(B5:B9)</f>
+        <v/>
+      </c>
+      <c r="C10" s="31">
+        <f>SUM(C5:C9)</f>
+        <v/>
+      </c>
+      <c r="D10" s="31">
+        <f>SUM(D5:D9)</f>
+        <v/>
+      </c>
+      <c r="E10" s="31">
+        <f>SUM(E5:E9)</f>
+        <v/>
+      </c>
+      <c r="F10" s="31">
+        <f>SUM(F5:F9)</f>
+        <v/>
+      </c>
+      <c r="G10" s="48">
         <f>IFERROR(F10/D10,"")</f>
         <v/>
       </c>
-      <c r="H10" s="43">
-        <f>SUMIFS(Planejado!$T$5:$T$14,Planejado!$G$5:$G$14,$A10)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="30" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="B11" s="31">
-        <f>SUM(B5:B10)</f>
-        <v/>
-      </c>
-      <c r="C11" s="31">
-        <f>SUM(C5:C10)</f>
-        <v/>
-      </c>
-      <c r="D11" s="31">
-        <f>SUM(D5:D10)</f>
-        <v/>
-      </c>
-      <c r="E11" s="31">
-        <f>SUM(E5:E10)</f>
-        <v/>
-      </c>
-      <c r="F11" s="31">
-        <f>SUM(F5:F10)</f>
-        <v/>
-      </c>
-      <c r="G11" s="48">
-        <f>IFERROR(F11/D11,"")</f>
-        <v/>
-      </c>
-      <c r="H11" s="31">
-        <f>SUM(H5:H10)</f>
+      <c r="H10" s="31">
+        <f>SUM(H5:H9)</f>
         <v/>
       </c>
     </row>
@@ -4916,7 +4680,7 @@
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="A1:G1"/>
   </mergeCells>
-  <conditionalFormatting sqref="F5:F10">
+  <conditionalFormatting sqref="F5:F9">
     <cfRule type="cellIs" priority="1" operator="greaterThan" dxfId="0">
       <formula>0</formula>
     </cfRule>
@@ -4999,17 +4763,17 @@
       </c>
       <c r="B5" s="50" t="inlineStr">
         <is>
-          <t>Encargos da Geovanna — CAMPO A PREENCHER</t>
+          <t>Custo total da Geovanna — A LANÇAR</t>
         </is>
       </c>
       <c r="C5" s="50" t="inlineStr">
         <is>
-          <t>A linha JUR-E02B recebe os encargos e benefícios sobre o salário bruto (INSS patronal, FGTS, provisões de 13º e férias, VT/VR, plano de saúde). Hoje está em branco.</t>
+          <t>O planejado dela é R$ 4.825,52/mês, que é o custo total orçado na ficha (salário + encargos de folha + benefícios). O dado disponível hoje é só o salário bruto, R$ 2.886,91/mês. O realizado está em branco.</t>
         </is>
       </c>
       <c r="D5" s="50" t="inlineStr">
         <is>
-          <t>Enquanto não for preenchida, a folha do Jurídico aparece R$ 1.938,61/mês abaixo do orçado — economia que não existe, é só encargo não lançado.</t>
+          <t>Lançar só o bruto contra um orçado de custo total mostraria economia de R$ 1.938,61/mês que não existe. Peça ao RH o custo total mensal dela, ou o bruto mais os encargos para somar antes de lançar.</t>
         </is>
       </c>
       <c r="E5" s="50" t="inlineStr">
@@ -5019,7 +4783,7 @@
       </c>
       <c r="F5" s="51" t="inlineStr">
         <is>
-          <t>PREENCHER</t>
+          <t>A LANÇAR</t>
         </is>
       </c>
     </row>

--- a/orcamento/Orcamento_JURIDICO_2026.xlsx
+++ b/orcamento/Orcamento_JURIDICO_2026.xlsx
@@ -3303,10 +3303,18 @@
         <f>Planejado!G5</f>
         <v/>
       </c>
-      <c r="H5" s="37" t="n"/>
-      <c r="I5" s="37" t="n"/>
-      <c r="J5" s="37" t="n"/>
-      <c r="K5" s="37" t="n"/>
+      <c r="H5" s="37" t="n">
+        <v>8818</v>
+      </c>
+      <c r="I5" s="37" t="n">
+        <v>8818</v>
+      </c>
+      <c r="J5" s="37" t="n">
+        <v>8818</v>
+      </c>
+      <c r="K5" s="37" t="n">
+        <v>8818</v>
+      </c>
       <c r="L5" s="37" t="n">
         <v>8818</v>
       </c>
@@ -3409,10 +3417,18 @@
         <f>Planejado!G7</f>
         <v/>
       </c>
-      <c r="H7" s="37" t="n"/>
-      <c r="I7" s="37" t="n"/>
-      <c r="J7" s="37" t="n"/>
-      <c r="K7" s="37" t="n"/>
+      <c r="H7" s="37" t="n">
+        <v>5500</v>
+      </c>
+      <c r="I7" s="37" t="n">
+        <v>5500</v>
+      </c>
+      <c r="J7" s="37" t="n">
+        <v>5500</v>
+      </c>
+      <c r="K7" s="37" t="n">
+        <v>5500</v>
+      </c>
       <c r="L7" s="37" t="n">
         <v>5500</v>
       </c>
@@ -3467,10 +3483,18 @@
         <f>Planejado!G8</f>
         <v/>
       </c>
-      <c r="H8" s="37" t="n"/>
-      <c r="I8" s="37" t="n"/>
-      <c r="J8" s="37" t="n"/>
-      <c r="K8" s="37" t="n"/>
+      <c r="H8" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" s="37" t="n">
+        <v>0</v>
+      </c>
       <c r="L8" s="37" t="n">
         <v>0</v>
       </c>
@@ -3525,10 +3549,18 @@
         <f>Planejado!G9</f>
         <v/>
       </c>
-      <c r="H9" s="37" t="n"/>
-      <c r="I9" s="37" t="n"/>
-      <c r="J9" s="37" t="n"/>
-      <c r="K9" s="37" t="n"/>
+      <c r="H9" s="37" t="n">
+        <v>136</v>
+      </c>
+      <c r="I9" s="37" t="n">
+        <v>136</v>
+      </c>
+      <c r="J9" s="37" t="n">
+        <v>136</v>
+      </c>
+      <c r="K9" s="37" t="n">
+        <v>136</v>
+      </c>
       <c r="L9" s="37" t="n">
         <v>136</v>
       </c>
@@ -3583,10 +3615,18 @@
         <f>Planejado!G10</f>
         <v/>
       </c>
-      <c r="H10" s="37" t="n"/>
-      <c r="I10" s="37" t="n"/>
-      <c r="J10" s="37" t="n"/>
-      <c r="K10" s="37" t="n"/>
+      <c r="H10" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" s="37" t="n">
+        <v>0</v>
+      </c>
       <c r="L10" s="37" t="n">
         <v>0</v>
       </c>
@@ -3641,10 +3681,18 @@
         <f>Planejado!G11</f>
         <v/>
       </c>
-      <c r="H11" s="37" t="n"/>
-      <c r="I11" s="37" t="n"/>
-      <c r="J11" s="37" t="n"/>
-      <c r="K11" s="37" t="n"/>
+      <c r="H11" s="37" t="n">
+        <v>970</v>
+      </c>
+      <c r="I11" s="37" t="n">
+        <v>970</v>
+      </c>
+      <c r="J11" s="37" t="n">
+        <v>970</v>
+      </c>
+      <c r="K11" s="37" t="n">
+        <v>970</v>
+      </c>
       <c r="L11" s="37" t="n">
         <v>970</v>
       </c>
@@ -3695,10 +3743,18 @@
         <f>Planejado!G12</f>
         <v/>
       </c>
-      <c r="H12" s="37" t="n"/>
-      <c r="I12" s="37" t="n"/>
-      <c r="J12" s="37" t="n"/>
-      <c r="K12" s="37" t="n"/>
+      <c r="H12" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="J12" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" s="37" t="n">
+        <v>0</v>
+      </c>
       <c r="L12" s="37" t="n">
         <v>0</v>
       </c>
@@ -3753,22 +3809,40 @@
         <f>Planejado!G13</f>
         <v/>
       </c>
-      <c r="H13" s="37" t="n"/>
-      <c r="I13" s="37" t="n"/>
-      <c r="J13" s="37" t="n"/>
-      <c r="K13" s="37" t="n"/>
-      <c r="L13" s="37" t="n"/>
-      <c r="M13" s="37" t="n"/>
-      <c r="N13" s="37" t="n"/>
+      <c r="H13" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="J13" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" s="37" t="n">
+        <v>0</v>
+      </c>
       <c r="O13" s="37" t="n"/>
       <c r="T13" s="33">
         <f>SUM(H13:S13)</f>
         <v/>
       </c>
-      <c r="U13" s="38" t="n"/>
+      <c r="U13" s="38" t="inlineStr">
+        <is>
+          <t>Gestora, 05/08/26</t>
+        </is>
+      </c>
       <c r="V13" s="38" t="inlineStr">
         <is>
-          <t>Bonificação de ago/26 a confirmar</t>
+          <t>Sem parcela no 1º semestre; bonificação de ago/26 a confirmar</t>
         </is>
       </c>
     </row>

--- a/orcamento/Orcamento_JURIDICO_2026.xlsx
+++ b/orcamento/Orcamento_JURIDICO_2026.xlsx
@@ -2560,7 +2560,7 @@
       </c>
       <c r="E7" s="25" t="inlineStr">
         <is>
-          <t>Advogada — reajuste permanente de R$ 5.000 para R$ 5.500 (revisado a partir de out/26)</t>
+          <t>Advogada — recebe R$ 5.500/mês desde jan/26 contra R$ 5.000 orçados. Planejado revisado para R$ 5.500 a partir de ago/26</t>
         </is>
       </c>
       <c r="F7" s="24" t="inlineStr">
@@ -2595,10 +2595,10 @@
         <v>5000</v>
       </c>
       <c r="O7" s="26" t="n">
-        <v>5000</v>
+        <v>5500</v>
       </c>
       <c r="P7" s="26" t="n">
-        <v>5000</v>
+        <v>5500</v>
       </c>
       <c r="Q7" s="26" t="n">
         <v>5500</v>
@@ -4869,17 +4869,17 @@
       </c>
       <c r="B6" s="53" t="inlineStr">
         <is>
-          <t>Reajuste da Thamar — revisão orçamentária</t>
+          <t>Thamar acima do orçado desde janeiro</t>
         </is>
       </c>
       <c r="C6" s="53" t="inlineStr">
         <is>
-          <t>Reajuste permanente de R$ 5.000 para R$ 5.500/mês, em vigor desde mai/26. O planejado foi mantido em R$ 5.000 nos meses já realizados (para o desvio ficar visível) e revisado para R$ 5.500 de out a dez.</t>
+          <t>Recebe R$ 5.500/mês desde jan/26 contra R$ 5.000 orçados. O planejado foi mantido em R$ 5.000 nos sete meses fechados (para o desvio ficar visível) e revisado para R$ 5.500 de ago a dez.</t>
         </is>
       </c>
       <c r="D6" s="53" t="inlineStr">
         <is>
-          <t>Desvio já incorrido de R$ 500/mês. Ao contrário do aumento do Vinicius, este estourou o orçado: não havia folga na linha dela.</t>
+          <t>R$ 3.500 já gastos acima do orçado em jan–jul, e mais R$ 2.500 previstos até dezembro. Ao contrário do aumento do Vinicius, este estourou o orçado: não havia folga na linha dela. Orçamento do Jurídico sobe para R$ 291.730,42.</t>
         </is>
       </c>
       <c r="E6" s="53" t="inlineStr">

--- a/orcamento/Orcamento_JURIDICO_2026.xlsx
+++ b/orcamento/Orcamento_JURIDICO_2026.xlsx
@@ -2560,7 +2560,7 @@
       </c>
       <c r="E7" s="25" t="inlineStr">
         <is>
-          <t>Advogada — recebe R$ 5.500/mês desde jan/26 contra R$ 5.000 orçados. Planejado revisado para R$ 5.500 a partir de ago/26</t>
+          <t>Advogada — recebia R$ 4.500/mês em jan–fev e passou a R$ 5.500 em mar/26 (aumento de R$ 1.000), contra R$ 5.000 orçados. Planejado revisado para R$ 5.500 a partir de ago/26</t>
         </is>
       </c>
       <c r="F7" s="24" t="inlineStr">
@@ -3418,10 +3418,10 @@
         <v/>
       </c>
       <c r="H7" s="37" t="n">
-        <v>5500</v>
+        <v>4500</v>
       </c>
       <c r="I7" s="37" t="n">
-        <v>5500</v>
+        <v>4500</v>
       </c>
       <c r="J7" s="37" t="n">
         <v>5500</v>
@@ -3450,7 +3450,7 @@
       </c>
       <c r="V7" s="38" t="inlineStr">
         <is>
-          <t>Reajuste permanente aplicado desde mai/26</t>
+          <t>R$ 4.500/mês em jan–fev; aumento de R$ 1.000 a partir de mar/26</t>
         </is>
       </c>
     </row>
@@ -4869,17 +4869,17 @@
       </c>
       <c r="B6" s="53" t="inlineStr">
         <is>
-          <t>Thamar acima do orçado desde janeiro</t>
+          <t>Aumento da Thamar em mar/26</t>
         </is>
       </c>
       <c r="C6" s="53" t="inlineStr">
         <is>
-          <t>Recebe R$ 5.500/mês desde jan/26 contra R$ 5.000 orçados. O planejado foi mantido em R$ 5.000 nos sete meses fechados (para o desvio ficar visível) e revisado para R$ 5.500 de ago a dez.</t>
+          <t>Recebia R$ 4.500/mês em jan e fev, abaixo dos R$ 5.000 orçados. Em mar/26 teve aumento de R$ 1.000 e passou a R$ 5.500, acima do orçado. O planejado foi mantido em R$ 5.000 nos sete meses fechados (para o desvio ficar visível) e revisado para R$ 5.500 de ago a dez.</t>
         </is>
       </c>
       <c r="D6" s="53" t="inlineStr">
         <is>
-          <t>R$ 3.500 já gastos acima do orçado em jan–jul, e mais R$ 2.500 previstos até dezembro. Ao contrário do aumento do Vinicius, este estourou o orçado: não havia folga na linha dela. Orçamento do Jurídico sobe para R$ 291.730,42.</t>
+          <t>No acumulado jan–jul o efeito líquido é de R$ 1.500 acima do orçado (−R$ 1.000 em jan–fev, +R$ 2.500 em mar–jul), e mais R$ 2.500 previstos até dezembro. Ao contrário do aumento do Vinicius, este estourou o orçado: não havia folga na linha dela.</t>
         </is>
       </c>
       <c r="E6" s="53" t="inlineStr">

--- a/orcamento/Orcamento_JURIDICO_2026.xlsx
+++ b/orcamento/Orcamento_JURIDICO_2026.xlsx
@@ -2560,7 +2560,7 @@
       </c>
       <c r="E7" s="25" t="inlineStr">
         <is>
-          <t>Advogada — recebia R$ 4.500/mês em jan–fev e passou a R$ 5.500 em mar/26 (aumento de R$ 1.000), contra R$ 5.000 orçados. Planejado revisado para R$ 5.500 a partir de ago/26</t>
+          <t>Advogada — recebia R$ 4.500/mês em jan–mar e passou a R$ 5.500 em abr/26 (aumento de R$ 1.000), contra R$ 5.000 orçados. Planejado revisado para R$ 5.500 a partir de ago/26</t>
         </is>
       </c>
       <c r="F7" s="24" t="inlineStr">
@@ -3424,7 +3424,7 @@
         <v>4500</v>
       </c>
       <c r="J7" s="37" t="n">
-        <v>5500</v>
+        <v>4500</v>
       </c>
       <c r="K7" s="37" t="n">
         <v>5500</v>
@@ -3450,7 +3450,7 @@
       </c>
       <c r="V7" s="38" t="inlineStr">
         <is>
-          <t>R$ 4.500/mês em jan–fev; aumento de R$ 1.000 a partir de mar/26</t>
+          <t>R$ 4.500/mês em jan–mar; aumento de R$ 1.000 a partir de abr/26</t>
         </is>
       </c>
     </row>
@@ -4869,17 +4869,17 @@
       </c>
       <c r="B6" s="53" t="inlineStr">
         <is>
-          <t>Aumento da Thamar em mar/26</t>
+          <t>Aumento da Thamar em abr/26</t>
         </is>
       </c>
       <c r="C6" s="53" t="inlineStr">
         <is>
-          <t>Recebia R$ 4.500/mês em jan e fev, abaixo dos R$ 5.000 orçados. Em mar/26 teve aumento de R$ 1.000 e passou a R$ 5.500, acima do orçado. O planejado foi mantido em R$ 5.000 nos sete meses fechados (para o desvio ficar visível) e revisado para R$ 5.500 de ago a dez.</t>
+          <t>Recebia R$ 4.500/mês de jan a mar, abaixo dos R$ 5.000 orçados. Em abr/26 teve aumento de R$ 1.000 e passou a R$ 5.500, acima do orçado. O planejado foi mantido em R$ 5.000 nos sete meses fechados (para o desvio ficar visível) e revisado para R$ 5.500 de ago a dez.</t>
         </is>
       </c>
       <c r="D6" s="53" t="inlineStr">
         <is>
-          <t>No acumulado jan–jul o efeito líquido é de R$ 1.500 acima do orçado (−R$ 1.000 em jan–fev, +R$ 2.500 em mar–jul), e mais R$ 2.500 previstos até dezembro. Ao contrário do aumento do Vinicius, este estourou o orçado: não havia folga na linha dela.</t>
+          <t>No acumulado jan–jul o efeito líquido é de apenas R$ 500 acima do orçado (−R$ 1.500 em jan–mar, +R$ 2.000 em abr–jul), e mais R$ 2.500 previstos até dezembro. Ao contrário do aumento do Vinicius, este estourou o orçado: não havia folga na linha dela.</t>
         </is>
       </c>
       <c r="E6" s="53" t="inlineStr">

--- a/orcamento/Orcamento_JURIDICO_2026.xlsx
+++ b/orcamento/Orcamento_JURIDICO_2026.xlsx
@@ -30,7 +30,7 @@
     <numFmt numFmtId="164" formatCode="R$ #,##0.00"/>
     <numFmt numFmtId="165" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="18">
+  <fonts count="19">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -95,6 +95,11 @@
       <sz val="9"/>
     </font>
     <font>
+      <b val="1"/>
+      <color rgb="009C0006"/>
+      <sz val="9"/>
+    </font>
+    <font>
       <color rgb="00000000"/>
       <sz val="10"/>
     </font>
@@ -112,7 +117,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="13">
+  <fills count="14">
     <fill>
       <patternFill/>
     </fill>
@@ -152,6 +157,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00FFF7DC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFC7CE"/>
       </patternFill>
     </fill>
     <fill>
@@ -201,7 +211,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="59">
+  <cellXfs count="60">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
@@ -214,26 +224,29 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="14" fillId="9" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="14" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="14" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="15" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="15" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="15" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="15" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="16" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="16" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="16" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="16" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -305,7 +318,7 @@
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -314,19 +327,19 @@
     <xf numFmtId="0" fontId="4" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1056,366 +1069,374 @@
         </is>
       </c>
     </row>
+    <row r="4" ht="20" customHeight="1">
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>⚠ Geovanna: realizado em salário bruto; orçado em custo total — o desvio desta linha não é economia.</t>
+        </is>
+      </c>
+    </row>
     <row r="5" ht="30" customHeight="1">
-      <c r="A5" s="6" t="inlineStr">
+      <c r="A5" s="7" t="inlineStr">
         <is>
           <t>Departamento</t>
         </is>
       </c>
-      <c r="B5" s="6" t="inlineStr">
+      <c r="B5" s="7" t="inlineStr">
         <is>
           <t>Bloco</t>
         </is>
       </c>
-      <c r="C5" s="6" t="inlineStr">
+      <c r="C5" s="7" t="inlineStr">
         <is>
           <t>Orçado do ano</t>
         </is>
       </c>
-      <c r="D5" s="6" t="inlineStr">
+      <c r="D5" s="7" t="inlineStr">
         <is>
           <t>Planejado acum.</t>
         </is>
       </c>
-      <c r="E5" s="6" t="inlineStr">
+      <c r="E5" s="7" t="inlineStr">
         <is>
           <t>Realizado acum.</t>
         </is>
       </c>
-      <c r="F5" s="6" t="inlineStr">
+      <c r="F5" s="7" t="inlineStr">
         <is>
           <t>Desvio (R$)</t>
         </is>
       </c>
-      <c r="G5" s="6" t="inlineStr">
+      <c r="G5" s="7" t="inlineStr">
         <is>
           <t>Desvio (%)</t>
         </is>
       </c>
-      <c r="H5" s="6" t="inlineStr">
+      <c r="H5" s="7" t="inlineStr">
         <is>
           <t>% Executado do ano</t>
         </is>
       </c>
-      <c r="I5" s="6" t="inlineStr">
+      <c r="I5" s="7" t="inlineStr">
         <is>
           <t>Linhas lançadas</t>
         </is>
       </c>
     </row>
     <row r="6" ht="22" customHeight="1">
-      <c r="A6" s="7" t="inlineStr">
+      <c r="A6" s="8" t="inlineStr">
         <is>
           <t>Jurídico</t>
         </is>
       </c>
-      <c r="B6" s="7" t="inlineStr">
+      <c r="B6" s="8" t="inlineStr">
         <is>
           <t>Equipe</t>
         </is>
       </c>
-      <c r="C6" s="8">
+      <c r="C6" s="9">
         <f>SUMIFS(Planejado!$T$5:$T$13,Planejado!$B$5:$B$13,"Jurídico",Planejado!$C$5:$C$13,"Equipe")</f>
         <v/>
       </c>
-      <c r="D6" s="8">
+      <c r="D6" s="9">
         <f>SUMIFS(Comparativo!$I$6:$I$14,Comparativo!$B$6:$B$14,"Jurídico",Comparativo!$C$6:$C$14,"Equipe")</f>
         <v/>
       </c>
-      <c r="E6" s="8">
+      <c r="E6" s="9">
         <f>SUMIFS(Comparativo!$J$6:$J$14,Comparativo!$B$6:$B$14,"Jurídico",Comparativo!$C$6:$C$14,"Equipe")</f>
         <v/>
       </c>
-      <c r="F6" s="8">
+      <c r="F6" s="9">
         <f>E6-D6</f>
         <v/>
       </c>
-      <c r="G6" s="9">
+      <c r="G6" s="10">
         <f>IFERROR(F6/D6,"")</f>
         <v/>
       </c>
-      <c r="H6" s="9">
+      <c r="H6" s="10">
         <f>IFERROR(E6/C6,"")</f>
         <v/>
       </c>
-      <c r="I6" s="10">
+      <c r="I6" s="11">
         <f>COUNTIFS(Comparativo!$P$6:$P$14,"&gt;0",Comparativo!$B$6:$B$14,"Jurídico",Comparativo!$C$6:$C$14,"Equipe")&amp;" de "&amp;COUNTIFS(Comparativo!$A$6:$A$14,"?*",Comparativo!$B$6:$B$14,"Jurídico",Comparativo!$C$6:$C$14,"Equipe")</f>
         <v/>
       </c>
     </row>
     <row r="7" ht="22" customHeight="1">
-      <c r="A7" s="7" t="inlineStr">
+      <c r="A7" s="8" t="inlineStr">
         <is>
           <t>Jurídico</t>
         </is>
       </c>
-      <c r="B7" s="7" t="inlineStr">
+      <c r="B7" s="8" t="inlineStr">
         <is>
           <t>Despesas</t>
         </is>
       </c>
-      <c r="C7" s="8">
+      <c r="C7" s="9">
         <f>SUMIFS(Planejado!$T$5:$T$13,Planejado!$B$5:$B$13,"Jurídico",Planejado!$C$5:$C$13,"Despesas")</f>
         <v/>
       </c>
-      <c r="D7" s="8">
+      <c r="D7" s="9">
         <f>SUMIFS(Comparativo!$I$6:$I$14,Comparativo!$B$6:$B$14,"Jurídico",Comparativo!$C$6:$C$14,"Despesas")</f>
         <v/>
       </c>
-      <c r="E7" s="8">
+      <c r="E7" s="9">
         <f>SUMIFS(Comparativo!$J$6:$J$14,Comparativo!$B$6:$B$14,"Jurídico",Comparativo!$C$6:$C$14,"Despesas")</f>
         <v/>
       </c>
-      <c r="F7" s="8">
+      <c r="F7" s="9">
         <f>E7-D7</f>
         <v/>
       </c>
-      <c r="G7" s="9">
+      <c r="G7" s="10">
         <f>IFERROR(F7/D7,"")</f>
         <v/>
       </c>
-      <c r="H7" s="9">
+      <c r="H7" s="10">
         <f>IFERROR(E7/C7,"")</f>
         <v/>
       </c>
-      <c r="I7" s="10">
+      <c r="I7" s="11">
         <f>COUNTIFS(Comparativo!$P$6:$P$14,"&gt;0",Comparativo!$B$6:$B$14,"Jurídico",Comparativo!$C$6:$C$14,"Despesas")&amp;" de "&amp;COUNTIFS(Comparativo!$A$6:$A$14,"?*",Comparativo!$B$6:$B$14,"Jurídico",Comparativo!$C$6:$C$14,"Despesas")</f>
         <v/>
       </c>
     </row>
     <row r="8" ht="22" customHeight="1">
-      <c r="A8" s="11" t="inlineStr">
+      <c r="A8" s="12" t="inlineStr">
         <is>
           <t>Jurídico</t>
         </is>
       </c>
-      <c r="B8" s="11" t="inlineStr">
+      <c r="B8" s="12" t="inlineStr">
         <is>
           <t>Equipe + Despesas</t>
         </is>
       </c>
-      <c r="C8" s="12">
+      <c r="C8" s="13">
         <f>SUMIFS(Planejado!$T$5:$T$13,Planejado!$B$5:$B$13,"Jurídico")</f>
         <v/>
       </c>
-      <c r="D8" s="12">
+      <c r="D8" s="13">
         <f>SUMIFS(Comparativo!$I$6:$I$14,Comparativo!$B$6:$B$14,"Jurídico")</f>
         <v/>
       </c>
-      <c r="E8" s="12">
+      <c r="E8" s="13">
         <f>SUMIFS(Comparativo!$J$6:$J$14,Comparativo!$B$6:$B$14,"Jurídico")</f>
         <v/>
       </c>
-      <c r="F8" s="12">
+      <c r="F8" s="13">
         <f>E8-D8</f>
         <v/>
       </c>
-      <c r="G8" s="13">
+      <c r="G8" s="14">
         <f>IFERROR(F8/D8,"")</f>
         <v/>
       </c>
-      <c r="H8" s="13">
+      <c r="H8" s="14">
         <f>IFERROR(E8/C8,"")</f>
         <v/>
       </c>
-      <c r="I8" s="14">
+      <c r="I8" s="15">
         <f>COUNTIFS(Comparativo!$P$6:$P$14,"&gt;0",Comparativo!$B$6:$B$14,"Jurídico")&amp;" de "&amp;COUNTIFS(Comparativo!$A$6:$A$14,"?*",Comparativo!$B$6:$B$14,"Jurídico")</f>
         <v/>
       </c>
     </row>
     <row r="11" ht="22" customHeight="1">
-      <c r="A11" s="15" t="inlineStr">
+      <c r="A11" s="16" t="inlineStr">
         <is>
           <t>MAIORES DESVIOS DO ACUMULADO (top 5 acima do orçado)</t>
         </is>
       </c>
     </row>
     <row r="12" ht="30" customHeight="1">
-      <c r="A12" s="6" t="inlineStr">
+      <c r="A12" s="7" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B12" s="6" t="inlineStr">
+      <c r="B12" s="7" t="inlineStr">
         <is>
           <t>Item</t>
         </is>
       </c>
-      <c r="C12" s="6" t="inlineStr">
+      <c r="C12" s="7" t="inlineStr">
         <is>
           <t>Departamento</t>
         </is>
       </c>
-      <c r="D12" s="6" t="inlineStr">
+      <c r="D12" s="7" t="inlineStr">
         <is>
           <t>Planejado acum.</t>
         </is>
       </c>
-      <c r="E12" s="6" t="inlineStr">
+      <c r="E12" s="7" t="inlineStr">
         <is>
           <t>Realizado acum.</t>
         </is>
       </c>
-      <c r="F12" s="6" t="inlineStr">
+      <c r="F12" s="7" t="inlineStr">
         <is>
           <t>Desvio (R$)</t>
         </is>
       </c>
-      <c r="G12" s="6" t="inlineStr">
+      <c r="G12" s="7" t="inlineStr">
         <is>
           <t>Desvio (%)</t>
         </is>
       </c>
-      <c r="H12" s="6" t="inlineStr"/>
+      <c r="H12" s="7" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="16" t="n">
+      <c r="A13" s="17" t="n">
         <v>1</v>
       </c>
-      <c r="B13" s="17">
+      <c r="B13" s="18">
         <f>IFERROR(INDEX(Comparativo!$D$6:$D$14,MATCH(LARGE(Comparativo!$O$6:$O$14,A13),Comparativo!$O$6:$O$14,0)),"")</f>
         <v/>
       </c>
-      <c r="C13" s="17">
+      <c r="C13" s="18">
         <f>IFERROR(INDEX(Comparativo!$B$6:$B$14,MATCH(LARGE(Comparativo!$O$6:$O$14,A13),Comparativo!$O$6:$O$14,0)),"")</f>
         <v/>
       </c>
-      <c r="D13" s="18">
+      <c r="D13" s="19">
         <f>IFERROR(INDEX(Comparativo!$I$6:$I$14,MATCH(LARGE(Comparativo!$O$6:$O$14,A13),Comparativo!$O$6:$O$14,0)),"")</f>
         <v/>
       </c>
-      <c r="E13" s="18">
+      <c r="E13" s="19">
         <f>IFERROR(INDEX(Comparativo!$J$6:$J$14,MATCH(LARGE(Comparativo!$O$6:$O$14,A13),Comparativo!$O$6:$O$14,0)),"")</f>
         <v/>
       </c>
-      <c r="F13" s="18">
+      <c r="F13" s="19">
         <f>IFERROR(INDEX(Comparativo!$K$6:$K$14,MATCH(LARGE(Comparativo!$O$6:$O$14,A13),Comparativo!$O$6:$O$14,0)),"")</f>
         <v/>
       </c>
-      <c r="G13" s="19">
+      <c r="G13" s="20">
         <f>IFERROR(F13/D13,"")</f>
         <v/>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="16" t="n">
+      <c r="A14" s="17" t="n">
         <v>2</v>
       </c>
-      <c r="B14" s="17">
+      <c r="B14" s="18">
         <f>IFERROR(INDEX(Comparativo!$D$6:$D$14,MATCH(LARGE(Comparativo!$O$6:$O$14,A14),Comparativo!$O$6:$O$14,0)),"")</f>
         <v/>
       </c>
-      <c r="C14" s="17">
+      <c r="C14" s="18">
         <f>IFERROR(INDEX(Comparativo!$B$6:$B$14,MATCH(LARGE(Comparativo!$O$6:$O$14,A14),Comparativo!$O$6:$O$14,0)),"")</f>
         <v/>
       </c>
-      <c r="D14" s="18">
+      <c r="D14" s="19">
         <f>IFERROR(INDEX(Comparativo!$I$6:$I$14,MATCH(LARGE(Comparativo!$O$6:$O$14,A14),Comparativo!$O$6:$O$14,0)),"")</f>
         <v/>
       </c>
-      <c r="E14" s="18">
+      <c r="E14" s="19">
         <f>IFERROR(INDEX(Comparativo!$J$6:$J$14,MATCH(LARGE(Comparativo!$O$6:$O$14,A14),Comparativo!$O$6:$O$14,0)),"")</f>
         <v/>
       </c>
-      <c r="F14" s="18">
+      <c r="F14" s="19">
         <f>IFERROR(INDEX(Comparativo!$K$6:$K$14,MATCH(LARGE(Comparativo!$O$6:$O$14,A14),Comparativo!$O$6:$O$14,0)),"")</f>
         <v/>
       </c>
-      <c r="G14" s="19">
+      <c r="G14" s="20">
         <f>IFERROR(F14/D14,"")</f>
         <v/>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="16" t="n">
+      <c r="A15" s="17" t="n">
         <v>3</v>
       </c>
-      <c r="B15" s="17">
+      <c r="B15" s="18">
         <f>IFERROR(INDEX(Comparativo!$D$6:$D$14,MATCH(LARGE(Comparativo!$O$6:$O$14,A15),Comparativo!$O$6:$O$14,0)),"")</f>
         <v/>
       </c>
-      <c r="C15" s="17">
+      <c r="C15" s="18">
         <f>IFERROR(INDEX(Comparativo!$B$6:$B$14,MATCH(LARGE(Comparativo!$O$6:$O$14,A15),Comparativo!$O$6:$O$14,0)),"")</f>
         <v/>
       </c>
-      <c r="D15" s="18">
+      <c r="D15" s="19">
         <f>IFERROR(INDEX(Comparativo!$I$6:$I$14,MATCH(LARGE(Comparativo!$O$6:$O$14,A15),Comparativo!$O$6:$O$14,0)),"")</f>
         <v/>
       </c>
-      <c r="E15" s="18">
+      <c r="E15" s="19">
         <f>IFERROR(INDEX(Comparativo!$J$6:$J$14,MATCH(LARGE(Comparativo!$O$6:$O$14,A15),Comparativo!$O$6:$O$14,0)),"")</f>
         <v/>
       </c>
-      <c r="F15" s="18">
+      <c r="F15" s="19">
         <f>IFERROR(INDEX(Comparativo!$K$6:$K$14,MATCH(LARGE(Comparativo!$O$6:$O$14,A15),Comparativo!$O$6:$O$14,0)),"")</f>
         <v/>
       </c>
-      <c r="G15" s="19">
+      <c r="G15" s="20">
         <f>IFERROR(F15/D15,"")</f>
         <v/>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="16" t="n">
+      <c r="A16" s="17" t="n">
         <v>4</v>
       </c>
-      <c r="B16" s="17">
+      <c r="B16" s="18">
         <f>IFERROR(INDEX(Comparativo!$D$6:$D$14,MATCH(LARGE(Comparativo!$O$6:$O$14,A16),Comparativo!$O$6:$O$14,0)),"")</f>
         <v/>
       </c>
-      <c r="C16" s="17">
+      <c r="C16" s="18">
         <f>IFERROR(INDEX(Comparativo!$B$6:$B$14,MATCH(LARGE(Comparativo!$O$6:$O$14,A16),Comparativo!$O$6:$O$14,0)),"")</f>
         <v/>
       </c>
-      <c r="D16" s="18">
+      <c r="D16" s="19">
         <f>IFERROR(INDEX(Comparativo!$I$6:$I$14,MATCH(LARGE(Comparativo!$O$6:$O$14,A16),Comparativo!$O$6:$O$14,0)),"")</f>
         <v/>
       </c>
-      <c r="E16" s="18">
+      <c r="E16" s="19">
         <f>IFERROR(INDEX(Comparativo!$J$6:$J$14,MATCH(LARGE(Comparativo!$O$6:$O$14,A16),Comparativo!$O$6:$O$14,0)),"")</f>
         <v/>
       </c>
-      <c r="F16" s="18">
+      <c r="F16" s="19">
         <f>IFERROR(INDEX(Comparativo!$K$6:$K$14,MATCH(LARGE(Comparativo!$O$6:$O$14,A16),Comparativo!$O$6:$O$14,0)),"")</f>
         <v/>
       </c>
-      <c r="G16" s="19">
+      <c r="G16" s="20">
         <f>IFERROR(F16/D16,"")</f>
         <v/>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="16" t="n">
+      <c r="A17" s="17" t="n">
         <v>5</v>
       </c>
-      <c r="B17" s="17">
+      <c r="B17" s="18">
         <f>IFERROR(INDEX(Comparativo!$D$6:$D$14,MATCH(LARGE(Comparativo!$O$6:$O$14,A17),Comparativo!$O$6:$O$14,0)),"")</f>
         <v/>
       </c>
-      <c r="C17" s="17">
+      <c r="C17" s="18">
         <f>IFERROR(INDEX(Comparativo!$B$6:$B$14,MATCH(LARGE(Comparativo!$O$6:$O$14,A17),Comparativo!$O$6:$O$14,0)),"")</f>
         <v/>
       </c>
-      <c r="D17" s="18">
+      <c r="D17" s="19">
         <f>IFERROR(INDEX(Comparativo!$I$6:$I$14,MATCH(LARGE(Comparativo!$O$6:$O$14,A17),Comparativo!$O$6:$O$14,0)),"")</f>
         <v/>
       </c>
-      <c r="E17" s="18">
+      <c r="E17" s="19">
         <f>IFERROR(INDEX(Comparativo!$J$6:$J$14,MATCH(LARGE(Comparativo!$O$6:$O$14,A17),Comparativo!$O$6:$O$14,0)),"")</f>
         <v/>
       </c>
-      <c r="F17" s="18">
+      <c r="F17" s="19">
         <f>IFERROR(INDEX(Comparativo!$K$6:$K$14,MATCH(LARGE(Comparativo!$O$6:$O$14,A17),Comparativo!$O$6:$O$14,0)),"")</f>
         <v/>
       </c>
-      <c r="G17" s="19">
+      <c r="G17" s="20">
         <f>IFERROR(F17/D17,"")</f>
         <v/>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="3">
+  <mergeCells count="4">
     <mergeCell ref="A1:I1"/>
+    <mergeCell ref="A4:I4"/>
     <mergeCell ref="A11:H11"/>
     <mergeCell ref="A2:I2"/>
   </mergeCells>
@@ -1470,740 +1491,741 @@
           <t>Mês de referência:</t>
         </is>
       </c>
-      <c r="B3" s="20" t="inlineStr">
+      <c r="B3" s="21" t="inlineStr">
         <is>
           <t>Jul/26</t>
         </is>
       </c>
-      <c r="C3" s="21" t="inlineStr">
+      <c r="C3" s="22" t="inlineStr">
         <is>
           <t>Mês nº:</t>
         </is>
       </c>
-      <c r="D3" s="22">
+      <c r="D3" s="23">
         <f>MATCH($B$3,Planejado!$H$4:$S$4,0)</f>
         <v/>
       </c>
     </row>
     <row r="5" ht="30" customHeight="1">
-      <c r="A5" s="6" t="inlineStr">
+      <c r="A5" s="7" t="inlineStr">
         <is>
           <t>ID</t>
         </is>
       </c>
-      <c r="B5" s="6" t="inlineStr">
+      <c r="B5" s="7" t="inlineStr">
         <is>
           <t>Departamento</t>
         </is>
       </c>
-      <c r="C5" s="6" t="inlineStr">
+      <c r="C5" s="7" t="inlineStr">
         <is>
           <t>Bloco</t>
         </is>
       </c>
-      <c r="D5" s="6" t="inlineStr">
+      <c r="D5" s="7" t="inlineStr">
         <is>
           <t>Descrição</t>
         </is>
       </c>
-      <c r="E5" s="6" t="inlineStr">
+      <c r="E5" s="7" t="inlineStr">
         <is>
           <t>Plano de Contas</t>
         </is>
       </c>
-      <c r="F5" s="6" t="inlineStr">
+      <c r="F5" s="7" t="inlineStr">
         <is>
           <t>Planejado no mês</t>
         </is>
       </c>
-      <c r="G5" s="6" t="inlineStr">
+      <c r="G5" s="7" t="inlineStr">
         <is>
           <t>Realizado no mês</t>
         </is>
       </c>
-      <c r="H5" s="6" t="inlineStr">
+      <c r="H5" s="7" t="inlineStr">
         <is>
           <t>Desvio no mês (R$)</t>
         </is>
       </c>
-      <c r="I5" s="6" t="inlineStr">
+      <c r="I5" s="7" t="inlineStr">
         <is>
           <t>Planejado acum.</t>
         </is>
       </c>
-      <c r="J5" s="6" t="inlineStr">
+      <c r="J5" s="7" t="inlineStr">
         <is>
           <t>Realizado acum.</t>
         </is>
       </c>
-      <c r="K5" s="6" t="inlineStr">
+      <c r="K5" s="7" t="inlineStr">
         <is>
           <t>Desvio acum. (R$)</t>
         </is>
       </c>
-      <c r="L5" s="6" t="inlineStr">
+      <c r="L5" s="7" t="inlineStr">
         <is>
           <t>Desvio acum. (%)</t>
         </is>
       </c>
-      <c r="M5" s="6" t="inlineStr">
+      <c r="M5" s="7" t="inlineStr">
         <is>
           <t>% Executado</t>
         </is>
       </c>
-      <c r="N5" s="6" t="inlineStr">
+      <c r="N5" s="7" t="inlineStr">
         <is>
           <t>Situação</t>
         </is>
       </c>
-      <c r="O5" s="23" t="inlineStr">
+      <c r="O5" s="24" t="inlineStr">
         <is>
           <t>(aux ranking)</t>
         </is>
       </c>
-      <c r="P5" s="23" t="inlineStr">
+      <c r="P5" s="24" t="inlineStr">
         <is>
           <t>(aux meses lançados)</t>
         </is>
       </c>
     </row>
     <row r="6" ht="24" customHeight="1">
-      <c r="A6" s="24">
+      <c r="A6" s="25">
         <f>Planejado!A5</f>
         <v/>
       </c>
-      <c r="B6" s="24">
+      <c r="B6" s="25">
         <f>Planejado!B5</f>
         <v/>
       </c>
-      <c r="C6" s="24">
+      <c r="C6" s="25">
         <f>Planejado!C5</f>
         <v/>
       </c>
-      <c r="D6" s="25">
+      <c r="D6" s="26">
         <f>Planejado!D5</f>
         <v/>
       </c>
-      <c r="E6" s="24">
+      <c r="E6" s="25">
         <f>Planejado!G5</f>
         <v/>
       </c>
-      <c r="F6" s="26">
+      <c r="F6" s="27">
         <f>INDEX(Planejado!$H5:$S5,$D$3)</f>
         <v/>
       </c>
-      <c r="G6" s="26">
+      <c r="G6" s="27">
         <f>INDEX(Realizado!$H5:$S5,$D$3)</f>
         <v/>
       </c>
-      <c r="H6" s="26">
+      <c r="H6" s="27">
         <f>G6-F6</f>
         <v/>
       </c>
-      <c r="I6" s="26">
+      <c r="I6" s="27">
         <f>SUMPRODUCT((COLUMN(Planejado!$H$4:$S$4)-COLUMN(Planejado!$H$4)+1&lt;=$D$3)*Planejado!$H5:$S5)</f>
         <v/>
       </c>
-      <c r="J6" s="26">
+      <c r="J6" s="27">
         <f>SUMPRODUCT((COLUMN(Realizado!$H$4:$S$4)-COLUMN(Realizado!$H$4)+1&lt;=$D$3)*Realizado!$H5:$S5)</f>
         <v/>
       </c>
-      <c r="K6" s="26">
+      <c r="K6" s="27">
         <f>J6-I6</f>
         <v/>
       </c>
-      <c r="L6" s="27">
+      <c r="L6" s="28">
         <f>IFERROR(K6/I6,"")</f>
         <v/>
       </c>
-      <c r="M6" s="27">
+      <c r="M6" s="28">
         <f>IFERROR(J6/I6,"")</f>
         <v/>
       </c>
-      <c r="N6" s="28">
+      <c r="N6" s="29">
         <f>IF(P6=0,"Sem lançamento",IF(AND(I6=0,J6=0),"—",IF(I6=0,"Não orçado",IF(K6&gt;0.05*I6,"Acima do orçado",IF(K6&lt;-0.05*I6,"Abaixo do orçado","Dentro do orçado")))))</f>
         <v/>
       </c>
-      <c r="O6" s="23">
+      <c r="O6" s="24">
         <f>IF(K6&gt;1,K6+ROW()/1000000,"")</f>
         <v/>
       </c>
-      <c r="P6" s="29">
+      <c r="P6" s="30">
         <f>SUMPRODUCT((COLUMN(Realizado!$H$4:$S$4)-COLUMN(Realizado!$H$4)+1&lt;=$D$3)*(Realizado!$H5:$S5&lt;&gt;""))</f>
         <v/>
       </c>
     </row>
     <row r="7" ht="24" customHeight="1">
-      <c r="A7" s="24">
+      <c r="A7" s="25">
         <f>Planejado!A6</f>
         <v/>
       </c>
-      <c r="B7" s="24">
+      <c r="B7" s="25">
         <f>Planejado!B6</f>
         <v/>
       </c>
-      <c r="C7" s="24">
+      <c r="C7" s="25">
         <f>Planejado!C6</f>
         <v/>
       </c>
-      <c r="D7" s="25">
+      <c r="D7" s="26">
         <f>Planejado!D6</f>
         <v/>
       </c>
-      <c r="E7" s="24">
+      <c r="E7" s="25">
         <f>Planejado!G6</f>
         <v/>
       </c>
-      <c r="F7" s="26">
+      <c r="F7" s="27">
         <f>INDEX(Planejado!$H6:$S6,$D$3)</f>
         <v/>
       </c>
-      <c r="G7" s="26">
+      <c r="G7" s="27">
         <f>INDEX(Realizado!$H6:$S6,$D$3)</f>
         <v/>
       </c>
-      <c r="H7" s="26">
+      <c r="H7" s="27">
         <f>G7-F7</f>
         <v/>
       </c>
-      <c r="I7" s="26">
+      <c r="I7" s="27">
         <f>SUMPRODUCT((COLUMN(Planejado!$H$4:$S$4)-COLUMN(Planejado!$H$4)+1&lt;=$D$3)*Planejado!$H6:$S6)</f>
         <v/>
       </c>
-      <c r="J7" s="26">
+      <c r="J7" s="27">
         <f>SUMPRODUCT((COLUMN(Realizado!$H$4:$S$4)-COLUMN(Realizado!$H$4)+1&lt;=$D$3)*Realizado!$H6:$S6)</f>
         <v/>
       </c>
-      <c r="K7" s="26">
+      <c r="K7" s="27">
         <f>J7-I7</f>
         <v/>
       </c>
-      <c r="L7" s="27">
+      <c r="L7" s="28">
         <f>IFERROR(K7/I7,"")</f>
         <v/>
       </c>
-      <c r="M7" s="27">
+      <c r="M7" s="28">
         <f>IFERROR(J7/I7,"")</f>
         <v/>
       </c>
-      <c r="N7" s="28">
-        <f>IF(P7=0,"Sem lançamento",IF(AND(I7=0,J7=0),"—",IF(I7=0,"Não orçado",IF(K7&gt;0.05*I7,"Acima do orçado",IF(K7&lt;-0.05*I7,"Abaixo do orçado","Dentro do orçado")))))</f>
-        <v/>
-      </c>
-      <c r="O7" s="23">
+      <c r="N7" s="29" t="inlineStr">
+        <is>
+          <t>⚠ Base diferente</t>
+        </is>
+      </c>
+      <c r="O7" s="24">
         <f>IF(K7&gt;1,K7+ROW()/1000000,"")</f>
         <v/>
       </c>
-      <c r="P7" s="29">
+      <c r="P7" s="30">
         <f>SUMPRODUCT((COLUMN(Realizado!$H$4:$S$4)-COLUMN(Realizado!$H$4)+1&lt;=$D$3)*(Realizado!$H6:$S6&lt;&gt;""))</f>
         <v/>
       </c>
     </row>
     <row r="8" ht="24" customHeight="1">
-      <c r="A8" s="24">
+      <c r="A8" s="25">
         <f>Planejado!A7</f>
         <v/>
       </c>
-      <c r="B8" s="24">
+      <c r="B8" s="25">
         <f>Planejado!B7</f>
         <v/>
       </c>
-      <c r="C8" s="24">
+      <c r="C8" s="25">
         <f>Planejado!C7</f>
         <v/>
       </c>
-      <c r="D8" s="25">
+      <c r="D8" s="26">
         <f>Planejado!D7</f>
         <v/>
       </c>
-      <c r="E8" s="24">
+      <c r="E8" s="25">
         <f>Planejado!G7</f>
         <v/>
       </c>
-      <c r="F8" s="26">
+      <c r="F8" s="27">
         <f>INDEX(Planejado!$H7:$S7,$D$3)</f>
         <v/>
       </c>
-      <c r="G8" s="26">
+      <c r="G8" s="27">
         <f>INDEX(Realizado!$H7:$S7,$D$3)</f>
         <v/>
       </c>
-      <c r="H8" s="26">
+      <c r="H8" s="27">
         <f>G8-F8</f>
         <v/>
       </c>
-      <c r="I8" s="26">
+      <c r="I8" s="27">
         <f>SUMPRODUCT((COLUMN(Planejado!$H$4:$S$4)-COLUMN(Planejado!$H$4)+1&lt;=$D$3)*Planejado!$H7:$S7)</f>
         <v/>
       </c>
-      <c r="J8" s="26">
+      <c r="J8" s="27">
         <f>SUMPRODUCT((COLUMN(Realizado!$H$4:$S$4)-COLUMN(Realizado!$H$4)+1&lt;=$D$3)*Realizado!$H7:$S7)</f>
         <v/>
       </c>
-      <c r="K8" s="26">
+      <c r="K8" s="27">
         <f>J8-I8</f>
         <v/>
       </c>
-      <c r="L8" s="27">
+      <c r="L8" s="28">
         <f>IFERROR(K8/I8,"")</f>
         <v/>
       </c>
-      <c r="M8" s="27">
+      <c r="M8" s="28">
         <f>IFERROR(J8/I8,"")</f>
         <v/>
       </c>
-      <c r="N8" s="28">
+      <c r="N8" s="29">
         <f>IF(P8=0,"Sem lançamento",IF(AND(I8=0,J8=0),"—",IF(I8=0,"Não orçado",IF(K8&gt;0.05*I8,"Acima do orçado",IF(K8&lt;-0.05*I8,"Abaixo do orçado","Dentro do orçado")))))</f>
         <v/>
       </c>
-      <c r="O8" s="23">
+      <c r="O8" s="24">
         <f>IF(K8&gt;1,K8+ROW()/1000000,"")</f>
         <v/>
       </c>
-      <c r="P8" s="29">
+      <c r="P8" s="30">
         <f>SUMPRODUCT((COLUMN(Realizado!$H$4:$S$4)-COLUMN(Realizado!$H$4)+1&lt;=$D$3)*(Realizado!$H7:$S7&lt;&gt;""))</f>
         <v/>
       </c>
     </row>
     <row r="9" ht="24" customHeight="1">
-      <c r="A9" s="24">
+      <c r="A9" s="25">
         <f>Planejado!A8</f>
         <v/>
       </c>
-      <c r="B9" s="24">
+      <c r="B9" s="25">
         <f>Planejado!B8</f>
         <v/>
       </c>
-      <c r="C9" s="24">
+      <c r="C9" s="25">
         <f>Planejado!C8</f>
         <v/>
       </c>
-      <c r="D9" s="25">
+      <c r="D9" s="26">
         <f>Planejado!D8</f>
         <v/>
       </c>
-      <c r="E9" s="24">
+      <c r="E9" s="25">
         <f>Planejado!G8</f>
         <v/>
       </c>
-      <c r="F9" s="26">
+      <c r="F9" s="27">
         <f>INDEX(Planejado!$H8:$S8,$D$3)</f>
         <v/>
       </c>
-      <c r="G9" s="26">
+      <c r="G9" s="27">
         <f>INDEX(Realizado!$H8:$S8,$D$3)</f>
         <v/>
       </c>
-      <c r="H9" s="26">
+      <c r="H9" s="27">
         <f>G9-F9</f>
         <v/>
       </c>
-      <c r="I9" s="26">
+      <c r="I9" s="27">
         <f>SUMPRODUCT((COLUMN(Planejado!$H$4:$S$4)-COLUMN(Planejado!$H$4)+1&lt;=$D$3)*Planejado!$H8:$S8)</f>
         <v/>
       </c>
-      <c r="J9" s="26">
+      <c r="J9" s="27">
         <f>SUMPRODUCT((COLUMN(Realizado!$H$4:$S$4)-COLUMN(Realizado!$H$4)+1&lt;=$D$3)*Realizado!$H8:$S8)</f>
         <v/>
       </c>
-      <c r="K9" s="26">
+      <c r="K9" s="27">
         <f>J9-I9</f>
         <v/>
       </c>
-      <c r="L9" s="27">
+      <c r="L9" s="28">
         <f>IFERROR(K9/I9,"")</f>
         <v/>
       </c>
-      <c r="M9" s="27">
+      <c r="M9" s="28">
         <f>IFERROR(J9/I9,"")</f>
         <v/>
       </c>
-      <c r="N9" s="28">
+      <c r="N9" s="29">
         <f>IF(P9=0,"Sem lançamento",IF(AND(I9=0,J9=0),"—",IF(I9=0,"Não orçado",IF(K9&gt;0.05*I9,"Acima do orçado",IF(K9&lt;-0.05*I9,"Abaixo do orçado","Dentro do orçado")))))</f>
         <v/>
       </c>
-      <c r="O9" s="23">
+      <c r="O9" s="24">
         <f>IF(K9&gt;1,K9+ROW()/1000000,"")</f>
         <v/>
       </c>
-      <c r="P9" s="29">
+      <c r="P9" s="30">
         <f>SUMPRODUCT((COLUMN(Realizado!$H$4:$S$4)-COLUMN(Realizado!$H$4)+1&lt;=$D$3)*(Realizado!$H8:$S8&lt;&gt;""))</f>
         <v/>
       </c>
     </row>
     <row r="10" ht="24" customHeight="1">
-      <c r="A10" s="24">
+      <c r="A10" s="25">
         <f>Planejado!A9</f>
         <v/>
       </c>
-      <c r="B10" s="24">
+      <c r="B10" s="25">
         <f>Planejado!B9</f>
         <v/>
       </c>
-      <c r="C10" s="24">
+      <c r="C10" s="25">
         <f>Planejado!C9</f>
         <v/>
       </c>
-      <c r="D10" s="25">
+      <c r="D10" s="26">
         <f>Planejado!D9</f>
         <v/>
       </c>
-      <c r="E10" s="24">
+      <c r="E10" s="25">
         <f>Planejado!G9</f>
         <v/>
       </c>
-      <c r="F10" s="26">
+      <c r="F10" s="27">
         <f>INDEX(Planejado!$H9:$S9,$D$3)</f>
         <v/>
       </c>
-      <c r="G10" s="26">
+      <c r="G10" s="27">
         <f>INDEX(Realizado!$H9:$S9,$D$3)</f>
         <v/>
       </c>
-      <c r="H10" s="26">
+      <c r="H10" s="27">
         <f>G10-F10</f>
         <v/>
       </c>
-      <c r="I10" s="26">
+      <c r="I10" s="27">
         <f>SUMPRODUCT((COLUMN(Planejado!$H$4:$S$4)-COLUMN(Planejado!$H$4)+1&lt;=$D$3)*Planejado!$H9:$S9)</f>
         <v/>
       </c>
-      <c r="J10" s="26">
+      <c r="J10" s="27">
         <f>SUMPRODUCT((COLUMN(Realizado!$H$4:$S$4)-COLUMN(Realizado!$H$4)+1&lt;=$D$3)*Realizado!$H9:$S9)</f>
         <v/>
       </c>
-      <c r="K10" s="26">
+      <c r="K10" s="27">
         <f>J10-I10</f>
         <v/>
       </c>
-      <c r="L10" s="27">
+      <c r="L10" s="28">
         <f>IFERROR(K10/I10,"")</f>
         <v/>
       </c>
-      <c r="M10" s="27">
+      <c r="M10" s="28">
         <f>IFERROR(J10/I10,"")</f>
         <v/>
       </c>
-      <c r="N10" s="28">
+      <c r="N10" s="29">
         <f>IF(P10=0,"Sem lançamento",IF(AND(I10=0,J10=0),"—",IF(I10=0,"Não orçado",IF(K10&gt;0.05*I10,"Acima do orçado",IF(K10&lt;-0.05*I10,"Abaixo do orçado","Dentro do orçado")))))</f>
         <v/>
       </c>
-      <c r="O10" s="23">
+      <c r="O10" s="24">
         <f>IF(K10&gt;1,K10+ROW()/1000000,"")</f>
         <v/>
       </c>
-      <c r="P10" s="29">
+      <c r="P10" s="30">
         <f>SUMPRODUCT((COLUMN(Realizado!$H$4:$S$4)-COLUMN(Realizado!$H$4)+1&lt;=$D$3)*(Realizado!$H9:$S9&lt;&gt;""))</f>
         <v/>
       </c>
     </row>
     <row r="11" ht="24" customHeight="1">
-      <c r="A11" s="24">
+      <c r="A11" s="25">
         <f>Planejado!A10</f>
         <v/>
       </c>
-      <c r="B11" s="24">
+      <c r="B11" s="25">
         <f>Planejado!B10</f>
         <v/>
       </c>
-      <c r="C11" s="24">
+      <c r="C11" s="25">
         <f>Planejado!C10</f>
         <v/>
       </c>
-      <c r="D11" s="25">
+      <c r="D11" s="26">
         <f>Planejado!D10</f>
         <v/>
       </c>
-      <c r="E11" s="24">
+      <c r="E11" s="25">
         <f>Planejado!G10</f>
         <v/>
       </c>
-      <c r="F11" s="26">
+      <c r="F11" s="27">
         <f>INDEX(Planejado!$H10:$S10,$D$3)</f>
         <v/>
       </c>
-      <c r="G11" s="26">
+      <c r="G11" s="27">
         <f>INDEX(Realizado!$H10:$S10,$D$3)</f>
         <v/>
       </c>
-      <c r="H11" s="26">
+      <c r="H11" s="27">
         <f>G11-F11</f>
         <v/>
       </c>
-      <c r="I11" s="26">
+      <c r="I11" s="27">
         <f>SUMPRODUCT((COLUMN(Planejado!$H$4:$S$4)-COLUMN(Planejado!$H$4)+1&lt;=$D$3)*Planejado!$H10:$S10)</f>
         <v/>
       </c>
-      <c r="J11" s="26">
+      <c r="J11" s="27">
         <f>SUMPRODUCT((COLUMN(Realizado!$H$4:$S$4)-COLUMN(Realizado!$H$4)+1&lt;=$D$3)*Realizado!$H10:$S10)</f>
         <v/>
       </c>
-      <c r="K11" s="26">
+      <c r="K11" s="27">
         <f>J11-I11</f>
         <v/>
       </c>
-      <c r="L11" s="27">
+      <c r="L11" s="28">
         <f>IFERROR(K11/I11,"")</f>
         <v/>
       </c>
-      <c r="M11" s="27">
+      <c r="M11" s="28">
         <f>IFERROR(J11/I11,"")</f>
         <v/>
       </c>
-      <c r="N11" s="28">
+      <c r="N11" s="29">
         <f>IF(P11=0,"Sem lançamento",IF(AND(I11=0,J11=0),"—",IF(I11=0,"Não orçado",IF(K11&gt;0.05*I11,"Acima do orçado",IF(K11&lt;-0.05*I11,"Abaixo do orçado","Dentro do orçado")))))</f>
         <v/>
       </c>
-      <c r="O11" s="23">
+      <c r="O11" s="24">
         <f>IF(K11&gt;1,K11+ROW()/1000000,"")</f>
         <v/>
       </c>
-      <c r="P11" s="29">
+      <c r="P11" s="30">
         <f>SUMPRODUCT((COLUMN(Realizado!$H$4:$S$4)-COLUMN(Realizado!$H$4)+1&lt;=$D$3)*(Realizado!$H10:$S10&lt;&gt;""))</f>
         <v/>
       </c>
     </row>
     <row r="12" ht="24" customHeight="1">
-      <c r="A12" s="24">
+      <c r="A12" s="25">
         <f>Planejado!A11</f>
         <v/>
       </c>
-      <c r="B12" s="24">
+      <c r="B12" s="25">
         <f>Planejado!B11</f>
         <v/>
       </c>
-      <c r="C12" s="24">
+      <c r="C12" s="25">
         <f>Planejado!C11</f>
         <v/>
       </c>
-      <c r="D12" s="25">
+      <c r="D12" s="26">
         <f>Planejado!D11</f>
         <v/>
       </c>
-      <c r="E12" s="24">
+      <c r="E12" s="25">
         <f>Planejado!G11</f>
         <v/>
       </c>
-      <c r="F12" s="26">
+      <c r="F12" s="27">
         <f>INDEX(Planejado!$H11:$S11,$D$3)</f>
         <v/>
       </c>
-      <c r="G12" s="26">
+      <c r="G12" s="27">
         <f>INDEX(Realizado!$H11:$S11,$D$3)</f>
         <v/>
       </c>
-      <c r="H12" s="26">
+      <c r="H12" s="27">
         <f>G12-F12</f>
         <v/>
       </c>
-      <c r="I12" s="26">
+      <c r="I12" s="27">
         <f>SUMPRODUCT((COLUMN(Planejado!$H$4:$S$4)-COLUMN(Planejado!$H$4)+1&lt;=$D$3)*Planejado!$H11:$S11)</f>
         <v/>
       </c>
-      <c r="J12" s="26">
+      <c r="J12" s="27">
         <f>SUMPRODUCT((COLUMN(Realizado!$H$4:$S$4)-COLUMN(Realizado!$H$4)+1&lt;=$D$3)*Realizado!$H11:$S11)</f>
         <v/>
       </c>
-      <c r="K12" s="26">
+      <c r="K12" s="27">
         <f>J12-I12</f>
         <v/>
       </c>
-      <c r="L12" s="27">
+      <c r="L12" s="28">
         <f>IFERROR(K12/I12,"")</f>
         <v/>
       </c>
-      <c r="M12" s="27">
+      <c r="M12" s="28">
         <f>IFERROR(J12/I12,"")</f>
         <v/>
       </c>
-      <c r="N12" s="28">
+      <c r="N12" s="29">
         <f>IF(P12=0,"Sem lançamento",IF(AND(I12=0,J12=0),"—",IF(I12=0,"Não orçado",IF(K12&gt;0.05*I12,"Acima do orçado",IF(K12&lt;-0.05*I12,"Abaixo do orçado","Dentro do orçado")))))</f>
         <v/>
       </c>
-      <c r="O12" s="23">
+      <c r="O12" s="24">
         <f>IF(K12&gt;1,K12+ROW()/1000000,"")</f>
         <v/>
       </c>
-      <c r="P12" s="29">
+      <c r="P12" s="30">
         <f>SUMPRODUCT((COLUMN(Realizado!$H$4:$S$4)-COLUMN(Realizado!$H$4)+1&lt;=$D$3)*(Realizado!$H11:$S11&lt;&gt;""))</f>
         <v/>
       </c>
     </row>
     <row r="13" ht="24" customHeight="1">
-      <c r="A13" s="24">
+      <c r="A13" s="25">
         <f>Planejado!A12</f>
         <v/>
       </c>
-      <c r="B13" s="24">
+      <c r="B13" s="25">
         <f>Planejado!B12</f>
         <v/>
       </c>
-      <c r="C13" s="24">
+      <c r="C13" s="25">
         <f>Planejado!C12</f>
         <v/>
       </c>
-      <c r="D13" s="25">
+      <c r="D13" s="26">
         <f>Planejado!D12</f>
         <v/>
       </c>
-      <c r="E13" s="24">
+      <c r="E13" s="25">
         <f>Planejado!G12</f>
         <v/>
       </c>
-      <c r="F13" s="26">
+      <c r="F13" s="27">
         <f>INDEX(Planejado!$H12:$S12,$D$3)</f>
         <v/>
       </c>
-      <c r="G13" s="26">
+      <c r="G13" s="27">
         <f>INDEX(Realizado!$H12:$S12,$D$3)</f>
         <v/>
       </c>
-      <c r="H13" s="26">
+      <c r="H13" s="27">
         <f>G13-F13</f>
         <v/>
       </c>
-      <c r="I13" s="26">
+      <c r="I13" s="27">
         <f>SUMPRODUCT((COLUMN(Planejado!$H$4:$S$4)-COLUMN(Planejado!$H$4)+1&lt;=$D$3)*Planejado!$H12:$S12)</f>
         <v/>
       </c>
-      <c r="J13" s="26">
+      <c r="J13" s="27">
         <f>SUMPRODUCT((COLUMN(Realizado!$H$4:$S$4)-COLUMN(Realizado!$H$4)+1&lt;=$D$3)*Realizado!$H12:$S12)</f>
         <v/>
       </c>
-      <c r="K13" s="26">
+      <c r="K13" s="27">
         <f>J13-I13</f>
         <v/>
       </c>
-      <c r="L13" s="27">
+      <c r="L13" s="28">
         <f>IFERROR(K13/I13,"")</f>
         <v/>
       </c>
-      <c r="M13" s="27">
+      <c r="M13" s="28">
         <f>IFERROR(J13/I13,"")</f>
         <v/>
       </c>
-      <c r="N13" s="28">
+      <c r="N13" s="29">
         <f>IF(P13=0,"Sem lançamento",IF(AND(I13=0,J13=0),"—",IF(I13=0,"Não orçado",IF(K13&gt;0.05*I13,"Acima do orçado",IF(K13&lt;-0.05*I13,"Abaixo do orçado","Dentro do orçado")))))</f>
         <v/>
       </c>
-      <c r="O13" s="23">
+      <c r="O13" s="24">
         <f>IF(K13&gt;1,K13+ROW()/1000000,"")</f>
         <v/>
       </c>
-      <c r="P13" s="29">
+      <c r="P13" s="30">
         <f>SUMPRODUCT((COLUMN(Realizado!$H$4:$S$4)-COLUMN(Realizado!$H$4)+1&lt;=$D$3)*(Realizado!$H12:$S12&lt;&gt;""))</f>
         <v/>
       </c>
     </row>
     <row r="14" ht="24" customHeight="1">
-      <c r="A14" s="24">
+      <c r="A14" s="25">
         <f>Planejado!A13</f>
         <v/>
       </c>
-      <c r="B14" s="24">
+      <c r="B14" s="25">
         <f>Planejado!B13</f>
         <v/>
       </c>
-      <c r="C14" s="24">
+      <c r="C14" s="25">
         <f>Planejado!C13</f>
         <v/>
       </c>
-      <c r="D14" s="25">
+      <c r="D14" s="26">
         <f>Planejado!D13</f>
         <v/>
       </c>
-      <c r="E14" s="24">
+      <c r="E14" s="25">
         <f>Planejado!G13</f>
         <v/>
       </c>
-      <c r="F14" s="26">
+      <c r="F14" s="27">
         <f>INDEX(Planejado!$H13:$S13,$D$3)</f>
         <v/>
       </c>
-      <c r="G14" s="26">
+      <c r="G14" s="27">
         <f>INDEX(Realizado!$H13:$S13,$D$3)</f>
         <v/>
       </c>
-      <c r="H14" s="26">
+      <c r="H14" s="27">
         <f>G14-F14</f>
         <v/>
       </c>
-      <c r="I14" s="26">
+      <c r="I14" s="27">
         <f>SUMPRODUCT((COLUMN(Planejado!$H$4:$S$4)-COLUMN(Planejado!$H$4)+1&lt;=$D$3)*Planejado!$H13:$S13)</f>
         <v/>
       </c>
-      <c r="J14" s="26">
+      <c r="J14" s="27">
         <f>SUMPRODUCT((COLUMN(Realizado!$H$4:$S$4)-COLUMN(Realizado!$H$4)+1&lt;=$D$3)*Realizado!$H13:$S13)</f>
         <v/>
       </c>
-      <c r="K14" s="26">
+      <c r="K14" s="27">
         <f>J14-I14</f>
         <v/>
       </c>
-      <c r="L14" s="27">
+      <c r="L14" s="28">
         <f>IFERROR(K14/I14,"")</f>
         <v/>
       </c>
-      <c r="M14" s="27">
+      <c r="M14" s="28">
         <f>IFERROR(J14/I14,"")</f>
         <v/>
       </c>
-      <c r="N14" s="28">
+      <c r="N14" s="29">
         <f>IF(P14=0,"Sem lançamento",IF(AND(I14=0,J14=0),"—",IF(I14=0,"Não orçado",IF(K14&gt;0.05*I14,"Acima do orçado",IF(K14&lt;-0.05*I14,"Abaixo do orçado","Dentro do orçado")))))</f>
         <v/>
       </c>
-      <c r="O14" s="23">
+      <c r="O14" s="24">
         <f>IF(K14&gt;1,K14+ROW()/1000000,"")</f>
         <v/>
       </c>
-      <c r="P14" s="29">
+      <c r="P14" s="30">
         <f>SUMPRODUCT((COLUMN(Realizado!$H$4:$S$4)-COLUMN(Realizado!$H$4)+1&lt;=$D$3)*(Realizado!$H13:$S13&lt;&gt;""))</f>
         <v/>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="30" t="inlineStr">
+      <c r="A27" s="31" t="inlineStr">
         <is>
           <t>TOTAL GERAL</t>
         </is>
       </c>
-      <c r="B27" s="30" t="n"/>
-      <c r="C27" s="30" t="n"/>
-      <c r="D27" s="30" t="n"/>
-      <c r="E27" s="30" t="n"/>
-      <c r="F27" s="31">
+      <c r="B27" s="31" t="n"/>
+      <c r="C27" s="31" t="n"/>
+      <c r="D27" s="31" t="n"/>
+      <c r="E27" s="31" t="n"/>
+      <c r="F27" s="32">
         <f>SUM(F6:F14)</f>
         <v/>
       </c>
-      <c r="G27" s="31">
+      <c r="G27" s="32">
         <f>SUM(G6:G14)</f>
         <v/>
       </c>
-      <c r="H27" s="31">
+      <c r="H27" s="32">
         <f>SUM(H6:H14)</f>
         <v/>
       </c>
-      <c r="I27" s="31">
+      <c r="I27" s="32">
         <f>SUM(I6:I14)</f>
         <v/>
       </c>
-      <c r="J27" s="31">
+      <c r="J27" s="32">
         <f>SUM(J6:J14)</f>
         <v/>
       </c>
-      <c r="K27" s="31">
+      <c r="K27" s="32">
         <f>SUM(K6:K14)</f>
         <v/>
       </c>
-      <c r="L27" s="32">
+      <c r="L27" s="33">
         <f>IFERROR(K27/I27,"")</f>
         <v/>
       </c>
-      <c r="M27" s="32">
+      <c r="M27" s="33">
         <f>IFERROR(J27/I27,"")</f>
         <v/>
       </c>
-      <c r="N27" s="30" t="n"/>
+      <c r="N27" s="31" t="n"/>
     </row>
   </sheetData>
   <autoFilter ref="A5:N14"/>
@@ -2282,825 +2304,825 @@
       </c>
     </row>
     <row r="4" ht="30" customHeight="1">
-      <c r="A4" s="6" t="inlineStr">
+      <c r="A4" s="7" t="inlineStr">
         <is>
           <t>ID</t>
         </is>
       </c>
-      <c r="B4" s="6" t="inlineStr">
+      <c r="B4" s="7" t="inlineStr">
         <is>
           <t>Departamento</t>
         </is>
       </c>
-      <c r="C4" s="6" t="inlineStr">
+      <c r="C4" s="7" t="inlineStr">
         <is>
           <t>Bloco</t>
         </is>
       </c>
-      <c r="D4" s="6" t="inlineStr">
+      <c r="D4" s="7" t="inlineStr">
         <is>
           <t>Descrição</t>
         </is>
       </c>
-      <c r="E4" s="6" t="inlineStr">
+      <c r="E4" s="7" t="inlineStr">
         <is>
           <t>Detalhe / Observação</t>
         </is>
       </c>
-      <c r="F4" s="6" t="inlineStr">
+      <c r="F4" s="7" t="inlineStr">
         <is>
           <t>Vínculo</t>
         </is>
       </c>
-      <c r="G4" s="6" t="inlineStr">
+      <c r="G4" s="7" t="inlineStr">
         <is>
           <t>Plano de Contas</t>
         </is>
       </c>
-      <c r="H4" s="6" t="inlineStr">
+      <c r="H4" s="7" t="inlineStr">
         <is>
           <t>Jan/26</t>
         </is>
       </c>
-      <c r="I4" s="6" t="inlineStr">
+      <c r="I4" s="7" t="inlineStr">
         <is>
           <t>Fev/26</t>
         </is>
       </c>
-      <c r="J4" s="6" t="inlineStr">
+      <c r="J4" s="7" t="inlineStr">
         <is>
           <t>Mar/26</t>
         </is>
       </c>
-      <c r="K4" s="6" t="inlineStr">
+      <c r="K4" s="7" t="inlineStr">
         <is>
           <t>Abr/26</t>
         </is>
       </c>
-      <c r="L4" s="6" t="inlineStr">
+      <c r="L4" s="7" t="inlineStr">
         <is>
           <t>Mai/26</t>
         </is>
       </c>
-      <c r="M4" s="6" t="inlineStr">
+      <c r="M4" s="7" t="inlineStr">
         <is>
           <t>Jun/26</t>
         </is>
       </c>
-      <c r="N4" s="6" t="inlineStr">
+      <c r="N4" s="7" t="inlineStr">
         <is>
           <t>Jul/26</t>
         </is>
       </c>
-      <c r="O4" s="6" t="inlineStr">
+      <c r="O4" s="7" t="inlineStr">
         <is>
           <t>Ago/26</t>
         </is>
       </c>
-      <c r="P4" s="6" t="inlineStr">
+      <c r="P4" s="7" t="inlineStr">
         <is>
           <t>Set/26</t>
         </is>
       </c>
-      <c r="Q4" s="6" t="inlineStr">
+      <c r="Q4" s="7" t="inlineStr">
         <is>
           <t>Out/26</t>
         </is>
       </c>
-      <c r="R4" s="6" t="inlineStr">
+      <c r="R4" s="7" t="inlineStr">
         <is>
           <t>Nov/26</t>
         </is>
       </c>
-      <c r="S4" s="6" t="inlineStr">
+      <c r="S4" s="7" t="inlineStr">
         <is>
           <t>Dez/26</t>
         </is>
       </c>
-      <c r="T4" s="6" t="inlineStr">
+      <c r="T4" s="7" t="inlineStr">
         <is>
           <t>TOTAL DO ANO</t>
         </is>
       </c>
     </row>
     <row r="5" ht="26" customHeight="1">
-      <c r="A5" s="24" t="inlineStr">
+      <c r="A5" s="25" t="inlineStr">
         <is>
           <t>JUR-E01</t>
         </is>
       </c>
-      <c r="B5" s="24" t="inlineStr">
+      <c r="B5" s="25" t="inlineStr">
         <is>
           <t>Jurídico</t>
         </is>
       </c>
-      <c r="C5" s="24" t="inlineStr">
+      <c r="C5" s="25" t="inlineStr">
         <is>
           <t>Equipe</t>
         </is>
       </c>
-      <c r="D5" s="25" t="inlineStr">
+      <c r="D5" s="26" t="inlineStr">
         <is>
           <t>Miguel Clepf</t>
         </is>
       </c>
-      <c r="E5" s="25" t="inlineStr">
+      <c r="E5" s="26" t="inlineStr">
         <is>
           <t>Advogado Júnior</t>
         </is>
       </c>
-      <c r="F5" s="24" t="inlineStr">
+      <c r="F5" s="25" t="inlineStr">
         <is>
           <t>PJ</t>
         </is>
       </c>
-      <c r="G5" s="24" t="inlineStr">
+      <c r="G5" s="25" t="inlineStr">
         <is>
           <t>Pessoal - PJ</t>
         </is>
       </c>
-      <c r="H5" s="26" t="n">
+      <c r="H5" s="27" t="n">
         <v>10000</v>
       </c>
-      <c r="I5" s="26" t="n">
+      <c r="I5" s="27" t="n">
         <v>10000</v>
       </c>
-      <c r="J5" s="26" t="n">
+      <c r="J5" s="27" t="n">
         <v>10000</v>
       </c>
-      <c r="K5" s="26" t="n">
+      <c r="K5" s="27" t="n">
         <v>10000</v>
       </c>
-      <c r="L5" s="26" t="n">
+      <c r="L5" s="27" t="n">
         <v>10000</v>
       </c>
-      <c r="M5" s="26" t="n">
+      <c r="M5" s="27" t="n">
         <v>10000</v>
       </c>
-      <c r="N5" s="26" t="n">
+      <c r="N5" s="27" t="n">
         <v>10000</v>
       </c>
-      <c r="O5" s="26" t="n">
+      <c r="O5" s="27" t="n">
         <v>10000</v>
       </c>
-      <c r="P5" s="26" t="n">
+      <c r="P5" s="27" t="n">
         <v>10000</v>
       </c>
-      <c r="Q5" s="26" t="n">
+      <c r="Q5" s="27" t="n">
         <v>10000</v>
       </c>
-      <c r="R5" s="26" t="n">
+      <c r="R5" s="27" t="n">
         <v>10000</v>
       </c>
-      <c r="S5" s="26" t="n">
+      <c r="S5" s="27" t="n">
         <v>10000</v>
       </c>
-      <c r="T5" s="33">
+      <c r="T5" s="34">
         <f>SUM(H5:S5)</f>
         <v/>
       </c>
     </row>
     <row r="6" ht="26" customHeight="1">
-      <c r="A6" s="24" t="inlineStr">
+      <c r="A6" s="25" t="inlineStr">
         <is>
           <t>JUR-E02</t>
         </is>
       </c>
-      <c r="B6" s="24" t="inlineStr">
+      <c r="B6" s="25" t="inlineStr">
         <is>
           <t>Jurídico</t>
         </is>
       </c>
-      <c r="C6" s="24" t="inlineStr">
+      <c r="C6" s="25" t="inlineStr">
         <is>
           <t>Equipe</t>
         </is>
       </c>
-      <c r="D6" s="25" t="inlineStr">
+      <c r="D6" s="26" t="inlineStr">
         <is>
           <t>Geovanna</t>
         </is>
       </c>
-      <c r="E6" s="25" t="inlineStr">
+      <c r="E6" s="26" t="inlineStr">
         <is>
           <t>Analista Administrativo — orçada pelo custo total (encargos de folha + benefícios). Salário bruto informado: R$ 2.886,91/mês</t>
         </is>
       </c>
-      <c r="F6" s="24" t="inlineStr">
+      <c r="F6" s="25" t="inlineStr">
         <is>
           <t>CLT</t>
         </is>
       </c>
-      <c r="G6" s="24" t="inlineStr">
+      <c r="G6" s="25" t="inlineStr">
         <is>
           <t>Pessoal - CLT</t>
         </is>
       </c>
-      <c r="H6" s="26" t="n">
+      <c r="H6" s="27" t="n">
         <v>4825.515</v>
       </c>
-      <c r="I6" s="26" t="n">
+      <c r="I6" s="27" t="n">
         <v>4825.515</v>
       </c>
-      <c r="J6" s="26" t="n">
+      <c r="J6" s="27" t="n">
         <v>4825.515</v>
       </c>
-      <c r="K6" s="26" t="n">
+      <c r="K6" s="27" t="n">
         <v>4825.515</v>
       </c>
-      <c r="L6" s="26" t="n">
+      <c r="L6" s="27" t="n">
         <v>4825.515</v>
       </c>
-      <c r="M6" s="26" t="n">
+      <c r="M6" s="27" t="n">
         <v>4825.515</v>
       </c>
-      <c r="N6" s="26" t="n">
+      <c r="N6" s="27" t="n">
         <v>4825.515</v>
       </c>
-      <c r="O6" s="26" t="n">
+      <c r="O6" s="27" t="n">
         <v>4825.515</v>
       </c>
-      <c r="P6" s="26" t="n">
+      <c r="P6" s="27" t="n">
         <v>4825.515</v>
       </c>
-      <c r="Q6" s="26" t="n">
+      <c r="Q6" s="27" t="n">
         <v>4825.515</v>
       </c>
-      <c r="R6" s="26" t="n">
+      <c r="R6" s="27" t="n">
         <v>4825.515</v>
       </c>
-      <c r="S6" s="26" t="n">
+      <c r="S6" s="27" t="n">
         <v>4825.515</v>
       </c>
-      <c r="T6" s="33">
+      <c r="T6" s="34">
         <f>SUM(H6:S6)</f>
         <v/>
       </c>
     </row>
     <row r="7" ht="26" customHeight="1">
-      <c r="A7" s="24" t="inlineStr">
+      <c r="A7" s="25" t="inlineStr">
         <is>
           <t>JUR-E03</t>
         </is>
       </c>
-      <c r="B7" s="24" t="inlineStr">
+      <c r="B7" s="25" t="inlineStr">
         <is>
           <t>Jurídico</t>
         </is>
       </c>
-      <c r="C7" s="24" t="inlineStr">
+      <c r="C7" s="25" t="inlineStr">
         <is>
           <t>Equipe</t>
         </is>
       </c>
-      <c r="D7" s="25" t="inlineStr">
+      <c r="D7" s="26" t="inlineStr">
         <is>
           <t>Thamar Victória</t>
         </is>
       </c>
-      <c r="E7" s="25" t="inlineStr">
+      <c r="E7" s="26" t="inlineStr">
         <is>
           <t>Advogada — recebia R$ 4.500/mês em jan–mar e passou a R$ 5.500 em abr/26 (aumento de R$ 1.000), contra R$ 5.000 orçados. Planejado revisado para R$ 5.500 a partir de ago/26</t>
         </is>
       </c>
-      <c r="F7" s="24" t="inlineStr">
+      <c r="F7" s="25" t="inlineStr">
         <is>
           <t>PJ</t>
         </is>
       </c>
-      <c r="G7" s="24" t="inlineStr">
+      <c r="G7" s="25" t="inlineStr">
         <is>
           <t>Pessoal - PJ</t>
         </is>
       </c>
-      <c r="H7" s="26" t="n">
+      <c r="H7" s="27" t="n">
         <v>5000</v>
       </c>
-      <c r="I7" s="26" t="n">
+      <c r="I7" s="27" t="n">
         <v>5000</v>
       </c>
-      <c r="J7" s="26" t="n">
+      <c r="J7" s="27" t="n">
         <v>5000</v>
       </c>
-      <c r="K7" s="26" t="n">
+      <c r="K7" s="27" t="n">
         <v>5000</v>
       </c>
-      <c r="L7" s="26" t="n">
+      <c r="L7" s="27" t="n">
         <v>5000</v>
       </c>
-      <c r="M7" s="26" t="n">
+      <c r="M7" s="27" t="n">
         <v>5000</v>
       </c>
-      <c r="N7" s="26" t="n">
+      <c r="N7" s="27" t="n">
         <v>5000</v>
       </c>
-      <c r="O7" s="26" t="n">
+      <c r="O7" s="27" t="n">
         <v>5500</v>
       </c>
-      <c r="P7" s="26" t="n">
+      <c r="P7" s="27" t="n">
         <v>5500</v>
       </c>
-      <c r="Q7" s="26" t="n">
+      <c r="Q7" s="27" t="n">
         <v>5500</v>
       </c>
-      <c r="R7" s="26" t="n">
+      <c r="R7" s="27" t="n">
         <v>5500</v>
       </c>
-      <c r="S7" s="26" t="n">
+      <c r="S7" s="27" t="n">
         <v>5500</v>
       </c>
-      <c r="T7" s="33">
+      <c r="T7" s="34">
         <f>SUM(H7:S7)</f>
         <v/>
       </c>
     </row>
     <row r="8" ht="26" customHeight="1">
-      <c r="A8" s="24" t="inlineStr">
+      <c r="A8" s="25" t="inlineStr">
         <is>
           <t>JUR-D01</t>
         </is>
       </c>
-      <c r="B8" s="24" t="inlineStr">
+      <c r="B8" s="25" t="inlineStr">
         <is>
           <t>Jurídico</t>
         </is>
       </c>
-      <c r="C8" s="24" t="inlineStr">
+      <c r="C8" s="25" t="inlineStr">
         <is>
           <t>Despesas</t>
         </is>
       </c>
-      <c r="D8" s="25" t="inlineStr">
+      <c r="D8" s="26" t="inlineStr">
         <is>
           <t>JUSFY</t>
         </is>
       </c>
-      <c r="E8" s="25" t="inlineStr">
+      <c r="E8" s="26" t="inlineStr">
         <is>
           <t>Fase de teste com objetivo de eliminar o Astrea</t>
         </is>
       </c>
-      <c r="F8" s="24" t="inlineStr"/>
-      <c r="G8" s="24" t="inlineStr">
+      <c r="F8" s="25" t="inlineStr"/>
+      <c r="G8" s="25" t="inlineStr">
         <is>
           <t>Licenças de Softwares</t>
         </is>
       </c>
-      <c r="H8" s="26" t="n">
+      <c r="H8" s="27" t="n">
         <v>100</v>
       </c>
-      <c r="I8" s="26" t="n">
+      <c r="I8" s="27" t="n">
         <v>100</v>
       </c>
-      <c r="J8" s="26" t="n">
+      <c r="J8" s="27" t="n">
         <v>100</v>
       </c>
-      <c r="K8" s="26" t="n">
+      <c r="K8" s="27" t="n">
         <v>100</v>
       </c>
-      <c r="L8" s="26" t="n">
+      <c r="L8" s="27" t="n">
         <v>100</v>
       </c>
-      <c r="M8" s="26" t="n">
+      <c r="M8" s="27" t="n">
         <v>100</v>
       </c>
-      <c r="N8" s="26" t="n">
+      <c r="N8" s="27" t="n">
         <v>100</v>
       </c>
-      <c r="O8" s="26" t="n">
+      <c r="O8" s="27" t="n">
         <v>100</v>
       </c>
-      <c r="P8" s="26" t="n">
+      <c r="P8" s="27" t="n">
         <v>100</v>
       </c>
-      <c r="Q8" s="26" t="n">
+      <c r="Q8" s="27" t="n">
         <v>100</v>
       </c>
-      <c r="R8" s="26" t="n">
+      <c r="R8" s="27" t="n">
         <v>100</v>
       </c>
-      <c r="S8" s="26" t="n">
+      <c r="S8" s="27" t="n">
         <v>100</v>
       </c>
-      <c r="T8" s="33">
+      <c r="T8" s="34">
         <f>SUM(H8:S8)</f>
         <v/>
       </c>
     </row>
     <row r="9" ht="26" customHeight="1">
-      <c r="A9" s="24" t="inlineStr">
+      <c r="A9" s="25" t="inlineStr">
         <is>
           <t>JUR-D02</t>
         </is>
       </c>
-      <c r="B9" s="24" t="inlineStr">
+      <c r="B9" s="25" t="inlineStr">
         <is>
           <t>Jurídico</t>
         </is>
       </c>
-      <c r="C9" s="24" t="inlineStr">
+      <c r="C9" s="25" t="inlineStr">
         <is>
           <t>Despesas</t>
         </is>
       </c>
-      <c r="D9" s="25" t="inlineStr">
+      <c r="D9" s="26" t="inlineStr">
         <is>
           <t>JUSBRASIL</t>
         </is>
       </c>
-      <c r="E9" s="25" t="inlineStr"/>
-      <c r="F9" s="24" t="inlineStr"/>
-      <c r="G9" s="24" t="inlineStr">
+      <c r="E9" s="26" t="inlineStr"/>
+      <c r="F9" s="25" t="inlineStr"/>
+      <c r="G9" s="25" t="inlineStr">
         <is>
           <t>Licenças de Softwares</t>
         </is>
       </c>
-      <c r="H9" s="26" t="n">
+      <c r="H9" s="27" t="n">
         <v>104.9</v>
       </c>
-      <c r="I9" s="26" t="n">
+      <c r="I9" s="27" t="n">
         <v>104.9</v>
       </c>
-      <c r="J9" s="26" t="n">
+      <c r="J9" s="27" t="n">
         <v>104.9</v>
       </c>
-      <c r="K9" s="26" t="n">
+      <c r="K9" s="27" t="n">
         <v>104.9</v>
       </c>
-      <c r="L9" s="26" t="n">
+      <c r="L9" s="27" t="n">
         <v>104.9</v>
       </c>
-      <c r="M9" s="26" t="n">
+      <c r="M9" s="27" t="n">
         <v>104.9</v>
       </c>
-      <c r="N9" s="26" t="n">
+      <c r="N9" s="27" t="n">
         <v>104.9</v>
       </c>
-      <c r="O9" s="26" t="n">
+      <c r="O9" s="27" t="n">
         <v>104.9</v>
       </c>
-      <c r="P9" s="26" t="n">
+      <c r="P9" s="27" t="n">
         <v>104.9</v>
       </c>
-      <c r="Q9" s="26" t="n">
+      <c r="Q9" s="27" t="n">
         <v>104.9</v>
       </c>
-      <c r="R9" s="26" t="n">
+      <c r="R9" s="27" t="n">
         <v>104.9</v>
       </c>
-      <c r="S9" s="26" t="n">
+      <c r="S9" s="27" t="n">
         <v>104.9</v>
       </c>
-      <c r="T9" s="33">
+      <c r="T9" s="34">
         <f>SUM(H9:S9)</f>
         <v/>
       </c>
     </row>
     <row r="10" ht="26" customHeight="1">
-      <c r="A10" s="24" t="inlineStr">
+      <c r="A10" s="25" t="inlineStr">
         <is>
           <t>JUR-D03</t>
         </is>
       </c>
-      <c r="B10" s="24" t="inlineStr">
+      <c r="B10" s="25" t="inlineStr">
         <is>
           <t>Jurídico</t>
         </is>
       </c>
-      <c r="C10" s="24" t="inlineStr">
+      <c r="C10" s="25" t="inlineStr">
         <is>
           <t>Despesas</t>
         </is>
       </c>
-      <c r="D10" s="25" t="inlineStr">
+      <c r="D10" s="26" t="inlineStr">
         <is>
           <t>ASTREA</t>
         </is>
       </c>
-      <c r="E10" s="25" t="inlineStr">
+      <c r="E10" s="26" t="inlineStr">
         <is>
           <t>Cancelado — realizado zerado desde mai/26</t>
         </is>
       </c>
-      <c r="F10" s="24" t="inlineStr"/>
-      <c r="G10" s="24" t="inlineStr">
+      <c r="F10" s="25" t="inlineStr"/>
+      <c r="G10" s="25" t="inlineStr">
         <is>
           <t>Licenças de Softwares</t>
         </is>
       </c>
-      <c r="H10" s="26" t="n">
+      <c r="H10" s="27" t="n">
         <v>112.07</v>
       </c>
-      <c r="I10" s="26" t="n">
+      <c r="I10" s="27" t="n">
         <v>112.07</v>
       </c>
-      <c r="J10" s="26" t="n">
+      <c r="J10" s="27" t="n">
         <v>112.07</v>
       </c>
-      <c r="K10" s="26" t="n">
+      <c r="K10" s="27" t="n">
         <v>112.07</v>
       </c>
-      <c r="L10" s="26" t="n">
+      <c r="L10" s="27" t="n">
         <v>112.07</v>
       </c>
-      <c r="M10" s="26" t="n">
+      <c r="M10" s="27" t="n">
         <v>112.07</v>
       </c>
-      <c r="N10" s="26" t="n">
+      <c r="N10" s="27" t="n">
         <v>112.07</v>
       </c>
-      <c r="O10" s="26" t="n">
+      <c r="O10" s="27" t="n">
         <v>112.07</v>
       </c>
-      <c r="P10" s="26" t="n">
+      <c r="P10" s="27" t="n">
         <v>112.07</v>
       </c>
-      <c r="Q10" s="26" t="n">
+      <c r="Q10" s="27" t="n">
         <v>112.07</v>
       </c>
-      <c r="R10" s="26" t="n">
+      <c r="R10" s="27" t="n">
         <v>112.07</v>
       </c>
-      <c r="S10" s="26" t="n">
+      <c r="S10" s="27" t="n">
         <v>112.07</v>
       </c>
-      <c r="T10" s="33">
+      <c r="T10" s="34">
         <f>SUM(H10:S10)</f>
         <v/>
       </c>
     </row>
     <row r="11" ht="26" customHeight="1">
-      <c r="A11" s="24" t="inlineStr">
+      <c r="A11" s="25" t="inlineStr">
         <is>
           <t>JUR-D04</t>
         </is>
       </c>
-      <c r="B11" s="24" t="inlineStr">
+      <c r="B11" s="25" t="inlineStr">
         <is>
           <t>Jurídico</t>
         </is>
       </c>
-      <c r="C11" s="24" t="inlineStr">
+      <c r="C11" s="25" t="inlineStr">
         <is>
           <t>Despesas</t>
         </is>
       </c>
-      <c r="D11" s="25" t="inlineStr">
+      <c r="D11" s="26" t="inlineStr">
         <is>
           <t>LEME</t>
         </is>
       </c>
-      <c r="E11" s="25" t="inlineStr"/>
-      <c r="F11" s="24" t="inlineStr"/>
-      <c r="G11" s="24" t="inlineStr">
+      <c r="E11" s="26" t="inlineStr"/>
+      <c r="F11" s="25" t="inlineStr"/>
+      <c r="G11" s="25" t="inlineStr">
         <is>
           <t>Licenças de Softwares</t>
         </is>
       </c>
-      <c r="H11" s="26" t="n">
+      <c r="H11" s="27" t="n">
         <v>1030</v>
       </c>
-      <c r="I11" s="26" t="n">
+      <c r="I11" s="27" t="n">
         <v>1030</v>
       </c>
-      <c r="J11" s="26" t="n">
+      <c r="J11" s="27" t="n">
         <v>1030</v>
       </c>
-      <c r="K11" s="26" t="n">
+      <c r="K11" s="27" t="n">
         <v>1030</v>
       </c>
-      <c r="L11" s="26" t="n">
+      <c r="L11" s="27" t="n">
         <v>1030</v>
       </c>
-      <c r="M11" s="26" t="n">
+      <c r="M11" s="27" t="n">
         <v>1030</v>
       </c>
-      <c r="N11" s="26" t="n">
+      <c r="N11" s="27" t="n">
         <v>1030</v>
       </c>
-      <c r="O11" s="26" t="n">
+      <c r="O11" s="27" t="n">
         <v>1030</v>
       </c>
-      <c r="P11" s="26" t="n">
+      <c r="P11" s="27" t="n">
         <v>1030</v>
       </c>
-      <c r="Q11" s="26" t="n">
+      <c r="Q11" s="27" t="n">
         <v>1030</v>
       </c>
-      <c r="R11" s="26" t="n">
+      <c r="R11" s="27" t="n">
         <v>1030</v>
       </c>
-      <c r="S11" s="26" t="n">
+      <c r="S11" s="27" t="n">
         <v>1030</v>
       </c>
-      <c r="T11" s="33">
+      <c r="T11" s="34">
         <f>SUM(H11:S11)</f>
         <v/>
       </c>
     </row>
     <row r="12" ht="26" customHeight="1">
-      <c r="A12" s="24" t="inlineStr">
+      <c r="A12" s="25" t="inlineStr">
         <is>
           <t>JUR-D05</t>
         </is>
       </c>
-      <c r="B12" s="24" t="inlineStr">
+      <c r="B12" s="25" t="inlineStr">
         <is>
           <t>Jurídico</t>
         </is>
       </c>
-      <c r="C12" s="24" t="inlineStr">
+      <c r="C12" s="25" t="inlineStr">
         <is>
           <t>Despesas</t>
         </is>
       </c>
-      <c r="D12" s="25" t="inlineStr">
+      <c r="D12" s="26" t="inlineStr">
         <is>
           <t>Cursos / Eventos / Network</t>
         </is>
       </c>
-      <c r="E12" s="25" t="inlineStr"/>
-      <c r="F12" s="24" t="inlineStr"/>
-      <c r="G12" s="24" t="inlineStr">
+      <c r="E12" s="26" t="inlineStr"/>
+      <c r="F12" s="25" t="inlineStr"/>
+      <c r="G12" s="25" t="inlineStr">
         <is>
           <t>Custeio de Treinamento</t>
         </is>
       </c>
-      <c r="H12" s="26" t="n">
+      <c r="H12" s="27" t="n">
         <v>1000</v>
       </c>
-      <c r="I12" s="26" t="n">
+      <c r="I12" s="27" t="n">
         <v>1000</v>
       </c>
-      <c r="J12" s="26" t="n">
+      <c r="J12" s="27" t="n">
         <v>1000</v>
       </c>
-      <c r="K12" s="26" t="n">
+      <c r="K12" s="27" t="n">
         <v>1000</v>
       </c>
-      <c r="L12" s="26" t="n">
+      <c r="L12" s="27" t="n">
         <v>1000</v>
       </c>
-      <c r="M12" s="26" t="n">
+      <c r="M12" s="27" t="n">
         <v>1000</v>
       </c>
-      <c r="N12" s="26" t="n">
+      <c r="N12" s="27" t="n">
         <v>1000</v>
       </c>
-      <c r="O12" s="26" t="n">
+      <c r="O12" s="27" t="n">
         <v>1000</v>
       </c>
-      <c r="P12" s="26" t="n">
+      <c r="P12" s="27" t="n">
         <v>1000</v>
       </c>
-      <c r="Q12" s="26" t="n">
+      <c r="Q12" s="27" t="n">
         <v>1000</v>
       </c>
-      <c r="R12" s="26" t="n">
+      <c r="R12" s="27" t="n">
         <v>1000</v>
       </c>
-      <c r="S12" s="26" t="n">
+      <c r="S12" s="27" t="n">
         <v>1000</v>
       </c>
-      <c r="T12" s="33">
+      <c r="T12" s="34">
         <f>SUM(H12:S12)</f>
         <v/>
       </c>
     </row>
     <row r="13" ht="26" customHeight="1">
-      <c r="A13" s="24" t="inlineStr">
+      <c r="A13" s="25" t="inlineStr">
         <is>
           <t>JUR-D06</t>
         </is>
       </c>
-      <c r="B13" s="24" t="inlineStr">
+      <c r="B13" s="25" t="inlineStr">
         <is>
           <t>Jurídico</t>
         </is>
       </c>
-      <c r="C13" s="24" t="inlineStr">
+      <c r="C13" s="25" t="inlineStr">
         <is>
           <t>Despesas</t>
         </is>
       </c>
-      <c r="D13" s="25" t="inlineStr">
+      <c r="D13" s="26" t="inlineStr">
         <is>
           <t>Bonificações trimestrais/semestrais do time</t>
         </is>
       </c>
-      <c r="E13" s="25" t="inlineStr">
+      <c r="E13" s="26" t="inlineStr">
         <is>
           <t>Participação em projetos e atingimento de resultados — CONFIRMAR se houve parcela no 1º quadrimestre</t>
         </is>
       </c>
-      <c r="F13" s="24" t="inlineStr"/>
-      <c r="G13" s="24" t="inlineStr">
+      <c r="F13" s="25" t="inlineStr"/>
+      <c r="G13" s="25" t="inlineStr">
         <is>
           <t>Prêmios</t>
         </is>
       </c>
-      <c r="H13" s="26" t="n">
+      <c r="H13" s="27" t="n">
         <v>0</v>
       </c>
-      <c r="I13" s="26" t="n">
+      <c r="I13" s="27" t="n">
         <v>0</v>
       </c>
-      <c r="J13" s="26" t="n">
+      <c r="J13" s="27" t="n">
         <v>0</v>
       </c>
-      <c r="K13" s="26" t="n">
+      <c r="K13" s="27" t="n">
         <v>0</v>
       </c>
-      <c r="L13" s="26" t="n">
+      <c r="L13" s="27" t="n">
         <v>0</v>
       </c>
-      <c r="M13" s="26" t="n">
+      <c r="M13" s="27" t="n">
         <v>0</v>
       </c>
-      <c r="N13" s="26" t="n">
+      <c r="N13" s="27" t="n">
         <v>0</v>
       </c>
-      <c r="O13" s="26" t="n">
+      <c r="O13" s="27" t="n">
         <v>10293.6</v>
       </c>
-      <c r="P13" s="26" t="n">
+      <c r="P13" s="27" t="n">
         <v>0</v>
       </c>
-      <c r="Q13" s="26" t="n">
+      <c r="Q13" s="27" t="n">
         <v>0</v>
       </c>
-      <c r="R13" s="26" t="n">
+      <c r="R13" s="27" t="n">
         <v>0</v>
       </c>
-      <c r="S13" s="26" t="n">
+      <c r="S13" s="27" t="n">
         <v>12867</v>
       </c>
-      <c r="T13" s="33">
+      <c r="T13" s="34">
         <f>SUM(H13:S13)</f>
         <v/>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="30" t="inlineStr">
+      <c r="A14" s="31" t="inlineStr">
         <is>
           <t>TOTAL GERAL</t>
         </is>
       </c>
-      <c r="B14" s="30" t="n"/>
-      <c r="C14" s="30" t="n"/>
-      <c r="D14" s="30" t="n"/>
-      <c r="E14" s="30" t="n"/>
-      <c r="F14" s="30" t="n"/>
-      <c r="G14" s="30" t="n"/>
-      <c r="H14" s="31">
+      <c r="B14" s="31" t="n"/>
+      <c r="C14" s="31" t="n"/>
+      <c r="D14" s="31" t="n"/>
+      <c r="E14" s="31" t="n"/>
+      <c r="F14" s="31" t="n"/>
+      <c r="G14" s="31" t="n"/>
+      <c r="H14" s="32">
         <f>SUM(H5:H13)</f>
         <v/>
       </c>
-      <c r="I14" s="31">
+      <c r="I14" s="32">
         <f>SUM(I5:I13)</f>
         <v/>
       </c>
-      <c r="J14" s="31">
+      <c r="J14" s="32">
         <f>SUM(J5:J13)</f>
         <v/>
       </c>
-      <c r="K14" s="31">
+      <c r="K14" s="32">
         <f>SUM(K5:K13)</f>
         <v/>
       </c>
-      <c r="L14" s="31">
+      <c r="L14" s="32">
         <f>SUM(L5:L13)</f>
         <v/>
       </c>
-      <c r="M14" s="31">
+      <c r="M14" s="32">
         <f>SUM(M5:M13)</f>
         <v/>
       </c>
-      <c r="N14" s="31">
+      <c r="N14" s="32">
         <f>SUM(N5:N13)</f>
         <v/>
       </c>
-      <c r="O14" s="31">
+      <c r="O14" s="32">
         <f>SUM(O5:O13)</f>
         <v/>
       </c>
-      <c r="P14" s="31">
+      <c r="P14" s="32">
         <f>SUM(P5:P13)</f>
         <v/>
       </c>
-      <c r="Q14" s="31">
+      <c r="Q14" s="32">
         <f>SUM(Q5:Q13)</f>
         <v/>
       </c>
-      <c r="R14" s="31">
+      <c r="R14" s="32">
         <f>SUM(R5:R13)</f>
         <v/>
       </c>
-      <c r="S14" s="31">
+      <c r="S14" s="32">
         <f>SUM(S5:S13)</f>
         <v/>
       </c>
-      <c r="T14" s="31">
+      <c r="T14" s="32">
         <f>SUM(T5:T13)</f>
         <v/>
       </c>
@@ -3163,755 +3185,773 @@
       </c>
     </row>
     <row r="4" ht="30" customHeight="1">
-      <c r="A4" s="34" t="inlineStr">
+      <c r="A4" s="35" t="inlineStr">
         <is>
           <t>ID</t>
         </is>
       </c>
-      <c r="B4" s="34" t="inlineStr">
+      <c r="B4" s="35" t="inlineStr">
         <is>
           <t>Departamento</t>
         </is>
       </c>
-      <c r="C4" s="34" t="inlineStr">
+      <c r="C4" s="35" t="inlineStr">
         <is>
           <t>Bloco</t>
         </is>
       </c>
-      <c r="D4" s="34" t="inlineStr">
+      <c r="D4" s="35" t="inlineStr">
         <is>
           <t>Descrição</t>
         </is>
       </c>
-      <c r="E4" s="34" t="inlineStr">
+      <c r="E4" s="35" t="inlineStr">
         <is>
           <t>Detalhe / Observação</t>
         </is>
       </c>
-      <c r="F4" s="34" t="inlineStr">
+      <c r="F4" s="35" t="inlineStr">
         <is>
           <t>Vínculo</t>
         </is>
       </c>
-      <c r="G4" s="34" t="inlineStr">
+      <c r="G4" s="35" t="inlineStr">
         <is>
           <t>Plano de Contas</t>
         </is>
       </c>
-      <c r="H4" s="34" t="inlineStr">
+      <c r="H4" s="35" t="inlineStr">
         <is>
           <t>Jan/26</t>
         </is>
       </c>
-      <c r="I4" s="34" t="inlineStr">
+      <c r="I4" s="35" t="inlineStr">
         <is>
           <t>Fev/26</t>
         </is>
       </c>
-      <c r="J4" s="34" t="inlineStr">
+      <c r="J4" s="35" t="inlineStr">
         <is>
           <t>Mar/26</t>
         </is>
       </c>
-      <c r="K4" s="34" t="inlineStr">
+      <c r="K4" s="35" t="inlineStr">
         <is>
           <t>Abr/26</t>
         </is>
       </c>
-      <c r="L4" s="34" t="inlineStr">
+      <c r="L4" s="35" t="inlineStr">
         <is>
           <t>Mai/26</t>
         </is>
       </c>
-      <c r="M4" s="34" t="inlineStr">
+      <c r="M4" s="35" t="inlineStr">
         <is>
           <t>Jun/26</t>
         </is>
       </c>
-      <c r="N4" s="34" t="inlineStr">
+      <c r="N4" s="35" t="inlineStr">
         <is>
           <t>Jul/26</t>
         </is>
       </c>
-      <c r="O4" s="34" t="inlineStr">
+      <c r="O4" s="35" t="inlineStr">
         <is>
           <t>Ago/26</t>
         </is>
       </c>
-      <c r="P4" s="34" t="inlineStr">
+      <c r="P4" s="35" t="inlineStr">
         <is>
           <t>Set/26</t>
         </is>
       </c>
-      <c r="Q4" s="34" t="inlineStr">
+      <c r="Q4" s="35" t="inlineStr">
         <is>
           <t>Out/26</t>
         </is>
       </c>
-      <c r="R4" s="34" t="inlineStr">
+      <c r="R4" s="35" t="inlineStr">
         <is>
           <t>Nov/26</t>
         </is>
       </c>
-      <c r="S4" s="34" t="inlineStr">
+      <c r="S4" s="35" t="inlineStr">
         <is>
           <t>Dez/26</t>
         </is>
       </c>
-      <c r="T4" s="34" t="inlineStr">
+      <c r="T4" s="35" t="inlineStr">
         <is>
           <t>TOTAL REALIZADO</t>
         </is>
       </c>
-      <c r="U4" s="34" t="inlineStr">
+      <c r="U4" s="35" t="inlineStr">
         <is>
           <t>Fonte do dado</t>
         </is>
       </c>
-      <c r="V4" s="34" t="inlineStr">
+      <c r="V4" s="35" t="inlineStr">
         <is>
           <t>Observações do mês</t>
         </is>
       </c>
     </row>
     <row r="5" ht="26" customHeight="1">
-      <c r="A5" s="35">
+      <c r="A5" s="36">
         <f>Planejado!A5</f>
         <v/>
       </c>
-      <c r="B5" s="35">
+      <c r="B5" s="36">
         <f>Planejado!B5</f>
         <v/>
       </c>
-      <c r="C5" s="35">
+      <c r="C5" s="36">
         <f>Planejado!C5</f>
         <v/>
       </c>
-      <c r="D5" s="36">
+      <c r="D5" s="37">
         <f>Planejado!D5</f>
         <v/>
       </c>
-      <c r="E5" s="36">
+      <c r="E5" s="37">
         <f>Planejado!E5</f>
         <v/>
       </c>
-      <c r="F5" s="35">
+      <c r="F5" s="36">
         <f>Planejado!F5</f>
         <v/>
       </c>
-      <c r="G5" s="35">
+      <c r="G5" s="36">
         <f>Planejado!G5</f>
         <v/>
       </c>
-      <c r="H5" s="37" t="n">
+      <c r="H5" s="38" t="n">
         <v>8818</v>
       </c>
-      <c r="I5" s="37" t="n">
+      <c r="I5" s="38" t="n">
         <v>8818</v>
       </c>
-      <c r="J5" s="37" t="n">
+      <c r="J5" s="38" t="n">
         <v>8818</v>
       </c>
-      <c r="K5" s="37" t="n">
+      <c r="K5" s="38" t="n">
         <v>8818</v>
       </c>
-      <c r="L5" s="37" t="n">
+      <c r="L5" s="38" t="n">
         <v>8818</v>
       </c>
-      <c r="M5" s="37" t="n">
+      <c r="M5" s="38" t="n">
         <v>8818</v>
       </c>
-      <c r="N5" s="37" t="n">
+      <c r="N5" s="38" t="n">
         <v>8818</v>
       </c>
-      <c r="O5" s="37" t="n"/>
-      <c r="T5" s="33">
+      <c r="O5" s="38" t="n"/>
+      <c r="T5" s="34">
         <f>SUM(H5:S5)</f>
         <v/>
       </c>
-      <c r="U5" s="38" t="inlineStr">
+      <c r="U5" s="39" t="inlineStr">
         <is>
           <t>Gestora, 05/08/26</t>
         </is>
       </c>
-      <c r="V5" s="38" t="inlineStr">
+      <c r="V5" s="39" t="inlineStr">
         <is>
           <t>Valor cheio da nota — R$ 1.182/mês abaixo do contratado</t>
         </is>
       </c>
     </row>
     <row r="6" ht="26" customHeight="1">
-      <c r="A6" s="35">
+      <c r="A6" s="36">
         <f>Planejado!A6</f>
         <v/>
       </c>
-      <c r="B6" s="35">
+      <c r="B6" s="36">
         <f>Planejado!B6</f>
         <v/>
       </c>
-      <c r="C6" s="35">
+      <c r="C6" s="36">
         <f>Planejado!C6</f>
         <v/>
       </c>
-      <c r="D6" s="36">
+      <c r="D6" s="37">
         <f>Planejado!D6</f>
         <v/>
       </c>
-      <c r="E6" s="36">
+      <c r="E6" s="37">
         <f>Planejado!E6</f>
         <v/>
       </c>
-      <c r="F6" s="35">
+      <c r="F6" s="36">
         <f>Planejado!F6</f>
         <v/>
       </c>
-      <c r="G6" s="35">
+      <c r="G6" s="36">
         <f>Planejado!G6</f>
         <v/>
       </c>
-      <c r="H6" s="37" t="n"/>
-      <c r="I6" s="37" t="n"/>
-      <c r="J6" s="37" t="n"/>
-      <c r="K6" s="37" t="n"/>
-      <c r="L6" s="37" t="n"/>
-      <c r="M6" s="37" t="n"/>
-      <c r="N6" s="37" t="n"/>
-      <c r="O6" s="37" t="n"/>
-      <c r="T6" s="33">
+      <c r="H6" s="38" t="n">
+        <v>2886.91</v>
+      </c>
+      <c r="I6" s="38" t="n">
+        <v>2886.91</v>
+      </c>
+      <c r="J6" s="38" t="n">
+        <v>2886.91</v>
+      </c>
+      <c r="K6" s="38" t="n">
+        <v>2886.91</v>
+      </c>
+      <c r="L6" s="38" t="n">
+        <v>2886.91</v>
+      </c>
+      <c r="M6" s="38" t="n">
+        <v>2886.91</v>
+      </c>
+      <c r="N6" s="38" t="n">
+        <v>2886.91</v>
+      </c>
+      <c r="O6" s="38" t="n"/>
+      <c r="T6" s="34">
         <f>SUM(H6:S6)</f>
         <v/>
       </c>
-      <c r="U6" s="38" t="n"/>
-      <c r="V6" s="38" t="inlineStr">
-        <is>
-          <t>PREENCHER com o CUSTO TOTAL. Bruto informado: R$ 2.886,91/mês — faltam encargos e benefícios</t>
+      <c r="U6" s="39" t="inlineStr">
+        <is>
+          <t>Gestora, 05/08/26</t>
+        </is>
+      </c>
+      <c r="V6" s="39" t="inlineStr">
+        <is>
+          <t>SALÁRIO BRUTO, sem alteração no ano. O orçado é custo total, então o desvio desta linha NÃO é economia: faltam encargos e benefícios (~R$ 1.938,61/mês)</t>
         </is>
       </c>
     </row>
     <row r="7" ht="26" customHeight="1">
-      <c r="A7" s="35">
+      <c r="A7" s="36">
         <f>Planejado!A7</f>
         <v/>
       </c>
-      <c r="B7" s="35">
+      <c r="B7" s="36">
         <f>Planejado!B7</f>
         <v/>
       </c>
-      <c r="C7" s="35">
+      <c r="C7" s="36">
         <f>Planejado!C7</f>
         <v/>
       </c>
-      <c r="D7" s="36">
+      <c r="D7" s="37">
         <f>Planejado!D7</f>
         <v/>
       </c>
-      <c r="E7" s="36">
+      <c r="E7" s="37">
         <f>Planejado!E7</f>
         <v/>
       </c>
-      <c r="F7" s="35">
+      <c r="F7" s="36">
         <f>Planejado!F7</f>
         <v/>
       </c>
-      <c r="G7" s="35">
+      <c r="G7" s="36">
         <f>Planejado!G7</f>
         <v/>
       </c>
-      <c r="H7" s="37" t="n">
+      <c r="H7" s="38" t="n">
         <v>4500</v>
       </c>
-      <c r="I7" s="37" t="n">
+      <c r="I7" s="38" t="n">
         <v>4500</v>
       </c>
-      <c r="J7" s="37" t="n">
+      <c r="J7" s="38" t="n">
         <v>4500</v>
       </c>
-      <c r="K7" s="37" t="n">
+      <c r="K7" s="38" t="n">
         <v>5500</v>
       </c>
-      <c r="L7" s="37" t="n">
+      <c r="L7" s="38" t="n">
         <v>5500</v>
       </c>
-      <c r="M7" s="37" t="n">
+      <c r="M7" s="38" t="n">
         <v>5500</v>
       </c>
-      <c r="N7" s="37" t="n">
+      <c r="N7" s="38" t="n">
         <v>5500</v>
       </c>
-      <c r="O7" s="37" t="n"/>
-      <c r="T7" s="33">
+      <c r="O7" s="38" t="n"/>
+      <c r="T7" s="34">
         <f>SUM(H7:S7)</f>
         <v/>
       </c>
-      <c r="U7" s="38" t="inlineStr">
+      <c r="U7" s="39" t="inlineStr">
         <is>
           <t>Gestora, 05/08/26</t>
         </is>
       </c>
-      <c r="V7" s="38" t="inlineStr">
+      <c r="V7" s="39" t="inlineStr">
         <is>
           <t>R$ 4.500/mês em jan–mar; aumento de R$ 1.000 a partir de abr/26</t>
         </is>
       </c>
     </row>
     <row r="8" ht="26" customHeight="1">
-      <c r="A8" s="35">
+      <c r="A8" s="36">
         <f>Planejado!A8</f>
         <v/>
       </c>
-      <c r="B8" s="35">
+      <c r="B8" s="36">
         <f>Planejado!B8</f>
         <v/>
       </c>
-      <c r="C8" s="35">
+      <c r="C8" s="36">
         <f>Planejado!C8</f>
         <v/>
       </c>
-      <c r="D8" s="36">
+      <c r="D8" s="37">
         <f>Planejado!D8</f>
         <v/>
       </c>
-      <c r="E8" s="36">
+      <c r="E8" s="37">
         <f>Planejado!E8</f>
         <v/>
       </c>
-      <c r="F8" s="35">
+      <c r="F8" s="36">
         <f>Planejado!F8</f>
         <v/>
       </c>
-      <c r="G8" s="35">
+      <c r="G8" s="36">
         <f>Planejado!G8</f>
         <v/>
       </c>
-      <c r="H8" s="37" t="n">
+      <c r="H8" s="38" t="n">
         <v>0</v>
       </c>
-      <c r="I8" s="37" t="n">
+      <c r="I8" s="38" t="n">
         <v>0</v>
       </c>
-      <c r="J8" s="37" t="n">
+      <c r="J8" s="38" t="n">
         <v>0</v>
       </c>
-      <c r="K8" s="37" t="n">
+      <c r="K8" s="38" t="n">
         <v>0</v>
       </c>
-      <c r="L8" s="37" t="n">
+      <c r="L8" s="38" t="n">
         <v>0</v>
       </c>
-      <c r="M8" s="37" t="n">
+      <c r="M8" s="38" t="n">
         <v>0</v>
       </c>
-      <c r="N8" s="37" t="n">
+      <c r="N8" s="38" t="n">
         <v>0</v>
       </c>
-      <c r="O8" s="37" t="n"/>
-      <c r="T8" s="33">
+      <c r="O8" s="38" t="n"/>
+      <c r="T8" s="34">
         <f>SUM(H8:S8)</f>
         <v/>
       </c>
-      <c r="U8" s="38" t="inlineStr">
+      <c r="U8" s="39" t="inlineStr">
         <is>
           <t>Gestora, 05/08/26</t>
         </is>
       </c>
-      <c r="V8" s="38" t="inlineStr">
+      <c r="V8" s="39" t="inlineStr">
         <is>
           <t>Ainda não iniciado — sem cobrança</t>
         </is>
       </c>
     </row>
     <row r="9" ht="26" customHeight="1">
-      <c r="A9" s="35">
+      <c r="A9" s="36">
         <f>Planejado!A9</f>
         <v/>
       </c>
-      <c r="B9" s="35">
+      <c r="B9" s="36">
         <f>Planejado!B9</f>
         <v/>
       </c>
-      <c r="C9" s="35">
+      <c r="C9" s="36">
         <f>Planejado!C9</f>
         <v/>
       </c>
-      <c r="D9" s="36">
+      <c r="D9" s="37">
         <f>Planejado!D9</f>
         <v/>
       </c>
-      <c r="E9" s="36">
+      <c r="E9" s="37">
         <f>Planejado!E9</f>
         <v/>
       </c>
-      <c r="F9" s="35">
+      <c r="F9" s="36">
         <f>Planejado!F9</f>
         <v/>
       </c>
-      <c r="G9" s="35">
+      <c r="G9" s="36">
         <f>Planejado!G9</f>
         <v/>
       </c>
-      <c r="H9" s="37" t="n">
+      <c r="H9" s="38" t="n">
         <v>136</v>
       </c>
-      <c r="I9" s="37" t="n">
+      <c r="I9" s="38" t="n">
         <v>136</v>
       </c>
-      <c r="J9" s="37" t="n">
+      <c r="J9" s="38" t="n">
         <v>136</v>
       </c>
-      <c r="K9" s="37" t="n">
+      <c r="K9" s="38" t="n">
         <v>136</v>
       </c>
-      <c r="L9" s="37" t="n">
+      <c r="L9" s="38" t="n">
         <v>136</v>
       </c>
-      <c r="M9" s="37" t="n">
+      <c r="M9" s="38" t="n">
         <v>136</v>
       </c>
-      <c r="N9" s="37" t="n">
+      <c r="N9" s="38" t="n">
         <v>136</v>
       </c>
-      <c r="O9" s="37" t="n"/>
-      <c r="T9" s="33">
+      <c r="O9" s="38" t="n"/>
+      <c r="T9" s="34">
         <f>SUM(H9:S9)</f>
         <v/>
       </c>
-      <c r="U9" s="38" t="inlineStr">
+      <c r="U9" s="39" t="inlineStr">
         <is>
           <t>Gestora, 05/08/26</t>
         </is>
       </c>
-      <c r="V9" s="38" t="inlineStr">
+      <c r="V9" s="39" t="inlineStr">
         <is>
           <t>Acima do orçado (R$ 104,90) — conferir contrato</t>
         </is>
       </c>
     </row>
     <row r="10" ht="26" customHeight="1">
-      <c r="A10" s="35">
+      <c r="A10" s="36">
         <f>Planejado!A10</f>
         <v/>
       </c>
-      <c r="B10" s="35">
+      <c r="B10" s="36">
         <f>Planejado!B10</f>
         <v/>
       </c>
-      <c r="C10" s="35">
+      <c r="C10" s="36">
         <f>Planejado!C10</f>
         <v/>
       </c>
-      <c r="D10" s="36">
+      <c r="D10" s="37">
         <f>Planejado!D10</f>
         <v/>
       </c>
-      <c r="E10" s="36">
+      <c r="E10" s="37">
         <f>Planejado!E10</f>
         <v/>
       </c>
-      <c r="F10" s="35">
+      <c r="F10" s="36">
         <f>Planejado!F10</f>
         <v/>
       </c>
-      <c r="G10" s="35">
+      <c r="G10" s="36">
         <f>Planejado!G10</f>
         <v/>
       </c>
-      <c r="H10" s="37" t="n">
+      <c r="H10" s="38" t="n">
         <v>0</v>
       </c>
-      <c r="I10" s="37" t="n">
+      <c r="I10" s="38" t="n">
         <v>0</v>
       </c>
-      <c r="J10" s="37" t="n">
+      <c r="J10" s="38" t="n">
         <v>0</v>
       </c>
-      <c r="K10" s="37" t="n">
+      <c r="K10" s="38" t="n">
         <v>0</v>
       </c>
-      <c r="L10" s="37" t="n">
+      <c r="L10" s="38" t="n">
         <v>0</v>
       </c>
-      <c r="M10" s="37" t="n">
+      <c r="M10" s="38" t="n">
         <v>0</v>
       </c>
-      <c r="N10" s="37" t="n">
+      <c r="N10" s="38" t="n">
         <v>0</v>
       </c>
-      <c r="O10" s="37" t="n"/>
-      <c r="T10" s="33">
+      <c r="O10" s="38" t="n"/>
+      <c r="T10" s="34">
         <f>SUM(H10:S10)</f>
         <v/>
       </c>
-      <c r="U10" s="38" t="inlineStr">
+      <c r="U10" s="39" t="inlineStr">
         <is>
           <t>Gestora, 05/08/26</t>
         </is>
       </c>
-      <c r="V10" s="38" t="inlineStr">
+      <c r="V10" s="39" t="inlineStr">
         <is>
           <t>Cancelado — sem cobrança</t>
         </is>
       </c>
     </row>
     <row r="11" ht="26" customHeight="1">
-      <c r="A11" s="35">
+      <c r="A11" s="36">
         <f>Planejado!A11</f>
         <v/>
       </c>
-      <c r="B11" s="35">
+      <c r="B11" s="36">
         <f>Planejado!B11</f>
         <v/>
       </c>
-      <c r="C11" s="35">
+      <c r="C11" s="36">
         <f>Planejado!C11</f>
         <v/>
       </c>
-      <c r="D11" s="36">
+      <c r="D11" s="37">
         <f>Planejado!D11</f>
         <v/>
       </c>
-      <c r="E11" s="36">
+      <c r="E11" s="37">
         <f>Planejado!E11</f>
         <v/>
       </c>
-      <c r="F11" s="35">
+      <c r="F11" s="36">
         <f>Planejado!F11</f>
         <v/>
       </c>
-      <c r="G11" s="35">
+      <c r="G11" s="36">
         <f>Planejado!G11</f>
         <v/>
       </c>
-      <c r="H11" s="37" t="n">
+      <c r="H11" s="38" t="n">
         <v>970</v>
       </c>
-      <c r="I11" s="37" t="n">
+      <c r="I11" s="38" t="n">
         <v>970</v>
       </c>
-      <c r="J11" s="37" t="n">
+      <c r="J11" s="38" t="n">
         <v>970</v>
       </c>
-      <c r="K11" s="37" t="n">
+      <c r="K11" s="38" t="n">
         <v>970</v>
       </c>
-      <c r="L11" s="37" t="n">
+      <c r="L11" s="38" t="n">
         <v>970</v>
       </c>
-      <c r="M11" s="37" t="n">
+      <c r="M11" s="38" t="n">
         <v>970</v>
       </c>
-      <c r="N11" s="37" t="n">
+      <c r="N11" s="38" t="n">
         <v>970</v>
       </c>
-      <c r="O11" s="37" t="n"/>
-      <c r="T11" s="33">
+      <c r="O11" s="38" t="n"/>
+      <c r="T11" s="34">
         <f>SUM(H11:S11)</f>
         <v/>
       </c>
-      <c r="U11" s="38" t="inlineStr">
+      <c r="U11" s="39" t="inlineStr">
         <is>
           <t>Gestora, 05/08/26</t>
         </is>
       </c>
-      <c r="V11" s="38" t="n"/>
+      <c r="V11" s="39" t="n"/>
     </row>
     <row r="12" ht="26" customHeight="1">
-      <c r="A12" s="35">
+      <c r="A12" s="36">
         <f>Planejado!A12</f>
         <v/>
       </c>
-      <c r="B12" s="35">
+      <c r="B12" s="36">
         <f>Planejado!B12</f>
         <v/>
       </c>
-      <c r="C12" s="35">
+      <c r="C12" s="36">
         <f>Planejado!C12</f>
         <v/>
       </c>
-      <c r="D12" s="36">
+      <c r="D12" s="37">
         <f>Planejado!D12</f>
         <v/>
       </c>
-      <c r="E12" s="36">
+      <c r="E12" s="37">
         <f>Planejado!E12</f>
         <v/>
       </c>
-      <c r="F12" s="35">
+      <c r="F12" s="36">
         <f>Planejado!F12</f>
         <v/>
       </c>
-      <c r="G12" s="35">
+      <c r="G12" s="36">
         <f>Planejado!G12</f>
         <v/>
       </c>
-      <c r="H12" s="37" t="n">
+      <c r="H12" s="38" t="n">
         <v>0</v>
       </c>
-      <c r="I12" s="37" t="n">
+      <c r="I12" s="38" t="n">
         <v>0</v>
       </c>
-      <c r="J12" s="37" t="n">
+      <c r="J12" s="38" t="n">
         <v>0</v>
       </c>
-      <c r="K12" s="37" t="n">
+      <c r="K12" s="38" t="n">
         <v>0</v>
       </c>
-      <c r="L12" s="37" t="n">
+      <c r="L12" s="38" t="n">
         <v>0</v>
       </c>
-      <c r="M12" s="37" t="n">
+      <c r="M12" s="38" t="n">
         <v>0</v>
       </c>
-      <c r="N12" s="37" t="n">
+      <c r="N12" s="38" t="n">
         <v>0</v>
       </c>
-      <c r="O12" s="37" t="n"/>
-      <c r="T12" s="33">
+      <c r="O12" s="38" t="n"/>
+      <c r="T12" s="34">
         <f>SUM(H12:S12)</f>
         <v/>
       </c>
-      <c r="U12" s="38" t="inlineStr">
+      <c r="U12" s="39" t="inlineStr">
         <is>
           <t>Gestora, 05/08/26</t>
         </is>
       </c>
-      <c r="V12" s="38" t="inlineStr">
+      <c r="V12" s="39" t="inlineStr">
         <is>
           <t>Sem gasto no período</t>
         </is>
       </c>
     </row>
     <row r="13" ht="26" customHeight="1">
-      <c r="A13" s="35">
+      <c r="A13" s="36">
         <f>Planejado!A13</f>
         <v/>
       </c>
-      <c r="B13" s="35">
+      <c r="B13" s="36">
         <f>Planejado!B13</f>
         <v/>
       </c>
-      <c r="C13" s="35">
+      <c r="C13" s="36">
         <f>Planejado!C13</f>
         <v/>
       </c>
-      <c r="D13" s="36">
+      <c r="D13" s="37">
         <f>Planejado!D13</f>
         <v/>
       </c>
-      <c r="E13" s="36">
+      <c r="E13" s="37">
         <f>Planejado!E13</f>
         <v/>
       </c>
-      <c r="F13" s="35">
+      <c r="F13" s="36">
         <f>Planejado!F13</f>
         <v/>
       </c>
-      <c r="G13" s="35">
+      <c r="G13" s="36">
         <f>Planejado!G13</f>
         <v/>
       </c>
-      <c r="H13" s="37" t="n">
+      <c r="H13" s="38" t="n">
         <v>0</v>
       </c>
-      <c r="I13" s="37" t="n">
+      <c r="I13" s="38" t="n">
         <v>0</v>
       </c>
-      <c r="J13" s="37" t="n">
+      <c r="J13" s="38" t="n">
         <v>0</v>
       </c>
-      <c r="K13" s="37" t="n">
+      <c r="K13" s="38" t="n">
         <v>0</v>
       </c>
-      <c r="L13" s="37" t="n">
+      <c r="L13" s="38" t="n">
         <v>0</v>
       </c>
-      <c r="M13" s="37" t="n">
+      <c r="M13" s="38" t="n">
         <v>0</v>
       </c>
-      <c r="N13" s="37" t="n">
+      <c r="N13" s="38" t="n">
         <v>0</v>
       </c>
-      <c r="O13" s="37" t="n"/>
-      <c r="T13" s="33">
+      <c r="O13" s="38" t="n"/>
+      <c r="T13" s="34">
         <f>SUM(H13:S13)</f>
         <v/>
       </c>
-      <c r="U13" s="38" t="inlineStr">
+      <c r="U13" s="39" t="inlineStr">
         <is>
           <t>Gestora, 05/08/26</t>
         </is>
       </c>
-      <c r="V13" s="38" t="inlineStr">
+      <c r="V13" s="39" t="inlineStr">
         <is>
           <t>Sem parcela no 1º semestre; bonificação de ago/26 a confirmar</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="39" t="inlineStr">
+      <c r="A14" s="40" t="inlineStr">
         <is>
           <t>TOTAL GERAL</t>
         </is>
       </c>
-      <c r="B14" s="39" t="n"/>
-      <c r="C14" s="39" t="n"/>
-      <c r="D14" s="39" t="n"/>
-      <c r="E14" s="39" t="n"/>
-      <c r="F14" s="39" t="n"/>
-      <c r="G14" s="39" t="n"/>
-      <c r="H14" s="40">
+      <c r="B14" s="40" t="n"/>
+      <c r="C14" s="40" t="n"/>
+      <c r="D14" s="40" t="n"/>
+      <c r="E14" s="40" t="n"/>
+      <c r="F14" s="40" t="n"/>
+      <c r="G14" s="40" t="n"/>
+      <c r="H14" s="41">
         <f>SUM(H5:H13)</f>
         <v/>
       </c>
-      <c r="I14" s="40">
+      <c r="I14" s="41">
         <f>SUM(I5:I13)</f>
         <v/>
       </c>
-      <c r="J14" s="40">
+      <c r="J14" s="41">
         <f>SUM(J5:J13)</f>
         <v/>
       </c>
-      <c r="K14" s="40">
+      <c r="K14" s="41">
         <f>SUM(K5:K13)</f>
         <v/>
       </c>
-      <c r="L14" s="40">
+      <c r="L14" s="41">
         <f>SUM(L5:L13)</f>
         <v/>
       </c>
-      <c r="M14" s="40">
+      <c r="M14" s="41">
         <f>SUM(M5:M13)</f>
         <v/>
       </c>
-      <c r="N14" s="40">
+      <c r="N14" s="41">
         <f>SUM(N5:N13)</f>
         <v/>
       </c>
-      <c r="O14" s="40">
+      <c r="O14" s="41">
         <f>SUM(O5:O13)</f>
         <v/>
       </c>
-      <c r="P14" s="40">
+      <c r="P14" s="41">
         <f>SUM(P5:P13)</f>
         <v/>
       </c>
-      <c r="Q14" s="40">
+      <c r="Q14" s="41">
         <f>SUM(Q5:Q13)</f>
         <v/>
       </c>
-      <c r="R14" s="40">
+      <c r="R14" s="41">
         <f>SUM(R5:R13)</f>
         <v/>
       </c>
-      <c r="S14" s="40">
+      <c r="S14" s="41">
         <f>SUM(S5:S13)</f>
         <v/>
       </c>
-      <c r="T14" s="40">
+      <c r="T14" s="41">
         <f>SUM(T5:T13)</f>
         <v/>
       </c>
-      <c r="U14" s="39" t="n"/>
-      <c r="V14" s="39" t="n"/>
+      <c r="U14" s="40" t="n"/>
+      <c r="V14" s="40" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -3956,495 +3996,495 @@
       </c>
     </row>
     <row r="4" ht="30" customHeight="1">
-      <c r="A4" s="6" t="inlineStr">
+      <c r="A4" s="7" t="inlineStr">
         <is>
           <t>Mês</t>
         </is>
       </c>
-      <c r="B4" s="6" t="inlineStr">
+      <c r="B4" s="7" t="inlineStr">
         <is>
           <t>Jurídico Plan.</t>
         </is>
       </c>
-      <c r="C4" s="6" t="inlineStr">
+      <c r="C4" s="7" t="inlineStr">
         <is>
           <t>Jurídico Real.</t>
         </is>
       </c>
-      <c r="D4" s="6" t="inlineStr">
+      <c r="D4" s="7" t="inlineStr">
         <is>
           <t>Total Plan.</t>
         </is>
       </c>
-      <c r="E4" s="6" t="inlineStr">
+      <c r="E4" s="7" t="inlineStr">
         <is>
           <t>Total Real.</t>
         </is>
       </c>
-      <c r="F4" s="6" t="inlineStr">
+      <c r="F4" s="7" t="inlineStr">
         <is>
           <t>Desvio do mês (R$)</t>
         </is>
       </c>
-      <c r="G4" s="6" t="inlineStr">
+      <c r="G4" s="7" t="inlineStr">
         <is>
           <t>Planejado acum.</t>
         </is>
       </c>
-      <c r="H4" s="6" t="inlineStr">
+      <c r="H4" s="7" t="inlineStr">
         <is>
           <t>Realizado acum.</t>
         </is>
       </c>
     </row>
     <row r="5" ht="20" customHeight="1">
-      <c r="A5" s="41" t="inlineStr">
+      <c r="A5" s="42" t="inlineStr">
         <is>
           <t>Jan/26</t>
         </is>
       </c>
-      <c r="B5" s="26">
+      <c r="B5" s="27">
         <f>SUMIFS(Planejado!$H$5:$H$13,Planejado!$B$5:$B$13,"Jurídico")</f>
         <v/>
       </c>
-      <c r="C5" s="26">
+      <c r="C5" s="27">
         <f>SUMIFS(Realizado!$H$5:$H$13,Realizado!$B$5:$B$13,"Jurídico")</f>
         <v/>
       </c>
-      <c r="D5" s="26">
+      <c r="D5" s="27">
         <f>B5</f>
         <v/>
       </c>
-      <c r="E5" s="26">
+      <c r="E5" s="27">
         <f>C5</f>
         <v/>
       </c>
-      <c r="F5" s="26">
+      <c r="F5" s="27">
         <f>E5-D5</f>
         <v/>
       </c>
-      <c r="G5" s="26">
+      <c r="G5" s="27">
         <f>SUM($D$5:D5)</f>
         <v/>
       </c>
-      <c r="H5" s="26">
+      <c r="H5" s="27">
         <f>SUM($E$5:E5)</f>
         <v/>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1">
-      <c r="A6" s="42" t="inlineStr">
+      <c r="A6" s="43" t="inlineStr">
         <is>
           <t>Fev/26</t>
         </is>
       </c>
-      <c r="B6" s="43">
+      <c r="B6" s="44">
         <f>SUMIFS(Planejado!$I$5:$I$13,Planejado!$B$5:$B$13,"Jurídico")</f>
         <v/>
       </c>
-      <c r="C6" s="43">
+      <c r="C6" s="44">
         <f>SUMIFS(Realizado!$I$5:$I$13,Realizado!$B$5:$B$13,"Jurídico")</f>
         <v/>
       </c>
-      <c r="D6" s="43">
+      <c r="D6" s="44">
         <f>B6</f>
         <v/>
       </c>
-      <c r="E6" s="43">
+      <c r="E6" s="44">
         <f>C6</f>
         <v/>
       </c>
-      <c r="F6" s="43">
+      <c r="F6" s="44">
         <f>E6-D6</f>
         <v/>
       </c>
-      <c r="G6" s="43">
+      <c r="G6" s="44">
         <f>SUM($D$5:D6)</f>
         <v/>
       </c>
-      <c r="H6" s="43">
+      <c r="H6" s="44">
         <f>SUM($E$5:E6)</f>
         <v/>
       </c>
     </row>
     <row r="7" ht="20" customHeight="1">
-      <c r="A7" s="41" t="inlineStr">
+      <c r="A7" s="42" t="inlineStr">
         <is>
           <t>Mar/26</t>
         </is>
       </c>
-      <c r="B7" s="26">
+      <c r="B7" s="27">
         <f>SUMIFS(Planejado!$J$5:$J$13,Planejado!$B$5:$B$13,"Jurídico")</f>
         <v/>
       </c>
-      <c r="C7" s="26">
+      <c r="C7" s="27">
         <f>SUMIFS(Realizado!$J$5:$J$13,Realizado!$B$5:$B$13,"Jurídico")</f>
         <v/>
       </c>
-      <c r="D7" s="26">
+      <c r="D7" s="27">
         <f>B7</f>
         <v/>
       </c>
-      <c r="E7" s="26">
+      <c r="E7" s="27">
         <f>C7</f>
         <v/>
       </c>
-      <c r="F7" s="26">
+      <c r="F7" s="27">
         <f>E7-D7</f>
         <v/>
       </c>
-      <c r="G7" s="26">
+      <c r="G7" s="27">
         <f>SUM($D$5:D7)</f>
         <v/>
       </c>
-      <c r="H7" s="26">
+      <c r="H7" s="27">
         <f>SUM($E$5:E7)</f>
         <v/>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1">
-      <c r="A8" s="42" t="inlineStr">
+      <c r="A8" s="43" t="inlineStr">
         <is>
           <t>Abr/26</t>
         </is>
       </c>
-      <c r="B8" s="43">
+      <c r="B8" s="44">
         <f>SUMIFS(Planejado!$K$5:$K$13,Planejado!$B$5:$B$13,"Jurídico")</f>
         <v/>
       </c>
-      <c r="C8" s="43">
+      <c r="C8" s="44">
         <f>SUMIFS(Realizado!$K$5:$K$13,Realizado!$B$5:$B$13,"Jurídico")</f>
         <v/>
       </c>
-      <c r="D8" s="43">
+      <c r="D8" s="44">
         <f>B8</f>
         <v/>
       </c>
-      <c r="E8" s="43">
+      <c r="E8" s="44">
         <f>C8</f>
         <v/>
       </c>
-      <c r="F8" s="43">
+      <c r="F8" s="44">
         <f>E8-D8</f>
         <v/>
       </c>
-      <c r="G8" s="43">
+      <c r="G8" s="44">
         <f>SUM($D$5:D8)</f>
         <v/>
       </c>
-      <c r="H8" s="43">
+      <c r="H8" s="44">
         <f>SUM($E$5:E8)</f>
         <v/>
       </c>
     </row>
     <row r="9" ht="20" customHeight="1">
-      <c r="A9" s="41" t="inlineStr">
+      <c r="A9" s="42" t="inlineStr">
         <is>
           <t>Mai/26</t>
         </is>
       </c>
-      <c r="B9" s="26">
+      <c r="B9" s="27">
         <f>SUMIFS(Planejado!$L$5:$L$13,Planejado!$B$5:$B$13,"Jurídico")</f>
         <v/>
       </c>
-      <c r="C9" s="26">
+      <c r="C9" s="27">
         <f>SUMIFS(Realizado!$L$5:$L$13,Realizado!$B$5:$B$13,"Jurídico")</f>
         <v/>
       </c>
-      <c r="D9" s="26">
+      <c r="D9" s="27">
         <f>B9</f>
         <v/>
       </c>
-      <c r="E9" s="26">
+      <c r="E9" s="27">
         <f>C9</f>
         <v/>
       </c>
-      <c r="F9" s="26">
+      <c r="F9" s="27">
         <f>E9-D9</f>
         <v/>
       </c>
-      <c r="G9" s="26">
+      <c r="G9" s="27">
         <f>SUM($D$5:D9)</f>
         <v/>
       </c>
-      <c r="H9" s="26">
+      <c r="H9" s="27">
         <f>SUM($E$5:E9)</f>
         <v/>
       </c>
     </row>
     <row r="10" ht="20" customHeight="1">
-      <c r="A10" s="42" t="inlineStr">
+      <c r="A10" s="43" t="inlineStr">
         <is>
           <t>Jun/26</t>
         </is>
       </c>
-      <c r="B10" s="43">
+      <c r="B10" s="44">
         <f>SUMIFS(Planejado!$M$5:$M$13,Planejado!$B$5:$B$13,"Jurídico")</f>
         <v/>
       </c>
-      <c r="C10" s="43">
+      <c r="C10" s="44">
         <f>SUMIFS(Realizado!$M$5:$M$13,Realizado!$B$5:$B$13,"Jurídico")</f>
         <v/>
       </c>
-      <c r="D10" s="43">
+      <c r="D10" s="44">
         <f>B10</f>
         <v/>
       </c>
-      <c r="E10" s="43">
+      <c r="E10" s="44">
         <f>C10</f>
         <v/>
       </c>
-      <c r="F10" s="43">
+      <c r="F10" s="44">
         <f>E10-D10</f>
         <v/>
       </c>
-      <c r="G10" s="43">
+      <c r="G10" s="44">
         <f>SUM($D$5:D10)</f>
         <v/>
       </c>
-      <c r="H10" s="43">
+      <c r="H10" s="44">
         <f>SUM($E$5:E10)</f>
         <v/>
       </c>
     </row>
     <row r="11" ht="20" customHeight="1">
-      <c r="A11" s="41" t="inlineStr">
+      <c r="A11" s="42" t="inlineStr">
         <is>
           <t>Jul/26</t>
         </is>
       </c>
-      <c r="B11" s="26">
+      <c r="B11" s="27">
         <f>SUMIFS(Planejado!$N$5:$N$13,Planejado!$B$5:$B$13,"Jurídico")</f>
         <v/>
       </c>
-      <c r="C11" s="26">
+      <c r="C11" s="27">
         <f>SUMIFS(Realizado!$N$5:$N$13,Realizado!$B$5:$B$13,"Jurídico")</f>
         <v/>
       </c>
-      <c r="D11" s="26">
+      <c r="D11" s="27">
         <f>B11</f>
         <v/>
       </c>
-      <c r="E11" s="26">
+      <c r="E11" s="27">
         <f>C11</f>
         <v/>
       </c>
-      <c r="F11" s="26">
+      <c r="F11" s="27">
         <f>E11-D11</f>
         <v/>
       </c>
-      <c r="G11" s="26">
+      <c r="G11" s="27">
         <f>SUM($D$5:D11)</f>
         <v/>
       </c>
-      <c r="H11" s="26">
+      <c r="H11" s="27">
         <f>SUM($E$5:E11)</f>
         <v/>
       </c>
     </row>
     <row r="12" ht="20" customHeight="1">
-      <c r="A12" s="42" t="inlineStr">
+      <c r="A12" s="43" t="inlineStr">
         <is>
           <t>Ago/26</t>
         </is>
       </c>
-      <c r="B12" s="43">
+      <c r="B12" s="44">
         <f>SUMIFS(Planejado!$O$5:$O$13,Planejado!$B$5:$B$13,"Jurídico")</f>
         <v/>
       </c>
-      <c r="C12" s="43">
+      <c r="C12" s="44">
         <f>SUMIFS(Realizado!$O$5:$O$13,Realizado!$B$5:$B$13,"Jurídico")</f>
         <v/>
       </c>
-      <c r="D12" s="43">
+      <c r="D12" s="44">
         <f>B12</f>
         <v/>
       </c>
-      <c r="E12" s="43">
+      <c r="E12" s="44">
         <f>C12</f>
         <v/>
       </c>
-      <c r="F12" s="43">
+      <c r="F12" s="44">
         <f>E12-D12</f>
         <v/>
       </c>
-      <c r="G12" s="43">
+      <c r="G12" s="44">
         <f>SUM($D$5:D12)</f>
         <v/>
       </c>
-      <c r="H12" s="43">
+      <c r="H12" s="44">
         <f>SUM($E$5:E12)</f>
         <v/>
       </c>
     </row>
     <row r="13" ht="20" customHeight="1">
-      <c r="A13" s="41" t="inlineStr">
+      <c r="A13" s="42" t="inlineStr">
         <is>
           <t>Set/26</t>
         </is>
       </c>
-      <c r="B13" s="26">
+      <c r="B13" s="27">
         <f>SUMIFS(Planejado!$P$5:$P$13,Planejado!$B$5:$B$13,"Jurídico")</f>
         <v/>
       </c>
-      <c r="C13" s="26">
+      <c r="C13" s="27">
         <f>SUMIFS(Realizado!$P$5:$P$13,Realizado!$B$5:$B$13,"Jurídico")</f>
         <v/>
       </c>
-      <c r="D13" s="26">
+      <c r="D13" s="27">
         <f>B13</f>
         <v/>
       </c>
-      <c r="E13" s="26">
+      <c r="E13" s="27">
         <f>C13</f>
         <v/>
       </c>
-      <c r="F13" s="26">
+      <c r="F13" s="27">
         <f>E13-D13</f>
         <v/>
       </c>
-      <c r="G13" s="26">
+      <c r="G13" s="27">
         <f>SUM($D$5:D13)</f>
         <v/>
       </c>
-      <c r="H13" s="26">
+      <c r="H13" s="27">
         <f>SUM($E$5:E13)</f>
         <v/>
       </c>
     </row>
     <row r="14" ht="20" customHeight="1">
-      <c r="A14" s="42" t="inlineStr">
+      <c r="A14" s="43" t="inlineStr">
         <is>
           <t>Out/26</t>
         </is>
       </c>
-      <c r="B14" s="43">
+      <c r="B14" s="44">
         <f>SUMIFS(Planejado!$Q$5:$Q$13,Planejado!$B$5:$B$13,"Jurídico")</f>
         <v/>
       </c>
-      <c r="C14" s="43">
+      <c r="C14" s="44">
         <f>SUMIFS(Realizado!$Q$5:$Q$13,Realizado!$B$5:$B$13,"Jurídico")</f>
         <v/>
       </c>
-      <c r="D14" s="43">
+      <c r="D14" s="44">
         <f>B14</f>
         <v/>
       </c>
-      <c r="E14" s="43">
+      <c r="E14" s="44">
         <f>C14</f>
         <v/>
       </c>
-      <c r="F14" s="43">
+      <c r="F14" s="44">
         <f>E14-D14</f>
         <v/>
       </c>
-      <c r="G14" s="43">
+      <c r="G14" s="44">
         <f>SUM($D$5:D14)</f>
         <v/>
       </c>
-      <c r="H14" s="43">
+      <c r="H14" s="44">
         <f>SUM($E$5:E14)</f>
         <v/>
       </c>
     </row>
     <row r="15" ht="20" customHeight="1">
-      <c r="A15" s="41" t="inlineStr">
+      <c r="A15" s="42" t="inlineStr">
         <is>
           <t>Nov/26</t>
         </is>
       </c>
-      <c r="B15" s="26">
+      <c r="B15" s="27">
         <f>SUMIFS(Planejado!$R$5:$R$13,Planejado!$B$5:$B$13,"Jurídico")</f>
         <v/>
       </c>
-      <c r="C15" s="26">
+      <c r="C15" s="27">
         <f>SUMIFS(Realizado!$R$5:$R$13,Realizado!$B$5:$B$13,"Jurídico")</f>
         <v/>
       </c>
-      <c r="D15" s="26">
+      <c r="D15" s="27">
         <f>B15</f>
         <v/>
       </c>
-      <c r="E15" s="26">
+      <c r="E15" s="27">
         <f>C15</f>
         <v/>
       </c>
-      <c r="F15" s="26">
+      <c r="F15" s="27">
         <f>E15-D15</f>
         <v/>
       </c>
-      <c r="G15" s="26">
+      <c r="G15" s="27">
         <f>SUM($D$5:D15)</f>
         <v/>
       </c>
-      <c r="H15" s="26">
+      <c r="H15" s="27">
         <f>SUM($E$5:E15)</f>
         <v/>
       </c>
     </row>
     <row r="16" ht="20" customHeight="1">
-      <c r="A16" s="42" t="inlineStr">
+      <c r="A16" s="43" t="inlineStr">
         <is>
           <t>Dez/26</t>
         </is>
       </c>
-      <c r="B16" s="43">
+      <c r="B16" s="44">
         <f>SUMIFS(Planejado!$S$5:$S$13,Planejado!$B$5:$B$13,"Jurídico")</f>
         <v/>
       </c>
-      <c r="C16" s="43">
+      <c r="C16" s="44">
         <f>SUMIFS(Realizado!$S$5:$S$13,Realizado!$B$5:$B$13,"Jurídico")</f>
         <v/>
       </c>
-      <c r="D16" s="43">
+      <c r="D16" s="44">
         <f>B16</f>
         <v/>
       </c>
-      <c r="E16" s="43">
+      <c r="E16" s="44">
         <f>C16</f>
         <v/>
       </c>
-      <c r="F16" s="43">
+      <c r="F16" s="44">
         <f>E16-D16</f>
         <v/>
       </c>
-      <c r="G16" s="43">
+      <c r="G16" s="44">
         <f>SUM($D$5:D16)</f>
         <v/>
       </c>
-      <c r="H16" s="43">
+      <c r="H16" s="44">
         <f>SUM($E$5:E16)</f>
         <v/>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="30" t="inlineStr">
+      <c r="A17" s="31" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B17" s="31">
+      <c r="B17" s="32">
         <f>SUM(B5:B16)</f>
         <v/>
       </c>
-      <c r="C17" s="31">
+      <c r="C17" s="32">
         <f>SUM(C5:C16)</f>
         <v/>
       </c>
-      <c r="D17" s="31">
+      <c r="D17" s="32">
         <f>SUM(D5:D16)</f>
         <v/>
       </c>
-      <c r="E17" s="31">
+      <c r="E17" s="32">
         <f>SUM(E5:E16)</f>
         <v/>
       </c>
-      <c r="F17" s="31">
+      <c r="F17" s="32">
         <f>SUM(F5:F16)</f>
         <v/>
       </c>
-      <c r="G17" s="30" t="n"/>
-      <c r="H17" s="30" t="n"/>
+      <c r="G17" s="31" t="n"/>
+      <c r="H17" s="31" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -4498,253 +4538,253 @@
       </c>
     </row>
     <row r="4" ht="30" customHeight="1">
-      <c r="A4" s="6" t="inlineStr">
+      <c r="A4" s="7" t="inlineStr">
         <is>
           <t>Plano de Contas</t>
         </is>
       </c>
-      <c r="B4" s="6" t="inlineStr">
+      <c r="B4" s="7" t="inlineStr">
         <is>
           <t>Jurídico — Plan.</t>
         </is>
       </c>
-      <c r="C4" s="6" t="inlineStr">
+      <c r="C4" s="7" t="inlineStr">
         <is>
           <t>Jurídico — Real.</t>
         </is>
       </c>
-      <c r="D4" s="6" t="inlineStr">
+      <c r="D4" s="7" t="inlineStr">
         <is>
           <t>Total Planejado acum.</t>
         </is>
       </c>
-      <c r="E4" s="6" t="inlineStr">
+      <c r="E4" s="7" t="inlineStr">
         <is>
           <t>Total Realizado acum.</t>
         </is>
       </c>
-      <c r="F4" s="6" t="inlineStr">
+      <c r="F4" s="7" t="inlineStr">
         <is>
           <t>Desvio (R$)</t>
         </is>
       </c>
-      <c r="G4" s="6" t="inlineStr">
+      <c r="G4" s="7" t="inlineStr">
         <is>
           <t>Desvio (%)</t>
         </is>
       </c>
-      <c r="H4" s="6" t="inlineStr">
+      <c r="H4" s="7" t="inlineStr">
         <is>
           <t>Orçado do ano</t>
         </is>
       </c>
     </row>
     <row r="5" ht="20" customHeight="1">
-      <c r="A5" s="44" t="inlineStr">
+      <c r="A5" s="45" t="inlineStr">
         <is>
           <t>Pessoal - CLT</t>
         </is>
       </c>
-      <c r="B5" s="26">
+      <c r="B5" s="27">
         <f>SUMIFS(Comparativo!$I$6:$I$14,Comparativo!$E$6:$E$14,$A5,Comparativo!$B$6:$B$14,"Jurídico")</f>
         <v/>
       </c>
-      <c r="C5" s="26">
+      <c r="C5" s="27">
         <f>SUMIFS(Comparativo!$J$6:$J$14,Comparativo!$E$6:$E$14,$A5,Comparativo!$B$6:$B$14,"Jurídico")</f>
         <v/>
       </c>
-      <c r="D5" s="26">
+      <c r="D5" s="27">
         <f>B5</f>
         <v/>
       </c>
-      <c r="E5" s="26">
+      <c r="E5" s="27">
         <f>C5</f>
         <v/>
       </c>
-      <c r="F5" s="26">
+      <c r="F5" s="27">
         <f>E5-D5</f>
         <v/>
       </c>
-      <c r="G5" s="45">
+      <c r="G5" s="46">
         <f>IFERROR(F5/D5,"")</f>
         <v/>
       </c>
-      <c r="H5" s="26">
+      <c r="H5" s="27">
         <f>SUMIFS(Planejado!$T$5:$T$13,Planejado!$G$5:$G$13,$A5)</f>
         <v/>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1">
-      <c r="A6" s="46" t="inlineStr">
+      <c r="A6" s="47" t="inlineStr">
         <is>
           <t>Pessoal - PJ</t>
         </is>
       </c>
-      <c r="B6" s="43">
+      <c r="B6" s="44">
         <f>SUMIFS(Comparativo!$I$6:$I$14,Comparativo!$E$6:$E$14,$A6,Comparativo!$B$6:$B$14,"Jurídico")</f>
         <v/>
       </c>
-      <c r="C6" s="43">
+      <c r="C6" s="44">
         <f>SUMIFS(Comparativo!$J$6:$J$14,Comparativo!$E$6:$E$14,$A6,Comparativo!$B$6:$B$14,"Jurídico")</f>
         <v/>
       </c>
-      <c r="D6" s="43">
+      <c r="D6" s="44">
         <f>B6</f>
         <v/>
       </c>
-      <c r="E6" s="43">
+      <c r="E6" s="44">
         <f>C6</f>
         <v/>
       </c>
-      <c r="F6" s="43">
+      <c r="F6" s="44">
         <f>E6-D6</f>
         <v/>
       </c>
-      <c r="G6" s="47">
+      <c r="G6" s="48">
         <f>IFERROR(F6/D6,"")</f>
         <v/>
       </c>
-      <c r="H6" s="43">
+      <c r="H6" s="44">
         <f>SUMIFS(Planejado!$T$5:$T$13,Planejado!$G$5:$G$13,$A6)</f>
         <v/>
       </c>
     </row>
     <row r="7" ht="20" customHeight="1">
-      <c r="A7" s="44" t="inlineStr">
+      <c r="A7" s="45" t="inlineStr">
         <is>
           <t>Licenças de Softwares</t>
         </is>
       </c>
-      <c r="B7" s="26">
+      <c r="B7" s="27">
         <f>SUMIFS(Comparativo!$I$6:$I$14,Comparativo!$E$6:$E$14,$A7,Comparativo!$B$6:$B$14,"Jurídico")</f>
         <v/>
       </c>
-      <c r="C7" s="26">
+      <c r="C7" s="27">
         <f>SUMIFS(Comparativo!$J$6:$J$14,Comparativo!$E$6:$E$14,$A7,Comparativo!$B$6:$B$14,"Jurídico")</f>
         <v/>
       </c>
-      <c r="D7" s="26">
+      <c r="D7" s="27">
         <f>B7</f>
         <v/>
       </c>
-      <c r="E7" s="26">
+      <c r="E7" s="27">
         <f>C7</f>
         <v/>
       </c>
-      <c r="F7" s="26">
+      <c r="F7" s="27">
         <f>E7-D7</f>
         <v/>
       </c>
-      <c r="G7" s="45">
+      <c r="G7" s="46">
         <f>IFERROR(F7/D7,"")</f>
         <v/>
       </c>
-      <c r="H7" s="26">
+      <c r="H7" s="27">
         <f>SUMIFS(Planejado!$T$5:$T$13,Planejado!$G$5:$G$13,$A7)</f>
         <v/>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1">
-      <c r="A8" s="46" t="inlineStr">
+      <c r="A8" s="47" t="inlineStr">
         <is>
           <t>Custeio de Treinamento</t>
         </is>
       </c>
-      <c r="B8" s="43">
+      <c r="B8" s="44">
         <f>SUMIFS(Comparativo!$I$6:$I$14,Comparativo!$E$6:$E$14,$A8,Comparativo!$B$6:$B$14,"Jurídico")</f>
         <v/>
       </c>
-      <c r="C8" s="43">
+      <c r="C8" s="44">
         <f>SUMIFS(Comparativo!$J$6:$J$14,Comparativo!$E$6:$E$14,$A8,Comparativo!$B$6:$B$14,"Jurídico")</f>
         <v/>
       </c>
-      <c r="D8" s="43">
+      <c r="D8" s="44">
         <f>B8</f>
         <v/>
       </c>
-      <c r="E8" s="43">
+      <c r="E8" s="44">
         <f>C8</f>
         <v/>
       </c>
-      <c r="F8" s="43">
+      <c r="F8" s="44">
         <f>E8-D8</f>
         <v/>
       </c>
-      <c r="G8" s="47">
+      <c r="G8" s="48">
         <f>IFERROR(F8/D8,"")</f>
         <v/>
       </c>
-      <c r="H8" s="43">
+      <c r="H8" s="44">
         <f>SUMIFS(Planejado!$T$5:$T$13,Planejado!$G$5:$G$13,$A8)</f>
         <v/>
       </c>
     </row>
     <row r="9" ht="20" customHeight="1">
-      <c r="A9" s="44" t="inlineStr">
+      <c r="A9" s="45" t="inlineStr">
         <is>
           <t>Prêmios</t>
         </is>
       </c>
-      <c r="B9" s="26">
+      <c r="B9" s="27">
         <f>SUMIFS(Comparativo!$I$6:$I$14,Comparativo!$E$6:$E$14,$A9,Comparativo!$B$6:$B$14,"Jurídico")</f>
         <v/>
       </c>
-      <c r="C9" s="26">
+      <c r="C9" s="27">
         <f>SUMIFS(Comparativo!$J$6:$J$14,Comparativo!$E$6:$E$14,$A9,Comparativo!$B$6:$B$14,"Jurídico")</f>
         <v/>
       </c>
-      <c r="D9" s="26">
+      <c r="D9" s="27">
         <f>B9</f>
         <v/>
       </c>
-      <c r="E9" s="26">
+      <c r="E9" s="27">
         <f>C9</f>
         <v/>
       </c>
-      <c r="F9" s="26">
+      <c r="F9" s="27">
         <f>E9-D9</f>
         <v/>
       </c>
-      <c r="G9" s="45">
+      <c r="G9" s="46">
         <f>IFERROR(F9/D9,"")</f>
         <v/>
       </c>
-      <c r="H9" s="26">
+      <c r="H9" s="27">
         <f>SUMIFS(Planejado!$T$5:$T$13,Planejado!$G$5:$G$13,$A9)</f>
         <v/>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="30" t="inlineStr">
+      <c r="A10" s="31" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B10" s="31">
+      <c r="B10" s="32">
         <f>SUM(B5:B9)</f>
         <v/>
       </c>
-      <c r="C10" s="31">
+      <c r="C10" s="32">
         <f>SUM(C5:C9)</f>
         <v/>
       </c>
-      <c r="D10" s="31">
+      <c r="D10" s="32">
         <f>SUM(D5:D9)</f>
         <v/>
       </c>
-      <c r="E10" s="31">
+      <c r="E10" s="32">
         <f>SUM(E5:E9)</f>
         <v/>
       </c>
-      <c r="F10" s="31">
+      <c r="F10" s="32">
         <f>SUM(F5:F9)</f>
         <v/>
       </c>
-      <c r="G10" s="48">
+      <c r="G10" s="49">
         <f>IFERROR(F10/D10,"")</f>
         <v/>
       </c>
-      <c r="H10" s="31">
+      <c r="H10" s="32">
         <f>SUM(H5:H9)</f>
         <v/>
       </c>
@@ -4798,320 +4838,320 @@
       </c>
     </row>
     <row r="4" ht="30" customHeight="1">
-      <c r="A4" s="6" t="inlineStr">
+      <c r="A4" s="7" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B4" s="6" t="inlineStr">
+      <c r="B4" s="7" t="inlineStr">
         <is>
           <t>Tema</t>
         </is>
       </c>
-      <c r="C4" s="6" t="inlineStr">
+      <c r="C4" s="7" t="inlineStr">
         <is>
           <t>O que está em aberto</t>
         </is>
       </c>
-      <c r="D4" s="6" t="inlineStr">
+      <c r="D4" s="7" t="inlineStr">
         <is>
           <t>Impacto no comparativo</t>
         </is>
       </c>
-      <c r="E4" s="6" t="inlineStr">
+      <c r="E4" s="7" t="inlineStr">
         <is>
           <t>Responsável</t>
         </is>
       </c>
-      <c r="F4" s="6" t="inlineStr">
+      <c r="F4" s="7" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
     </row>
     <row r="5" ht="58" customHeight="1">
-      <c r="A5" s="49" t="inlineStr">
+      <c r="A5" s="50" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="B5" s="50" t="inlineStr">
-        <is>
-          <t>Custo total da Geovanna — A LANÇAR</t>
-        </is>
-      </c>
-      <c r="C5" s="50" t="inlineStr">
-        <is>
-          <t>O planejado dela é R$ 4.825,52/mês, que é o custo total orçado na ficha (salário + encargos de folha + benefícios). O dado disponível hoje é só o salário bruto, R$ 2.886,91/mês. O realizado está em branco.</t>
-        </is>
-      </c>
-      <c r="D5" s="50" t="inlineStr">
-        <is>
-          <t>Lançar só o bruto contra um orçado de custo total mostraria economia de R$ 1.938,61/mês que não existe. Peça ao RH o custo total mensal dela, ou o bruto mais os encargos para somar antes de lançar.</t>
-        </is>
-      </c>
-      <c r="E5" s="50" t="inlineStr">
+      <c r="B5" s="51" t="inlineStr">
+        <is>
+          <t>Geovanna — realizado em base diferente do orçado</t>
+        </is>
+      </c>
+      <c r="C5" s="51" t="inlineStr">
+        <is>
+          <t>O planejado dela é R$ 4.825,52/mês, que é o CUSTO TOTAL orçado na ficha (salário + encargos de folha + benefícios). O realizado lançado é o SALÁRIO BRUTO, R$ 2.886,91/mês, confirmado sem alteração no ano. São bases diferentes.</t>
+        </is>
+      </c>
+      <c r="D5" s="51" t="inlineStr">
+        <is>
+          <t>O desvio desta linha (−R$ 1.938,61/mês, −R$ 13.570,24 no acumulado jan–jul) NÃO é economia: é o encargo que falta do lado do realizado. Para fechar, peça ao RH o custo total mensal dela — ou o percentual de encargos da empresa, que dá para calcular a partir do bruto.</t>
+        </is>
+      </c>
+      <c r="E5" s="51" t="inlineStr">
         <is>
           <t>Cristiane + RH</t>
         </is>
       </c>
-      <c r="F5" s="51" t="inlineStr">
+      <c r="F5" s="52" t="inlineStr">
+        <is>
+          <t>BASE DIFERENTE</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="58" customHeight="1">
+      <c r="A6" s="53" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B6" s="54" t="inlineStr">
+        <is>
+          <t>Aumento da Thamar em abr/26</t>
+        </is>
+      </c>
+      <c r="C6" s="54" t="inlineStr">
+        <is>
+          <t>Recebia R$ 4.500/mês de jan a mar, abaixo dos R$ 5.000 orçados. Em abr/26 teve aumento de R$ 1.000 e passou a R$ 5.500, acima do orçado. O planejado foi mantido em R$ 5.000 nos sete meses fechados (para o desvio ficar visível) e revisado para R$ 5.500 de ago a dez.</t>
+        </is>
+      </c>
+      <c r="D6" s="54" t="inlineStr">
+        <is>
+          <t>No acumulado jan–jul o efeito líquido é de apenas R$ 500 acima do orçado (−R$ 1.500 em jan–mar, +R$ 2.000 em abr–jul), e mais R$ 2.500 previstos até dezembro. Ao contrário do aumento do Vinicius, este estourou o orçado: não havia folga na linha dela.</t>
+        </is>
+      </c>
+      <c r="E6" s="54" t="inlineStr">
+        <is>
+          <t>Cristiane</t>
+        </is>
+      </c>
+      <c r="F6" s="55" t="inlineStr">
+        <is>
+          <t>APLICADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="50" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B7" s="51" t="inlineStr">
+        <is>
+          <t>Jusbrasil 30% acima do orçado</t>
+        </is>
+      </c>
+      <c r="C7" s="51" t="inlineStr">
+        <is>
+          <t>Orçado R$ 104,90/mês, realizado R$ 136,00/mês em mai, jun e jul.</t>
+        </is>
+      </c>
+      <c r="D7" s="51" t="inlineStr">
+        <is>
+          <t>Menor desvio em reais (R$ 31,10/mês), mas o maior em percentual. Vale conferir se houve reajuste contratual ou mudança de plano.</t>
+        </is>
+      </c>
+      <c r="E7" s="51" t="inlineStr">
+        <is>
+          <t>Cristiane</t>
+        </is>
+      </c>
+      <c r="F7" s="56" t="inlineStr">
+        <is>
+          <t>EM ABERTO</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="58" customHeight="1">
+      <c r="A8" s="53" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="B8" s="54" t="inlineStr">
+        <is>
+          <t>Bonificação de ago/26 do Jurídico</t>
+        </is>
+      </c>
+      <c r="C8" s="54" t="inlineStr">
+        <is>
+          <t>Estão orçados R$ 10.293,60 em agosto e R$ 12.867,00 em dezembro. O realizado de agosto ainda não foi informado.</t>
+        </is>
+      </c>
+      <c r="D8" s="54" t="inlineStr">
+        <is>
+          <t>É a maior despesa isolada do Jurídico no segundo semestre.</t>
+        </is>
+      </c>
+      <c r="E8" s="54" t="inlineStr">
+        <is>
+          <t>Cristiane</t>
+        </is>
+      </c>
+      <c r="F8" s="56" t="inlineStr">
+        <is>
+          <t>EM ABERTO</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="58" customHeight="1">
+      <c r="A9" s="50" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="B9" s="51" t="inlineStr">
+        <is>
+          <t>Planejado de jan a abr — CONFERIR</t>
+        </is>
+      </c>
+      <c r="C9" s="51" t="inlineStr">
+        <is>
+          <t>O 1º quadrimestre foi preenchido replicando os valores mensais conhecidos, porque a ficha original só trazia o grid de mai a dez. Exceções tratadas: Jonathan começa em abr, Thamar a R$ 5.000 (pré-reajuste), Vinicius com bruto de R$ 2.570,52 e Adapta a R$ 1.300 (valor até jun).</t>
+        </is>
+      </c>
+      <c r="D9" s="51" t="inlineStr">
+        <is>
+          <t>Se algum contrato tinha valor diferente no 1º quadrimestre, ou se houve bonificação nesse período, o planejado de jan a abr precisa ser corrigido antes de comparar com o realizado.</t>
+        </is>
+      </c>
+      <c r="E9" s="51" t="inlineStr">
+        <is>
+          <t>Cristiane</t>
+        </is>
+      </c>
+      <c r="F9" s="57" t="inlineStr">
+        <is>
+          <t>CONFERIR</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="58" customHeight="1">
+      <c r="A10" s="53" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="B10" s="54" t="inlineStr">
+        <is>
+          <t>Realizado de jan a abr — A LANÇAR</t>
+        </is>
+      </c>
+      <c r="C10" s="54" t="inlineStr">
+        <is>
+          <t>As colunas de jan a abr estão em branco na aba Realizado. Só mai, jun e jul foram informados.</t>
+        </is>
+      </c>
+      <c r="D10" s="54" t="inlineStr">
+        <is>
+          <t>São 4 dos 7 meses já fechados do ano. Sem eles o acumulado e o Painel refletem menos da metade do período decorrido.</t>
+        </is>
+      </c>
+      <c r="E10" s="54" t="inlineStr">
+        <is>
+          <t>Cristiane</t>
+        </is>
+      </c>
+      <c r="F10" s="52" t="inlineStr">
         <is>
           <t>A LANÇAR</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="58" customHeight="1">
-      <c r="A6" s="52" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="B6" s="53" t="inlineStr">
-        <is>
-          <t>Aumento da Thamar em abr/26</t>
-        </is>
-      </c>
-      <c r="C6" s="53" t="inlineStr">
-        <is>
-          <t>Recebia R$ 4.500/mês de jan a mar, abaixo dos R$ 5.000 orçados. Em abr/26 teve aumento de R$ 1.000 e passou a R$ 5.500, acima do orçado. O planejado foi mantido em R$ 5.000 nos sete meses fechados (para o desvio ficar visível) e revisado para R$ 5.500 de ago a dez.</t>
-        </is>
-      </c>
-      <c r="D6" s="53" t="inlineStr">
-        <is>
-          <t>No acumulado jan–jul o efeito líquido é de apenas R$ 500 acima do orçado (−R$ 1.500 em jan–mar, +R$ 2.000 em abr–jul), e mais R$ 2.500 previstos até dezembro. Ao contrário do aumento do Vinicius, este estourou o orçado: não havia folga na linha dela.</t>
-        </is>
-      </c>
-      <c r="E6" s="53" t="inlineStr">
+    <row r="11" ht="58" customHeight="1">
+      <c r="A11" s="50" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B11" s="51" t="inlineStr">
+        <is>
+          <t>Origem do valor realizado</t>
+        </is>
+      </c>
+      <c r="C11" s="51" t="inlineStr">
+        <is>
+          <t>Ainda não definido se o realizado virá de lançamento manual, de relatório do financeiro/ERP por centro de custo, ou misto. Até aqui os números vieram informados pela gestora.</t>
+        </is>
+      </c>
+      <c r="D11" s="51" t="inlineStr">
+        <is>
+          <t>Sem fonte definida o realizado pode divergir da contabilidade e o comparativo perde valor na apresentação à diretoria.</t>
+        </is>
+      </c>
+      <c r="E11" s="51" t="inlineStr">
+        <is>
+          <t>Cristiane + Financeiro</t>
+        </is>
+      </c>
+      <c r="F11" s="56" t="inlineStr">
+        <is>
+          <t>EM ABERTO</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="58" customHeight="1">
+      <c r="A12" s="53" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B12" s="54" t="inlineStr">
+        <is>
+          <t>Jusfy x Astrea</t>
+        </is>
+      </c>
+      <c r="C12" s="54" t="inlineStr">
+        <is>
+          <t>O risco era pagar os dois em paralelo. O realizado de mai–jul mostra Astrea em R$ 0 (cancelado) e Jusfy em R$ 0 (ainda não iniciado) — no momento não há custo de nenhum dos dois.</t>
+        </is>
+      </c>
+      <c r="D12" s="54" t="inlineStr">
+        <is>
+          <t>Economia de R$ 212,07/mês enquanto durar. Falta decidir se o Jusfy entra e quando, para ajustar o planejado dos meses seguintes.</t>
+        </is>
+      </c>
+      <c r="E12" s="54" t="inlineStr">
         <is>
           <t>Cristiane</t>
         </is>
       </c>
-      <c r="F6" s="54" t="inlineStr">
-        <is>
-          <t>APLICADO</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="58" customHeight="1">
-      <c r="A7" s="49" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="B7" s="50" t="inlineStr">
-        <is>
-          <t>Jusbrasil 30% acima do orçado</t>
-        </is>
-      </c>
-      <c r="C7" s="50" t="inlineStr">
-        <is>
-          <t>Orçado R$ 104,90/mês, realizado R$ 136,00/mês em mai, jun e jul.</t>
-        </is>
-      </c>
-      <c r="D7" s="50" t="inlineStr">
-        <is>
-          <t>Menor desvio em reais (R$ 31,10/mês), mas o maior em percentual. Vale conferir se houve reajuste contratual ou mudança de plano.</t>
-        </is>
-      </c>
-      <c r="E7" s="50" t="inlineStr">
-        <is>
-          <t>Cristiane</t>
-        </is>
-      </c>
-      <c r="F7" s="55" t="inlineStr">
-        <is>
-          <t>EM ABERTO</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="58" customHeight="1">
-      <c r="A8" s="52" t="inlineStr">
-        <is>
-          <t>E</t>
-        </is>
-      </c>
-      <c r="B8" s="53" t="inlineStr">
-        <is>
-          <t>Bonificação de ago/26 do Jurídico</t>
-        </is>
-      </c>
-      <c r="C8" s="53" t="inlineStr">
-        <is>
-          <t>Estão orçados R$ 10.293,60 em agosto e R$ 12.867,00 em dezembro. O realizado de agosto ainda não foi informado.</t>
-        </is>
-      </c>
-      <c r="D8" s="53" t="inlineStr">
-        <is>
-          <t>É a maior despesa isolada do Jurídico no segundo semestre.</t>
-        </is>
-      </c>
-      <c r="E8" s="53" t="inlineStr">
-        <is>
-          <t>Cristiane</t>
-        </is>
-      </c>
-      <c r="F8" s="55" t="inlineStr">
-        <is>
-          <t>EM ABERTO</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="58" customHeight="1">
-      <c r="A9" s="49" t="inlineStr">
-        <is>
-          <t>H</t>
-        </is>
-      </c>
-      <c r="B9" s="50" t="inlineStr">
-        <is>
-          <t>Planejado de jan a abr — CONFERIR</t>
-        </is>
-      </c>
-      <c r="C9" s="50" t="inlineStr">
-        <is>
-          <t>O 1º quadrimestre foi preenchido replicando os valores mensais conhecidos, porque a ficha original só trazia o grid de mai a dez. Exceções tratadas: Jonathan começa em abr, Thamar a R$ 5.000 (pré-reajuste), Vinicius com bruto de R$ 2.570,52 e Adapta a R$ 1.300 (valor até jun).</t>
-        </is>
-      </c>
-      <c r="D9" s="50" t="inlineStr">
-        <is>
-          <t>Se algum contrato tinha valor diferente no 1º quadrimestre, ou se houve bonificação nesse período, o planejado de jan a abr precisa ser corrigido antes de comparar com o realizado.</t>
-        </is>
-      </c>
-      <c r="E9" s="50" t="inlineStr">
-        <is>
-          <t>Cristiane</t>
-        </is>
-      </c>
-      <c r="F9" s="56" t="inlineStr">
-        <is>
-          <t>CONFERIR</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="58" customHeight="1">
-      <c r="A10" s="52" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="B10" s="53" t="inlineStr">
-        <is>
-          <t>Realizado de jan a abr — A LANÇAR</t>
-        </is>
-      </c>
-      <c r="C10" s="53" t="inlineStr">
-        <is>
-          <t>As colunas de jan a abr estão em branco na aba Realizado. Só mai, jun e jul foram informados.</t>
-        </is>
-      </c>
-      <c r="D10" s="53" t="inlineStr">
-        <is>
-          <t>São 4 dos 7 meses já fechados do ano. Sem eles o acumulado e o Painel refletem menos da metade do período decorrido.</t>
-        </is>
-      </c>
-      <c r="E10" s="53" t="inlineStr">
-        <is>
-          <t>Cristiane</t>
-        </is>
-      </c>
-      <c r="F10" s="51" t="inlineStr">
-        <is>
-          <t>A LANÇAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="58" customHeight="1">
-      <c r="A11" s="49" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="B11" s="50" t="inlineStr">
-        <is>
-          <t>Origem do valor realizado</t>
-        </is>
-      </c>
-      <c r="C11" s="50" t="inlineStr">
-        <is>
-          <t>Ainda não definido se o realizado virá de lançamento manual, de relatório do financeiro/ERP por centro de custo, ou misto. Até aqui os números vieram informados pela gestora.</t>
-        </is>
-      </c>
-      <c r="D11" s="50" t="inlineStr">
-        <is>
-          <t>Sem fonte definida o realizado pode divergir da contabilidade e o comparativo perde valor na apresentação à diretoria.</t>
-        </is>
-      </c>
-      <c r="E11" s="50" t="inlineStr">
+      <c r="F12" s="55" t="inlineStr">
+        <is>
+          <t>RESOLVIDO</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="58" customHeight="1">
+      <c r="A13" s="50" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B13" s="51" t="inlineStr">
+        <is>
+          <t>Critério de competência x caixa</t>
+        </is>
+      </c>
+      <c r="C13" s="51" t="inlineStr">
+        <is>
+          <t>Definir se o realizado será lançado pela data de pagamento (caixa) ou pelo mês de referência da despesa (competência).</t>
+        </is>
+      </c>
+      <c r="D13" s="51" t="inlineStr">
+        <is>
+          <t>Misturar os dois critérios gera desvio artificial em meses de virada, principalmente em folha e prêmios.</t>
+        </is>
+      </c>
+      <c r="E13" s="51" t="inlineStr">
         <is>
           <t>Cristiane + Financeiro</t>
         </is>
       </c>
-      <c r="F11" s="55" t="inlineStr">
-        <is>
-          <t>EM ABERTO</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="58" customHeight="1">
-      <c r="A12" s="52" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="B12" s="53" t="inlineStr">
-        <is>
-          <t>Jusfy x Astrea</t>
-        </is>
-      </c>
-      <c r="C12" s="53" t="inlineStr">
-        <is>
-          <t>O risco era pagar os dois em paralelo. O realizado de mai–jul mostra Astrea em R$ 0 (cancelado) e Jusfy em R$ 0 (ainda não iniciado) — no momento não há custo de nenhum dos dois.</t>
-        </is>
-      </c>
-      <c r="D12" s="53" t="inlineStr">
-        <is>
-          <t>Economia de R$ 212,07/mês enquanto durar. Falta decidir se o Jusfy entra e quando, para ajustar o planejado dos meses seguintes.</t>
-        </is>
-      </c>
-      <c r="E12" s="53" t="inlineStr">
-        <is>
-          <t>Cristiane</t>
-        </is>
-      </c>
-      <c r="F12" s="54" t="inlineStr">
-        <is>
-          <t>RESOLVIDO</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="58" customHeight="1">
-      <c r="A13" s="49" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="B13" s="50" t="inlineStr">
-        <is>
-          <t>Critério de competência x caixa</t>
-        </is>
-      </c>
-      <c r="C13" s="50" t="inlineStr">
-        <is>
-          <t>Definir se o realizado será lançado pela data de pagamento (caixa) ou pelo mês de referência da despesa (competência).</t>
-        </is>
-      </c>
-      <c r="D13" s="50" t="inlineStr">
-        <is>
-          <t>Misturar os dois critérios gera desvio artificial em meses de virada, principalmente em folha e prêmios.</t>
-        </is>
-      </c>
-      <c r="E13" s="50" t="inlineStr">
-        <is>
-          <t>Cristiane + Financeiro</t>
-        </is>
-      </c>
-      <c r="F13" s="55" t="inlineStr">
+      <c r="F13" s="56" t="inlineStr">
         <is>
           <t>EM ABERTO</t>
         </is>
@@ -5155,67 +5195,67 @@
       </c>
     </row>
     <row r="4" ht="22" customHeight="1">
-      <c r="A4" s="15" t="inlineStr">
+      <c r="A4" s="16" t="inlineStr">
         <is>
           <t>ROTINA MENSAL</t>
         </is>
       </c>
     </row>
     <row r="5" ht="34" customHeight="1">
-      <c r="A5" s="57" t="inlineStr">
+      <c r="A5" s="58" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="B5" s="58" t="inlineStr">
+      <c r="B5" s="59" t="inlineStr">
         <is>
           <t>Abra a aba REALIZADO e preencha apenas as células amarelas do mês que fechou. Se o item não teve gasto no mês, digite 0 — deixar em branco significa 'ainda não lancei'.</t>
         </is>
       </c>
     </row>
     <row r="6" ht="34" customHeight="1">
-      <c r="A6" s="57" t="inlineStr">
+      <c r="A6" s="58" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="B6" s="58" t="inlineStr">
+      <c r="B6" s="59" t="inlineStr">
         <is>
           <t>Preencha a coluna 'Fonte do dado' (ex.: relatório do financeiro, nota fiscal, extrato do cartão) para o número ser auditável depois.</t>
         </is>
       </c>
     </row>
     <row r="7" ht="34" customHeight="1">
-      <c r="A7" s="57" t="inlineStr">
+      <c r="A7" s="58" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="B7" s="58" t="inlineStr">
+      <c r="B7" s="59" t="inlineStr">
         <is>
           <t>Vá na aba COMPARATIVO e selecione o mês em B3. Todas as demais abas acompanham essa escolha.</t>
         </is>
       </c>
     </row>
     <row r="8" ht="34" customHeight="1">
-      <c r="A8" s="57" t="inlineStr">
+      <c r="A8" s="58" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="B8" s="58" t="inlineStr">
+      <c r="B8" s="59" t="inlineStr">
         <is>
           <t>Confira o PAINEL: ele mostra o desvio por departamento e os 5 maiores estouros do acumulado. É a tela para levar à diretoria.</t>
         </is>
       </c>
     </row>
     <row r="9" ht="34" customHeight="1">
-      <c r="A9" s="57" t="inlineStr">
+      <c r="A9" s="58" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="B9" s="58" t="inlineStr">
+      <c r="B9" s="59" t="inlineStr">
         <is>
           <t>Atualize a aba PENDÊNCIAS conforme as decisões forem sendo tomadas.</t>
         </is>
@@ -5223,67 +5263,67 @@
     </row>
     <row r="10" ht="8" customHeight="1"/>
     <row r="11" ht="22" customHeight="1">
-      <c r="A11" s="15" t="inlineStr">
+      <c r="A11" s="16" t="inlineStr">
         <is>
           <t>COMO LER OS NÚMEROS</t>
         </is>
       </c>
     </row>
     <row r="12" ht="34" customHeight="1">
-      <c r="A12" s="57" t="inlineStr">
+      <c r="A12" s="58" t="inlineStr">
         <is>
           <t>Desvio positivo (vermelho)</t>
         </is>
       </c>
-      <c r="B12" s="58" t="inlineStr">
+      <c r="B12" s="59" t="inlineStr">
         <is>
           <t>Gastou ACIMA do orçado.</t>
         </is>
       </c>
     </row>
     <row r="13" ht="34" customHeight="1">
-      <c r="A13" s="57" t="inlineStr">
+      <c r="A13" s="58" t="inlineStr">
         <is>
           <t>Desvio negativo (verde)</t>
         </is>
       </c>
-      <c r="B13" s="58" t="inlineStr">
+      <c r="B13" s="59" t="inlineStr">
         <is>
           <t>Gastou ABAIXO do orçado — economia ou despesa ainda não realizada.</t>
         </is>
       </c>
     </row>
     <row r="14" ht="34" customHeight="1">
-      <c r="A14" s="57" t="inlineStr">
+      <c r="A14" s="58" t="inlineStr">
         <is>
           <t>Planejado acum.</t>
         </is>
       </c>
-      <c r="B14" s="58" t="inlineStr">
+      <c r="B14" s="59" t="inlineStr">
         <is>
           <t>Soma de maio até o mês selecionado.</t>
         </is>
       </c>
     </row>
     <row r="15" ht="34" customHeight="1">
-      <c r="A15" s="57" t="inlineStr">
+      <c r="A15" s="58" t="inlineStr">
         <is>
           <t>% Executado</t>
         </is>
       </c>
-      <c r="B15" s="58" t="inlineStr">
+      <c r="B15" s="59" t="inlineStr">
         <is>
           <t>Realizado acumulado ÷ Planejado acumulado. Perto de 100% = no ritmo.</t>
         </is>
       </c>
     </row>
     <row r="16" ht="34" customHeight="1">
-      <c r="A16" s="57" t="inlineStr">
+      <c r="A16" s="58" t="inlineStr">
         <is>
           <t>Sem lançamento</t>
         </is>
       </c>
-      <c r="B16" s="58" t="inlineStr">
+      <c r="B16" s="59" t="inlineStr">
         <is>
           <t>Nada foi lançado no realizado ainda — não confunda com economia.</t>
         </is>
@@ -5291,43 +5331,43 @@
     </row>
     <row r="17" ht="8" customHeight="1"/>
     <row r="18" ht="22" customHeight="1">
-      <c r="A18" s="15" t="inlineStr">
+      <c r="A18" s="16" t="inlineStr">
         <is>
           <t>REGRAS DA PLANILHA</t>
         </is>
       </c>
     </row>
     <row r="19" ht="34" customHeight="1">
-      <c r="A19" s="57" t="inlineStr">
+      <c r="A19" s="58" t="inlineStr">
         <is>
           <t>Não altere</t>
         </is>
       </c>
-      <c r="B19" s="58" t="inlineStr">
+      <c r="B19" s="59" t="inlineStr">
         <is>
           <t>As colunas de identificação da aba Realizado (A a G) são fórmulas que espelham a aba Planejado. Alterar quebra o comparativo.</t>
         </is>
       </c>
     </row>
     <row r="20" ht="34" customHeight="1">
-      <c r="A20" s="57" t="inlineStr">
+      <c r="A20" s="58" t="inlineStr">
         <is>
           <t>Nova linha de orçamento</t>
         </is>
       </c>
-      <c r="B20" s="58" t="inlineStr">
+      <c r="B20" s="59" t="inlineStr">
         <is>
           <t>Insira na aba Planejado e replique a mesma linha na aba Realizado e na aba Comparativo, mantendo o mesmo ID.</t>
         </is>
       </c>
     </row>
     <row r="21" ht="34" customHeight="1">
-      <c r="A21" s="57" t="inlineStr">
+      <c r="A21" s="58" t="inlineStr">
         <is>
           <t>Revisão de orçamento</t>
         </is>
       </c>
-      <c r="B21" s="58" t="inlineStr">
+      <c r="B21" s="59" t="inlineStr">
         <is>
           <t>Se a diretoria aprovar um valor novo, altere na aba Planejado e registre o motivo na aba Pendências.</t>
         </is>

--- a/orcamento/Orcamento_JURIDICO_2026.xlsx
+++ b/orcamento/Orcamento_JURIDICO_2026.xlsx
@@ -30,7 +30,7 @@
     <numFmt numFmtId="164" formatCode="R$ #,##0.00"/>
     <numFmt numFmtId="165" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="19">
+  <fonts count="25">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -111,13 +111,42 @@
     <font>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00000000"/>
       <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="001E6B3A"/>
+      <sz val="14"/>
+    </font>
+    <font>
+      <i val="1"/>
+      <color rgb="009C0006"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="001E6B3A"/>
+      <sz val="9"/>
     </font>
     <font>
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="14">
+  <fills count="15">
     <fill>
       <patternFill/>
     </fill>
@@ -166,12 +195,17 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F8CBAD"/>
+        <fgColor rgb="001E6B3A"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00E2EFDA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F8CBAD"/>
       </patternFill>
     </fill>
     <fill>
@@ -211,7 +245,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="60">
+  <cellXfs count="72">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
@@ -246,7 +280,30 @@
     <xf numFmtId="0" fontId="16" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="17" fillId="10" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="18" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="20" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="18" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -254,7 +311,11 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="23" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="22" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
@@ -275,6 +336,7 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="6" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="6" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -318,7 +380,7 @@
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -330,16 +392,16 @@
     <xf numFmtId="0" fontId="5" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="14" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1025,7 +1087,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I17"/>
+  <dimension ref="A1:I34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1243,202 +1305,529 @@
         <v/>
       </c>
     </row>
-    <row r="11" ht="22" customHeight="1">
+    <row r="11" ht="24" customHeight="1">
       <c r="A11" s="16" t="inlineStr">
         <is>
+          <t>ECONOMIA GERADA — acumulado de janeiro até o mês de referência</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="20" customHeight="1">
+      <c r="A12" s="17" t="inlineStr">
+        <is>
+          <t>Economia bruta</t>
+        </is>
+      </c>
+      <c r="B12" s="17" t="n"/>
+      <c r="C12" s="18">
+        <f>-SUMIF(Comparativo!$Q$6:$Q$14,"&lt;0")</f>
+        <v/>
+      </c>
+      <c r="D12" s="19" t="inlineStr">
+        <is>
+          <t>Soma de tudo que ficou abaixo do orçado</t>
+        </is>
+      </c>
+      <c r="E12" s="19" t="n"/>
+      <c r="F12" s="19" t="n"/>
+      <c r="G12" s="19" t="n"/>
+      <c r="H12" s="19" t="n"/>
+      <c r="I12" s="19" t="n"/>
+    </row>
+    <row r="13" ht="20" customHeight="1">
+      <c r="A13" s="17" t="inlineStr">
+        <is>
+          <t>(−) Gastos acima do orçado</t>
+        </is>
+      </c>
+      <c r="B13" s="17" t="n"/>
+      <c r="C13" s="18">
+        <f>-SUMIF(Comparativo!$Q$6:$Q$14,"&gt;0")</f>
+        <v/>
+      </c>
+      <c r="D13" s="19" t="inlineStr">
+        <is>
+          <t>Estouros que consomem parte da economia</t>
+        </is>
+      </c>
+      <c r="E13" s="19" t="n"/>
+      <c r="F13" s="19" t="n"/>
+      <c r="G13" s="19" t="n"/>
+      <c r="H13" s="19" t="n"/>
+      <c r="I13" s="19" t="n"/>
+    </row>
+    <row r="14" ht="26" customHeight="1">
+      <c r="A14" s="20">
+        <f> ECONOMIA LÍQUIDA</f>
+        <v/>
+      </c>
+      <c r="B14" s="20" t="n"/>
+      <c r="C14" s="21">
+        <f>-SUM(Comparativo!$Q$6:$Q$14)</f>
+        <v/>
+      </c>
+      <c r="D14" s="22" t="inlineStr">
+        <is>
+          <t>O número defensável: só linhas comparáveis</t>
+        </is>
+      </c>
+      <c r="E14" s="22" t="n"/>
+      <c r="F14" s="22" t="n"/>
+      <c r="G14" s="22" t="n"/>
+      <c r="H14" s="22" t="n"/>
+      <c r="I14" s="22" t="n"/>
+    </row>
+    <row r="15" ht="20" customHeight="1">
+      <c r="A15" s="17" t="inlineStr">
+        <is>
+          <t>Projeção para o ano</t>
+        </is>
+      </c>
+      <c r="B15" s="17" t="n"/>
+      <c r="C15" s="18">
+        <f>IFERROR(-SUM(Comparativo!$Q$6:$Q$14)/Comparativo!$D$3*12,"")</f>
+        <v/>
+      </c>
+      <c r="D15" s="19" t="inlineStr">
+        <is>
+          <t>Extrapolação linear, se o padrão dos meses fechados se mantiver</t>
+        </is>
+      </c>
+      <c r="E15" s="19" t="n"/>
+      <c r="F15" s="19" t="n"/>
+      <c r="G15" s="19" t="n"/>
+      <c r="H15" s="19" t="n"/>
+      <c r="I15" s="19" t="n"/>
+    </row>
+    <row r="16" ht="20" customHeight="1">
+      <c r="A16" s="17" t="inlineStr">
+        <is>
+          <t>% sobre o orçado do período</t>
+        </is>
+      </c>
+      <c r="B16" s="17" t="n"/>
+      <c r="C16" s="23">
+        <f>IFERROR(-SUM(Comparativo!$Q$6:$Q$14)/SUM(Comparativo!$S$6:$S$14),"")</f>
+        <v/>
+      </c>
+      <c r="D16" s="19" t="inlineStr">
+        <is>
+          <t>Economia líquida ÷ planejado das linhas que entram na conta</t>
+        </is>
+      </c>
+      <c r="E16" s="19" t="n"/>
+      <c r="F16" s="19" t="n"/>
+      <c r="G16" s="19" t="n"/>
+      <c r="H16" s="19" t="n"/>
+      <c r="I16" s="19" t="n"/>
+    </row>
+    <row r="17" ht="18" customHeight="1">
+      <c r="A17" s="24" t="inlineStr">
+        <is>
+          <t>Fora desta conta: linhas sem nenhum lançamento; Geovanna (base diferente). Só entra o que foi efetivamente lançado e é comparável.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="22" customHeight="1">
+      <c r="A19" s="25" t="inlineStr">
+        <is>
+          <t>DE ONDE VEIO A ECONOMIA (top 5)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="30" customHeight="1">
+      <c r="A20" s="7" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B20" s="7" t="inlineStr">
+        <is>
+          <t>Item</t>
+        </is>
+      </c>
+      <c r="C20" s="7" t="inlineStr">
+        <is>
+          <t>Departamento</t>
+        </is>
+      </c>
+      <c r="D20" s="7" t="inlineStr">
+        <is>
+          <t>Planejado acum.</t>
+        </is>
+      </c>
+      <c r="E20" s="7" t="inlineStr">
+        <is>
+          <t>Realizado acum.</t>
+        </is>
+      </c>
+      <c r="F20" s="7" t="inlineStr">
+        <is>
+          <t>Economia (R$)</t>
+        </is>
+      </c>
+      <c r="G20" s="7" t="inlineStr">
+        <is>
+          <t>% da linha</t>
+        </is>
+      </c>
+      <c r="H20" s="7" t="inlineStr"/>
+      <c r="I20" s="7" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="B21" s="27">
+        <f>IFERROR(INDEX(Comparativo!$D$6:$D$14,MATCH(LARGE(Comparativo!$R$6:$R$14,A21),Comparativo!$R$6:$R$14,0)),"")</f>
+        <v/>
+      </c>
+      <c r="C21" s="27">
+        <f>IFERROR(INDEX(Comparativo!$B$6:$B$14,MATCH(LARGE(Comparativo!$R$6:$R$14,A21),Comparativo!$R$6:$R$14,0)),"")</f>
+        <v/>
+      </c>
+      <c r="D21" s="28">
+        <f>IFERROR(INDEX(Comparativo!$I$6:$I$14,MATCH(LARGE(Comparativo!$R$6:$R$14,A21),Comparativo!$R$6:$R$14,0)),"")</f>
+        <v/>
+      </c>
+      <c r="E21" s="28">
+        <f>IFERROR(INDEX(Comparativo!$J$6:$J$14,MATCH(LARGE(Comparativo!$R$6:$R$14,A21),Comparativo!$R$6:$R$14,0)),"")</f>
+        <v/>
+      </c>
+      <c r="F21" s="29">
+        <f>IFERROR(-IFERROR(INDEX(Comparativo!$K$6:$K$14,MATCH(LARGE(Comparativo!$R$6:$R$14,A21),Comparativo!$R$6:$R$14,0)),""),"")</f>
+        <v/>
+      </c>
+      <c r="G21" s="30">
+        <f>IFERROR(F21/D21,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="B22" s="27">
+        <f>IFERROR(INDEX(Comparativo!$D$6:$D$14,MATCH(LARGE(Comparativo!$R$6:$R$14,A22),Comparativo!$R$6:$R$14,0)),"")</f>
+        <v/>
+      </c>
+      <c r="C22" s="27">
+        <f>IFERROR(INDEX(Comparativo!$B$6:$B$14,MATCH(LARGE(Comparativo!$R$6:$R$14,A22),Comparativo!$R$6:$R$14,0)),"")</f>
+        <v/>
+      </c>
+      <c r="D22" s="28">
+        <f>IFERROR(INDEX(Comparativo!$I$6:$I$14,MATCH(LARGE(Comparativo!$R$6:$R$14,A22),Comparativo!$R$6:$R$14,0)),"")</f>
+        <v/>
+      </c>
+      <c r="E22" s="28">
+        <f>IFERROR(INDEX(Comparativo!$J$6:$J$14,MATCH(LARGE(Comparativo!$R$6:$R$14,A22),Comparativo!$R$6:$R$14,0)),"")</f>
+        <v/>
+      </c>
+      <c r="F22" s="29">
+        <f>IFERROR(-IFERROR(INDEX(Comparativo!$K$6:$K$14,MATCH(LARGE(Comparativo!$R$6:$R$14,A22),Comparativo!$R$6:$R$14,0)),""),"")</f>
+        <v/>
+      </c>
+      <c r="G22" s="30">
+        <f>IFERROR(F22/D22,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="B23" s="27">
+        <f>IFERROR(INDEX(Comparativo!$D$6:$D$14,MATCH(LARGE(Comparativo!$R$6:$R$14,A23),Comparativo!$R$6:$R$14,0)),"")</f>
+        <v/>
+      </c>
+      <c r="C23" s="27">
+        <f>IFERROR(INDEX(Comparativo!$B$6:$B$14,MATCH(LARGE(Comparativo!$R$6:$R$14,A23),Comparativo!$R$6:$R$14,0)),"")</f>
+        <v/>
+      </c>
+      <c r="D23" s="28">
+        <f>IFERROR(INDEX(Comparativo!$I$6:$I$14,MATCH(LARGE(Comparativo!$R$6:$R$14,A23),Comparativo!$R$6:$R$14,0)),"")</f>
+        <v/>
+      </c>
+      <c r="E23" s="28">
+        <f>IFERROR(INDEX(Comparativo!$J$6:$J$14,MATCH(LARGE(Comparativo!$R$6:$R$14,A23),Comparativo!$R$6:$R$14,0)),"")</f>
+        <v/>
+      </c>
+      <c r="F23" s="29">
+        <f>IFERROR(-IFERROR(INDEX(Comparativo!$K$6:$K$14,MATCH(LARGE(Comparativo!$R$6:$R$14,A23),Comparativo!$R$6:$R$14,0)),""),"")</f>
+        <v/>
+      </c>
+      <c r="G23" s="30">
+        <f>IFERROR(F23/D23,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="B24" s="27">
+        <f>IFERROR(INDEX(Comparativo!$D$6:$D$14,MATCH(LARGE(Comparativo!$R$6:$R$14,A24),Comparativo!$R$6:$R$14,0)),"")</f>
+        <v/>
+      </c>
+      <c r="C24" s="27">
+        <f>IFERROR(INDEX(Comparativo!$B$6:$B$14,MATCH(LARGE(Comparativo!$R$6:$R$14,A24),Comparativo!$R$6:$R$14,0)),"")</f>
+        <v/>
+      </c>
+      <c r="D24" s="28">
+        <f>IFERROR(INDEX(Comparativo!$I$6:$I$14,MATCH(LARGE(Comparativo!$R$6:$R$14,A24),Comparativo!$R$6:$R$14,0)),"")</f>
+        <v/>
+      </c>
+      <c r="E24" s="28">
+        <f>IFERROR(INDEX(Comparativo!$J$6:$J$14,MATCH(LARGE(Comparativo!$R$6:$R$14,A24),Comparativo!$R$6:$R$14,0)),"")</f>
+        <v/>
+      </c>
+      <c r="F24" s="29">
+        <f>IFERROR(-IFERROR(INDEX(Comparativo!$K$6:$K$14,MATCH(LARGE(Comparativo!$R$6:$R$14,A24),Comparativo!$R$6:$R$14,0)),""),"")</f>
+        <v/>
+      </c>
+      <c r="G24" s="30">
+        <f>IFERROR(F24/D24,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="26" t="n">
+        <v>5</v>
+      </c>
+      <c r="B25" s="27">
+        <f>IFERROR(INDEX(Comparativo!$D$6:$D$14,MATCH(LARGE(Comparativo!$R$6:$R$14,A25),Comparativo!$R$6:$R$14,0)),"")</f>
+        <v/>
+      </c>
+      <c r="C25" s="27">
+        <f>IFERROR(INDEX(Comparativo!$B$6:$B$14,MATCH(LARGE(Comparativo!$R$6:$R$14,A25),Comparativo!$R$6:$R$14,0)),"")</f>
+        <v/>
+      </c>
+      <c r="D25" s="28">
+        <f>IFERROR(INDEX(Comparativo!$I$6:$I$14,MATCH(LARGE(Comparativo!$R$6:$R$14,A25),Comparativo!$R$6:$R$14,0)),"")</f>
+        <v/>
+      </c>
+      <c r="E25" s="28">
+        <f>IFERROR(INDEX(Comparativo!$J$6:$J$14,MATCH(LARGE(Comparativo!$R$6:$R$14,A25),Comparativo!$R$6:$R$14,0)),"")</f>
+        <v/>
+      </c>
+      <c r="F25" s="29">
+        <f>IFERROR(-IFERROR(INDEX(Comparativo!$K$6:$K$14,MATCH(LARGE(Comparativo!$R$6:$R$14,A25),Comparativo!$R$6:$R$14,0)),""),"")</f>
+        <v/>
+      </c>
+      <c r="G25" s="30">
+        <f>IFERROR(F25/D25,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28" ht="22" customHeight="1">
+      <c r="A28" s="31" t="inlineStr">
+        <is>
           <t>MAIORES DESVIOS DO ACUMULADO (top 5 acima do orçado)</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="30" customHeight="1">
-      <c r="A12" s="7" t="inlineStr">
+    <row r="29" ht="30" customHeight="1">
+      <c r="A29" s="7" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B12" s="7" t="inlineStr">
+      <c r="B29" s="7" t="inlineStr">
         <is>
           <t>Item</t>
         </is>
       </c>
-      <c r="C12" s="7" t="inlineStr">
+      <c r="C29" s="7" t="inlineStr">
         <is>
           <t>Departamento</t>
         </is>
       </c>
-      <c r="D12" s="7" t="inlineStr">
+      <c r="D29" s="7" t="inlineStr">
         <is>
           <t>Planejado acum.</t>
         </is>
       </c>
-      <c r="E12" s="7" t="inlineStr">
+      <c r="E29" s="7" t="inlineStr">
         <is>
           <t>Realizado acum.</t>
         </is>
       </c>
-      <c r="F12" s="7" t="inlineStr">
+      <c r="F29" s="7" t="inlineStr">
         <is>
           <t>Desvio (R$)</t>
         </is>
       </c>
-      <c r="G12" s="7" t="inlineStr">
+      <c r="G29" s="7" t="inlineStr">
         <is>
           <t>Desvio (%)</t>
         </is>
       </c>
-      <c r="H12" s="7" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="17" t="n">
+      <c r="H29" s="7" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="26" t="n">
         <v>1</v>
       </c>
-      <c r="B13" s="18">
-        <f>IFERROR(INDEX(Comparativo!$D$6:$D$14,MATCH(LARGE(Comparativo!$O$6:$O$14,A13),Comparativo!$O$6:$O$14,0)),"")</f>
-        <v/>
-      </c>
-      <c r="C13" s="18">
-        <f>IFERROR(INDEX(Comparativo!$B$6:$B$14,MATCH(LARGE(Comparativo!$O$6:$O$14,A13),Comparativo!$O$6:$O$14,0)),"")</f>
-        <v/>
-      </c>
-      <c r="D13" s="19">
-        <f>IFERROR(INDEX(Comparativo!$I$6:$I$14,MATCH(LARGE(Comparativo!$O$6:$O$14,A13),Comparativo!$O$6:$O$14,0)),"")</f>
-        <v/>
-      </c>
-      <c r="E13" s="19">
-        <f>IFERROR(INDEX(Comparativo!$J$6:$J$14,MATCH(LARGE(Comparativo!$O$6:$O$14,A13),Comparativo!$O$6:$O$14,0)),"")</f>
-        <v/>
-      </c>
-      <c r="F13" s="19">
-        <f>IFERROR(INDEX(Comparativo!$K$6:$K$14,MATCH(LARGE(Comparativo!$O$6:$O$14,A13),Comparativo!$O$6:$O$14,0)),"")</f>
-        <v/>
-      </c>
-      <c r="G13" s="20">
-        <f>IFERROR(F13/D13,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="17" t="n">
+      <c r="B30" s="27">
+        <f>IFERROR(INDEX(Comparativo!$D$6:$D$14,MATCH(LARGE(Comparativo!$O$6:$O$14,A30),Comparativo!$O$6:$O$14,0)),"")</f>
+        <v/>
+      </c>
+      <c r="C30" s="27">
+        <f>IFERROR(INDEX(Comparativo!$B$6:$B$14,MATCH(LARGE(Comparativo!$O$6:$O$14,A30),Comparativo!$O$6:$O$14,0)),"")</f>
+        <v/>
+      </c>
+      <c r="D30" s="28">
+        <f>IFERROR(INDEX(Comparativo!$I$6:$I$14,MATCH(LARGE(Comparativo!$O$6:$O$14,A30),Comparativo!$O$6:$O$14,0)),"")</f>
+        <v/>
+      </c>
+      <c r="E30" s="28">
+        <f>IFERROR(INDEX(Comparativo!$J$6:$J$14,MATCH(LARGE(Comparativo!$O$6:$O$14,A30),Comparativo!$O$6:$O$14,0)),"")</f>
+        <v/>
+      </c>
+      <c r="F30" s="28">
+        <f>IFERROR(INDEX(Comparativo!$K$6:$K$14,MATCH(LARGE(Comparativo!$O$6:$O$14,A30),Comparativo!$O$6:$O$14,0)),"")</f>
+        <v/>
+      </c>
+      <c r="G30" s="30">
+        <f>IFERROR(F30/D30,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="26" t="n">
         <v>2</v>
       </c>
-      <c r="B14" s="18">
-        <f>IFERROR(INDEX(Comparativo!$D$6:$D$14,MATCH(LARGE(Comparativo!$O$6:$O$14,A14),Comparativo!$O$6:$O$14,0)),"")</f>
-        <v/>
-      </c>
-      <c r="C14" s="18">
-        <f>IFERROR(INDEX(Comparativo!$B$6:$B$14,MATCH(LARGE(Comparativo!$O$6:$O$14,A14),Comparativo!$O$6:$O$14,0)),"")</f>
-        <v/>
-      </c>
-      <c r="D14" s="19">
-        <f>IFERROR(INDEX(Comparativo!$I$6:$I$14,MATCH(LARGE(Comparativo!$O$6:$O$14,A14),Comparativo!$O$6:$O$14,0)),"")</f>
-        <v/>
-      </c>
-      <c r="E14" s="19">
-        <f>IFERROR(INDEX(Comparativo!$J$6:$J$14,MATCH(LARGE(Comparativo!$O$6:$O$14,A14),Comparativo!$O$6:$O$14,0)),"")</f>
-        <v/>
-      </c>
-      <c r="F14" s="19">
-        <f>IFERROR(INDEX(Comparativo!$K$6:$K$14,MATCH(LARGE(Comparativo!$O$6:$O$14,A14),Comparativo!$O$6:$O$14,0)),"")</f>
-        <v/>
-      </c>
-      <c r="G14" s="20">
-        <f>IFERROR(F14/D14,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="17" t="n">
+      <c r="B31" s="27">
+        <f>IFERROR(INDEX(Comparativo!$D$6:$D$14,MATCH(LARGE(Comparativo!$O$6:$O$14,A31),Comparativo!$O$6:$O$14,0)),"")</f>
+        <v/>
+      </c>
+      <c r="C31" s="27">
+        <f>IFERROR(INDEX(Comparativo!$B$6:$B$14,MATCH(LARGE(Comparativo!$O$6:$O$14,A31),Comparativo!$O$6:$O$14,0)),"")</f>
+        <v/>
+      </c>
+      <c r="D31" s="28">
+        <f>IFERROR(INDEX(Comparativo!$I$6:$I$14,MATCH(LARGE(Comparativo!$O$6:$O$14,A31),Comparativo!$O$6:$O$14,0)),"")</f>
+        <v/>
+      </c>
+      <c r="E31" s="28">
+        <f>IFERROR(INDEX(Comparativo!$J$6:$J$14,MATCH(LARGE(Comparativo!$O$6:$O$14,A31),Comparativo!$O$6:$O$14,0)),"")</f>
+        <v/>
+      </c>
+      <c r="F31" s="28">
+        <f>IFERROR(INDEX(Comparativo!$K$6:$K$14,MATCH(LARGE(Comparativo!$O$6:$O$14,A31),Comparativo!$O$6:$O$14,0)),"")</f>
+        <v/>
+      </c>
+      <c r="G31" s="30">
+        <f>IFERROR(F31/D31,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="26" t="n">
         <v>3</v>
       </c>
-      <c r="B15" s="18">
-        <f>IFERROR(INDEX(Comparativo!$D$6:$D$14,MATCH(LARGE(Comparativo!$O$6:$O$14,A15),Comparativo!$O$6:$O$14,0)),"")</f>
-        <v/>
-      </c>
-      <c r="C15" s="18">
-        <f>IFERROR(INDEX(Comparativo!$B$6:$B$14,MATCH(LARGE(Comparativo!$O$6:$O$14,A15),Comparativo!$O$6:$O$14,0)),"")</f>
-        <v/>
-      </c>
-      <c r="D15" s="19">
-        <f>IFERROR(INDEX(Comparativo!$I$6:$I$14,MATCH(LARGE(Comparativo!$O$6:$O$14,A15),Comparativo!$O$6:$O$14,0)),"")</f>
-        <v/>
-      </c>
-      <c r="E15" s="19">
-        <f>IFERROR(INDEX(Comparativo!$J$6:$J$14,MATCH(LARGE(Comparativo!$O$6:$O$14,A15),Comparativo!$O$6:$O$14,0)),"")</f>
-        <v/>
-      </c>
-      <c r="F15" s="19">
-        <f>IFERROR(INDEX(Comparativo!$K$6:$K$14,MATCH(LARGE(Comparativo!$O$6:$O$14,A15),Comparativo!$O$6:$O$14,0)),"")</f>
-        <v/>
-      </c>
-      <c r="G15" s="20">
-        <f>IFERROR(F15/D15,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="17" t="n">
+      <c r="B32" s="27">
+        <f>IFERROR(INDEX(Comparativo!$D$6:$D$14,MATCH(LARGE(Comparativo!$O$6:$O$14,A32),Comparativo!$O$6:$O$14,0)),"")</f>
+        <v/>
+      </c>
+      <c r="C32" s="27">
+        <f>IFERROR(INDEX(Comparativo!$B$6:$B$14,MATCH(LARGE(Comparativo!$O$6:$O$14,A32),Comparativo!$O$6:$O$14,0)),"")</f>
+        <v/>
+      </c>
+      <c r="D32" s="28">
+        <f>IFERROR(INDEX(Comparativo!$I$6:$I$14,MATCH(LARGE(Comparativo!$O$6:$O$14,A32),Comparativo!$O$6:$O$14,0)),"")</f>
+        <v/>
+      </c>
+      <c r="E32" s="28">
+        <f>IFERROR(INDEX(Comparativo!$J$6:$J$14,MATCH(LARGE(Comparativo!$O$6:$O$14,A32),Comparativo!$O$6:$O$14,0)),"")</f>
+        <v/>
+      </c>
+      <c r="F32" s="28">
+        <f>IFERROR(INDEX(Comparativo!$K$6:$K$14,MATCH(LARGE(Comparativo!$O$6:$O$14,A32),Comparativo!$O$6:$O$14,0)),"")</f>
+        <v/>
+      </c>
+      <c r="G32" s="30">
+        <f>IFERROR(F32/D32,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="26" t="n">
         <v>4</v>
       </c>
-      <c r="B16" s="18">
-        <f>IFERROR(INDEX(Comparativo!$D$6:$D$14,MATCH(LARGE(Comparativo!$O$6:$O$14,A16),Comparativo!$O$6:$O$14,0)),"")</f>
-        <v/>
-      </c>
-      <c r="C16" s="18">
-        <f>IFERROR(INDEX(Comparativo!$B$6:$B$14,MATCH(LARGE(Comparativo!$O$6:$O$14,A16),Comparativo!$O$6:$O$14,0)),"")</f>
-        <v/>
-      </c>
-      <c r="D16" s="19">
-        <f>IFERROR(INDEX(Comparativo!$I$6:$I$14,MATCH(LARGE(Comparativo!$O$6:$O$14,A16),Comparativo!$O$6:$O$14,0)),"")</f>
-        <v/>
-      </c>
-      <c r="E16" s="19">
-        <f>IFERROR(INDEX(Comparativo!$J$6:$J$14,MATCH(LARGE(Comparativo!$O$6:$O$14,A16),Comparativo!$O$6:$O$14,0)),"")</f>
-        <v/>
-      </c>
-      <c r="F16" s="19">
-        <f>IFERROR(INDEX(Comparativo!$K$6:$K$14,MATCH(LARGE(Comparativo!$O$6:$O$14,A16),Comparativo!$O$6:$O$14,0)),"")</f>
-        <v/>
-      </c>
-      <c r="G16" s="20">
-        <f>IFERROR(F16/D16,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="17" t="n">
+      <c r="B33" s="27">
+        <f>IFERROR(INDEX(Comparativo!$D$6:$D$14,MATCH(LARGE(Comparativo!$O$6:$O$14,A33),Comparativo!$O$6:$O$14,0)),"")</f>
+        <v/>
+      </c>
+      <c r="C33" s="27">
+        <f>IFERROR(INDEX(Comparativo!$B$6:$B$14,MATCH(LARGE(Comparativo!$O$6:$O$14,A33),Comparativo!$O$6:$O$14,0)),"")</f>
+        <v/>
+      </c>
+      <c r="D33" s="28">
+        <f>IFERROR(INDEX(Comparativo!$I$6:$I$14,MATCH(LARGE(Comparativo!$O$6:$O$14,A33),Comparativo!$O$6:$O$14,0)),"")</f>
+        <v/>
+      </c>
+      <c r="E33" s="28">
+        <f>IFERROR(INDEX(Comparativo!$J$6:$J$14,MATCH(LARGE(Comparativo!$O$6:$O$14,A33),Comparativo!$O$6:$O$14,0)),"")</f>
+        <v/>
+      </c>
+      <c r="F33" s="28">
+        <f>IFERROR(INDEX(Comparativo!$K$6:$K$14,MATCH(LARGE(Comparativo!$O$6:$O$14,A33),Comparativo!$O$6:$O$14,0)),"")</f>
+        <v/>
+      </c>
+      <c r="G33" s="30">
+        <f>IFERROR(F33/D33,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="26" t="n">
         <v>5</v>
       </c>
-      <c r="B17" s="18">
-        <f>IFERROR(INDEX(Comparativo!$D$6:$D$14,MATCH(LARGE(Comparativo!$O$6:$O$14,A17),Comparativo!$O$6:$O$14,0)),"")</f>
-        <v/>
-      </c>
-      <c r="C17" s="18">
-        <f>IFERROR(INDEX(Comparativo!$B$6:$B$14,MATCH(LARGE(Comparativo!$O$6:$O$14,A17),Comparativo!$O$6:$O$14,0)),"")</f>
-        <v/>
-      </c>
-      <c r="D17" s="19">
-        <f>IFERROR(INDEX(Comparativo!$I$6:$I$14,MATCH(LARGE(Comparativo!$O$6:$O$14,A17),Comparativo!$O$6:$O$14,0)),"")</f>
-        <v/>
-      </c>
-      <c r="E17" s="19">
-        <f>IFERROR(INDEX(Comparativo!$J$6:$J$14,MATCH(LARGE(Comparativo!$O$6:$O$14,A17),Comparativo!$O$6:$O$14,0)),"")</f>
-        <v/>
-      </c>
-      <c r="F17" s="19">
-        <f>IFERROR(INDEX(Comparativo!$K$6:$K$14,MATCH(LARGE(Comparativo!$O$6:$O$14,A17),Comparativo!$O$6:$O$14,0)),"")</f>
-        <v/>
-      </c>
-      <c r="G17" s="20">
-        <f>IFERROR(F17/D17,"")</f>
+      <c r="B34" s="27">
+        <f>IFERROR(INDEX(Comparativo!$D$6:$D$14,MATCH(LARGE(Comparativo!$O$6:$O$14,A34),Comparativo!$O$6:$O$14,0)),"")</f>
+        <v/>
+      </c>
+      <c r="C34" s="27">
+        <f>IFERROR(INDEX(Comparativo!$B$6:$B$14,MATCH(LARGE(Comparativo!$O$6:$O$14,A34),Comparativo!$O$6:$O$14,0)),"")</f>
+        <v/>
+      </c>
+      <c r="D34" s="28">
+        <f>IFERROR(INDEX(Comparativo!$I$6:$I$14,MATCH(LARGE(Comparativo!$O$6:$O$14,A34),Comparativo!$O$6:$O$14,0)),"")</f>
+        <v/>
+      </c>
+      <c r="E34" s="28">
+        <f>IFERROR(INDEX(Comparativo!$J$6:$J$14,MATCH(LARGE(Comparativo!$O$6:$O$14,A34),Comparativo!$O$6:$O$14,0)),"")</f>
+        <v/>
+      </c>
+      <c r="F34" s="28">
+        <f>IFERROR(INDEX(Comparativo!$K$6:$K$14,MATCH(LARGE(Comparativo!$O$6:$O$14,A34),Comparativo!$O$6:$O$14,0)),"")</f>
+        <v/>
+      </c>
+      <c r="G34" s="30">
+        <f>IFERROR(F34/D34,"")</f>
         <v/>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="4">
+  <mergeCells count="17">
+    <mergeCell ref="A16:B16"/>
+    <mergeCell ref="A2:I2"/>
+    <mergeCell ref="A11:I11"/>
+    <mergeCell ref="A15:B15"/>
+    <mergeCell ref="D13:I13"/>
+    <mergeCell ref="D14:I14"/>
+    <mergeCell ref="D15:I15"/>
+    <mergeCell ref="A19:I19"/>
     <mergeCell ref="A1:I1"/>
+    <mergeCell ref="A17:I17"/>
+    <mergeCell ref="A13:B13"/>
+    <mergeCell ref="A14:B14"/>
+    <mergeCell ref="D12:I12"/>
+    <mergeCell ref="A28:H28"/>
+    <mergeCell ref="D16:I16"/>
     <mergeCell ref="A4:I4"/>
-    <mergeCell ref="A11:H11"/>
-    <mergeCell ref="A2:I2"/>
+    <mergeCell ref="A12:B12"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1450,7 +1839,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P27"/>
+  <dimension ref="A1:S27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1469,6 +1858,9 @@
     <col width="17" customWidth="1" min="14" max="14"/>
     <col hidden="1" width="10" customWidth="1" min="15" max="15"/>
     <col hidden="1" width="13" customWidth="1" min="16" max="16"/>
+    <col hidden="1" width="13" customWidth="1" min="17" max="17"/>
+    <col hidden="1" width="13" customWidth="1" min="18" max="18"/>
+    <col hidden="1" width="13" customWidth="1" min="19" max="19"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -1491,17 +1883,17 @@
           <t>Mês de referência:</t>
         </is>
       </c>
-      <c r="B3" s="21" t="inlineStr">
+      <c r="B3" s="32" t="inlineStr">
         <is>
           <t>Jul/26</t>
         </is>
       </c>
-      <c r="C3" s="22" t="inlineStr">
+      <c r="C3" s="33" t="inlineStr">
         <is>
           <t>Mês nº:</t>
         </is>
       </c>
-      <c r="D3" s="23">
+      <c r="D3" s="34">
         <f>MATCH($B$3,Planejado!$H$4:$S$4,0)</f>
         <v/>
       </c>
@@ -1577,655 +1969,775 @@
           <t>Situação</t>
         </is>
       </c>
-      <c r="O5" s="24" t="inlineStr">
+      <c r="O5" s="35" t="inlineStr">
         <is>
           <t>(aux ranking)</t>
         </is>
       </c>
-      <c r="P5" s="24" t="inlineStr">
+      <c r="P5" s="35" t="inlineStr">
         <is>
           <t>(aux meses lançados)</t>
         </is>
       </c>
+      <c r="Q5" s="35" t="inlineStr">
+        <is>
+          <t>(aux desvio comparável)</t>
+        </is>
+      </c>
+      <c r="R5" s="35" t="inlineStr">
+        <is>
+          <t>(aux ranking economia)</t>
+        </is>
+      </c>
+      <c r="S5" s="35" t="inlineStr">
+        <is>
+          <t>(aux planejado comparável)</t>
+        </is>
+      </c>
     </row>
     <row r="6" ht="24" customHeight="1">
-      <c r="A6" s="25">
+      <c r="A6" s="36">
         <f>Planejado!A5</f>
         <v/>
       </c>
-      <c r="B6" s="25">
+      <c r="B6" s="36">
         <f>Planejado!B5</f>
         <v/>
       </c>
-      <c r="C6" s="25">
+      <c r="C6" s="36">
         <f>Planejado!C5</f>
         <v/>
       </c>
-      <c r="D6" s="26">
+      <c r="D6" s="37">
         <f>Planejado!D5</f>
         <v/>
       </c>
-      <c r="E6" s="25">
+      <c r="E6" s="36">
         <f>Planejado!G5</f>
         <v/>
       </c>
-      <c r="F6" s="27">
+      <c r="F6" s="38">
         <f>INDEX(Planejado!$H5:$S5,$D$3)</f>
         <v/>
       </c>
-      <c r="G6" s="27">
+      <c r="G6" s="38">
         <f>INDEX(Realizado!$H5:$S5,$D$3)</f>
         <v/>
       </c>
-      <c r="H6" s="27">
+      <c r="H6" s="38">
         <f>G6-F6</f>
         <v/>
       </c>
-      <c r="I6" s="27">
+      <c r="I6" s="38">
         <f>SUMPRODUCT((COLUMN(Planejado!$H$4:$S$4)-COLUMN(Planejado!$H$4)+1&lt;=$D$3)*Planejado!$H5:$S5)</f>
         <v/>
       </c>
-      <c r="J6" s="27">
+      <c r="J6" s="38">
         <f>SUMPRODUCT((COLUMN(Realizado!$H$4:$S$4)-COLUMN(Realizado!$H$4)+1&lt;=$D$3)*Realizado!$H5:$S5)</f>
         <v/>
       </c>
-      <c r="K6" s="27">
+      <c r="K6" s="38">
         <f>J6-I6</f>
         <v/>
       </c>
-      <c r="L6" s="28">
+      <c r="L6" s="39">
         <f>IFERROR(K6/I6,"")</f>
         <v/>
       </c>
-      <c r="M6" s="28">
+      <c r="M6" s="39">
         <f>IFERROR(J6/I6,"")</f>
         <v/>
       </c>
-      <c r="N6" s="29">
+      <c r="N6" s="40">
         <f>IF(P6=0,"Sem lançamento",IF(AND(I6=0,J6=0),"—",IF(I6=0,"Não orçado",IF(K6&gt;0.05*I6,"Acima do orçado",IF(K6&lt;-0.05*I6,"Abaixo do orçado","Dentro do orçado")))))</f>
         <v/>
       </c>
-      <c r="O6" s="24">
+      <c r="O6" s="35">
         <f>IF(K6&gt;1,K6+ROW()/1000000,"")</f>
         <v/>
       </c>
-      <c r="P6" s="30">
+      <c r="P6" s="41">
         <f>SUMPRODUCT((COLUMN(Realizado!$H$4:$S$4)-COLUMN(Realizado!$H$4)+1&lt;=$D$3)*(Realizado!$H5:$S5&lt;&gt;""))</f>
         <v/>
       </c>
+      <c r="Q6" s="42">
+        <f>IF(P6=0,"",K6)</f>
+        <v/>
+      </c>
+      <c r="R6" s="42">
+        <f>IF(AND(Q6&lt;&gt;"",Q6&lt;-1),-Q6+ROW()/1000000,"")</f>
+        <v/>
+      </c>
+      <c r="S6" s="42">
+        <f>IF(Q6="","",I6)</f>
+        <v/>
+      </c>
     </row>
     <row r="7" ht="24" customHeight="1">
-      <c r="A7" s="25">
+      <c r="A7" s="36">
         <f>Planejado!A6</f>
         <v/>
       </c>
-      <c r="B7" s="25">
+      <c r="B7" s="36">
         <f>Planejado!B6</f>
         <v/>
       </c>
-      <c r="C7" s="25">
+      <c r="C7" s="36">
         <f>Planejado!C6</f>
         <v/>
       </c>
-      <c r="D7" s="26">
+      <c r="D7" s="37">
         <f>Planejado!D6</f>
         <v/>
       </c>
-      <c r="E7" s="25">
+      <c r="E7" s="36">
         <f>Planejado!G6</f>
         <v/>
       </c>
-      <c r="F7" s="27">
+      <c r="F7" s="38">
         <f>INDEX(Planejado!$H6:$S6,$D$3)</f>
         <v/>
       </c>
-      <c r="G7" s="27">
+      <c r="G7" s="38">
         <f>INDEX(Realizado!$H6:$S6,$D$3)</f>
         <v/>
       </c>
-      <c r="H7" s="27">
+      <c r="H7" s="38">
         <f>G7-F7</f>
         <v/>
       </c>
-      <c r="I7" s="27">
+      <c r="I7" s="38">
         <f>SUMPRODUCT((COLUMN(Planejado!$H$4:$S$4)-COLUMN(Planejado!$H$4)+1&lt;=$D$3)*Planejado!$H6:$S6)</f>
         <v/>
       </c>
-      <c r="J7" s="27">
+      <c r="J7" s="38">
         <f>SUMPRODUCT((COLUMN(Realizado!$H$4:$S$4)-COLUMN(Realizado!$H$4)+1&lt;=$D$3)*Realizado!$H6:$S6)</f>
         <v/>
       </c>
-      <c r="K7" s="27">
+      <c r="K7" s="38">
         <f>J7-I7</f>
         <v/>
       </c>
-      <c r="L7" s="28">
+      <c r="L7" s="39">
         <f>IFERROR(K7/I7,"")</f>
         <v/>
       </c>
-      <c r="M7" s="28">
+      <c r="M7" s="39">
         <f>IFERROR(J7/I7,"")</f>
         <v/>
       </c>
-      <c r="N7" s="29" t="inlineStr">
+      <c r="N7" s="40" t="inlineStr">
         <is>
           <t>⚠ Base diferente</t>
         </is>
       </c>
-      <c r="O7" s="24">
+      <c r="O7" s="35">
         <f>IF(K7&gt;1,K7+ROW()/1000000,"")</f>
         <v/>
       </c>
-      <c r="P7" s="30">
+      <c r="P7" s="41">
         <f>SUMPRODUCT((COLUMN(Realizado!$H$4:$S$4)-COLUMN(Realizado!$H$4)+1&lt;=$D$3)*(Realizado!$H6:$S6&lt;&gt;""))</f>
         <v/>
       </c>
+      <c r="Q7" s="42" t="n"/>
+      <c r="R7" s="42">
+        <f>IF(AND(Q7&lt;&gt;"",Q7&lt;-1),-Q7+ROW()/1000000,"")</f>
+        <v/>
+      </c>
+      <c r="S7" s="42">
+        <f>IF(Q7="","",I7)</f>
+        <v/>
+      </c>
     </row>
     <row r="8" ht="24" customHeight="1">
-      <c r="A8" s="25">
+      <c r="A8" s="36">
         <f>Planejado!A7</f>
         <v/>
       </c>
-      <c r="B8" s="25">
+      <c r="B8" s="36">
         <f>Planejado!B7</f>
         <v/>
       </c>
-      <c r="C8" s="25">
+      <c r="C8" s="36">
         <f>Planejado!C7</f>
         <v/>
       </c>
-      <c r="D8" s="26">
+      <c r="D8" s="37">
         <f>Planejado!D7</f>
         <v/>
       </c>
-      <c r="E8" s="25">
+      <c r="E8" s="36">
         <f>Planejado!G7</f>
         <v/>
       </c>
-      <c r="F8" s="27">
+      <c r="F8" s="38">
         <f>INDEX(Planejado!$H7:$S7,$D$3)</f>
         <v/>
       </c>
-      <c r="G8" s="27">
+      <c r="G8" s="38">
         <f>INDEX(Realizado!$H7:$S7,$D$3)</f>
         <v/>
       </c>
-      <c r="H8" s="27">
+      <c r="H8" s="38">
         <f>G8-F8</f>
         <v/>
       </c>
-      <c r="I8" s="27">
+      <c r="I8" s="38">
         <f>SUMPRODUCT((COLUMN(Planejado!$H$4:$S$4)-COLUMN(Planejado!$H$4)+1&lt;=$D$3)*Planejado!$H7:$S7)</f>
         <v/>
       </c>
-      <c r="J8" s="27">
+      <c r="J8" s="38">
         <f>SUMPRODUCT((COLUMN(Realizado!$H$4:$S$4)-COLUMN(Realizado!$H$4)+1&lt;=$D$3)*Realizado!$H7:$S7)</f>
         <v/>
       </c>
-      <c r="K8" s="27">
+      <c r="K8" s="38">
         <f>J8-I8</f>
         <v/>
       </c>
-      <c r="L8" s="28">
+      <c r="L8" s="39">
         <f>IFERROR(K8/I8,"")</f>
         <v/>
       </c>
-      <c r="M8" s="28">
+      <c r="M8" s="39">
         <f>IFERROR(J8/I8,"")</f>
         <v/>
       </c>
-      <c r="N8" s="29">
+      <c r="N8" s="40">
         <f>IF(P8=0,"Sem lançamento",IF(AND(I8=0,J8=0),"—",IF(I8=0,"Não orçado",IF(K8&gt;0.05*I8,"Acima do orçado",IF(K8&lt;-0.05*I8,"Abaixo do orçado","Dentro do orçado")))))</f>
         <v/>
       </c>
-      <c r="O8" s="24">
+      <c r="O8" s="35">
         <f>IF(K8&gt;1,K8+ROW()/1000000,"")</f>
         <v/>
       </c>
-      <c r="P8" s="30">
+      <c r="P8" s="41">
         <f>SUMPRODUCT((COLUMN(Realizado!$H$4:$S$4)-COLUMN(Realizado!$H$4)+1&lt;=$D$3)*(Realizado!$H7:$S7&lt;&gt;""))</f>
         <v/>
       </c>
+      <c r="Q8" s="42">
+        <f>IF(P8=0,"",K8)</f>
+        <v/>
+      </c>
+      <c r="R8" s="42">
+        <f>IF(AND(Q8&lt;&gt;"",Q8&lt;-1),-Q8+ROW()/1000000,"")</f>
+        <v/>
+      </c>
+      <c r="S8" s="42">
+        <f>IF(Q8="","",I8)</f>
+        <v/>
+      </c>
     </row>
     <row r="9" ht="24" customHeight="1">
-      <c r="A9" s="25">
+      <c r="A9" s="36">
         <f>Planejado!A8</f>
         <v/>
       </c>
-      <c r="B9" s="25">
+      <c r="B9" s="36">
         <f>Planejado!B8</f>
         <v/>
       </c>
-      <c r="C9" s="25">
+      <c r="C9" s="36">
         <f>Planejado!C8</f>
         <v/>
       </c>
-      <c r="D9" s="26">
+      <c r="D9" s="37">
         <f>Planejado!D8</f>
         <v/>
       </c>
-      <c r="E9" s="25">
+      <c r="E9" s="36">
         <f>Planejado!G8</f>
         <v/>
       </c>
-      <c r="F9" s="27">
+      <c r="F9" s="38">
         <f>INDEX(Planejado!$H8:$S8,$D$3)</f>
         <v/>
       </c>
-      <c r="G9" s="27">
+      <c r="G9" s="38">
         <f>INDEX(Realizado!$H8:$S8,$D$3)</f>
         <v/>
       </c>
-      <c r="H9" s="27">
+      <c r="H9" s="38">
         <f>G9-F9</f>
         <v/>
       </c>
-      <c r="I9" s="27">
+      <c r="I9" s="38">
         <f>SUMPRODUCT((COLUMN(Planejado!$H$4:$S$4)-COLUMN(Planejado!$H$4)+1&lt;=$D$3)*Planejado!$H8:$S8)</f>
         <v/>
       </c>
-      <c r="J9" s="27">
+      <c r="J9" s="38">
         <f>SUMPRODUCT((COLUMN(Realizado!$H$4:$S$4)-COLUMN(Realizado!$H$4)+1&lt;=$D$3)*Realizado!$H8:$S8)</f>
         <v/>
       </c>
-      <c r="K9" s="27">
+      <c r="K9" s="38">
         <f>J9-I9</f>
         <v/>
       </c>
-      <c r="L9" s="28">
+      <c r="L9" s="39">
         <f>IFERROR(K9/I9,"")</f>
         <v/>
       </c>
-      <c r="M9" s="28">
+      <c r="M9" s="39">
         <f>IFERROR(J9/I9,"")</f>
         <v/>
       </c>
-      <c r="N9" s="29">
+      <c r="N9" s="40">
         <f>IF(P9=0,"Sem lançamento",IF(AND(I9=0,J9=0),"—",IF(I9=0,"Não orçado",IF(K9&gt;0.05*I9,"Acima do orçado",IF(K9&lt;-0.05*I9,"Abaixo do orçado","Dentro do orçado")))))</f>
         <v/>
       </c>
-      <c r="O9" s="24">
+      <c r="O9" s="35">
         <f>IF(K9&gt;1,K9+ROW()/1000000,"")</f>
         <v/>
       </c>
-      <c r="P9" s="30">
+      <c r="P9" s="41">
         <f>SUMPRODUCT((COLUMN(Realizado!$H$4:$S$4)-COLUMN(Realizado!$H$4)+1&lt;=$D$3)*(Realizado!$H8:$S8&lt;&gt;""))</f>
         <v/>
       </c>
+      <c r="Q9" s="42">
+        <f>IF(P9=0,"",K9)</f>
+        <v/>
+      </c>
+      <c r="R9" s="42">
+        <f>IF(AND(Q9&lt;&gt;"",Q9&lt;-1),-Q9+ROW()/1000000,"")</f>
+        <v/>
+      </c>
+      <c r="S9" s="42">
+        <f>IF(Q9="","",I9)</f>
+        <v/>
+      </c>
     </row>
     <row r="10" ht="24" customHeight="1">
-      <c r="A10" s="25">
+      <c r="A10" s="36">
         <f>Planejado!A9</f>
         <v/>
       </c>
-      <c r="B10" s="25">
+      <c r="B10" s="36">
         <f>Planejado!B9</f>
         <v/>
       </c>
-      <c r="C10" s="25">
+      <c r="C10" s="36">
         <f>Planejado!C9</f>
         <v/>
       </c>
-      <c r="D10" s="26">
+      <c r="D10" s="37">
         <f>Planejado!D9</f>
         <v/>
       </c>
-      <c r="E10" s="25">
+      <c r="E10" s="36">
         <f>Planejado!G9</f>
         <v/>
       </c>
-      <c r="F10" s="27">
+      <c r="F10" s="38">
         <f>INDEX(Planejado!$H9:$S9,$D$3)</f>
         <v/>
       </c>
-      <c r="G10" s="27">
+      <c r="G10" s="38">
         <f>INDEX(Realizado!$H9:$S9,$D$3)</f>
         <v/>
       </c>
-      <c r="H10" s="27">
+      <c r="H10" s="38">
         <f>G10-F10</f>
         <v/>
       </c>
-      <c r="I10" s="27">
+      <c r="I10" s="38">
         <f>SUMPRODUCT((COLUMN(Planejado!$H$4:$S$4)-COLUMN(Planejado!$H$4)+1&lt;=$D$3)*Planejado!$H9:$S9)</f>
         <v/>
       </c>
-      <c r="J10" s="27">
+      <c r="J10" s="38">
         <f>SUMPRODUCT((COLUMN(Realizado!$H$4:$S$4)-COLUMN(Realizado!$H$4)+1&lt;=$D$3)*Realizado!$H9:$S9)</f>
         <v/>
       </c>
-      <c r="K10" s="27">
+      <c r="K10" s="38">
         <f>J10-I10</f>
         <v/>
       </c>
-      <c r="L10" s="28">
+      <c r="L10" s="39">
         <f>IFERROR(K10/I10,"")</f>
         <v/>
       </c>
-      <c r="M10" s="28">
+      <c r="M10" s="39">
         <f>IFERROR(J10/I10,"")</f>
         <v/>
       </c>
-      <c r="N10" s="29">
+      <c r="N10" s="40">
         <f>IF(P10=0,"Sem lançamento",IF(AND(I10=0,J10=0),"—",IF(I10=0,"Não orçado",IF(K10&gt;0.05*I10,"Acima do orçado",IF(K10&lt;-0.05*I10,"Abaixo do orçado","Dentro do orçado")))))</f>
         <v/>
       </c>
-      <c r="O10" s="24">
+      <c r="O10" s="35">
         <f>IF(K10&gt;1,K10+ROW()/1000000,"")</f>
         <v/>
       </c>
-      <c r="P10" s="30">
+      <c r="P10" s="41">
         <f>SUMPRODUCT((COLUMN(Realizado!$H$4:$S$4)-COLUMN(Realizado!$H$4)+1&lt;=$D$3)*(Realizado!$H9:$S9&lt;&gt;""))</f>
         <v/>
       </c>
+      <c r="Q10" s="42">
+        <f>IF(P10=0,"",K10)</f>
+        <v/>
+      </c>
+      <c r="R10" s="42">
+        <f>IF(AND(Q10&lt;&gt;"",Q10&lt;-1),-Q10+ROW()/1000000,"")</f>
+        <v/>
+      </c>
+      <c r="S10" s="42">
+        <f>IF(Q10="","",I10)</f>
+        <v/>
+      </c>
     </row>
     <row r="11" ht="24" customHeight="1">
-      <c r="A11" s="25">
+      <c r="A11" s="36">
         <f>Planejado!A10</f>
         <v/>
       </c>
-      <c r="B11" s="25">
+      <c r="B11" s="36">
         <f>Planejado!B10</f>
         <v/>
       </c>
-      <c r="C11" s="25">
+      <c r="C11" s="36">
         <f>Planejado!C10</f>
         <v/>
       </c>
-      <c r="D11" s="26">
+      <c r="D11" s="37">
         <f>Planejado!D10</f>
         <v/>
       </c>
-      <c r="E11" s="25">
+      <c r="E11" s="36">
         <f>Planejado!G10</f>
         <v/>
       </c>
-      <c r="F11" s="27">
+      <c r="F11" s="38">
         <f>INDEX(Planejado!$H10:$S10,$D$3)</f>
         <v/>
       </c>
-      <c r="G11" s="27">
+      <c r="G11" s="38">
         <f>INDEX(Realizado!$H10:$S10,$D$3)</f>
         <v/>
       </c>
-      <c r="H11" s="27">
+      <c r="H11" s="38">
         <f>G11-F11</f>
         <v/>
       </c>
-      <c r="I11" s="27">
+      <c r="I11" s="38">
         <f>SUMPRODUCT((COLUMN(Planejado!$H$4:$S$4)-COLUMN(Planejado!$H$4)+1&lt;=$D$3)*Planejado!$H10:$S10)</f>
         <v/>
       </c>
-      <c r="J11" s="27">
+      <c r="J11" s="38">
         <f>SUMPRODUCT((COLUMN(Realizado!$H$4:$S$4)-COLUMN(Realizado!$H$4)+1&lt;=$D$3)*Realizado!$H10:$S10)</f>
         <v/>
       </c>
-      <c r="K11" s="27">
+      <c r="K11" s="38">
         <f>J11-I11</f>
         <v/>
       </c>
-      <c r="L11" s="28">
+      <c r="L11" s="39">
         <f>IFERROR(K11/I11,"")</f>
         <v/>
       </c>
-      <c r="M11" s="28">
+      <c r="M11" s="39">
         <f>IFERROR(J11/I11,"")</f>
         <v/>
       </c>
-      <c r="N11" s="29">
+      <c r="N11" s="40">
         <f>IF(P11=0,"Sem lançamento",IF(AND(I11=0,J11=0),"—",IF(I11=0,"Não orçado",IF(K11&gt;0.05*I11,"Acima do orçado",IF(K11&lt;-0.05*I11,"Abaixo do orçado","Dentro do orçado")))))</f>
         <v/>
       </c>
-      <c r="O11" s="24">
+      <c r="O11" s="35">
         <f>IF(K11&gt;1,K11+ROW()/1000000,"")</f>
         <v/>
       </c>
-      <c r="P11" s="30">
+      <c r="P11" s="41">
         <f>SUMPRODUCT((COLUMN(Realizado!$H$4:$S$4)-COLUMN(Realizado!$H$4)+1&lt;=$D$3)*(Realizado!$H10:$S10&lt;&gt;""))</f>
         <v/>
       </c>
+      <c r="Q11" s="42">
+        <f>IF(P11=0,"",K11)</f>
+        <v/>
+      </c>
+      <c r="R11" s="42">
+        <f>IF(AND(Q11&lt;&gt;"",Q11&lt;-1),-Q11+ROW()/1000000,"")</f>
+        <v/>
+      </c>
+      <c r="S11" s="42">
+        <f>IF(Q11="","",I11)</f>
+        <v/>
+      </c>
     </row>
     <row r="12" ht="24" customHeight="1">
-      <c r="A12" s="25">
+      <c r="A12" s="36">
         <f>Planejado!A11</f>
         <v/>
       </c>
-      <c r="B12" s="25">
+      <c r="B12" s="36">
         <f>Planejado!B11</f>
         <v/>
       </c>
-      <c r="C12" s="25">
+      <c r="C12" s="36">
         <f>Planejado!C11</f>
         <v/>
       </c>
-      <c r="D12" s="26">
+      <c r="D12" s="37">
         <f>Planejado!D11</f>
         <v/>
       </c>
-      <c r="E12" s="25">
+      <c r="E12" s="36">
         <f>Planejado!G11</f>
         <v/>
       </c>
-      <c r="F12" s="27">
+      <c r="F12" s="38">
         <f>INDEX(Planejado!$H11:$S11,$D$3)</f>
         <v/>
       </c>
-      <c r="G12" s="27">
+      <c r="G12" s="38">
         <f>INDEX(Realizado!$H11:$S11,$D$3)</f>
         <v/>
       </c>
-      <c r="H12" s="27">
+      <c r="H12" s="38">
         <f>G12-F12</f>
         <v/>
       </c>
-      <c r="I12" s="27">
+      <c r="I12" s="38">
         <f>SUMPRODUCT((COLUMN(Planejado!$H$4:$S$4)-COLUMN(Planejado!$H$4)+1&lt;=$D$3)*Planejado!$H11:$S11)</f>
         <v/>
       </c>
-      <c r="J12" s="27">
+      <c r="J12" s="38">
         <f>SUMPRODUCT((COLUMN(Realizado!$H$4:$S$4)-COLUMN(Realizado!$H$4)+1&lt;=$D$3)*Realizado!$H11:$S11)</f>
         <v/>
       </c>
-      <c r="K12" s="27">
+      <c r="K12" s="38">
         <f>J12-I12</f>
         <v/>
       </c>
-      <c r="L12" s="28">
+      <c r="L12" s="39">
         <f>IFERROR(K12/I12,"")</f>
         <v/>
       </c>
-      <c r="M12" s="28">
+      <c r="M12" s="39">
         <f>IFERROR(J12/I12,"")</f>
         <v/>
       </c>
-      <c r="N12" s="29">
+      <c r="N12" s="40">
         <f>IF(P12=0,"Sem lançamento",IF(AND(I12=0,J12=0),"—",IF(I12=0,"Não orçado",IF(K12&gt;0.05*I12,"Acima do orçado",IF(K12&lt;-0.05*I12,"Abaixo do orçado","Dentro do orçado")))))</f>
         <v/>
       </c>
-      <c r="O12" s="24">
+      <c r="O12" s="35">
         <f>IF(K12&gt;1,K12+ROW()/1000000,"")</f>
         <v/>
       </c>
-      <c r="P12" s="30">
+      <c r="P12" s="41">
         <f>SUMPRODUCT((COLUMN(Realizado!$H$4:$S$4)-COLUMN(Realizado!$H$4)+1&lt;=$D$3)*(Realizado!$H11:$S11&lt;&gt;""))</f>
         <v/>
       </c>
+      <c r="Q12" s="42">
+        <f>IF(P12=0,"",K12)</f>
+        <v/>
+      </c>
+      <c r="R12" s="42">
+        <f>IF(AND(Q12&lt;&gt;"",Q12&lt;-1),-Q12+ROW()/1000000,"")</f>
+        <v/>
+      </c>
+      <c r="S12" s="42">
+        <f>IF(Q12="","",I12)</f>
+        <v/>
+      </c>
     </row>
     <row r="13" ht="24" customHeight="1">
-      <c r="A13" s="25">
+      <c r="A13" s="36">
         <f>Planejado!A12</f>
         <v/>
       </c>
-      <c r="B13" s="25">
+      <c r="B13" s="36">
         <f>Planejado!B12</f>
         <v/>
       </c>
-      <c r="C13" s="25">
+      <c r="C13" s="36">
         <f>Planejado!C12</f>
         <v/>
       </c>
-      <c r="D13" s="26">
+      <c r="D13" s="37">
         <f>Planejado!D12</f>
         <v/>
       </c>
-      <c r="E13" s="25">
+      <c r="E13" s="36">
         <f>Planejado!G12</f>
         <v/>
       </c>
-      <c r="F13" s="27">
+      <c r="F13" s="38">
         <f>INDEX(Planejado!$H12:$S12,$D$3)</f>
         <v/>
       </c>
-      <c r="G13" s="27">
+      <c r="G13" s="38">
         <f>INDEX(Realizado!$H12:$S12,$D$3)</f>
         <v/>
       </c>
-      <c r="H13" s="27">
+      <c r="H13" s="38">
         <f>G13-F13</f>
         <v/>
       </c>
-      <c r="I13" s="27">
+      <c r="I13" s="38">
         <f>SUMPRODUCT((COLUMN(Planejado!$H$4:$S$4)-COLUMN(Planejado!$H$4)+1&lt;=$D$3)*Planejado!$H12:$S12)</f>
         <v/>
       </c>
-      <c r="J13" s="27">
+      <c r="J13" s="38">
         <f>SUMPRODUCT((COLUMN(Realizado!$H$4:$S$4)-COLUMN(Realizado!$H$4)+1&lt;=$D$3)*Realizado!$H12:$S12)</f>
         <v/>
       </c>
-      <c r="K13" s="27">
+      <c r="K13" s="38">
         <f>J13-I13</f>
         <v/>
       </c>
-      <c r="L13" s="28">
+      <c r="L13" s="39">
         <f>IFERROR(K13/I13,"")</f>
         <v/>
       </c>
-      <c r="M13" s="28">
+      <c r="M13" s="39">
         <f>IFERROR(J13/I13,"")</f>
         <v/>
       </c>
-      <c r="N13" s="29">
+      <c r="N13" s="40">
         <f>IF(P13=0,"Sem lançamento",IF(AND(I13=0,J13=0),"—",IF(I13=0,"Não orçado",IF(K13&gt;0.05*I13,"Acima do orçado",IF(K13&lt;-0.05*I13,"Abaixo do orçado","Dentro do orçado")))))</f>
         <v/>
       </c>
-      <c r="O13" s="24">
+      <c r="O13" s="35">
         <f>IF(K13&gt;1,K13+ROW()/1000000,"")</f>
         <v/>
       </c>
-      <c r="P13" s="30">
+      <c r="P13" s="41">
         <f>SUMPRODUCT((COLUMN(Realizado!$H$4:$S$4)-COLUMN(Realizado!$H$4)+1&lt;=$D$3)*(Realizado!$H12:$S12&lt;&gt;""))</f>
         <v/>
       </c>
+      <c r="Q13" s="42">
+        <f>IF(P13=0,"",K13)</f>
+        <v/>
+      </c>
+      <c r="R13" s="42">
+        <f>IF(AND(Q13&lt;&gt;"",Q13&lt;-1),-Q13+ROW()/1000000,"")</f>
+        <v/>
+      </c>
+      <c r="S13" s="42">
+        <f>IF(Q13="","",I13)</f>
+        <v/>
+      </c>
     </row>
     <row r="14" ht="24" customHeight="1">
-      <c r="A14" s="25">
+      <c r="A14" s="36">
         <f>Planejado!A13</f>
         <v/>
       </c>
-      <c r="B14" s="25">
+      <c r="B14" s="36">
         <f>Planejado!B13</f>
         <v/>
       </c>
-      <c r="C14" s="25">
+      <c r="C14" s="36">
         <f>Planejado!C13</f>
         <v/>
       </c>
-      <c r="D14" s="26">
+      <c r="D14" s="37">
         <f>Planejado!D13</f>
         <v/>
       </c>
-      <c r="E14" s="25">
+      <c r="E14" s="36">
         <f>Planejado!G13</f>
         <v/>
       </c>
-      <c r="F14" s="27">
+      <c r="F14" s="38">
         <f>INDEX(Planejado!$H13:$S13,$D$3)</f>
         <v/>
       </c>
-      <c r="G14" s="27">
+      <c r="G14" s="38">
         <f>INDEX(Realizado!$H13:$S13,$D$3)</f>
         <v/>
       </c>
-      <c r="H14" s="27">
+      <c r="H14" s="38">
         <f>G14-F14</f>
         <v/>
       </c>
-      <c r="I14" s="27">
+      <c r="I14" s="38">
         <f>SUMPRODUCT((COLUMN(Planejado!$H$4:$S$4)-COLUMN(Planejado!$H$4)+1&lt;=$D$3)*Planejado!$H13:$S13)</f>
         <v/>
       </c>
-      <c r="J14" s="27">
+      <c r="J14" s="38">
         <f>SUMPRODUCT((COLUMN(Realizado!$H$4:$S$4)-COLUMN(Realizado!$H$4)+1&lt;=$D$3)*Realizado!$H13:$S13)</f>
         <v/>
       </c>
-      <c r="K14" s="27">
+      <c r="K14" s="38">
         <f>J14-I14</f>
         <v/>
       </c>
-      <c r="L14" s="28">
+      <c r="L14" s="39">
         <f>IFERROR(K14/I14,"")</f>
         <v/>
       </c>
-      <c r="M14" s="28">
+      <c r="M14" s="39">
         <f>IFERROR(J14/I14,"")</f>
         <v/>
       </c>
-      <c r="N14" s="29">
+      <c r="N14" s="40">
         <f>IF(P14=0,"Sem lançamento",IF(AND(I14=0,J14=0),"—",IF(I14=0,"Não orçado",IF(K14&gt;0.05*I14,"Acima do orçado",IF(K14&lt;-0.05*I14,"Abaixo do orçado","Dentro do orçado")))))</f>
         <v/>
       </c>
-      <c r="O14" s="24">
+      <c r="O14" s="35">
         <f>IF(K14&gt;1,K14+ROW()/1000000,"")</f>
         <v/>
       </c>
-      <c r="P14" s="30">
+      <c r="P14" s="41">
         <f>SUMPRODUCT((COLUMN(Realizado!$H$4:$S$4)-COLUMN(Realizado!$H$4)+1&lt;=$D$3)*(Realizado!$H13:$S13&lt;&gt;""))</f>
         <v/>
       </c>
+      <c r="Q14" s="42">
+        <f>IF(P14=0,"",K14)</f>
+        <v/>
+      </c>
+      <c r="R14" s="42">
+        <f>IF(AND(Q14&lt;&gt;"",Q14&lt;-1),-Q14+ROW()/1000000,"")</f>
+        <v/>
+      </c>
+      <c r="S14" s="42">
+        <f>IF(Q14="","",I14)</f>
+        <v/>
+      </c>
     </row>
     <row r="27">
-      <c r="A27" s="31" t="inlineStr">
+      <c r="A27" s="43" t="inlineStr">
         <is>
           <t>TOTAL GERAL</t>
         </is>
       </c>
-      <c r="B27" s="31" t="n"/>
-      <c r="C27" s="31" t="n"/>
-      <c r="D27" s="31" t="n"/>
-      <c r="E27" s="31" t="n"/>
-      <c r="F27" s="32">
+      <c r="B27" s="43" t="n"/>
+      <c r="C27" s="43" t="n"/>
+      <c r="D27" s="43" t="n"/>
+      <c r="E27" s="43" t="n"/>
+      <c r="F27" s="44">
         <f>SUM(F6:F14)</f>
         <v/>
       </c>
-      <c r="G27" s="32">
+      <c r="G27" s="44">
         <f>SUM(G6:G14)</f>
         <v/>
       </c>
-      <c r="H27" s="32">
+      <c r="H27" s="44">
         <f>SUM(H6:H14)</f>
         <v/>
       </c>
-      <c r="I27" s="32">
+      <c r="I27" s="44">
         <f>SUM(I6:I14)</f>
         <v/>
       </c>
-      <c r="J27" s="32">
+      <c r="J27" s="44">
         <f>SUM(J6:J14)</f>
         <v/>
       </c>
-      <c r="K27" s="32">
+      <c r="K27" s="44">
         <f>SUM(K6:K14)</f>
         <v/>
       </c>
-      <c r="L27" s="33">
+      <c r="L27" s="45">
         <f>IFERROR(K27/I27,"")</f>
         <v/>
       </c>
-      <c r="M27" s="33">
+      <c r="M27" s="45">
         <f>IFERROR(J27/I27,"")</f>
         <v/>
       </c>
-      <c r="N27" s="31" t="n"/>
+      <c r="N27" s="43" t="n"/>
     </row>
   </sheetData>
   <autoFilter ref="A5:N14"/>
@@ -2406,723 +2918,723 @@
       </c>
     </row>
     <row r="5" ht="26" customHeight="1">
-      <c r="A5" s="25" t="inlineStr">
+      <c r="A5" s="36" t="inlineStr">
         <is>
           <t>JUR-E01</t>
         </is>
       </c>
-      <c r="B5" s="25" t="inlineStr">
+      <c r="B5" s="36" t="inlineStr">
         <is>
           <t>Jurídico</t>
         </is>
       </c>
-      <c r="C5" s="25" t="inlineStr">
+      <c r="C5" s="36" t="inlineStr">
         <is>
           <t>Equipe</t>
         </is>
       </c>
-      <c r="D5" s="26" t="inlineStr">
+      <c r="D5" s="37" t="inlineStr">
         <is>
           <t>Miguel Clepf</t>
         </is>
       </c>
-      <c r="E5" s="26" t="inlineStr">
+      <c r="E5" s="37" t="inlineStr">
         <is>
           <t>Advogado Júnior</t>
         </is>
       </c>
-      <c r="F5" s="25" t="inlineStr">
+      <c r="F5" s="36" t="inlineStr">
         <is>
           <t>PJ</t>
         </is>
       </c>
-      <c r="G5" s="25" t="inlineStr">
+      <c r="G5" s="36" t="inlineStr">
         <is>
           <t>Pessoal - PJ</t>
         </is>
       </c>
-      <c r="H5" s="27" t="n">
+      <c r="H5" s="38" t="n">
         <v>10000</v>
       </c>
-      <c r="I5" s="27" t="n">
+      <c r="I5" s="38" t="n">
         <v>10000</v>
       </c>
-      <c r="J5" s="27" t="n">
+      <c r="J5" s="38" t="n">
         <v>10000</v>
       </c>
-      <c r="K5" s="27" t="n">
+      <c r="K5" s="38" t="n">
         <v>10000</v>
       </c>
-      <c r="L5" s="27" t="n">
+      <c r="L5" s="38" t="n">
         <v>10000</v>
       </c>
-      <c r="M5" s="27" t="n">
+      <c r="M5" s="38" t="n">
         <v>10000</v>
       </c>
-      <c r="N5" s="27" t="n">
+      <c r="N5" s="38" t="n">
         <v>10000</v>
       </c>
-      <c r="O5" s="27" t="n">
+      <c r="O5" s="38" t="n">
         <v>10000</v>
       </c>
-      <c r="P5" s="27" t="n">
+      <c r="P5" s="38" t="n">
         <v>10000</v>
       </c>
-      <c r="Q5" s="27" t="n">
+      <c r="Q5" s="38" t="n">
         <v>10000</v>
       </c>
-      <c r="R5" s="27" t="n">
+      <c r="R5" s="38" t="n">
         <v>10000</v>
       </c>
-      <c r="S5" s="27" t="n">
+      <c r="S5" s="38" t="n">
         <v>10000</v>
       </c>
-      <c r="T5" s="34">
+      <c r="T5" s="46">
         <f>SUM(H5:S5)</f>
         <v/>
       </c>
     </row>
     <row r="6" ht="26" customHeight="1">
-      <c r="A6" s="25" t="inlineStr">
+      <c r="A6" s="36" t="inlineStr">
         <is>
           <t>JUR-E02</t>
         </is>
       </c>
-      <c r="B6" s="25" t="inlineStr">
+      <c r="B6" s="36" t="inlineStr">
         <is>
           <t>Jurídico</t>
         </is>
       </c>
-      <c r="C6" s="25" t="inlineStr">
+      <c r="C6" s="36" t="inlineStr">
         <is>
           <t>Equipe</t>
         </is>
       </c>
-      <c r="D6" s="26" t="inlineStr">
+      <c r="D6" s="37" t="inlineStr">
         <is>
           <t>Geovanna</t>
         </is>
       </c>
-      <c r="E6" s="26" t="inlineStr">
+      <c r="E6" s="37" t="inlineStr">
         <is>
           <t>Analista Administrativo — orçada pelo custo total (encargos de folha + benefícios). Salário bruto informado: R$ 2.886,91/mês</t>
         </is>
       </c>
-      <c r="F6" s="25" t="inlineStr">
+      <c r="F6" s="36" t="inlineStr">
         <is>
           <t>CLT</t>
         </is>
       </c>
-      <c r="G6" s="25" t="inlineStr">
+      <c r="G6" s="36" t="inlineStr">
         <is>
           <t>Pessoal - CLT</t>
         </is>
       </c>
-      <c r="H6" s="27" t="n">
+      <c r="H6" s="38" t="n">
         <v>4825.515</v>
       </c>
-      <c r="I6" s="27" t="n">
+      <c r="I6" s="38" t="n">
         <v>4825.515</v>
       </c>
-      <c r="J6" s="27" t="n">
+      <c r="J6" s="38" t="n">
         <v>4825.515</v>
       </c>
-      <c r="K6" s="27" t="n">
+      <c r="K6" s="38" t="n">
         <v>4825.515</v>
       </c>
-      <c r="L6" s="27" t="n">
+      <c r="L6" s="38" t="n">
         <v>4825.515</v>
       </c>
-      <c r="M6" s="27" t="n">
+      <c r="M6" s="38" t="n">
         <v>4825.515</v>
       </c>
-      <c r="N6" s="27" t="n">
+      <c r="N6" s="38" t="n">
         <v>4825.515</v>
       </c>
-      <c r="O6" s="27" t="n">
+      <c r="O6" s="38" t="n">
         <v>4825.515</v>
       </c>
-      <c r="P6" s="27" t="n">
+      <c r="P6" s="38" t="n">
         <v>4825.515</v>
       </c>
-      <c r="Q6" s="27" t="n">
+      <c r="Q6" s="38" t="n">
         <v>4825.515</v>
       </c>
-      <c r="R6" s="27" t="n">
+      <c r="R6" s="38" t="n">
         <v>4825.515</v>
       </c>
-      <c r="S6" s="27" t="n">
+      <c r="S6" s="38" t="n">
         <v>4825.515</v>
       </c>
-      <c r="T6" s="34">
+      <c r="T6" s="46">
         <f>SUM(H6:S6)</f>
         <v/>
       </c>
     </row>
     <row r="7" ht="26" customHeight="1">
-      <c r="A7" s="25" t="inlineStr">
+      <c r="A7" s="36" t="inlineStr">
         <is>
           <t>JUR-E03</t>
         </is>
       </c>
-      <c r="B7" s="25" t="inlineStr">
+      <c r="B7" s="36" t="inlineStr">
         <is>
           <t>Jurídico</t>
         </is>
       </c>
-      <c r="C7" s="25" t="inlineStr">
+      <c r="C7" s="36" t="inlineStr">
         <is>
           <t>Equipe</t>
         </is>
       </c>
-      <c r="D7" s="26" t="inlineStr">
+      <c r="D7" s="37" t="inlineStr">
         <is>
           <t>Thamar Victória</t>
         </is>
       </c>
-      <c r="E7" s="26" t="inlineStr">
+      <c r="E7" s="37" t="inlineStr">
         <is>
           <t>Advogada — recebia R$ 4.500/mês em jan–mar e passou a R$ 5.500 em abr/26 (aumento de R$ 1.000), contra R$ 5.000 orçados. Planejado revisado para R$ 5.500 a partir de ago/26</t>
         </is>
       </c>
-      <c r="F7" s="25" t="inlineStr">
+      <c r="F7" s="36" t="inlineStr">
         <is>
           <t>PJ</t>
         </is>
       </c>
-      <c r="G7" s="25" t="inlineStr">
+      <c r="G7" s="36" t="inlineStr">
         <is>
           <t>Pessoal - PJ</t>
         </is>
       </c>
-      <c r="H7" s="27" t="n">
+      <c r="H7" s="38" t="n">
         <v>5000</v>
       </c>
-      <c r="I7" s="27" t="n">
+      <c r="I7" s="38" t="n">
         <v>5000</v>
       </c>
-      <c r="J7" s="27" t="n">
+      <c r="J7" s="38" t="n">
         <v>5000</v>
       </c>
-      <c r="K7" s="27" t="n">
+      <c r="K7" s="38" t="n">
         <v>5000</v>
       </c>
-      <c r="L7" s="27" t="n">
+      <c r="L7" s="38" t="n">
         <v>5000</v>
       </c>
-      <c r="M7" s="27" t="n">
+      <c r="M7" s="38" t="n">
         <v>5000</v>
       </c>
-      <c r="N7" s="27" t="n">
+      <c r="N7" s="38" t="n">
         <v>5000</v>
       </c>
-      <c r="O7" s="27" t="n">
+      <c r="O7" s="38" t="n">
         <v>5500</v>
       </c>
-      <c r="P7" s="27" t="n">
+      <c r="P7" s="38" t="n">
         <v>5500</v>
       </c>
-      <c r="Q7" s="27" t="n">
+      <c r="Q7" s="38" t="n">
         <v>5500</v>
       </c>
-      <c r="R7" s="27" t="n">
+      <c r="R7" s="38" t="n">
         <v>5500</v>
       </c>
-      <c r="S7" s="27" t="n">
+      <c r="S7" s="38" t="n">
         <v>5500</v>
       </c>
-      <c r="T7" s="34">
+      <c r="T7" s="46">
         <f>SUM(H7:S7)</f>
         <v/>
       </c>
     </row>
     <row r="8" ht="26" customHeight="1">
-      <c r="A8" s="25" t="inlineStr">
+      <c r="A8" s="36" t="inlineStr">
         <is>
           <t>JUR-D01</t>
         </is>
       </c>
-      <c r="B8" s="25" t="inlineStr">
+      <c r="B8" s="36" t="inlineStr">
         <is>
           <t>Jurídico</t>
         </is>
       </c>
-      <c r="C8" s="25" t="inlineStr">
+      <c r="C8" s="36" t="inlineStr">
         <is>
           <t>Despesas</t>
         </is>
       </c>
-      <c r="D8" s="26" t="inlineStr">
+      <c r="D8" s="37" t="inlineStr">
         <is>
           <t>JUSFY</t>
         </is>
       </c>
-      <c r="E8" s="26" t="inlineStr">
+      <c r="E8" s="37" t="inlineStr">
         <is>
           <t>Fase de teste com objetivo de eliminar o Astrea</t>
         </is>
       </c>
-      <c r="F8" s="25" t="inlineStr"/>
-      <c r="G8" s="25" t="inlineStr">
+      <c r="F8" s="36" t="inlineStr"/>
+      <c r="G8" s="36" t="inlineStr">
         <is>
           <t>Licenças de Softwares</t>
         </is>
       </c>
-      <c r="H8" s="27" t="n">
+      <c r="H8" s="38" t="n">
         <v>100</v>
       </c>
-      <c r="I8" s="27" t="n">
+      <c r="I8" s="38" t="n">
         <v>100</v>
       </c>
-      <c r="J8" s="27" t="n">
+      <c r="J8" s="38" t="n">
         <v>100</v>
       </c>
-      <c r="K8" s="27" t="n">
+      <c r="K8" s="38" t="n">
         <v>100</v>
       </c>
-      <c r="L8" s="27" t="n">
+      <c r="L8" s="38" t="n">
         <v>100</v>
       </c>
-      <c r="M8" s="27" t="n">
+      <c r="M8" s="38" t="n">
         <v>100</v>
       </c>
-      <c r="N8" s="27" t="n">
+      <c r="N8" s="38" t="n">
         <v>100</v>
       </c>
-      <c r="O8" s="27" t="n">
+      <c r="O8" s="38" t="n">
         <v>100</v>
       </c>
-      <c r="P8" s="27" t="n">
+      <c r="P8" s="38" t="n">
         <v>100</v>
       </c>
-      <c r="Q8" s="27" t="n">
+      <c r="Q8" s="38" t="n">
         <v>100</v>
       </c>
-      <c r="R8" s="27" t="n">
+      <c r="R8" s="38" t="n">
         <v>100</v>
       </c>
-      <c r="S8" s="27" t="n">
+      <c r="S8" s="38" t="n">
         <v>100</v>
       </c>
-      <c r="T8" s="34">
+      <c r="T8" s="46">
         <f>SUM(H8:S8)</f>
         <v/>
       </c>
     </row>
     <row r="9" ht="26" customHeight="1">
-      <c r="A9" s="25" t="inlineStr">
+      <c r="A9" s="36" t="inlineStr">
         <is>
           <t>JUR-D02</t>
         </is>
       </c>
-      <c r="B9" s="25" t="inlineStr">
+      <c r="B9" s="36" t="inlineStr">
         <is>
           <t>Jurídico</t>
         </is>
       </c>
-      <c r="C9" s="25" t="inlineStr">
+      <c r="C9" s="36" t="inlineStr">
         <is>
           <t>Despesas</t>
         </is>
       </c>
-      <c r="D9" s="26" t="inlineStr">
+      <c r="D9" s="37" t="inlineStr">
         <is>
           <t>JUSBRASIL</t>
         </is>
       </c>
-      <c r="E9" s="26" t="inlineStr"/>
-      <c r="F9" s="25" t="inlineStr"/>
-      <c r="G9" s="25" t="inlineStr">
+      <c r="E9" s="37" t="inlineStr"/>
+      <c r="F9" s="36" t="inlineStr"/>
+      <c r="G9" s="36" t="inlineStr">
         <is>
           <t>Licenças de Softwares</t>
         </is>
       </c>
-      <c r="H9" s="27" t="n">
+      <c r="H9" s="38" t="n">
         <v>104.9</v>
       </c>
-      <c r="I9" s="27" t="n">
+      <c r="I9" s="38" t="n">
         <v>104.9</v>
       </c>
-      <c r="J9" s="27" t="n">
+      <c r="J9" s="38" t="n">
         <v>104.9</v>
       </c>
-      <c r="K9" s="27" t="n">
+      <c r="K9" s="38" t="n">
         <v>104.9</v>
       </c>
-      <c r="L9" s="27" t="n">
+      <c r="L9" s="38" t="n">
         <v>104.9</v>
       </c>
-      <c r="M9" s="27" t="n">
+      <c r="M9" s="38" t="n">
         <v>104.9</v>
       </c>
-      <c r="N9" s="27" t="n">
+      <c r="N9" s="38" t="n">
         <v>104.9</v>
       </c>
-      <c r="O9" s="27" t="n">
+      <c r="O9" s="38" t="n">
         <v>104.9</v>
       </c>
-      <c r="P9" s="27" t="n">
+      <c r="P9" s="38" t="n">
         <v>104.9</v>
       </c>
-      <c r="Q9" s="27" t="n">
+      <c r="Q9" s="38" t="n">
         <v>104.9</v>
       </c>
-      <c r="R9" s="27" t="n">
+      <c r="R9" s="38" t="n">
         <v>104.9</v>
       </c>
-      <c r="S9" s="27" t="n">
+      <c r="S9" s="38" t="n">
         <v>104.9</v>
       </c>
-      <c r="T9" s="34">
+      <c r="T9" s="46">
         <f>SUM(H9:S9)</f>
         <v/>
       </c>
     </row>
     <row r="10" ht="26" customHeight="1">
-      <c r="A10" s="25" t="inlineStr">
+      <c r="A10" s="36" t="inlineStr">
         <is>
           <t>JUR-D03</t>
         </is>
       </c>
-      <c r="B10" s="25" t="inlineStr">
+      <c r="B10" s="36" t="inlineStr">
         <is>
           <t>Jurídico</t>
         </is>
       </c>
-      <c r="C10" s="25" t="inlineStr">
+      <c r="C10" s="36" t="inlineStr">
         <is>
           <t>Despesas</t>
         </is>
       </c>
-      <c r="D10" s="26" t="inlineStr">
+      <c r="D10" s="37" t="inlineStr">
         <is>
           <t>ASTREA</t>
         </is>
       </c>
-      <c r="E10" s="26" t="inlineStr">
+      <c r="E10" s="37" t="inlineStr">
         <is>
           <t>Cancelado — realizado zerado desde mai/26</t>
         </is>
       </c>
-      <c r="F10" s="25" t="inlineStr"/>
-      <c r="G10" s="25" t="inlineStr">
+      <c r="F10" s="36" t="inlineStr"/>
+      <c r="G10" s="36" t="inlineStr">
         <is>
           <t>Licenças de Softwares</t>
         </is>
       </c>
-      <c r="H10" s="27" t="n">
+      <c r="H10" s="38" t="n">
         <v>112.07</v>
       </c>
-      <c r="I10" s="27" t="n">
+      <c r="I10" s="38" t="n">
         <v>112.07</v>
       </c>
-      <c r="J10" s="27" t="n">
+      <c r="J10" s="38" t="n">
         <v>112.07</v>
       </c>
-      <c r="K10" s="27" t="n">
+      <c r="K10" s="38" t="n">
         <v>112.07</v>
       </c>
-      <c r="L10" s="27" t="n">
+      <c r="L10" s="38" t="n">
         <v>112.07</v>
       </c>
-      <c r="M10" s="27" t="n">
+      <c r="M10" s="38" t="n">
         <v>112.07</v>
       </c>
-      <c r="N10" s="27" t="n">
+      <c r="N10" s="38" t="n">
         <v>112.07</v>
       </c>
-      <c r="O10" s="27" t="n">
+      <c r="O10" s="38" t="n">
         <v>112.07</v>
       </c>
-      <c r="P10" s="27" t="n">
+      <c r="P10" s="38" t="n">
         <v>112.07</v>
       </c>
-      <c r="Q10" s="27" t="n">
+      <c r="Q10" s="38" t="n">
         <v>112.07</v>
       </c>
-      <c r="R10" s="27" t="n">
+      <c r="R10" s="38" t="n">
         <v>112.07</v>
       </c>
-      <c r="S10" s="27" t="n">
+      <c r="S10" s="38" t="n">
         <v>112.07</v>
       </c>
-      <c r="T10" s="34">
+      <c r="T10" s="46">
         <f>SUM(H10:S10)</f>
         <v/>
       </c>
     </row>
     <row r="11" ht="26" customHeight="1">
-      <c r="A11" s="25" t="inlineStr">
+      <c r="A11" s="36" t="inlineStr">
         <is>
           <t>JUR-D04</t>
         </is>
       </c>
-      <c r="B11" s="25" t="inlineStr">
+      <c r="B11" s="36" t="inlineStr">
         <is>
           <t>Jurídico</t>
         </is>
       </c>
-      <c r="C11" s="25" t="inlineStr">
+      <c r="C11" s="36" t="inlineStr">
         <is>
           <t>Despesas</t>
         </is>
       </c>
-      <c r="D11" s="26" t="inlineStr">
+      <c r="D11" s="37" t="inlineStr">
         <is>
           <t>LEME</t>
         </is>
       </c>
-      <c r="E11" s="26" t="inlineStr"/>
-      <c r="F11" s="25" t="inlineStr"/>
-      <c r="G11" s="25" t="inlineStr">
+      <c r="E11" s="37" t="inlineStr"/>
+      <c r="F11" s="36" t="inlineStr"/>
+      <c r="G11" s="36" t="inlineStr">
         <is>
           <t>Licenças de Softwares</t>
         </is>
       </c>
-      <c r="H11" s="27" t="n">
+      <c r="H11" s="38" t="n">
         <v>1030</v>
       </c>
-      <c r="I11" s="27" t="n">
+      <c r="I11" s="38" t="n">
         <v>1030</v>
       </c>
-      <c r="J11" s="27" t="n">
+      <c r="J11" s="38" t="n">
         <v>1030</v>
       </c>
-      <c r="K11" s="27" t="n">
+      <c r="K11" s="38" t="n">
         <v>1030</v>
       </c>
-      <c r="L11" s="27" t="n">
+      <c r="L11" s="38" t="n">
         <v>1030</v>
       </c>
-      <c r="M11" s="27" t="n">
+      <c r="M11" s="38" t="n">
         <v>1030</v>
       </c>
-      <c r="N11" s="27" t="n">
+      <c r="N11" s="38" t="n">
         <v>1030</v>
       </c>
-      <c r="O11" s="27" t="n">
+      <c r="O11" s="38" t="n">
         <v>1030</v>
       </c>
-      <c r="P11" s="27" t="n">
+      <c r="P11" s="38" t="n">
         <v>1030</v>
       </c>
-      <c r="Q11" s="27" t="n">
+      <c r="Q11" s="38" t="n">
         <v>1030</v>
       </c>
-      <c r="R11" s="27" t="n">
+      <c r="R11" s="38" t="n">
         <v>1030</v>
       </c>
-      <c r="S11" s="27" t="n">
+      <c r="S11" s="38" t="n">
         <v>1030</v>
       </c>
-      <c r="T11" s="34">
+      <c r="T11" s="46">
         <f>SUM(H11:S11)</f>
         <v/>
       </c>
     </row>
     <row r="12" ht="26" customHeight="1">
-      <c r="A12" s="25" t="inlineStr">
+      <c r="A12" s="36" t="inlineStr">
         <is>
           <t>JUR-D05</t>
         </is>
       </c>
-      <c r="B12" s="25" t="inlineStr">
+      <c r="B12" s="36" t="inlineStr">
         <is>
           <t>Jurídico</t>
         </is>
       </c>
-      <c r="C12" s="25" t="inlineStr">
+      <c r="C12" s="36" t="inlineStr">
         <is>
           <t>Despesas</t>
         </is>
       </c>
-      <c r="D12" s="26" t="inlineStr">
+      <c r="D12" s="37" t="inlineStr">
         <is>
           <t>Cursos / Eventos / Network</t>
         </is>
       </c>
-      <c r="E12" s="26" t="inlineStr"/>
-      <c r="F12" s="25" t="inlineStr"/>
-      <c r="G12" s="25" t="inlineStr">
+      <c r="E12" s="37" t="inlineStr"/>
+      <c r="F12" s="36" t="inlineStr"/>
+      <c r="G12" s="36" t="inlineStr">
         <is>
           <t>Custeio de Treinamento</t>
         </is>
       </c>
-      <c r="H12" s="27" t="n">
+      <c r="H12" s="38" t="n">
         <v>1000</v>
       </c>
-      <c r="I12" s="27" t="n">
+      <c r="I12" s="38" t="n">
         <v>1000</v>
       </c>
-      <c r="J12" s="27" t="n">
+      <c r="J12" s="38" t="n">
         <v>1000</v>
       </c>
-      <c r="K12" s="27" t="n">
+      <c r="K12" s="38" t="n">
         <v>1000</v>
       </c>
-      <c r="L12" s="27" t="n">
+      <c r="L12" s="38" t="n">
         <v>1000</v>
       </c>
-      <c r="M12" s="27" t="n">
+      <c r="M12" s="38" t="n">
         <v>1000</v>
       </c>
-      <c r="N12" s="27" t="n">
+      <c r="N12" s="38" t="n">
         <v>1000</v>
       </c>
-      <c r="O12" s="27" t="n">
+      <c r="O12" s="38" t="n">
         <v>1000</v>
       </c>
-      <c r="P12" s="27" t="n">
+      <c r="P12" s="38" t="n">
         <v>1000</v>
       </c>
-      <c r="Q12" s="27" t="n">
+      <c r="Q12" s="38" t="n">
         <v>1000</v>
       </c>
-      <c r="R12" s="27" t="n">
+      <c r="R12" s="38" t="n">
         <v>1000</v>
       </c>
-      <c r="S12" s="27" t="n">
+      <c r="S12" s="38" t="n">
         <v>1000</v>
       </c>
-      <c r="T12" s="34">
+      <c r="T12" s="46">
         <f>SUM(H12:S12)</f>
         <v/>
       </c>
     </row>
     <row r="13" ht="26" customHeight="1">
-      <c r="A13" s="25" t="inlineStr">
+      <c r="A13" s="36" t="inlineStr">
         <is>
           <t>JUR-D06</t>
         </is>
       </c>
-      <c r="B13" s="25" t="inlineStr">
+      <c r="B13" s="36" t="inlineStr">
         <is>
           <t>Jurídico</t>
         </is>
       </c>
-      <c r="C13" s="25" t="inlineStr">
+      <c r="C13" s="36" t="inlineStr">
         <is>
           <t>Despesas</t>
         </is>
       </c>
-      <c r="D13" s="26" t="inlineStr">
+      <c r="D13" s="37" t="inlineStr">
         <is>
           <t>Bonificações trimestrais/semestrais do time</t>
         </is>
       </c>
-      <c r="E13" s="26" t="inlineStr">
+      <c r="E13" s="37" t="inlineStr">
         <is>
           <t>Participação em projetos e atingimento de resultados — CONFIRMAR se houve parcela no 1º quadrimestre</t>
         </is>
       </c>
-      <c r="F13" s="25" t="inlineStr"/>
-      <c r="G13" s="25" t="inlineStr">
+      <c r="F13" s="36" t="inlineStr"/>
+      <c r="G13" s="36" t="inlineStr">
         <is>
           <t>Prêmios</t>
         </is>
       </c>
-      <c r="H13" s="27" t="n">
+      <c r="H13" s="38" t="n">
         <v>0</v>
       </c>
-      <c r="I13" s="27" t="n">
+      <c r="I13" s="38" t="n">
         <v>0</v>
       </c>
-      <c r="J13" s="27" t="n">
+      <c r="J13" s="38" t="n">
         <v>0</v>
       </c>
-      <c r="K13" s="27" t="n">
+      <c r="K13" s="38" t="n">
         <v>0</v>
       </c>
-      <c r="L13" s="27" t="n">
+      <c r="L13" s="38" t="n">
         <v>0</v>
       </c>
-      <c r="M13" s="27" t="n">
+      <c r="M13" s="38" t="n">
         <v>0</v>
       </c>
-      <c r="N13" s="27" t="n">
+      <c r="N13" s="38" t="n">
         <v>0</v>
       </c>
-      <c r="O13" s="27" t="n">
+      <c r="O13" s="38" t="n">
         <v>10293.6</v>
       </c>
-      <c r="P13" s="27" t="n">
+      <c r="P13" s="38" t="n">
         <v>0</v>
       </c>
-      <c r="Q13" s="27" t="n">
+      <c r="Q13" s="38" t="n">
         <v>0</v>
       </c>
-      <c r="R13" s="27" t="n">
+      <c r="R13" s="38" t="n">
         <v>0</v>
       </c>
-      <c r="S13" s="27" t="n">
+      <c r="S13" s="38" t="n">
         <v>12867</v>
       </c>
-      <c r="T13" s="34">
+      <c r="T13" s="46">
         <f>SUM(H13:S13)</f>
         <v/>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="31" t="inlineStr">
+      <c r="A14" s="43" t="inlineStr">
         <is>
           <t>TOTAL GERAL</t>
         </is>
       </c>
-      <c r="B14" s="31" t="n"/>
-      <c r="C14" s="31" t="n"/>
-      <c r="D14" s="31" t="n"/>
-      <c r="E14" s="31" t="n"/>
-      <c r="F14" s="31" t="n"/>
-      <c r="G14" s="31" t="n"/>
-      <c r="H14" s="32">
+      <c r="B14" s="43" t="n"/>
+      <c r="C14" s="43" t="n"/>
+      <c r="D14" s="43" t="n"/>
+      <c r="E14" s="43" t="n"/>
+      <c r="F14" s="43" t="n"/>
+      <c r="G14" s="43" t="n"/>
+      <c r="H14" s="44">
         <f>SUM(H5:H13)</f>
         <v/>
       </c>
-      <c r="I14" s="32">
+      <c r="I14" s="44">
         <f>SUM(I5:I13)</f>
         <v/>
       </c>
-      <c r="J14" s="32">
+      <c r="J14" s="44">
         <f>SUM(J5:J13)</f>
         <v/>
       </c>
-      <c r="K14" s="32">
+      <c r="K14" s="44">
         <f>SUM(K5:K13)</f>
         <v/>
       </c>
-      <c r="L14" s="32">
+      <c r="L14" s="44">
         <f>SUM(L5:L13)</f>
         <v/>
       </c>
-      <c r="M14" s="32">
+      <c r="M14" s="44">
         <f>SUM(M5:M13)</f>
         <v/>
       </c>
-      <c r="N14" s="32">
+      <c r="N14" s="44">
         <f>SUM(N5:N13)</f>
         <v/>
       </c>
-      <c r="O14" s="32">
+      <c r="O14" s="44">
         <f>SUM(O5:O13)</f>
         <v/>
       </c>
-      <c r="P14" s="32">
+      <c r="P14" s="44">
         <f>SUM(P5:P13)</f>
         <v/>
       </c>
-      <c r="Q14" s="32">
+      <c r="Q14" s="44">
         <f>SUM(Q5:Q13)</f>
         <v/>
       </c>
-      <c r="R14" s="32">
+      <c r="R14" s="44">
         <f>SUM(R5:R13)</f>
         <v/>
       </c>
-      <c r="S14" s="32">
+      <c r="S14" s="44">
         <f>SUM(S5:S13)</f>
         <v/>
       </c>
-      <c r="T14" s="32">
+      <c r="T14" s="44">
         <f>SUM(T5:T13)</f>
         <v/>
       </c>
@@ -3185,773 +3697,773 @@
       </c>
     </row>
     <row r="4" ht="30" customHeight="1">
-      <c r="A4" s="35" t="inlineStr">
+      <c r="A4" s="47" t="inlineStr">
         <is>
           <t>ID</t>
         </is>
       </c>
-      <c r="B4" s="35" t="inlineStr">
+      <c r="B4" s="47" t="inlineStr">
         <is>
           <t>Departamento</t>
         </is>
       </c>
-      <c r="C4" s="35" t="inlineStr">
+      <c r="C4" s="47" t="inlineStr">
         <is>
           <t>Bloco</t>
         </is>
       </c>
-      <c r="D4" s="35" t="inlineStr">
+      <c r="D4" s="47" t="inlineStr">
         <is>
           <t>Descrição</t>
         </is>
       </c>
-      <c r="E4" s="35" t="inlineStr">
+      <c r="E4" s="47" t="inlineStr">
         <is>
           <t>Detalhe / Observação</t>
         </is>
       </c>
-      <c r="F4" s="35" t="inlineStr">
+      <c r="F4" s="47" t="inlineStr">
         <is>
           <t>Vínculo</t>
         </is>
       </c>
-      <c r="G4" s="35" t="inlineStr">
+      <c r="G4" s="47" t="inlineStr">
         <is>
           <t>Plano de Contas</t>
         </is>
       </c>
-      <c r="H4" s="35" t="inlineStr">
+      <c r="H4" s="47" t="inlineStr">
         <is>
           <t>Jan/26</t>
         </is>
       </c>
-      <c r="I4" s="35" t="inlineStr">
+      <c r="I4" s="47" t="inlineStr">
         <is>
           <t>Fev/26</t>
         </is>
       </c>
-      <c r="J4" s="35" t="inlineStr">
+      <c r="J4" s="47" t="inlineStr">
         <is>
           <t>Mar/26</t>
         </is>
       </c>
-      <c r="K4" s="35" t="inlineStr">
+      <c r="K4" s="47" t="inlineStr">
         <is>
           <t>Abr/26</t>
         </is>
       </c>
-      <c r="L4" s="35" t="inlineStr">
+      <c r="L4" s="47" t="inlineStr">
         <is>
           <t>Mai/26</t>
         </is>
       </c>
-      <c r="M4" s="35" t="inlineStr">
+      <c r="M4" s="47" t="inlineStr">
         <is>
           <t>Jun/26</t>
         </is>
       </c>
-      <c r="N4" s="35" t="inlineStr">
+      <c r="N4" s="47" t="inlineStr">
         <is>
           <t>Jul/26</t>
         </is>
       </c>
-      <c r="O4" s="35" t="inlineStr">
+      <c r="O4" s="47" t="inlineStr">
         <is>
           <t>Ago/26</t>
         </is>
       </c>
-      <c r="P4" s="35" t="inlineStr">
+      <c r="P4" s="47" t="inlineStr">
         <is>
           <t>Set/26</t>
         </is>
       </c>
-      <c r="Q4" s="35" t="inlineStr">
+      <c r="Q4" s="47" t="inlineStr">
         <is>
           <t>Out/26</t>
         </is>
       </c>
-      <c r="R4" s="35" t="inlineStr">
+      <c r="R4" s="47" t="inlineStr">
         <is>
           <t>Nov/26</t>
         </is>
       </c>
-      <c r="S4" s="35" t="inlineStr">
+      <c r="S4" s="47" t="inlineStr">
         <is>
           <t>Dez/26</t>
         </is>
       </c>
-      <c r="T4" s="35" t="inlineStr">
+      <c r="T4" s="47" t="inlineStr">
         <is>
           <t>TOTAL REALIZADO</t>
         </is>
       </c>
-      <c r="U4" s="35" t="inlineStr">
+      <c r="U4" s="47" t="inlineStr">
         <is>
           <t>Fonte do dado</t>
         </is>
       </c>
-      <c r="V4" s="35" t="inlineStr">
+      <c r="V4" s="47" t="inlineStr">
         <is>
           <t>Observações do mês</t>
         </is>
       </c>
     </row>
     <row r="5" ht="26" customHeight="1">
-      <c r="A5" s="36">
+      <c r="A5" s="48">
         <f>Planejado!A5</f>
         <v/>
       </c>
-      <c r="B5" s="36">
+      <c r="B5" s="48">
         <f>Planejado!B5</f>
         <v/>
       </c>
-      <c r="C5" s="36">
+      <c r="C5" s="48">
         <f>Planejado!C5</f>
         <v/>
       </c>
-      <c r="D5" s="37">
+      <c r="D5" s="49">
         <f>Planejado!D5</f>
         <v/>
       </c>
-      <c r="E5" s="37">
+      <c r="E5" s="49">
         <f>Planejado!E5</f>
         <v/>
       </c>
-      <c r="F5" s="36">
+      <c r="F5" s="48">
         <f>Planejado!F5</f>
         <v/>
       </c>
-      <c r="G5" s="36">
+      <c r="G5" s="48">
         <f>Planejado!G5</f>
         <v/>
       </c>
-      <c r="H5" s="38" t="n">
+      <c r="H5" s="50" t="n">
         <v>8818</v>
       </c>
-      <c r="I5" s="38" t="n">
+      <c r="I5" s="50" t="n">
         <v>8818</v>
       </c>
-      <c r="J5" s="38" t="n">
+      <c r="J5" s="50" t="n">
         <v>8818</v>
       </c>
-      <c r="K5" s="38" t="n">
+      <c r="K5" s="50" t="n">
         <v>8818</v>
       </c>
-      <c r="L5" s="38" t="n">
+      <c r="L5" s="50" t="n">
         <v>8818</v>
       </c>
-      <c r="M5" s="38" t="n">
+      <c r="M5" s="50" t="n">
         <v>8818</v>
       </c>
-      <c r="N5" s="38" t="n">
+      <c r="N5" s="50" t="n">
         <v>8818</v>
       </c>
-      <c r="O5" s="38" t="n"/>
-      <c r="T5" s="34">
+      <c r="O5" s="50" t="n"/>
+      <c r="T5" s="46">
         <f>SUM(H5:S5)</f>
         <v/>
       </c>
-      <c r="U5" s="39" t="inlineStr">
+      <c r="U5" s="51" t="inlineStr">
         <is>
           <t>Gestora, 05/08/26</t>
         </is>
       </c>
-      <c r="V5" s="39" t="inlineStr">
+      <c r="V5" s="51" t="inlineStr">
         <is>
           <t>Valor cheio da nota — R$ 1.182/mês abaixo do contratado</t>
         </is>
       </c>
     </row>
     <row r="6" ht="26" customHeight="1">
-      <c r="A6" s="36">
+      <c r="A6" s="48">
         <f>Planejado!A6</f>
         <v/>
       </c>
-      <c r="B6" s="36">
+      <c r="B6" s="48">
         <f>Planejado!B6</f>
         <v/>
       </c>
-      <c r="C6" s="36">
+      <c r="C6" s="48">
         <f>Planejado!C6</f>
         <v/>
       </c>
-      <c r="D6" s="37">
+      <c r="D6" s="49">
         <f>Planejado!D6</f>
         <v/>
       </c>
-      <c r="E6" s="37">
+      <c r="E6" s="49">
         <f>Planejado!E6</f>
         <v/>
       </c>
-      <c r="F6" s="36">
+      <c r="F6" s="48">
         <f>Planejado!F6</f>
         <v/>
       </c>
-      <c r="G6" s="36">
+      <c r="G6" s="48">
         <f>Planejado!G6</f>
         <v/>
       </c>
-      <c r="H6" s="38" t="n">
+      <c r="H6" s="50" t="n">
         <v>2886.91</v>
       </c>
-      <c r="I6" s="38" t="n">
+      <c r="I6" s="50" t="n">
         <v>2886.91</v>
       </c>
-      <c r="J6" s="38" t="n">
+      <c r="J6" s="50" t="n">
         <v>2886.91</v>
       </c>
-      <c r="K6" s="38" t="n">
+      <c r="K6" s="50" t="n">
         <v>2886.91</v>
       </c>
-      <c r="L6" s="38" t="n">
+      <c r="L6" s="50" t="n">
         <v>2886.91</v>
       </c>
-      <c r="M6" s="38" t="n">
+      <c r="M6" s="50" t="n">
         <v>2886.91</v>
       </c>
-      <c r="N6" s="38" t="n">
+      <c r="N6" s="50" t="n">
         <v>2886.91</v>
       </c>
-      <c r="O6" s="38" t="n"/>
-      <c r="T6" s="34">
+      <c r="O6" s="50" t="n"/>
+      <c r="T6" s="46">
         <f>SUM(H6:S6)</f>
         <v/>
       </c>
-      <c r="U6" s="39" t="inlineStr">
+      <c r="U6" s="51" t="inlineStr">
         <is>
           <t>Gestora, 05/08/26</t>
         </is>
       </c>
-      <c r="V6" s="39" t="inlineStr">
+      <c r="V6" s="51" t="inlineStr">
         <is>
           <t>SALÁRIO BRUTO, sem alteração no ano. O orçado é custo total, então o desvio desta linha NÃO é economia: faltam encargos e benefícios (~R$ 1.938,61/mês)</t>
         </is>
       </c>
     </row>
     <row r="7" ht="26" customHeight="1">
-      <c r="A7" s="36">
+      <c r="A7" s="48">
         <f>Planejado!A7</f>
         <v/>
       </c>
-      <c r="B7" s="36">
+      <c r="B7" s="48">
         <f>Planejado!B7</f>
         <v/>
       </c>
-      <c r="C7" s="36">
+      <c r="C7" s="48">
         <f>Planejado!C7</f>
         <v/>
       </c>
-      <c r="D7" s="37">
+      <c r="D7" s="49">
         <f>Planejado!D7</f>
         <v/>
       </c>
-      <c r="E7" s="37">
+      <c r="E7" s="49">
         <f>Planejado!E7</f>
         <v/>
       </c>
-      <c r="F7" s="36">
+      <c r="F7" s="48">
         <f>Planejado!F7</f>
         <v/>
       </c>
-      <c r="G7" s="36">
+      <c r="G7" s="48">
         <f>Planejado!G7</f>
         <v/>
       </c>
-      <c r="H7" s="38" t="n">
+      <c r="H7" s="50" t="n">
         <v>4500</v>
       </c>
-      <c r="I7" s="38" t="n">
+      <c r="I7" s="50" t="n">
         <v>4500</v>
       </c>
-      <c r="J7" s="38" t="n">
+      <c r="J7" s="50" t="n">
         <v>4500</v>
       </c>
-      <c r="K7" s="38" t="n">
+      <c r="K7" s="50" t="n">
         <v>5500</v>
       </c>
-      <c r="L7" s="38" t="n">
+      <c r="L7" s="50" t="n">
         <v>5500</v>
       </c>
-      <c r="M7" s="38" t="n">
+      <c r="M7" s="50" t="n">
         <v>5500</v>
       </c>
-      <c r="N7" s="38" t="n">
+      <c r="N7" s="50" t="n">
         <v>5500</v>
       </c>
-      <c r="O7" s="38" t="n"/>
-      <c r="T7" s="34">
+      <c r="O7" s="50" t="n"/>
+      <c r="T7" s="46">
         <f>SUM(H7:S7)</f>
         <v/>
       </c>
-      <c r="U7" s="39" t="inlineStr">
+      <c r="U7" s="51" t="inlineStr">
         <is>
           <t>Gestora, 05/08/26</t>
         </is>
       </c>
-      <c r="V7" s="39" t="inlineStr">
+      <c r="V7" s="51" t="inlineStr">
         <is>
           <t>R$ 4.500/mês em jan–mar; aumento de R$ 1.000 a partir de abr/26</t>
         </is>
       </c>
     </row>
     <row r="8" ht="26" customHeight="1">
-      <c r="A8" s="36">
+      <c r="A8" s="48">
         <f>Planejado!A8</f>
         <v/>
       </c>
-      <c r="B8" s="36">
+      <c r="B8" s="48">
         <f>Planejado!B8</f>
         <v/>
       </c>
-      <c r="C8" s="36">
+      <c r="C8" s="48">
         <f>Planejado!C8</f>
         <v/>
       </c>
-      <c r="D8" s="37">
+      <c r="D8" s="49">
         <f>Planejado!D8</f>
         <v/>
       </c>
-      <c r="E8" s="37">
+      <c r="E8" s="49">
         <f>Planejado!E8</f>
         <v/>
       </c>
-      <c r="F8" s="36">
+      <c r="F8" s="48">
         <f>Planejado!F8</f>
         <v/>
       </c>
-      <c r="G8" s="36">
+      <c r="G8" s="48">
         <f>Planejado!G8</f>
         <v/>
       </c>
-      <c r="H8" s="38" t="n">
+      <c r="H8" s="50" t="n">
         <v>0</v>
       </c>
-      <c r="I8" s="38" t="n">
+      <c r="I8" s="50" t="n">
         <v>0</v>
       </c>
-      <c r="J8" s="38" t="n">
+      <c r="J8" s="50" t="n">
         <v>0</v>
       </c>
-      <c r="K8" s="38" t="n">
+      <c r="K8" s="50" t="n">
         <v>0</v>
       </c>
-      <c r="L8" s="38" t="n">
+      <c r="L8" s="50" t="n">
         <v>0</v>
       </c>
-      <c r="M8" s="38" t="n">
+      <c r="M8" s="50" t="n">
         <v>0</v>
       </c>
-      <c r="N8" s="38" t="n">
+      <c r="N8" s="50" t="n">
         <v>0</v>
       </c>
-      <c r="O8" s="38" t="n"/>
-      <c r="T8" s="34">
+      <c r="O8" s="50" t="n"/>
+      <c r="T8" s="46">
         <f>SUM(H8:S8)</f>
         <v/>
       </c>
-      <c r="U8" s="39" t="inlineStr">
+      <c r="U8" s="51" t="inlineStr">
         <is>
           <t>Gestora, 05/08/26</t>
         </is>
       </c>
-      <c r="V8" s="39" t="inlineStr">
+      <c r="V8" s="51" t="inlineStr">
         <is>
           <t>Ainda não iniciado — sem cobrança</t>
         </is>
       </c>
     </row>
     <row r="9" ht="26" customHeight="1">
-      <c r="A9" s="36">
+      <c r="A9" s="48">
         <f>Planejado!A9</f>
         <v/>
       </c>
-      <c r="B9" s="36">
+      <c r="B9" s="48">
         <f>Planejado!B9</f>
         <v/>
       </c>
-      <c r="C9" s="36">
+      <c r="C9" s="48">
         <f>Planejado!C9</f>
         <v/>
       </c>
-      <c r="D9" s="37">
+      <c r="D9" s="49">
         <f>Planejado!D9</f>
         <v/>
       </c>
-      <c r="E9" s="37">
+      <c r="E9" s="49">
         <f>Planejado!E9</f>
         <v/>
       </c>
-      <c r="F9" s="36">
+      <c r="F9" s="48">
         <f>Planejado!F9</f>
         <v/>
       </c>
-      <c r="G9" s="36">
+      <c r="G9" s="48">
         <f>Planejado!G9</f>
         <v/>
       </c>
-      <c r="H9" s="38" t="n">
+      <c r="H9" s="50" t="n">
         <v>136</v>
       </c>
-      <c r="I9" s="38" t="n">
+      <c r="I9" s="50" t="n">
         <v>136</v>
       </c>
-      <c r="J9" s="38" t="n">
+      <c r="J9" s="50" t="n">
         <v>136</v>
       </c>
-      <c r="K9" s="38" t="n">
+      <c r="K9" s="50" t="n">
         <v>136</v>
       </c>
-      <c r="L9" s="38" t="n">
+      <c r="L9" s="50" t="n">
         <v>136</v>
       </c>
-      <c r="M9" s="38" t="n">
+      <c r="M9" s="50" t="n">
         <v>136</v>
       </c>
-      <c r="N9" s="38" t="n">
+      <c r="N9" s="50" t="n">
         <v>136</v>
       </c>
-      <c r="O9" s="38" t="n"/>
-      <c r="T9" s="34">
+      <c r="O9" s="50" t="n"/>
+      <c r="T9" s="46">
         <f>SUM(H9:S9)</f>
         <v/>
       </c>
-      <c r="U9" s="39" t="inlineStr">
+      <c r="U9" s="51" t="inlineStr">
         <is>
           <t>Gestora, 05/08/26</t>
         </is>
       </c>
-      <c r="V9" s="39" t="inlineStr">
+      <c r="V9" s="51" t="inlineStr">
         <is>
           <t>Acima do orçado (R$ 104,90) — conferir contrato</t>
         </is>
       </c>
     </row>
     <row r="10" ht="26" customHeight="1">
-      <c r="A10" s="36">
+      <c r="A10" s="48">
         <f>Planejado!A10</f>
         <v/>
       </c>
-      <c r="B10" s="36">
+      <c r="B10" s="48">
         <f>Planejado!B10</f>
         <v/>
       </c>
-      <c r="C10" s="36">
+      <c r="C10" s="48">
         <f>Planejado!C10</f>
         <v/>
       </c>
-      <c r="D10" s="37">
+      <c r="D10" s="49">
         <f>Planejado!D10</f>
         <v/>
       </c>
-      <c r="E10" s="37">
+      <c r="E10" s="49">
         <f>Planejado!E10</f>
         <v/>
       </c>
-      <c r="F10" s="36">
+      <c r="F10" s="48">
         <f>Planejado!F10</f>
         <v/>
       </c>
-      <c r="G10" s="36">
+      <c r="G10" s="48">
         <f>Planejado!G10</f>
         <v/>
       </c>
-      <c r="H10" s="38" t="n">
+      <c r="H10" s="50" t="n">
         <v>0</v>
       </c>
-      <c r="I10" s="38" t="n">
+      <c r="I10" s="50" t="n">
         <v>0</v>
       </c>
-      <c r="J10" s="38" t="n">
+      <c r="J10" s="50" t="n">
         <v>0</v>
       </c>
-      <c r="K10" s="38" t="n">
+      <c r="K10" s="50" t="n">
         <v>0</v>
       </c>
-      <c r="L10" s="38" t="n">
+      <c r="L10" s="50" t="n">
         <v>0</v>
       </c>
-      <c r="M10" s="38" t="n">
+      <c r="M10" s="50" t="n">
         <v>0</v>
       </c>
-      <c r="N10" s="38" t="n">
+      <c r="N10" s="50" t="n">
         <v>0</v>
       </c>
-      <c r="O10" s="38" t="n"/>
-      <c r="T10" s="34">
+      <c r="O10" s="50" t="n"/>
+      <c r="T10" s="46">
         <f>SUM(H10:S10)</f>
         <v/>
       </c>
-      <c r="U10" s="39" t="inlineStr">
+      <c r="U10" s="51" t="inlineStr">
         <is>
           <t>Gestora, 05/08/26</t>
         </is>
       </c>
-      <c r="V10" s="39" t="inlineStr">
+      <c r="V10" s="51" t="inlineStr">
         <is>
           <t>Cancelado — sem cobrança</t>
         </is>
       </c>
     </row>
     <row r="11" ht="26" customHeight="1">
-      <c r="A11" s="36">
+      <c r="A11" s="48">
         <f>Planejado!A11</f>
         <v/>
       </c>
-      <c r="B11" s="36">
+      <c r="B11" s="48">
         <f>Planejado!B11</f>
         <v/>
       </c>
-      <c r="C11" s="36">
+      <c r="C11" s="48">
         <f>Planejado!C11</f>
         <v/>
       </c>
-      <c r="D11" s="37">
+      <c r="D11" s="49">
         <f>Planejado!D11</f>
         <v/>
       </c>
-      <c r="E11" s="37">
+      <c r="E11" s="49">
         <f>Planejado!E11</f>
         <v/>
       </c>
-      <c r="F11" s="36">
+      <c r="F11" s="48">
         <f>Planejado!F11</f>
         <v/>
       </c>
-      <c r="G11" s="36">
+      <c r="G11" s="48">
         <f>Planejado!G11</f>
         <v/>
       </c>
-      <c r="H11" s="38" t="n">
+      <c r="H11" s="50" t="n">
         <v>970</v>
       </c>
-      <c r="I11" s="38" t="n">
+      <c r="I11" s="50" t="n">
         <v>970</v>
       </c>
-      <c r="J11" s="38" t="n">
+      <c r="J11" s="50" t="n">
         <v>970</v>
       </c>
-      <c r="K11" s="38" t="n">
+      <c r="K11" s="50" t="n">
         <v>970</v>
       </c>
-      <c r="L11" s="38" t="n">
+      <c r="L11" s="50" t="n">
         <v>970</v>
       </c>
-      <c r="M11" s="38" t="n">
+      <c r="M11" s="50" t="n">
         <v>970</v>
       </c>
-      <c r="N11" s="38" t="n">
+      <c r="N11" s="50" t="n">
         <v>970</v>
       </c>
-      <c r="O11" s="38" t="n"/>
-      <c r="T11" s="34">
+      <c r="O11" s="50" t="n"/>
+      <c r="T11" s="46">
         <f>SUM(H11:S11)</f>
         <v/>
       </c>
-      <c r="U11" s="39" t="inlineStr">
+      <c r="U11" s="51" t="inlineStr">
         <is>
           <t>Gestora, 05/08/26</t>
         </is>
       </c>
-      <c r="V11" s="39" t="n"/>
+      <c r="V11" s="51" t="n"/>
     </row>
     <row r="12" ht="26" customHeight="1">
-      <c r="A12" s="36">
+      <c r="A12" s="48">
         <f>Planejado!A12</f>
         <v/>
       </c>
-      <c r="B12" s="36">
+      <c r="B12" s="48">
         <f>Planejado!B12</f>
         <v/>
       </c>
-      <c r="C12" s="36">
+      <c r="C12" s="48">
         <f>Planejado!C12</f>
         <v/>
       </c>
-      <c r="D12" s="37">
+      <c r="D12" s="49">
         <f>Planejado!D12</f>
         <v/>
       </c>
-      <c r="E12" s="37">
+      <c r="E12" s="49">
         <f>Planejado!E12</f>
         <v/>
       </c>
-      <c r="F12" s="36">
+      <c r="F12" s="48">
         <f>Planejado!F12</f>
         <v/>
       </c>
-      <c r="G12" s="36">
+      <c r="G12" s="48">
         <f>Planejado!G12</f>
         <v/>
       </c>
-      <c r="H12" s="38" t="n">
+      <c r="H12" s="50" t="n">
         <v>0</v>
       </c>
-      <c r="I12" s="38" t="n">
+      <c r="I12" s="50" t="n">
         <v>0</v>
       </c>
-      <c r="J12" s="38" t="n">
+      <c r="J12" s="50" t="n">
         <v>0</v>
       </c>
-      <c r="K12" s="38" t="n">
+      <c r="K12" s="50" t="n">
         <v>0</v>
       </c>
-      <c r="L12" s="38" t="n">
+      <c r="L12" s="50" t="n">
         <v>0</v>
       </c>
-      <c r="M12" s="38" t="n">
+      <c r="M12" s="50" t="n">
         <v>0</v>
       </c>
-      <c r="N12" s="38" t="n">
+      <c r="N12" s="50" t="n">
         <v>0</v>
       </c>
-      <c r="O12" s="38" t="n"/>
-      <c r="T12" s="34">
+      <c r="O12" s="50" t="n"/>
+      <c r="T12" s="46">
         <f>SUM(H12:S12)</f>
         <v/>
       </c>
-      <c r="U12" s="39" t="inlineStr">
+      <c r="U12" s="51" t="inlineStr">
         <is>
           <t>Gestora, 05/08/26</t>
         </is>
       </c>
-      <c r="V12" s="39" t="inlineStr">
+      <c r="V12" s="51" t="inlineStr">
         <is>
           <t>Sem gasto no período</t>
         </is>
       </c>
     </row>
     <row r="13" ht="26" customHeight="1">
-      <c r="A13" s="36">
+      <c r="A13" s="48">
         <f>Planejado!A13</f>
         <v/>
       </c>
-      <c r="B13" s="36">
+      <c r="B13" s="48">
         <f>Planejado!B13</f>
         <v/>
       </c>
-      <c r="C13" s="36">
+      <c r="C13" s="48">
         <f>Planejado!C13</f>
         <v/>
       </c>
-      <c r="D13" s="37">
+      <c r="D13" s="49">
         <f>Planejado!D13</f>
         <v/>
       </c>
-      <c r="E13" s="37">
+      <c r="E13" s="49">
         <f>Planejado!E13</f>
         <v/>
       </c>
-      <c r="F13" s="36">
+      <c r="F13" s="48">
         <f>Planejado!F13</f>
         <v/>
       </c>
-      <c r="G13" s="36">
+      <c r="G13" s="48">
         <f>Planejado!G13</f>
         <v/>
       </c>
-      <c r="H13" s="38" t="n">
+      <c r="H13" s="50" t="n">
         <v>0</v>
       </c>
-      <c r="I13" s="38" t="n">
+      <c r="I13" s="50" t="n">
         <v>0</v>
       </c>
-      <c r="J13" s="38" t="n">
+      <c r="J13" s="50" t="n">
         <v>0</v>
       </c>
-      <c r="K13" s="38" t="n">
+      <c r="K13" s="50" t="n">
         <v>0</v>
       </c>
-      <c r="L13" s="38" t="n">
+      <c r="L13" s="50" t="n">
         <v>0</v>
       </c>
-      <c r="M13" s="38" t="n">
+      <c r="M13" s="50" t="n">
         <v>0</v>
       </c>
-      <c r="N13" s="38" t="n">
+      <c r="N13" s="50" t="n">
         <v>0</v>
       </c>
-      <c r="O13" s="38" t="n"/>
-      <c r="T13" s="34">
+      <c r="O13" s="50" t="n"/>
+      <c r="T13" s="46">
         <f>SUM(H13:S13)</f>
         <v/>
       </c>
-      <c r="U13" s="39" t="inlineStr">
+      <c r="U13" s="51" t="inlineStr">
         <is>
           <t>Gestora, 05/08/26</t>
         </is>
       </c>
-      <c r="V13" s="39" t="inlineStr">
+      <c r="V13" s="51" t="inlineStr">
         <is>
           <t>Sem parcela no 1º semestre; bonificação de ago/26 a confirmar</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="40" t="inlineStr">
+      <c r="A14" s="52" t="inlineStr">
         <is>
           <t>TOTAL GERAL</t>
         </is>
       </c>
-      <c r="B14" s="40" t="n"/>
-      <c r="C14" s="40" t="n"/>
-      <c r="D14" s="40" t="n"/>
-      <c r="E14" s="40" t="n"/>
-      <c r="F14" s="40" t="n"/>
-      <c r="G14" s="40" t="n"/>
-      <c r="H14" s="41">
+      <c r="B14" s="52" t="n"/>
+      <c r="C14" s="52" t="n"/>
+      <c r="D14" s="52" t="n"/>
+      <c r="E14" s="52" t="n"/>
+      <c r="F14" s="52" t="n"/>
+      <c r="G14" s="52" t="n"/>
+      <c r="H14" s="53">
         <f>SUM(H5:H13)</f>
         <v/>
       </c>
-      <c r="I14" s="41">
+      <c r="I14" s="53">
         <f>SUM(I5:I13)</f>
         <v/>
       </c>
-      <c r="J14" s="41">
+      <c r="J14" s="53">
         <f>SUM(J5:J13)</f>
         <v/>
       </c>
-      <c r="K14" s="41">
+      <c r="K14" s="53">
         <f>SUM(K5:K13)</f>
         <v/>
       </c>
-      <c r="L14" s="41">
+      <c r="L14" s="53">
         <f>SUM(L5:L13)</f>
         <v/>
       </c>
-      <c r="M14" s="41">
+      <c r="M14" s="53">
         <f>SUM(M5:M13)</f>
         <v/>
       </c>
-      <c r="N14" s="41">
+      <c r="N14" s="53">
         <f>SUM(N5:N13)</f>
         <v/>
       </c>
-      <c r="O14" s="41">
+      <c r="O14" s="53">
         <f>SUM(O5:O13)</f>
         <v/>
       </c>
-      <c r="P14" s="41">
+      <c r="P14" s="53">
         <f>SUM(P5:P13)</f>
         <v/>
       </c>
-      <c r="Q14" s="41">
+      <c r="Q14" s="53">
         <f>SUM(Q5:Q13)</f>
         <v/>
       </c>
-      <c r="R14" s="41">
+      <c r="R14" s="53">
         <f>SUM(R5:R13)</f>
         <v/>
       </c>
-      <c r="S14" s="41">
+      <c r="S14" s="53">
         <f>SUM(S5:S13)</f>
         <v/>
       </c>
-      <c r="T14" s="41">
+      <c r="T14" s="53">
         <f>SUM(T5:T13)</f>
         <v/>
       </c>
-      <c r="U14" s="40" t="n"/>
-      <c r="V14" s="40" t="n"/>
+      <c r="U14" s="52" t="n"/>
+      <c r="V14" s="52" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -4038,453 +4550,453 @@
       </c>
     </row>
     <row r="5" ht="20" customHeight="1">
-      <c r="A5" s="42" t="inlineStr">
+      <c r="A5" s="54" t="inlineStr">
         <is>
           <t>Jan/26</t>
         </is>
       </c>
-      <c r="B5" s="27">
+      <c r="B5" s="38">
         <f>SUMIFS(Planejado!$H$5:$H$13,Planejado!$B$5:$B$13,"Jurídico")</f>
         <v/>
       </c>
-      <c r="C5" s="27">
+      <c r="C5" s="38">
         <f>SUMIFS(Realizado!$H$5:$H$13,Realizado!$B$5:$B$13,"Jurídico")</f>
         <v/>
       </c>
-      <c r="D5" s="27">
+      <c r="D5" s="38">
         <f>B5</f>
         <v/>
       </c>
-      <c r="E5" s="27">
+      <c r="E5" s="38">
         <f>C5</f>
         <v/>
       </c>
-      <c r="F5" s="27">
+      <c r="F5" s="38">
         <f>E5-D5</f>
         <v/>
       </c>
-      <c r="G5" s="27">
+      <c r="G5" s="38">
         <f>SUM($D$5:D5)</f>
         <v/>
       </c>
-      <c r="H5" s="27">
+      <c r="H5" s="38">
         <f>SUM($E$5:E5)</f>
         <v/>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1">
-      <c r="A6" s="43" t="inlineStr">
+      <c r="A6" s="55" t="inlineStr">
         <is>
           <t>Fev/26</t>
         </is>
       </c>
-      <c r="B6" s="44">
+      <c r="B6" s="56">
         <f>SUMIFS(Planejado!$I$5:$I$13,Planejado!$B$5:$B$13,"Jurídico")</f>
         <v/>
       </c>
-      <c r="C6" s="44">
+      <c r="C6" s="56">
         <f>SUMIFS(Realizado!$I$5:$I$13,Realizado!$B$5:$B$13,"Jurídico")</f>
         <v/>
       </c>
-      <c r="D6" s="44">
+      <c r="D6" s="56">
         <f>B6</f>
         <v/>
       </c>
-      <c r="E6" s="44">
+      <c r="E6" s="56">
         <f>C6</f>
         <v/>
       </c>
-      <c r="F6" s="44">
+      <c r="F6" s="56">
         <f>E6-D6</f>
         <v/>
       </c>
-      <c r="G6" s="44">
+      <c r="G6" s="56">
         <f>SUM($D$5:D6)</f>
         <v/>
       </c>
-      <c r="H6" s="44">
+      <c r="H6" s="56">
         <f>SUM($E$5:E6)</f>
         <v/>
       </c>
     </row>
     <row r="7" ht="20" customHeight="1">
-      <c r="A7" s="42" t="inlineStr">
+      <c r="A7" s="54" t="inlineStr">
         <is>
           <t>Mar/26</t>
         </is>
       </c>
-      <c r="B7" s="27">
+      <c r="B7" s="38">
         <f>SUMIFS(Planejado!$J$5:$J$13,Planejado!$B$5:$B$13,"Jurídico")</f>
         <v/>
       </c>
-      <c r="C7" s="27">
+      <c r="C7" s="38">
         <f>SUMIFS(Realizado!$J$5:$J$13,Realizado!$B$5:$B$13,"Jurídico")</f>
         <v/>
       </c>
-      <c r="D7" s="27">
+      <c r="D7" s="38">
         <f>B7</f>
         <v/>
       </c>
-      <c r="E7" s="27">
+      <c r="E7" s="38">
         <f>C7</f>
         <v/>
       </c>
-      <c r="F7" s="27">
+      <c r="F7" s="38">
         <f>E7-D7</f>
         <v/>
       </c>
-      <c r="G7" s="27">
+      <c r="G7" s="38">
         <f>SUM($D$5:D7)</f>
         <v/>
       </c>
-      <c r="H7" s="27">
+      <c r="H7" s="38">
         <f>SUM($E$5:E7)</f>
         <v/>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1">
-      <c r="A8" s="43" t="inlineStr">
+      <c r="A8" s="55" t="inlineStr">
         <is>
           <t>Abr/26</t>
         </is>
       </c>
-      <c r="B8" s="44">
+      <c r="B8" s="56">
         <f>SUMIFS(Planejado!$K$5:$K$13,Planejado!$B$5:$B$13,"Jurídico")</f>
         <v/>
       </c>
-      <c r="C8" s="44">
+      <c r="C8" s="56">
         <f>SUMIFS(Realizado!$K$5:$K$13,Realizado!$B$5:$B$13,"Jurídico")</f>
         <v/>
       </c>
-      <c r="D8" s="44">
+      <c r="D8" s="56">
         <f>B8</f>
         <v/>
       </c>
-      <c r="E8" s="44">
+      <c r="E8" s="56">
         <f>C8</f>
         <v/>
       </c>
-      <c r="F8" s="44">
+      <c r="F8" s="56">
         <f>E8-D8</f>
         <v/>
       </c>
-      <c r="G8" s="44">
+      <c r="G8" s="56">
         <f>SUM($D$5:D8)</f>
         <v/>
       </c>
-      <c r="H8" s="44">
+      <c r="H8" s="56">
         <f>SUM($E$5:E8)</f>
         <v/>
       </c>
     </row>
     <row r="9" ht="20" customHeight="1">
-      <c r="A9" s="42" t="inlineStr">
+      <c r="A9" s="54" t="inlineStr">
         <is>
           <t>Mai/26</t>
         </is>
       </c>
-      <c r="B9" s="27">
+      <c r="B9" s="38">
         <f>SUMIFS(Planejado!$L$5:$L$13,Planejado!$B$5:$B$13,"Jurídico")</f>
         <v/>
       </c>
-      <c r="C9" s="27">
+      <c r="C9" s="38">
         <f>SUMIFS(Realizado!$L$5:$L$13,Realizado!$B$5:$B$13,"Jurídico")</f>
         <v/>
       </c>
-      <c r="D9" s="27">
+      <c r="D9" s="38">
         <f>B9</f>
         <v/>
       </c>
-      <c r="E9" s="27">
+      <c r="E9" s="38">
         <f>C9</f>
         <v/>
       </c>
-      <c r="F9" s="27">
+      <c r="F9" s="38">
         <f>E9-D9</f>
         <v/>
       </c>
-      <c r="G9" s="27">
+      <c r="G9" s="38">
         <f>SUM($D$5:D9)</f>
         <v/>
       </c>
-      <c r="H9" s="27">
+      <c r="H9" s="38">
         <f>SUM($E$5:E9)</f>
         <v/>
       </c>
     </row>
     <row r="10" ht="20" customHeight="1">
-      <c r="A10" s="43" t="inlineStr">
+      <c r="A10" s="55" t="inlineStr">
         <is>
           <t>Jun/26</t>
         </is>
       </c>
-      <c r="B10" s="44">
+      <c r="B10" s="56">
         <f>SUMIFS(Planejado!$M$5:$M$13,Planejado!$B$5:$B$13,"Jurídico")</f>
         <v/>
       </c>
-      <c r="C10" s="44">
+      <c r="C10" s="56">
         <f>SUMIFS(Realizado!$M$5:$M$13,Realizado!$B$5:$B$13,"Jurídico")</f>
         <v/>
       </c>
-      <c r="D10" s="44">
+      <c r="D10" s="56">
         <f>B10</f>
         <v/>
       </c>
-      <c r="E10" s="44">
+      <c r="E10" s="56">
         <f>C10</f>
         <v/>
       </c>
-      <c r="F10" s="44">
+      <c r="F10" s="56">
         <f>E10-D10</f>
         <v/>
       </c>
-      <c r="G10" s="44">
+      <c r="G10" s="56">
         <f>SUM($D$5:D10)</f>
         <v/>
       </c>
-      <c r="H10" s="44">
+      <c r="H10" s="56">
         <f>SUM($E$5:E10)</f>
         <v/>
       </c>
     </row>
     <row r="11" ht="20" customHeight="1">
-      <c r="A11" s="42" t="inlineStr">
+      <c r="A11" s="54" t="inlineStr">
         <is>
           <t>Jul/26</t>
         </is>
       </c>
-      <c r="B11" s="27">
+      <c r="B11" s="38">
         <f>SUMIFS(Planejado!$N$5:$N$13,Planejado!$B$5:$B$13,"Jurídico")</f>
         <v/>
       </c>
-      <c r="C11" s="27">
+      <c r="C11" s="38">
         <f>SUMIFS(Realizado!$N$5:$N$13,Realizado!$B$5:$B$13,"Jurídico")</f>
         <v/>
       </c>
-      <c r="D11" s="27">
+      <c r="D11" s="38">
         <f>B11</f>
         <v/>
       </c>
-      <c r="E11" s="27">
+      <c r="E11" s="38">
         <f>C11</f>
         <v/>
       </c>
-      <c r="F11" s="27">
+      <c r="F11" s="38">
         <f>E11-D11</f>
         <v/>
       </c>
-      <c r="G11" s="27">
+      <c r="G11" s="38">
         <f>SUM($D$5:D11)</f>
         <v/>
       </c>
-      <c r="H11" s="27">
+      <c r="H11" s="38">
         <f>SUM($E$5:E11)</f>
         <v/>
       </c>
     </row>
     <row r="12" ht="20" customHeight="1">
-      <c r="A12" s="43" t="inlineStr">
+      <c r="A12" s="55" t="inlineStr">
         <is>
           <t>Ago/26</t>
         </is>
       </c>
-      <c r="B12" s="44">
+      <c r="B12" s="56">
         <f>SUMIFS(Planejado!$O$5:$O$13,Planejado!$B$5:$B$13,"Jurídico")</f>
         <v/>
       </c>
-      <c r="C12" s="44">
+      <c r="C12" s="56">
         <f>SUMIFS(Realizado!$O$5:$O$13,Realizado!$B$5:$B$13,"Jurídico")</f>
         <v/>
       </c>
-      <c r="D12" s="44">
+      <c r="D12" s="56">
         <f>B12</f>
         <v/>
       </c>
-      <c r="E12" s="44">
+      <c r="E12" s="56">
         <f>C12</f>
         <v/>
       </c>
-      <c r="F12" s="44">
+      <c r="F12" s="56">
         <f>E12-D12</f>
         <v/>
       </c>
-      <c r="G12" s="44">
+      <c r="G12" s="56">
         <f>SUM($D$5:D12)</f>
         <v/>
       </c>
-      <c r="H12" s="44">
+      <c r="H12" s="56">
         <f>SUM($E$5:E12)</f>
         <v/>
       </c>
     </row>
     <row r="13" ht="20" customHeight="1">
-      <c r="A13" s="42" t="inlineStr">
+      <c r="A13" s="54" t="inlineStr">
         <is>
           <t>Set/26</t>
         </is>
       </c>
-      <c r="B13" s="27">
+      <c r="B13" s="38">
         <f>SUMIFS(Planejado!$P$5:$P$13,Planejado!$B$5:$B$13,"Jurídico")</f>
         <v/>
       </c>
-      <c r="C13" s="27">
+      <c r="C13" s="38">
         <f>SUMIFS(Realizado!$P$5:$P$13,Realizado!$B$5:$B$13,"Jurídico")</f>
         <v/>
       </c>
-      <c r="D13" s="27">
+      <c r="D13" s="38">
         <f>B13</f>
         <v/>
       </c>
-      <c r="E13" s="27">
+      <c r="E13" s="38">
         <f>C13</f>
         <v/>
       </c>
-      <c r="F13" s="27">
+      <c r="F13" s="38">
         <f>E13-D13</f>
         <v/>
       </c>
-      <c r="G13" s="27">
+      <c r="G13" s="38">
         <f>SUM($D$5:D13)</f>
         <v/>
       </c>
-      <c r="H13" s="27">
+      <c r="H13" s="38">
         <f>SUM($E$5:E13)</f>
         <v/>
       </c>
     </row>
     <row r="14" ht="20" customHeight="1">
-      <c r="A14" s="43" t="inlineStr">
+      <c r="A14" s="55" t="inlineStr">
         <is>
           <t>Out/26</t>
         </is>
       </c>
-      <c r="B14" s="44">
+      <c r="B14" s="56">
         <f>SUMIFS(Planejado!$Q$5:$Q$13,Planejado!$B$5:$B$13,"Jurídico")</f>
         <v/>
       </c>
-      <c r="C14" s="44">
+      <c r="C14" s="56">
         <f>SUMIFS(Realizado!$Q$5:$Q$13,Realizado!$B$5:$B$13,"Jurídico")</f>
         <v/>
       </c>
-      <c r="D14" s="44">
+      <c r="D14" s="56">
         <f>B14</f>
         <v/>
       </c>
-      <c r="E14" s="44">
+      <c r="E14" s="56">
         <f>C14</f>
         <v/>
       </c>
-      <c r="F14" s="44">
+      <c r="F14" s="56">
         <f>E14-D14</f>
         <v/>
       </c>
-      <c r="G14" s="44">
+      <c r="G14" s="56">
         <f>SUM($D$5:D14)</f>
         <v/>
       </c>
-      <c r="H14" s="44">
+      <c r="H14" s="56">
         <f>SUM($E$5:E14)</f>
         <v/>
       </c>
     </row>
     <row r="15" ht="20" customHeight="1">
-      <c r="A15" s="42" t="inlineStr">
+      <c r="A15" s="54" t="inlineStr">
         <is>
           <t>Nov/26</t>
         </is>
       </c>
-      <c r="B15" s="27">
+      <c r="B15" s="38">
         <f>SUMIFS(Planejado!$R$5:$R$13,Planejado!$B$5:$B$13,"Jurídico")</f>
         <v/>
       </c>
-      <c r="C15" s="27">
+      <c r="C15" s="38">
         <f>SUMIFS(Realizado!$R$5:$R$13,Realizado!$B$5:$B$13,"Jurídico")</f>
         <v/>
       </c>
-      <c r="D15" s="27">
+      <c r="D15" s="38">
         <f>B15</f>
         <v/>
       </c>
-      <c r="E15" s="27">
+      <c r="E15" s="38">
         <f>C15</f>
         <v/>
       </c>
-      <c r="F15" s="27">
+      <c r="F15" s="38">
         <f>E15-D15</f>
         <v/>
       </c>
-      <c r="G15" s="27">
+      <c r="G15" s="38">
         <f>SUM($D$5:D15)</f>
         <v/>
       </c>
-      <c r="H15" s="27">
+      <c r="H15" s="38">
         <f>SUM($E$5:E15)</f>
         <v/>
       </c>
     </row>
     <row r="16" ht="20" customHeight="1">
-      <c r="A16" s="43" t="inlineStr">
+      <c r="A16" s="55" t="inlineStr">
         <is>
           <t>Dez/26</t>
         </is>
       </c>
-      <c r="B16" s="44">
+      <c r="B16" s="56">
         <f>SUMIFS(Planejado!$S$5:$S$13,Planejado!$B$5:$B$13,"Jurídico")</f>
         <v/>
       </c>
-      <c r="C16" s="44">
+      <c r="C16" s="56">
         <f>SUMIFS(Realizado!$S$5:$S$13,Realizado!$B$5:$B$13,"Jurídico")</f>
         <v/>
       </c>
-      <c r="D16" s="44">
+      <c r="D16" s="56">
         <f>B16</f>
         <v/>
       </c>
-      <c r="E16" s="44">
+      <c r="E16" s="56">
         <f>C16</f>
         <v/>
       </c>
-      <c r="F16" s="44">
+      <c r="F16" s="56">
         <f>E16-D16</f>
         <v/>
       </c>
-      <c r="G16" s="44">
+      <c r="G16" s="56">
         <f>SUM($D$5:D16)</f>
         <v/>
       </c>
-      <c r="H16" s="44">
+      <c r="H16" s="56">
         <f>SUM($E$5:E16)</f>
         <v/>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="31" t="inlineStr">
+      <c r="A17" s="43" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B17" s="32">
+      <c r="B17" s="44">
         <f>SUM(B5:B16)</f>
         <v/>
       </c>
-      <c r="C17" s="32">
+      <c r="C17" s="44">
         <f>SUM(C5:C16)</f>
         <v/>
       </c>
-      <c r="D17" s="32">
+      <c r="D17" s="44">
         <f>SUM(D5:D16)</f>
         <v/>
       </c>
-      <c r="E17" s="32">
+      <c r="E17" s="44">
         <f>SUM(E5:E16)</f>
         <v/>
       </c>
-      <c r="F17" s="32">
+      <c r="F17" s="44">
         <f>SUM(F5:F16)</f>
         <v/>
       </c>
-      <c r="G17" s="31" t="n"/>
-      <c r="H17" s="31" t="n"/>
+      <c r="G17" s="43" t="n"/>
+      <c r="H17" s="43" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -4580,211 +5092,211 @@
       </c>
     </row>
     <row r="5" ht="20" customHeight="1">
-      <c r="A5" s="45" t="inlineStr">
+      <c r="A5" s="57" t="inlineStr">
         <is>
           <t>Pessoal - CLT</t>
         </is>
       </c>
-      <c r="B5" s="27">
+      <c r="B5" s="38">
         <f>SUMIFS(Comparativo!$I$6:$I$14,Comparativo!$E$6:$E$14,$A5,Comparativo!$B$6:$B$14,"Jurídico")</f>
         <v/>
       </c>
-      <c r="C5" s="27">
+      <c r="C5" s="38">
         <f>SUMIFS(Comparativo!$J$6:$J$14,Comparativo!$E$6:$E$14,$A5,Comparativo!$B$6:$B$14,"Jurídico")</f>
         <v/>
       </c>
-      <c r="D5" s="27">
+      <c r="D5" s="38">
         <f>B5</f>
         <v/>
       </c>
-      <c r="E5" s="27">
+      <c r="E5" s="38">
         <f>C5</f>
         <v/>
       </c>
-      <c r="F5" s="27">
+      <c r="F5" s="38">
         <f>E5-D5</f>
         <v/>
       </c>
-      <c r="G5" s="46">
+      <c r="G5" s="58">
         <f>IFERROR(F5/D5,"")</f>
         <v/>
       </c>
-      <c r="H5" s="27">
+      <c r="H5" s="38">
         <f>SUMIFS(Planejado!$T$5:$T$13,Planejado!$G$5:$G$13,$A5)</f>
         <v/>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1">
-      <c r="A6" s="47" t="inlineStr">
+      <c r="A6" s="59" t="inlineStr">
         <is>
           <t>Pessoal - PJ</t>
         </is>
       </c>
-      <c r="B6" s="44">
+      <c r="B6" s="56">
         <f>SUMIFS(Comparativo!$I$6:$I$14,Comparativo!$E$6:$E$14,$A6,Comparativo!$B$6:$B$14,"Jurídico")</f>
         <v/>
       </c>
-      <c r="C6" s="44">
+      <c r="C6" s="56">
         <f>SUMIFS(Comparativo!$J$6:$J$14,Comparativo!$E$6:$E$14,$A6,Comparativo!$B$6:$B$14,"Jurídico")</f>
         <v/>
       </c>
-      <c r="D6" s="44">
+      <c r="D6" s="56">
         <f>B6</f>
         <v/>
       </c>
-      <c r="E6" s="44">
+      <c r="E6" s="56">
         <f>C6</f>
         <v/>
       </c>
-      <c r="F6" s="44">
+      <c r="F6" s="56">
         <f>E6-D6</f>
         <v/>
       </c>
-      <c r="G6" s="48">
+      <c r="G6" s="60">
         <f>IFERROR(F6/D6,"")</f>
         <v/>
       </c>
-      <c r="H6" s="44">
+      <c r="H6" s="56">
         <f>SUMIFS(Planejado!$T$5:$T$13,Planejado!$G$5:$G$13,$A6)</f>
         <v/>
       </c>
     </row>
     <row r="7" ht="20" customHeight="1">
-      <c r="A7" s="45" t="inlineStr">
+      <c r="A7" s="57" t="inlineStr">
         <is>
           <t>Licenças de Softwares</t>
         </is>
       </c>
-      <c r="B7" s="27">
+      <c r="B7" s="38">
         <f>SUMIFS(Comparativo!$I$6:$I$14,Comparativo!$E$6:$E$14,$A7,Comparativo!$B$6:$B$14,"Jurídico")</f>
         <v/>
       </c>
-      <c r="C7" s="27">
+      <c r="C7" s="38">
         <f>SUMIFS(Comparativo!$J$6:$J$14,Comparativo!$E$6:$E$14,$A7,Comparativo!$B$6:$B$14,"Jurídico")</f>
         <v/>
       </c>
-      <c r="D7" s="27">
+      <c r="D7" s="38">
         <f>B7</f>
         <v/>
       </c>
-      <c r="E7" s="27">
+      <c r="E7" s="38">
         <f>C7</f>
         <v/>
       </c>
-      <c r="F7" s="27">
+      <c r="F7" s="38">
         <f>E7-D7</f>
         <v/>
       </c>
-      <c r="G7" s="46">
+      <c r="G7" s="58">
         <f>IFERROR(F7/D7,"")</f>
         <v/>
       </c>
-      <c r="H7" s="27">
+      <c r="H7" s="38">
         <f>SUMIFS(Planejado!$T$5:$T$13,Planejado!$G$5:$G$13,$A7)</f>
         <v/>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1">
-      <c r="A8" s="47" t="inlineStr">
+      <c r="A8" s="59" t="inlineStr">
         <is>
           <t>Custeio de Treinamento</t>
         </is>
       </c>
-      <c r="B8" s="44">
+      <c r="B8" s="56">
         <f>SUMIFS(Comparativo!$I$6:$I$14,Comparativo!$E$6:$E$14,$A8,Comparativo!$B$6:$B$14,"Jurídico")</f>
         <v/>
       </c>
-      <c r="C8" s="44">
+      <c r="C8" s="56">
         <f>SUMIFS(Comparativo!$J$6:$J$14,Comparativo!$E$6:$E$14,$A8,Comparativo!$B$6:$B$14,"Jurídico")</f>
         <v/>
       </c>
-      <c r="D8" s="44">
+      <c r="D8" s="56">
         <f>B8</f>
         <v/>
       </c>
-      <c r="E8" s="44">
+      <c r="E8" s="56">
         <f>C8</f>
         <v/>
       </c>
-      <c r="F8" s="44">
+      <c r="F8" s="56">
         <f>E8-D8</f>
         <v/>
       </c>
-      <c r="G8" s="48">
+      <c r="G8" s="60">
         <f>IFERROR(F8/D8,"")</f>
         <v/>
       </c>
-      <c r="H8" s="44">
+      <c r="H8" s="56">
         <f>SUMIFS(Planejado!$T$5:$T$13,Planejado!$G$5:$G$13,$A8)</f>
         <v/>
       </c>
     </row>
     <row r="9" ht="20" customHeight="1">
-      <c r="A9" s="45" t="inlineStr">
+      <c r="A9" s="57" t="inlineStr">
         <is>
           <t>Prêmios</t>
         </is>
       </c>
-      <c r="B9" s="27">
+      <c r="B9" s="38">
         <f>SUMIFS(Comparativo!$I$6:$I$14,Comparativo!$E$6:$E$14,$A9,Comparativo!$B$6:$B$14,"Jurídico")</f>
         <v/>
       </c>
-      <c r="C9" s="27">
+      <c r="C9" s="38">
         <f>SUMIFS(Comparativo!$J$6:$J$14,Comparativo!$E$6:$E$14,$A9,Comparativo!$B$6:$B$14,"Jurídico")</f>
         <v/>
       </c>
-      <c r="D9" s="27">
+      <c r="D9" s="38">
         <f>B9</f>
         <v/>
       </c>
-      <c r="E9" s="27">
+      <c r="E9" s="38">
         <f>C9</f>
         <v/>
       </c>
-      <c r="F9" s="27">
+      <c r="F9" s="38">
         <f>E9-D9</f>
         <v/>
       </c>
-      <c r="G9" s="46">
+      <c r="G9" s="58">
         <f>IFERROR(F9/D9,"")</f>
         <v/>
       </c>
-      <c r="H9" s="27">
+      <c r="H9" s="38">
         <f>SUMIFS(Planejado!$T$5:$T$13,Planejado!$G$5:$G$13,$A9)</f>
         <v/>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="31" t="inlineStr">
+      <c r="A10" s="43" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B10" s="32">
+      <c r="B10" s="44">
         <f>SUM(B5:B9)</f>
         <v/>
       </c>
-      <c r="C10" s="32">
+      <c r="C10" s="44">
         <f>SUM(C5:C9)</f>
         <v/>
       </c>
-      <c r="D10" s="32">
+      <c r="D10" s="44">
         <f>SUM(D5:D9)</f>
         <v/>
       </c>
-      <c r="E10" s="32">
+      <c r="E10" s="44">
         <f>SUM(E5:E9)</f>
         <v/>
       </c>
-      <c r="F10" s="32">
+      <c r="F10" s="44">
         <f>SUM(F5:F9)</f>
         <v/>
       </c>
-      <c r="G10" s="49">
+      <c r="G10" s="61">
         <f>IFERROR(F10/D10,"")</f>
         <v/>
       </c>
-      <c r="H10" s="32">
+      <c r="H10" s="44">
         <f>SUM(H5:H9)</f>
         <v/>
       </c>
@@ -4870,288 +5382,288 @@
       </c>
     </row>
     <row r="5" ht="58" customHeight="1">
-      <c r="A5" s="50" t="inlineStr">
+      <c r="A5" s="62" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="B5" s="51" t="inlineStr">
+      <c r="B5" s="63" t="inlineStr">
         <is>
           <t>Geovanna — realizado em base diferente do orçado</t>
         </is>
       </c>
-      <c r="C5" s="51" t="inlineStr">
+      <c r="C5" s="63" t="inlineStr">
         <is>
           <t>O planejado dela é R$ 4.825,52/mês, que é o CUSTO TOTAL orçado na ficha (salário + encargos de folha + benefícios). O realizado lançado é o SALÁRIO BRUTO, R$ 2.886,91/mês, confirmado sem alteração no ano. São bases diferentes.</t>
         </is>
       </c>
-      <c r="D5" s="51" t="inlineStr">
+      <c r="D5" s="63" t="inlineStr">
         <is>
           <t>O desvio desta linha (−R$ 1.938,61/mês, −R$ 13.570,24 no acumulado jan–jul) NÃO é economia: é o encargo que falta do lado do realizado. Para fechar, peça ao RH o custo total mensal dela — ou o percentual de encargos da empresa, que dá para calcular a partir do bruto.</t>
         </is>
       </c>
-      <c r="E5" s="51" t="inlineStr">
+      <c r="E5" s="63" t="inlineStr">
         <is>
           <t>Cristiane + RH</t>
         </is>
       </c>
-      <c r="F5" s="52" t="inlineStr">
+      <c r="F5" s="64" t="inlineStr">
         <is>
           <t>BASE DIFERENTE</t>
         </is>
       </c>
     </row>
     <row r="6" ht="58" customHeight="1">
-      <c r="A6" s="53" t="inlineStr">
+      <c r="A6" s="65" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="B6" s="54" t="inlineStr">
+      <c r="B6" s="66" t="inlineStr">
         <is>
           <t>Aumento da Thamar em abr/26</t>
         </is>
       </c>
-      <c r="C6" s="54" t="inlineStr">
+      <c r="C6" s="66" t="inlineStr">
         <is>
           <t>Recebia R$ 4.500/mês de jan a mar, abaixo dos R$ 5.000 orçados. Em abr/26 teve aumento de R$ 1.000 e passou a R$ 5.500, acima do orçado. O planejado foi mantido em R$ 5.000 nos sete meses fechados (para o desvio ficar visível) e revisado para R$ 5.500 de ago a dez.</t>
         </is>
       </c>
-      <c r="D6" s="54" t="inlineStr">
+      <c r="D6" s="66" t="inlineStr">
         <is>
           <t>No acumulado jan–jul o efeito líquido é de apenas R$ 500 acima do orçado (−R$ 1.500 em jan–mar, +R$ 2.000 em abr–jul), e mais R$ 2.500 previstos até dezembro. Ao contrário do aumento do Vinicius, este estourou o orçado: não havia folga na linha dela.</t>
         </is>
       </c>
-      <c r="E6" s="54" t="inlineStr">
+      <c r="E6" s="66" t="inlineStr">
         <is>
           <t>Cristiane</t>
         </is>
       </c>
-      <c r="F6" s="55" t="inlineStr">
+      <c r="F6" s="67" t="inlineStr">
         <is>
           <t>APLICADO</t>
         </is>
       </c>
     </row>
     <row r="7" ht="58" customHeight="1">
-      <c r="A7" s="50" t="inlineStr">
+      <c r="A7" s="62" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="B7" s="51" t="inlineStr">
+      <c r="B7" s="63" t="inlineStr">
         <is>
           <t>Jusbrasil 30% acima do orçado</t>
         </is>
       </c>
-      <c r="C7" s="51" t="inlineStr">
+      <c r="C7" s="63" t="inlineStr">
         <is>
           <t>Orçado R$ 104,90/mês, realizado R$ 136,00/mês em mai, jun e jul.</t>
         </is>
       </c>
-      <c r="D7" s="51" t="inlineStr">
+      <c r="D7" s="63" t="inlineStr">
         <is>
           <t>Menor desvio em reais (R$ 31,10/mês), mas o maior em percentual. Vale conferir se houve reajuste contratual ou mudança de plano.</t>
         </is>
       </c>
-      <c r="E7" s="51" t="inlineStr">
+      <c r="E7" s="63" t="inlineStr">
         <is>
           <t>Cristiane</t>
         </is>
       </c>
-      <c r="F7" s="56" t="inlineStr">
+      <c r="F7" s="68" t="inlineStr">
         <is>
           <t>EM ABERTO</t>
         </is>
       </c>
     </row>
     <row r="8" ht="58" customHeight="1">
-      <c r="A8" s="53" t="inlineStr">
+      <c r="A8" s="65" t="inlineStr">
         <is>
           <t>E</t>
         </is>
       </c>
-      <c r="B8" s="54" t="inlineStr">
+      <c r="B8" s="66" t="inlineStr">
         <is>
           <t>Bonificação de ago/26 do Jurídico</t>
         </is>
       </c>
-      <c r="C8" s="54" t="inlineStr">
+      <c r="C8" s="66" t="inlineStr">
         <is>
           <t>Estão orçados R$ 10.293,60 em agosto e R$ 12.867,00 em dezembro. O realizado de agosto ainda não foi informado.</t>
         </is>
       </c>
-      <c r="D8" s="54" t="inlineStr">
+      <c r="D8" s="66" t="inlineStr">
         <is>
           <t>É a maior despesa isolada do Jurídico no segundo semestre.</t>
         </is>
       </c>
-      <c r="E8" s="54" t="inlineStr">
+      <c r="E8" s="66" t="inlineStr">
         <is>
           <t>Cristiane</t>
         </is>
       </c>
-      <c r="F8" s="56" t="inlineStr">
+      <c r="F8" s="68" t="inlineStr">
         <is>
           <t>EM ABERTO</t>
         </is>
       </c>
     </row>
     <row r="9" ht="58" customHeight="1">
-      <c r="A9" s="50" t="inlineStr">
+      <c r="A9" s="62" t="inlineStr">
         <is>
           <t>H</t>
         </is>
       </c>
-      <c r="B9" s="51" t="inlineStr">
+      <c r="B9" s="63" t="inlineStr">
         <is>
           <t>Planejado de jan a abr — CONFERIR</t>
         </is>
       </c>
-      <c r="C9" s="51" t="inlineStr">
+      <c r="C9" s="63" t="inlineStr">
         <is>
           <t>O 1º quadrimestre foi preenchido replicando os valores mensais conhecidos, porque a ficha original só trazia o grid de mai a dez. Exceções tratadas: Jonathan começa em abr, Thamar a R$ 5.000 (pré-reajuste), Vinicius com bruto de R$ 2.570,52 e Adapta a R$ 1.300 (valor até jun).</t>
         </is>
       </c>
-      <c r="D9" s="51" t="inlineStr">
+      <c r="D9" s="63" t="inlineStr">
         <is>
           <t>Se algum contrato tinha valor diferente no 1º quadrimestre, ou se houve bonificação nesse período, o planejado de jan a abr precisa ser corrigido antes de comparar com o realizado.</t>
         </is>
       </c>
-      <c r="E9" s="51" t="inlineStr">
+      <c r="E9" s="63" t="inlineStr">
         <is>
           <t>Cristiane</t>
         </is>
       </c>
-      <c r="F9" s="57" t="inlineStr">
+      <c r="F9" s="69" t="inlineStr">
         <is>
           <t>CONFERIR</t>
         </is>
       </c>
     </row>
     <row r="10" ht="58" customHeight="1">
-      <c r="A10" s="53" t="inlineStr">
+      <c r="A10" s="65" t="inlineStr">
         <is>
           <t>I</t>
         </is>
       </c>
-      <c r="B10" s="54" t="inlineStr">
+      <c r="B10" s="66" t="inlineStr">
         <is>
           <t>Realizado de jan a abr — A LANÇAR</t>
         </is>
       </c>
-      <c r="C10" s="54" t="inlineStr">
+      <c r="C10" s="66" t="inlineStr">
         <is>
           <t>As colunas de jan a abr estão em branco na aba Realizado. Só mai, jun e jul foram informados.</t>
         </is>
       </c>
-      <c r="D10" s="54" t="inlineStr">
+      <c r="D10" s="66" t="inlineStr">
         <is>
           <t>São 4 dos 7 meses já fechados do ano. Sem eles o acumulado e o Painel refletem menos da metade do período decorrido.</t>
         </is>
       </c>
-      <c r="E10" s="54" t="inlineStr">
+      <c r="E10" s="66" t="inlineStr">
         <is>
           <t>Cristiane</t>
         </is>
       </c>
-      <c r="F10" s="52" t="inlineStr">
+      <c r="F10" s="64" t="inlineStr">
         <is>
           <t>A LANÇAR</t>
         </is>
       </c>
     </row>
     <row r="11" ht="58" customHeight="1">
-      <c r="A11" s="50" t="inlineStr">
+      <c r="A11" s="62" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="B11" s="51" t="inlineStr">
+      <c r="B11" s="63" t="inlineStr">
         <is>
           <t>Origem do valor realizado</t>
         </is>
       </c>
-      <c r="C11" s="51" t="inlineStr">
+      <c r="C11" s="63" t="inlineStr">
         <is>
           <t>Ainda não definido se o realizado virá de lançamento manual, de relatório do financeiro/ERP por centro de custo, ou misto. Até aqui os números vieram informados pela gestora.</t>
         </is>
       </c>
-      <c r="D11" s="51" t="inlineStr">
+      <c r="D11" s="63" t="inlineStr">
         <is>
           <t>Sem fonte definida o realizado pode divergir da contabilidade e o comparativo perde valor na apresentação à diretoria.</t>
         </is>
       </c>
-      <c r="E11" s="51" t="inlineStr">
+      <c r="E11" s="63" t="inlineStr">
         <is>
           <t>Cristiane + Financeiro</t>
         </is>
       </c>
-      <c r="F11" s="56" t="inlineStr">
+      <c r="F11" s="68" t="inlineStr">
         <is>
           <t>EM ABERTO</t>
         </is>
       </c>
     </row>
     <row r="12" ht="58" customHeight="1">
-      <c r="A12" s="53" t="inlineStr">
+      <c r="A12" s="65" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="B12" s="54" t="inlineStr">
+      <c r="B12" s="66" t="inlineStr">
         <is>
           <t>Jusfy x Astrea</t>
         </is>
       </c>
-      <c r="C12" s="54" t="inlineStr">
+      <c r="C12" s="66" t="inlineStr">
         <is>
           <t>O risco era pagar os dois em paralelo. O realizado de mai–jul mostra Astrea em R$ 0 (cancelado) e Jusfy em R$ 0 (ainda não iniciado) — no momento não há custo de nenhum dos dois.</t>
         </is>
       </c>
-      <c r="D12" s="54" t="inlineStr">
+      <c r="D12" s="66" t="inlineStr">
         <is>
           <t>Economia de R$ 212,07/mês enquanto durar. Falta decidir se o Jusfy entra e quando, para ajustar o planejado dos meses seguintes.</t>
         </is>
       </c>
-      <c r="E12" s="54" t="inlineStr">
+      <c r="E12" s="66" t="inlineStr">
         <is>
           <t>Cristiane</t>
         </is>
       </c>
-      <c r="F12" s="55" t="inlineStr">
+      <c r="F12" s="67" t="inlineStr">
         <is>
           <t>RESOLVIDO</t>
         </is>
       </c>
     </row>
     <row r="13" ht="58" customHeight="1">
-      <c r="A13" s="50" t="inlineStr">
+      <c r="A13" s="62" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="B13" s="51" t="inlineStr">
+      <c r="B13" s="63" t="inlineStr">
         <is>
           <t>Critério de competência x caixa</t>
         </is>
       </c>
-      <c r="C13" s="51" t="inlineStr">
+      <c r="C13" s="63" t="inlineStr">
         <is>
           <t>Definir se o realizado será lançado pela data de pagamento (caixa) ou pelo mês de referência da despesa (competência).</t>
         </is>
       </c>
-      <c r="D13" s="51" t="inlineStr">
+      <c r="D13" s="63" t="inlineStr">
         <is>
           <t>Misturar os dois critérios gera desvio artificial em meses de virada, principalmente em folha e prêmios.</t>
         </is>
       </c>
-      <c r="E13" s="51" t="inlineStr">
+      <c r="E13" s="63" t="inlineStr">
         <is>
           <t>Cristiane + Financeiro</t>
         </is>
       </c>
-      <c r="F13" s="56" t="inlineStr">
+      <c r="F13" s="68" t="inlineStr">
         <is>
           <t>EM ABERTO</t>
         </is>
@@ -5195,67 +5707,67 @@
       </c>
     </row>
     <row r="4" ht="22" customHeight="1">
-      <c r="A4" s="16" t="inlineStr">
+      <c r="A4" s="31" t="inlineStr">
         <is>
           <t>ROTINA MENSAL</t>
         </is>
       </c>
     </row>
     <row r="5" ht="34" customHeight="1">
-      <c r="A5" s="58" t="inlineStr">
+      <c r="A5" s="70" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="B5" s="59" t="inlineStr">
+      <c r="B5" s="71" t="inlineStr">
         <is>
           <t>Abra a aba REALIZADO e preencha apenas as células amarelas do mês que fechou. Se o item não teve gasto no mês, digite 0 — deixar em branco significa 'ainda não lancei'.</t>
         </is>
       </c>
     </row>
     <row r="6" ht="34" customHeight="1">
-      <c r="A6" s="58" t="inlineStr">
+      <c r="A6" s="70" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="B6" s="59" t="inlineStr">
+      <c r="B6" s="71" t="inlineStr">
         <is>
           <t>Preencha a coluna 'Fonte do dado' (ex.: relatório do financeiro, nota fiscal, extrato do cartão) para o número ser auditável depois.</t>
         </is>
       </c>
     </row>
     <row r="7" ht="34" customHeight="1">
-      <c r="A7" s="58" t="inlineStr">
+      <c r="A7" s="70" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="B7" s="59" t="inlineStr">
+      <c r="B7" s="71" t="inlineStr">
         <is>
           <t>Vá na aba COMPARATIVO e selecione o mês em B3. Todas as demais abas acompanham essa escolha.</t>
         </is>
       </c>
     </row>
     <row r="8" ht="34" customHeight="1">
-      <c r="A8" s="58" t="inlineStr">
+      <c r="A8" s="70" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="B8" s="59" t="inlineStr">
+      <c r="B8" s="71" t="inlineStr">
         <is>
           <t>Confira o PAINEL: ele mostra o desvio por departamento e os 5 maiores estouros do acumulado. É a tela para levar à diretoria.</t>
         </is>
       </c>
     </row>
     <row r="9" ht="34" customHeight="1">
-      <c r="A9" s="58" t="inlineStr">
+      <c r="A9" s="70" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="B9" s="59" t="inlineStr">
+      <c r="B9" s="71" t="inlineStr">
         <is>
           <t>Atualize a aba PENDÊNCIAS conforme as decisões forem sendo tomadas.</t>
         </is>
@@ -5263,67 +5775,67 @@
     </row>
     <row r="10" ht="8" customHeight="1"/>
     <row r="11" ht="22" customHeight="1">
-      <c r="A11" s="16" t="inlineStr">
+      <c r="A11" s="31" t="inlineStr">
         <is>
           <t>COMO LER OS NÚMEROS</t>
         </is>
       </c>
     </row>
     <row r="12" ht="34" customHeight="1">
-      <c r="A12" s="58" t="inlineStr">
+      <c r="A12" s="70" t="inlineStr">
         <is>
           <t>Desvio positivo (vermelho)</t>
         </is>
       </c>
-      <c r="B12" s="59" t="inlineStr">
+      <c r="B12" s="71" t="inlineStr">
         <is>
           <t>Gastou ACIMA do orçado.</t>
         </is>
       </c>
     </row>
     <row r="13" ht="34" customHeight="1">
-      <c r="A13" s="58" t="inlineStr">
+      <c r="A13" s="70" t="inlineStr">
         <is>
           <t>Desvio negativo (verde)</t>
         </is>
       </c>
-      <c r="B13" s="59" t="inlineStr">
+      <c r="B13" s="71" t="inlineStr">
         <is>
           <t>Gastou ABAIXO do orçado — economia ou despesa ainda não realizada.</t>
         </is>
       </c>
     </row>
     <row r="14" ht="34" customHeight="1">
-      <c r="A14" s="58" t="inlineStr">
+      <c r="A14" s="70" t="inlineStr">
         <is>
           <t>Planejado acum.</t>
         </is>
       </c>
-      <c r="B14" s="59" t="inlineStr">
+      <c r="B14" s="71" t="inlineStr">
         <is>
           <t>Soma de maio até o mês selecionado.</t>
         </is>
       </c>
     </row>
     <row r="15" ht="34" customHeight="1">
-      <c r="A15" s="58" t="inlineStr">
+      <c r="A15" s="70" t="inlineStr">
         <is>
           <t>% Executado</t>
         </is>
       </c>
-      <c r="B15" s="59" t="inlineStr">
+      <c r="B15" s="71" t="inlineStr">
         <is>
           <t>Realizado acumulado ÷ Planejado acumulado. Perto de 100% = no ritmo.</t>
         </is>
       </c>
     </row>
     <row r="16" ht="34" customHeight="1">
-      <c r="A16" s="58" t="inlineStr">
+      <c r="A16" s="70" t="inlineStr">
         <is>
           <t>Sem lançamento</t>
         </is>
       </c>
-      <c r="B16" s="59" t="inlineStr">
+      <c r="B16" s="71" t="inlineStr">
         <is>
           <t>Nada foi lançado no realizado ainda — não confunda com economia.</t>
         </is>
@@ -5331,43 +5843,43 @@
     </row>
     <row r="17" ht="8" customHeight="1"/>
     <row r="18" ht="22" customHeight="1">
-      <c r="A18" s="16" t="inlineStr">
+      <c r="A18" s="31" t="inlineStr">
         <is>
           <t>REGRAS DA PLANILHA</t>
         </is>
       </c>
     </row>
     <row r="19" ht="34" customHeight="1">
-      <c r="A19" s="58" t="inlineStr">
+      <c r="A19" s="70" t="inlineStr">
         <is>
           <t>Não altere</t>
         </is>
       </c>
-      <c r="B19" s="59" t="inlineStr">
+      <c r="B19" s="71" t="inlineStr">
         <is>
           <t>As colunas de identificação da aba Realizado (A a G) são fórmulas que espelham a aba Planejado. Alterar quebra o comparativo.</t>
         </is>
       </c>
     </row>
     <row r="20" ht="34" customHeight="1">
-      <c r="A20" s="58" t="inlineStr">
+      <c r="A20" s="70" t="inlineStr">
         <is>
           <t>Nova linha de orçamento</t>
         </is>
       </c>
-      <c r="B20" s="59" t="inlineStr">
+      <c r="B20" s="71" t="inlineStr">
         <is>
           <t>Insira na aba Planejado e replique a mesma linha na aba Realizado e na aba Comparativo, mantendo o mesmo ID.</t>
         </is>
       </c>
     </row>
     <row r="21" ht="34" customHeight="1">
-      <c r="A21" s="58" t="inlineStr">
+      <c r="A21" s="70" t="inlineStr">
         <is>
           <t>Revisão de orçamento</t>
         </is>
       </c>
-      <c r="B21" s="59" t="inlineStr">
+      <c r="B21" s="71" t="inlineStr">
         <is>
           <t>Se a diretoria aprovar um valor novo, altere na aba Planejado e registre o motivo na aba Pendências.</t>
         </is>

--- a/orcamento/Orcamento_JURIDICO_2026.xlsx
+++ b/orcamento/Orcamento_JURIDICO_2026.xlsx
@@ -3838,27 +3838,29 @@
         <v/>
       </c>
       <c r="H5" s="50" t="n">
+        <v>6750</v>
+      </c>
+      <c r="I5" s="50" t="n">
+        <v>6750</v>
+      </c>
+      <c r="J5" s="50" t="n">
+        <v>6750</v>
+      </c>
+      <c r="K5" s="50" t="n">
+        <v>6750</v>
+      </c>
+      <c r="L5" s="50" t="n">
+        <v>6750</v>
+      </c>
+      <c r="M5" s="50" t="n">
+        <v>6750</v>
+      </c>
+      <c r="N5" s="50" t="n">
+        <v>6750</v>
+      </c>
+      <c r="O5" s="50" t="n">
         <v>8818</v>
       </c>
-      <c r="I5" s="50" t="n">
-        <v>8818</v>
-      </c>
-      <c r="J5" s="50" t="n">
-        <v>8818</v>
-      </c>
-      <c r="K5" s="50" t="n">
-        <v>8818</v>
-      </c>
-      <c r="L5" s="50" t="n">
-        <v>8818</v>
-      </c>
-      <c r="M5" s="50" t="n">
-        <v>8818</v>
-      </c>
-      <c r="N5" s="50" t="n">
-        <v>8818</v>
-      </c>
-      <c r="O5" s="50" t="n"/>
       <c r="T5" s="46">
         <f>SUM(H5:S5)</f>
         <v/>
@@ -3870,7 +3872,7 @@
       </c>
       <c r="V5" s="51" t="inlineStr">
         <is>
-          <t>Valor cheio da nota — R$ 1.182/mês abaixo do contratado</t>
+          <t>R$ 6.750/mês de jan a jul; R$ 8.818 pagos em 01/08 (ref. julho). Lançado por caixa</t>
         </is>
       </c>
     </row>
@@ -5645,17 +5647,17 @@
       </c>
       <c r="B13" s="63" t="inlineStr">
         <is>
-          <t>Critério de competência x caixa</t>
+          <t>Competência x caixa — DEFASAGEM CONFIRMADA</t>
         </is>
       </c>
       <c r="C13" s="63" t="inlineStr">
         <is>
-          <t>Definir se o realizado será lançado pela data de pagamento (caixa) ou pelo mês de referência da despesa (competência).</t>
+          <t>O pagamento do Miguel de 01/08/26 refere-se a julho, então há pelo menos um prestador cujo pagamento cai no mês seguinte ao da prestação. Todo o realizado está lançado por CAIXA (mês em que o pagamento saiu), que é como os valores foram informados.</t>
         </is>
       </c>
       <c r="D13" s="63" t="inlineStr">
         <is>
-          <t>Misturar os dois critérios gera desvio artificial em meses de virada, principalmente em folha e prêmios.</t>
+          <t>Consequência: o valor lançado em jan/26 pode ser referente a dez/2025, e o serviço de dez/26 só aparecerá em jan/2027 — o ano fecha com 12 pagamentos, mas defasados em relação ao orçamento, que é de competência. Vale conferir quais contratos pagam no mês seguinte e decidir se o comparativo passa para competência.</t>
         </is>
       </c>
       <c r="E13" s="63" t="inlineStr">
@@ -5663,9 +5665,9 @@
           <t>Cristiane + Financeiro</t>
         </is>
       </c>
-      <c r="F13" s="68" t="inlineStr">
-        <is>
-          <t>EM ABERTO</t>
+      <c r="F13" s="69" t="inlineStr">
+        <is>
+          <t>DECIDIR</t>
         </is>
       </c>
     </row>

--- a/orcamento/Orcamento_JURIDICO_2026.xlsx
+++ b/orcamento/Orcamento_JURIDICO_2026.xlsx
@@ -146,7 +146,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="15">
+  <fills count="16">
     <fill>
       <patternFill/>
     </fill>
@@ -218,6 +218,11 @@
         <fgColor rgb="00FFE699"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFD966"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -245,7 +250,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="72">
+  <cellXfs count="73">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
@@ -396,6 +401,9 @@
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="14" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="15" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -1839,7 +1847,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S27"/>
+  <dimension ref="A1:S31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -2695,49 +2703,49 @@
         <v/>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="43" t="inlineStr">
+    <row r="31">
+      <c r="A31" s="43" t="inlineStr">
         <is>
           <t>TOTAL GERAL</t>
         </is>
       </c>
-      <c r="B27" s="43" t="n"/>
-      <c r="C27" s="43" t="n"/>
-      <c r="D27" s="43" t="n"/>
-      <c r="E27" s="43" t="n"/>
-      <c r="F27" s="44">
+      <c r="B31" s="43" t="n"/>
+      <c r="C31" s="43" t="n"/>
+      <c r="D31" s="43" t="n"/>
+      <c r="E31" s="43" t="n"/>
+      <c r="F31" s="44">
         <f>SUM(F6:F14)</f>
         <v/>
       </c>
-      <c r="G27" s="44">
+      <c r="G31" s="44">
         <f>SUM(G6:G14)</f>
         <v/>
       </c>
-      <c r="H27" s="44">
+      <c r="H31" s="44">
         <f>SUM(H6:H14)</f>
         <v/>
       </c>
-      <c r="I27" s="44">
+      <c r="I31" s="44">
         <f>SUM(I6:I14)</f>
         <v/>
       </c>
-      <c r="J27" s="44">
+      <c r="J31" s="44">
         <f>SUM(J6:J14)</f>
         <v/>
       </c>
-      <c r="K27" s="44">
+      <c r="K31" s="44">
         <f>SUM(K6:K14)</f>
         <v/>
       </c>
-      <c r="L27" s="45">
-        <f>IFERROR(K27/I27,"")</f>
-        <v/>
-      </c>
-      <c r="M27" s="45">
-        <f>IFERROR(J27/I27,"")</f>
-        <v/>
-      </c>
-      <c r="N27" s="43" t="n"/>
+      <c r="L31" s="45">
+        <f>IFERROR(K31/I31,"")</f>
+        <v/>
+      </c>
+      <c r="M31" s="45">
+        <f>IFERROR(J31/I31,"")</f>
+        <v/>
+      </c>
+      <c r="N31" s="43" t="n"/>
     </row>
   </sheetData>
   <autoFilter ref="A5:N14"/>
@@ -3242,7 +3250,11 @@
           <t>JUSBRASIL</t>
         </is>
       </c>
-      <c r="E9" s="37" t="inlineStr"/>
+      <c r="E9" s="37" t="inlineStr">
+        <is>
+          <t>ORÇAMENTO VEIO ERRADO: orçado R$ 104,90/mês, custo real R$ 136,00/mês. Corrigir na revisão orçamentária</t>
+        </is>
+      </c>
       <c r="F9" s="36" t="inlineStr"/>
       <c r="G9" s="36" t="inlineStr">
         <is>
@@ -3313,7 +3325,7 @@
       </c>
       <c r="E10" s="37" t="inlineStr">
         <is>
-          <t>Cancelado — realizado zerado desde mai/26</t>
+          <t>ORÇAMENTO VEIO ERRADO: orçado R$ 112,07/mês, custo real R$ 346,00/mês. Corrigir na revisão orçamentária</t>
         </is>
       </c>
       <c r="F10" s="36" t="inlineStr"/>
@@ -4136,7 +4148,7 @@
       </c>
       <c r="V9" s="51" t="inlineStr">
         <is>
-          <t>Acima do orçado (R$ 104,90) — conferir contrato</t>
+          <t>R$ 136,00/mês contra R$ 104,90 orçados. Erro no orçamento original</t>
         </is>
       </c>
     </row>
@@ -4170,25 +4182,25 @@
         <v/>
       </c>
       <c r="H10" s="50" t="n">
-        <v>0</v>
+        <v>346</v>
       </c>
       <c r="I10" s="50" t="n">
-        <v>0</v>
+        <v>346</v>
       </c>
       <c r="J10" s="50" t="n">
-        <v>0</v>
+        <v>346</v>
       </c>
       <c r="K10" s="50" t="n">
-        <v>0</v>
+        <v>346</v>
       </c>
       <c r="L10" s="50" t="n">
-        <v>0</v>
+        <v>346</v>
       </c>
       <c r="M10" s="50" t="n">
-        <v>0</v>
+        <v>346</v>
       </c>
       <c r="N10" s="50" t="n">
-        <v>0</v>
+        <v>346</v>
       </c>
       <c r="O10" s="50" t="n"/>
       <c r="T10" s="46">
@@ -4202,7 +4214,7 @@
       </c>
       <c r="V10" s="51" t="inlineStr">
         <is>
-          <t>Cancelado — sem cobrança</t>
+          <t>R$ 346,00/mês — 3x o orçado (R$ 112,07). Erro no orçamento original</t>
         </is>
       </c>
     </row>
@@ -5326,7 +5338,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F13"/>
+  <dimension ref="A1:F14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -5620,12 +5632,12 @@
       </c>
       <c r="C12" s="66" t="inlineStr">
         <is>
-          <t>O risco era pagar os dois em paralelo. O realizado de mai–jul mostra Astrea em R$ 0 (cancelado) e Jusfy em R$ 0 (ainda não iniciado) — no momento não há custo de nenhum dos dois.</t>
+          <t>O Astrea NÃO foi cancelado: custa R$ 346,00/mês e segue ativo. O Jusfy está em R$ 0 — ainda não iniciado. A informação anterior de que o Astrea estava zerado foi corrigida pela gestora.</t>
         </is>
       </c>
       <c r="D12" s="66" t="inlineStr">
         <is>
-          <t>Economia de R$ 212,07/mês enquanto durar. Falta decidir se o Jusfy entra e quando, para ajustar o planejado dos meses seguintes.</t>
+          <t>O Astrea sozinho consome R$ 4.152/ano. Se o Jusfy entrar e o objetivo era substituí-lo, essa é a economia em jogo — e ela é maior do que parecia, porque o custo real do Astrea é 3x o que estava orçado.</t>
         </is>
       </c>
       <c r="E12" s="66" t="inlineStr">
@@ -5633,39 +5645,71 @@
           <t>Cristiane</t>
         </is>
       </c>
-      <c r="F12" s="67" t="inlineStr">
-        <is>
-          <t>RESOLVIDO</t>
+      <c r="F12" s="68" t="inlineStr">
+        <is>
+          <t>EM ABERTO</t>
         </is>
       </c>
     </row>
     <row r="13" ht="58" customHeight="1">
       <c r="A13" s="62" t="inlineStr">
         <is>
+          <t>K</t>
+        </is>
+      </c>
+      <c r="B13" s="63" t="inlineStr">
+        <is>
+          <t>ORÇAMENTO VEIO ERRADO — Astrea e Jusbrasil</t>
+        </is>
+      </c>
+      <c r="C13" s="63" t="inlineStr">
+        <is>
+          <t>Os dois valores já chegaram errados na ficha de orçamento que a gestora recebeu. Astrea: orçado R$ 112,07/mês, custo real R$ 346,00 (3,1x). Jusbrasil: orçado R$ 104,90/mês, custo real R$ 136,00 (1,3x). PAUTA PARA A REUNIÃO COM A DIRETORIA.</t>
+        </is>
+      </c>
+      <c r="D13" s="63" t="inlineStr">
+        <is>
+          <t>O planejado dessas duas linhas foi mantido como está na ficha, para o erro ficar visível no comparativo. Subdimensionamento de R$ 3.180,36 no ano (R$ 2.807,16 do Astrea + R$ 373,20 do Jusbrasil). Não é estouro de gestão: é erro na origem do orçamento, e precisa de correção formal.</t>
+        </is>
+      </c>
+      <c r="E13" s="63" t="inlineStr">
+        <is>
+          <t>Cristiane + Diretoria</t>
+        </is>
+      </c>
+      <c r="F13" s="70" t="inlineStr">
+        <is>
+          <t>PAUTA REUNIÃO</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="58" customHeight="1">
+      <c r="A14" s="65" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="B13" s="63" t="inlineStr">
+      <c r="B14" s="66" t="inlineStr">
         <is>
           <t>Competência x caixa — DEFASAGEM CONFIRMADA</t>
         </is>
       </c>
-      <c r="C13" s="63" t="inlineStr">
+      <c r="C14" s="66" t="inlineStr">
         <is>
           <t>O pagamento do Miguel de 01/08/26 refere-se a julho, então há pelo menos um prestador cujo pagamento cai no mês seguinte ao da prestação. Todo o realizado está lançado por CAIXA (mês em que o pagamento saiu), que é como os valores foram informados.</t>
         </is>
       </c>
-      <c r="D13" s="63" t="inlineStr">
+      <c r="D14" s="66" t="inlineStr">
         <is>
           <t>Consequência: o valor lançado em jan/26 pode ser referente a dez/2025, e o serviço de dez/26 só aparecerá em jan/2027 — o ano fecha com 12 pagamentos, mas defasados em relação ao orçamento, que é de competência. Vale conferir quais contratos pagam no mês seguinte e decidir se o comparativo passa para competência.</t>
         </is>
       </c>
-      <c r="E13" s="63" t="inlineStr">
+      <c r="E14" s="66" t="inlineStr">
         <is>
           <t>Cristiane + Financeiro</t>
         </is>
       </c>
-      <c r="F13" s="69" t="inlineStr">
+      <c r="F14" s="69" t="inlineStr">
         <is>
           <t>DECIDIR</t>
         </is>
@@ -5716,60 +5760,60 @@
       </c>
     </row>
     <row r="5" ht="34" customHeight="1">
-      <c r="A5" s="70" t="inlineStr">
+      <c r="A5" s="71" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="B5" s="71" t="inlineStr">
+      <c r="B5" s="72" t="inlineStr">
         <is>
           <t>Abra a aba REALIZADO e preencha apenas as células amarelas do mês que fechou. Se o item não teve gasto no mês, digite 0 — deixar em branco significa 'ainda não lancei'.</t>
         </is>
       </c>
     </row>
     <row r="6" ht="34" customHeight="1">
-      <c r="A6" s="70" t="inlineStr">
+      <c r="A6" s="71" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="B6" s="71" t="inlineStr">
+      <c r="B6" s="72" t="inlineStr">
         <is>
           <t>Preencha a coluna 'Fonte do dado' (ex.: relatório do financeiro, nota fiscal, extrato do cartão) para o número ser auditável depois.</t>
         </is>
       </c>
     </row>
     <row r="7" ht="34" customHeight="1">
-      <c r="A7" s="70" t="inlineStr">
+      <c r="A7" s="71" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="B7" s="71" t="inlineStr">
+      <c r="B7" s="72" t="inlineStr">
         <is>
           <t>Vá na aba COMPARATIVO e selecione o mês em B3. Todas as demais abas acompanham essa escolha.</t>
         </is>
       </c>
     </row>
     <row r="8" ht="34" customHeight="1">
-      <c r="A8" s="70" t="inlineStr">
+      <c r="A8" s="71" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="B8" s="71" t="inlineStr">
+      <c r="B8" s="72" t="inlineStr">
         <is>
           <t>Confira o PAINEL: ele mostra o desvio por departamento e os 5 maiores estouros do acumulado. É a tela para levar à diretoria.</t>
         </is>
       </c>
     </row>
     <row r="9" ht="34" customHeight="1">
-      <c r="A9" s="70" t="inlineStr">
+      <c r="A9" s="71" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="B9" s="71" t="inlineStr">
+      <c r="B9" s="72" t="inlineStr">
         <is>
           <t>Atualize a aba PENDÊNCIAS conforme as decisões forem sendo tomadas.</t>
         </is>
@@ -5784,60 +5828,60 @@
       </c>
     </row>
     <row r="12" ht="34" customHeight="1">
-      <c r="A12" s="70" t="inlineStr">
+      <c r="A12" s="71" t="inlineStr">
         <is>
           <t>Desvio positivo (vermelho)</t>
         </is>
       </c>
-      <c r="B12" s="71" t="inlineStr">
+      <c r="B12" s="72" t="inlineStr">
         <is>
           <t>Gastou ACIMA do orçado.</t>
         </is>
       </c>
     </row>
     <row r="13" ht="34" customHeight="1">
-      <c r="A13" s="70" t="inlineStr">
+      <c r="A13" s="71" t="inlineStr">
         <is>
           <t>Desvio negativo (verde)</t>
         </is>
       </c>
-      <c r="B13" s="71" t="inlineStr">
+      <c r="B13" s="72" t="inlineStr">
         <is>
           <t>Gastou ABAIXO do orçado — economia ou despesa ainda não realizada.</t>
         </is>
       </c>
     </row>
     <row r="14" ht="34" customHeight="1">
-      <c r="A14" s="70" t="inlineStr">
+      <c r="A14" s="71" t="inlineStr">
         <is>
           <t>Planejado acum.</t>
         </is>
       </c>
-      <c r="B14" s="71" t="inlineStr">
+      <c r="B14" s="72" t="inlineStr">
         <is>
           <t>Soma de maio até o mês selecionado.</t>
         </is>
       </c>
     </row>
     <row r="15" ht="34" customHeight="1">
-      <c r="A15" s="70" t="inlineStr">
+      <c r="A15" s="71" t="inlineStr">
         <is>
           <t>% Executado</t>
         </is>
       </c>
-      <c r="B15" s="71" t="inlineStr">
+      <c r="B15" s="72" t="inlineStr">
         <is>
           <t>Realizado acumulado ÷ Planejado acumulado. Perto de 100% = no ritmo.</t>
         </is>
       </c>
     </row>
     <row r="16" ht="34" customHeight="1">
-      <c r="A16" s="70" t="inlineStr">
+      <c r="A16" s="71" t="inlineStr">
         <is>
           <t>Sem lançamento</t>
         </is>
       </c>
-      <c r="B16" s="71" t="inlineStr">
+      <c r="B16" s="72" t="inlineStr">
         <is>
           <t>Nada foi lançado no realizado ainda — não confunda com economia.</t>
         </is>
@@ -5852,36 +5896,36 @@
       </c>
     </row>
     <row r="19" ht="34" customHeight="1">
-      <c r="A19" s="70" t="inlineStr">
+      <c r="A19" s="71" t="inlineStr">
         <is>
           <t>Não altere</t>
         </is>
       </c>
-      <c r="B19" s="71" t="inlineStr">
+      <c r="B19" s="72" t="inlineStr">
         <is>
           <t>As colunas de identificação da aba Realizado (A a G) são fórmulas que espelham a aba Planejado. Alterar quebra o comparativo.</t>
         </is>
       </c>
     </row>
     <row r="20" ht="34" customHeight="1">
-      <c r="A20" s="70" t="inlineStr">
+      <c r="A20" s="71" t="inlineStr">
         <is>
           <t>Nova linha de orçamento</t>
         </is>
       </c>
-      <c r="B20" s="71" t="inlineStr">
+      <c r="B20" s="72" t="inlineStr">
         <is>
           <t>Insira na aba Planejado e replique a mesma linha na aba Realizado e na aba Comparativo, mantendo o mesmo ID.</t>
         </is>
       </c>
     </row>
     <row r="21" ht="34" customHeight="1">
-      <c r="A21" s="70" t="inlineStr">
+      <c r="A21" s="71" t="inlineStr">
         <is>
           <t>Revisão de orçamento</t>
         </is>
       </c>
-      <c r="B21" s="71" t="inlineStr">
+      <c r="B21" s="72" t="inlineStr">
         <is>
           <t>Se a diretoria aprovar um valor novo, altere na aba Planejado e registre o motivo na aba Pendências.</t>
         </is>

--- a/orcamento/Orcamento_JURIDICO_2026.xlsx
+++ b/orcamento/Orcamento_JURIDICO_2026.xlsx
@@ -224,7 +224,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFE699"/>
+        <fgColor rgb="00FFD966"/>
       </patternFill>
     </fill>
     <fill>
@@ -234,7 +234,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFD966"/>
+        <fgColor rgb="00FFE699"/>
       </patternFill>
     </fill>
     <fill>
@@ -17077,25 +17077,25 @@
         <v/>
       </c>
       <c r="H10" s="50" t="n">
-        <v>346</v>
+        <v>1346.28</v>
       </c>
       <c r="I10" s="50" t="n">
-        <v>346</v>
+        <v>5385.12</v>
       </c>
       <c r="J10" s="50" t="n">
-        <v>346</v>
+        <v>0</v>
       </c>
       <c r="K10" s="50" t="n">
-        <v>346</v>
+        <v>0</v>
       </c>
       <c r="L10" s="50" t="n">
-        <v>346</v>
+        <v>0</v>
       </c>
       <c r="M10" s="50" t="n">
-        <v>346</v>
+        <v>0</v>
       </c>
       <c r="N10" s="50" t="n">
-        <v>346</v>
+        <v>0</v>
       </c>
       <c r="O10" s="50" t="n"/>
       <c r="T10" s="46">
@@ -17104,12 +17104,12 @@
       </c>
       <c r="U10" s="51" t="inlineStr">
         <is>
-          <t>Gestora, 05/08/26</t>
+          <t>Extrato do financeiro</t>
         </is>
       </c>
       <c r="V10" s="51" t="inlineStr">
         <is>
-          <t>R$ 346,00/mês — 3x o orçado (R$ 112,07). Erro no orçamento original</t>
+          <t>Anuidade 2026 = R$ 6.731,40 em 5x de R$ 1.346,28, quitada em fev (competência até abr). Sem cobrança de mar em diante</t>
         </is>
       </c>
     </row>
@@ -18233,7 +18233,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F15"/>
+  <dimension ref="A1:F16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -18426,7 +18426,7 @@
       </c>
       <c r="B9" s="63" t="inlineStr">
         <is>
-          <t>Planejado de jan a abr — CONFERIR</t>
+          <t>Planejado de jan a abr — conferido</t>
         </is>
       </c>
       <c r="C9" s="63" t="inlineStr">
@@ -18436,7 +18436,7 @@
       </c>
       <c r="D9" s="63" t="inlineStr">
         <is>
-          <t>Se algum contrato tinha valor diferente no 1º quadrimestre, ou se houve bonificação nesse período, o planejado de jan a abr precisa ser corrigido antes de comparar com o realizado.</t>
+          <t>Conferido e validado pela gestora: os valores replicados estão corretos, nenhum ajuste necessário.</t>
         </is>
       </c>
       <c r="E9" s="63" t="inlineStr">
@@ -18444,9 +18444,9 @@
           <t>Cristiane</t>
         </is>
       </c>
-      <c r="F9" s="69" t="inlineStr">
-        <is>
-          <t>CONFERIR</t>
+      <c r="F9" s="67" t="inlineStr">
+        <is>
+          <t>APLICADO</t>
         </is>
       </c>
     </row>
@@ -18476,9 +18476,9 @@
           <t>Cristiane</t>
         </is>
       </c>
-      <c r="F10" s="70" t="inlineStr">
-        <is>
-          <t>EM ANDAMENTO</t>
+      <c r="F10" s="67" t="inlineStr">
+        <is>
+          <t>APLICADO</t>
         </is>
       </c>
     </row>
@@ -18508,7 +18508,7 @@
           <t>Cristiane + Diretoria</t>
         </is>
       </c>
-      <c r="F11" s="71" t="inlineStr">
+      <c r="F11" s="69" t="inlineStr">
         <is>
           <t>PAUTA REUNIÃO</t>
         </is>
@@ -18554,17 +18554,17 @@
       </c>
       <c r="B13" s="63" t="inlineStr">
         <is>
-          <t>Jusfy x Astrea</t>
+          <t>Jusfy — nunca iniciado</t>
         </is>
       </c>
       <c r="C13" s="63" t="inlineStr">
         <is>
-          <t>O Astrea NÃO foi cancelado: custa R$ 346,00/mês e segue ativo. O Jusfy está em R$ 0 — ainda não iniciado. A informação anterior de que o Astrea estava zerado foi corrigida pela gestora.</t>
+          <t>O Jusfy entrou na ficha porque o orçamento foi montado em nov/dez de 2025, durante a fase de experimento. Em janeiro a decisão foi cancelar, e o serviço nunca chegou a ser iniciado. Custo zero o ano todo.</t>
         </is>
       </c>
       <c r="D13" s="63" t="inlineStr">
         <is>
-          <t>O Astrea sozinho consome R$ 4.152/ano. Se o Jusfy entrar e o objetivo era substituí-lo, essa é a economia em jogo — e ela é maior do que parecia, porque o custo real do Astrea é 3x o que estava orçado.</t>
+          <t>Os R$ 1.200 orçados no ano nunca serão usados. Não é economia de gestão: é item que já nasceu fora do escopo e deve sair na revisão do orçamento.</t>
         </is>
       </c>
       <c r="E13" s="63" t="inlineStr">
@@ -18572,71 +18572,103 @@
           <t>Cristiane</t>
         </is>
       </c>
-      <c r="F13" s="68" t="inlineStr">
-        <is>
-          <t>EM ABERTO</t>
+      <c r="F13" s="67" t="inlineStr">
+        <is>
+          <t>RESOLVIDO</t>
         </is>
       </c>
     </row>
     <row r="14" ht="58" customHeight="1">
       <c r="A14" s="65" t="inlineStr">
         <is>
-          <t>K</t>
+          <t>N</t>
         </is>
       </c>
       <c r="B14" s="66" t="inlineStr">
         <is>
-          <t>ORÇAMENTO VEIO ERRADO — Astrea e Jusbrasil</t>
+          <t>Astrea — anuidade quitada e cancelamento em curso</t>
         </is>
       </c>
       <c r="C14" s="66" t="inlineStr">
         <is>
-          <t>Os dois valores já chegaram errados na ficha de orçamento que a gestora recebeu. Astrea: orçado R$ 112,07/mês, custo real R$ 346,00 (3,1x). Jusbrasil: orçado R$ 104,90/mês, custo real R$ 136,00 (1,3x). PAUTA PARA A REUNIÃO COM A DIRETORIA.</t>
+          <t>A anuidade 2026 custou R$ 6.731,40, parcelada em 5x de R$ 1.346,28. Pelo extrato, uma parcela foi paga em jan e as outras quatro em fev (incluindo R$ 4.038,84 de antecipação); por competência as parcelas vão até abr/26. Não há e não haverá cobrança de mar em diante. O cancelamento formal foi solicitado em ago/26 e aguarda confirmação por e-mail do fornecedor.</t>
         </is>
       </c>
       <c r="D14" s="66" t="inlineStr">
         <is>
-          <t>O planejado dessas duas linhas foi mantido como está na ficha, para o erro ficar visível no comparativo. Subdimensionamento de R$ 3.180,36 no ano (R$ 2.807,16 do Astrea + R$ 373,20 do Jusbrasil). Não é estouro de gestão: é erro na origem do orçamento, e precisa de correção formal.</t>
+          <t>O realizado das linhas de mar a dez é zero de fato, não falta de lançamento. Guardar a confirmação por e-mail do cancelamento para não haver renovação automática da anuidade 2027.</t>
         </is>
       </c>
       <c r="E14" s="66" t="inlineStr">
         <is>
-          <t>Cristiane + Diretoria</t>
-        </is>
-      </c>
-      <c r="F14" s="71" t="inlineStr">
-        <is>
-          <t>PAUTA REUNIÃO</t>
+          <t>Cristiane</t>
+        </is>
+      </c>
+      <c r="F14" s="70" t="inlineStr">
+        <is>
+          <t>EM ANDAMENTO</t>
         </is>
       </c>
     </row>
     <row r="15" ht="58" customHeight="1">
       <c r="A15" s="62" t="inlineStr">
         <is>
+          <t>K</t>
+        </is>
+      </c>
+      <c r="B15" s="63" t="inlineStr">
+        <is>
+          <t>ORÇAMENTO VEIO ERRADO — Astrea e Jusbrasil</t>
+        </is>
+      </c>
+      <c r="C15" s="63" t="inlineStr">
+        <is>
+          <t>ASTREA: orçado R$ 112,07/mês, o que dá R$ 1.344,84 no ano — praticamente o valor de UMA das cinco parcelas (R$ 1.346,28). Quem montou a ficha tomou uma parcela pelo custo total do ano. O custo real da anuidade foi R$ 6.731,40, 5x o orçado. JUSBRASIL: orçado R$ 104,90/mês contra R$ 136,00 reais (1,3x), R$ 373,20 no ano. PAUTA PARA A REUNIÃO COM A DIRETORIA.</t>
+        </is>
+      </c>
+      <c r="D15" s="63" t="inlineStr">
+        <is>
+          <t>Subdimensionamento de R$ 5.759,76 no ano (R$ 5.386,56 do Astrea + R$ 373,20 do Jusbrasil). O planejado das duas linhas foi mantido como veio na ficha, de propósito, para o erro aparecer no comparativo em vez de ser corrigido em silêncio. Não é estouro de gestão: é erro na origem. Como o Astrea será cancelado, o efeito prático é só de 2026 — mas o método de orçar serviços parcelados precisa ser revisto para o ano que vem.</t>
+        </is>
+      </c>
+      <c r="E15" s="63" t="inlineStr">
+        <is>
+          <t>Cristiane + Diretoria</t>
+        </is>
+      </c>
+      <c r="F15" s="69" t="inlineStr">
+        <is>
+          <t>PAUTA REUNIÃO</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="58" customHeight="1">
+      <c r="A16" s="65" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="B15" s="63" t="inlineStr">
+      <c r="B16" s="66" t="inlineStr">
         <is>
           <t>Competência x caixa — DEFASAGEM CONFIRMADA</t>
         </is>
       </c>
-      <c r="C15" s="63" t="inlineStr">
+      <c r="C16" s="66" t="inlineStr">
         <is>
           <t>O pagamento do Miguel de 01/08/26 refere-se a julho, então há pelo menos um prestador cujo pagamento cai no mês seguinte ao da prestação. Todo o realizado está lançado por CAIXA (mês em que o pagamento saiu), que é como os valores foram informados.</t>
         </is>
       </c>
-      <c r="D15" s="63" t="inlineStr">
+      <c r="D16" s="66" t="inlineStr">
         <is>
           <t>Consequência: o valor lançado em jan/26 pode ser referente a dez/2025, e o serviço de dez/26 só aparecerá em jan/2027 — o ano fecha com 12 pagamentos, mas defasados em relação ao orçamento, que é de competência. Com a extração vindo do SIENGE, basta escolher o regime na hora de gerar o relatório: definir isso UMA vez e manter, para o histórico não misturar critérios.</t>
         </is>
       </c>
-      <c r="E15" s="63" t="inlineStr">
+      <c r="E16" s="66" t="inlineStr">
         <is>
           <t>Cristiane + Financeiro</t>
         </is>
       </c>
-      <c r="F15" s="69" t="inlineStr">
+      <c r="F16" s="71" t="inlineStr">
         <is>
           <t>DECIDIR</t>
         </is>

--- a/orcamento/Orcamento_JURIDICO_2026.xlsx
+++ b/orcamento/Orcamento_JURIDICO_2026.xlsx
@@ -19,8 +19,8 @@
     <sheet name="Contas Pagas (detalhe)" sheetId="10" state="visible" r:id="rId10"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Comparativo'!$A$5:$N$14</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Planejado'!$A$4:$T$13</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Comparativo'!$A$5:$N$15</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Planejado'!$A$4:$T$14</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'Contas Pagas (resumo)'!$A$4:$L$39</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'Contas Pagas (detalhe)'!$A$4:$H$323</definedName>
   </definedNames>
@@ -1236,15 +1236,15 @@
         </is>
       </c>
       <c r="C6" s="9">
-        <f>SUMIFS(Planejado!$T$5:$T$13,Planejado!$B$5:$B$13,"Jurídico",Planejado!$C$5:$C$13,"Equipe")</f>
+        <f>SUMIFS(Planejado!$T$5:$T$14,Planejado!$B$5:$B$14,"Jurídico",Planejado!$C$5:$C$14,"Equipe")</f>
         <v/>
       </c>
       <c r="D6" s="9">
-        <f>SUMIFS(Comparativo!$I$6:$I$14,Comparativo!$B$6:$B$14,"Jurídico",Comparativo!$C$6:$C$14,"Equipe")</f>
+        <f>SUMIFS(Comparativo!$I$6:$I$15,Comparativo!$B$6:$B$15,"Jurídico",Comparativo!$C$6:$C$15,"Equipe")</f>
         <v/>
       </c>
       <c r="E6" s="9">
-        <f>SUMIFS(Comparativo!$J$6:$J$14,Comparativo!$B$6:$B$14,"Jurídico",Comparativo!$C$6:$C$14,"Equipe")</f>
+        <f>SUMIFS(Comparativo!$J$6:$J$15,Comparativo!$B$6:$B$15,"Jurídico",Comparativo!$C$6:$C$15,"Equipe")</f>
         <v/>
       </c>
       <c r="F6" s="9">
@@ -1260,7 +1260,7 @@
         <v/>
       </c>
       <c r="I6" s="11">
-        <f>COUNTIFS(Comparativo!$P$6:$P$14,"&gt;0",Comparativo!$B$6:$B$14,"Jurídico",Comparativo!$C$6:$C$14,"Equipe")&amp;" de "&amp;COUNTIFS(Comparativo!$A$6:$A$14,"?*",Comparativo!$B$6:$B$14,"Jurídico",Comparativo!$C$6:$C$14,"Equipe")</f>
+        <f>COUNTIFS(Comparativo!$P$6:$P$15,"&gt;0",Comparativo!$B$6:$B$15,"Jurídico",Comparativo!$C$6:$C$15,"Equipe")&amp;" de "&amp;COUNTIFS(Comparativo!$A$6:$A$15,"?*",Comparativo!$B$6:$B$15,"Jurídico",Comparativo!$C$6:$C$15,"Equipe")</f>
         <v/>
       </c>
     </row>
@@ -1276,15 +1276,15 @@
         </is>
       </c>
       <c r="C7" s="9">
-        <f>SUMIFS(Planejado!$T$5:$T$13,Planejado!$B$5:$B$13,"Jurídico",Planejado!$C$5:$C$13,"Despesas")</f>
+        <f>SUMIFS(Planejado!$T$5:$T$14,Planejado!$B$5:$B$14,"Jurídico",Planejado!$C$5:$C$14,"Despesas")</f>
         <v/>
       </c>
       <c r="D7" s="9">
-        <f>SUMIFS(Comparativo!$I$6:$I$14,Comparativo!$B$6:$B$14,"Jurídico",Comparativo!$C$6:$C$14,"Despesas")</f>
+        <f>SUMIFS(Comparativo!$I$6:$I$15,Comparativo!$B$6:$B$15,"Jurídico",Comparativo!$C$6:$C$15,"Despesas")</f>
         <v/>
       </c>
       <c r="E7" s="9">
-        <f>SUMIFS(Comparativo!$J$6:$J$14,Comparativo!$B$6:$B$14,"Jurídico",Comparativo!$C$6:$C$14,"Despesas")</f>
+        <f>SUMIFS(Comparativo!$J$6:$J$15,Comparativo!$B$6:$B$15,"Jurídico",Comparativo!$C$6:$C$15,"Despesas")</f>
         <v/>
       </c>
       <c r="F7" s="9">
@@ -1300,7 +1300,7 @@
         <v/>
       </c>
       <c r="I7" s="11">
-        <f>COUNTIFS(Comparativo!$P$6:$P$14,"&gt;0",Comparativo!$B$6:$B$14,"Jurídico",Comparativo!$C$6:$C$14,"Despesas")&amp;" de "&amp;COUNTIFS(Comparativo!$A$6:$A$14,"?*",Comparativo!$B$6:$B$14,"Jurídico",Comparativo!$C$6:$C$14,"Despesas")</f>
+        <f>COUNTIFS(Comparativo!$P$6:$P$15,"&gt;0",Comparativo!$B$6:$B$15,"Jurídico",Comparativo!$C$6:$C$15,"Despesas")&amp;" de "&amp;COUNTIFS(Comparativo!$A$6:$A$15,"?*",Comparativo!$B$6:$B$15,"Jurídico",Comparativo!$C$6:$C$15,"Despesas")</f>
         <v/>
       </c>
     </row>
@@ -1316,15 +1316,15 @@
         </is>
       </c>
       <c r="C8" s="13">
-        <f>SUMIFS(Planejado!$T$5:$T$13,Planejado!$B$5:$B$13,"Jurídico")</f>
+        <f>SUMIFS(Planejado!$T$5:$T$14,Planejado!$B$5:$B$14,"Jurídico")</f>
         <v/>
       </c>
       <c r="D8" s="13">
-        <f>SUMIFS(Comparativo!$I$6:$I$14,Comparativo!$B$6:$B$14,"Jurídico")</f>
+        <f>SUMIFS(Comparativo!$I$6:$I$15,Comparativo!$B$6:$B$15,"Jurídico")</f>
         <v/>
       </c>
       <c r="E8" s="13">
-        <f>SUMIFS(Comparativo!$J$6:$J$14,Comparativo!$B$6:$B$14,"Jurídico")</f>
+        <f>SUMIFS(Comparativo!$J$6:$J$15,Comparativo!$B$6:$B$15,"Jurídico")</f>
         <v/>
       </c>
       <c r="F8" s="13">
@@ -1340,7 +1340,7 @@
         <v/>
       </c>
       <c r="I8" s="15">
-        <f>COUNTIFS(Comparativo!$P$6:$P$14,"&gt;0",Comparativo!$B$6:$B$14,"Jurídico")&amp;" de "&amp;COUNTIFS(Comparativo!$A$6:$A$14,"?*",Comparativo!$B$6:$B$14,"Jurídico")</f>
+        <f>COUNTIFS(Comparativo!$P$6:$P$15,"&gt;0",Comparativo!$B$6:$B$15,"Jurídico")&amp;" de "&amp;COUNTIFS(Comparativo!$A$6:$A$15,"?*",Comparativo!$B$6:$B$15,"Jurídico")</f>
         <v/>
       </c>
     </row>
@@ -1359,7 +1359,7 @@
       </c>
       <c r="B12" s="17" t="n"/>
       <c r="C12" s="18">
-        <f>-SUMIF(Comparativo!$Q$6:$Q$14,"&lt;0")</f>
+        <f>-SUMIF(Comparativo!$Q$6:$Q$15,"&lt;0")</f>
         <v/>
       </c>
       <c r="D12" s="19" t="inlineStr">
@@ -1381,7 +1381,7 @@
       </c>
       <c r="B13" s="17" t="n"/>
       <c r="C13" s="18">
-        <f>-SUMIF(Comparativo!$Q$6:$Q$14,"&gt;0")</f>
+        <f>-SUMIF(Comparativo!$Q$6:$Q$15,"&gt;0")</f>
         <v/>
       </c>
       <c r="D13" s="19" t="inlineStr">
@@ -1402,7 +1402,7 @@
       </c>
       <c r="B14" s="20" t="n"/>
       <c r="C14" s="21">
-        <f>-SUM(Comparativo!$Q$6:$Q$14)</f>
+        <f>-SUM(Comparativo!$Q$6:$Q$15)</f>
         <v/>
       </c>
       <c r="D14" s="22" t="inlineStr">
@@ -1424,7 +1424,7 @@
       </c>
       <c r="B15" s="17" t="n"/>
       <c r="C15" s="18">
-        <f>IFERROR(-SUM(Comparativo!$Q$6:$Q$14)/Comparativo!$D$3*12,"")</f>
+        <f>IFERROR(-SUM(Comparativo!$Q$6:$Q$15)/Comparativo!$D$3*12,"")</f>
         <v/>
       </c>
       <c r="D15" s="19" t="inlineStr">
@@ -1446,7 +1446,7 @@
       </c>
       <c r="B16" s="17" t="n"/>
       <c r="C16" s="23">
-        <f>IFERROR(-SUM(Comparativo!$Q$6:$Q$14)/SUM(Comparativo!$S$6:$S$14),"")</f>
+        <f>IFERROR(-SUM(Comparativo!$Q$6:$Q$15)/SUM(Comparativo!$S$6:$S$15),"")</f>
         <v/>
       </c>
       <c r="D16" s="19" t="inlineStr">
@@ -1518,23 +1518,23 @@
         <v>1</v>
       </c>
       <c r="B21" s="27">
-        <f>IFERROR(INDEX(Comparativo!$D$6:$D$14,MATCH(LARGE(Comparativo!$R$6:$R$14,A21),Comparativo!$R$6:$R$14,0)),"")</f>
+        <f>IFERROR(INDEX(Comparativo!$D$6:$D$15,MATCH(LARGE(Comparativo!$R$6:$R$15,A21),Comparativo!$R$6:$R$15,0)),"")</f>
         <v/>
       </c>
       <c r="C21" s="27">
-        <f>IFERROR(INDEX(Comparativo!$B$6:$B$14,MATCH(LARGE(Comparativo!$R$6:$R$14,A21),Comparativo!$R$6:$R$14,0)),"")</f>
+        <f>IFERROR(INDEX(Comparativo!$B$6:$B$15,MATCH(LARGE(Comparativo!$R$6:$R$15,A21),Comparativo!$R$6:$R$15,0)),"")</f>
         <v/>
       </c>
       <c r="D21" s="28">
-        <f>IFERROR(INDEX(Comparativo!$I$6:$I$14,MATCH(LARGE(Comparativo!$R$6:$R$14,A21),Comparativo!$R$6:$R$14,0)),"")</f>
+        <f>IFERROR(INDEX(Comparativo!$I$6:$I$15,MATCH(LARGE(Comparativo!$R$6:$R$15,A21),Comparativo!$R$6:$R$15,0)),"")</f>
         <v/>
       </c>
       <c r="E21" s="28">
-        <f>IFERROR(INDEX(Comparativo!$J$6:$J$14,MATCH(LARGE(Comparativo!$R$6:$R$14,A21),Comparativo!$R$6:$R$14,0)),"")</f>
+        <f>IFERROR(INDEX(Comparativo!$J$6:$J$15,MATCH(LARGE(Comparativo!$R$6:$R$15,A21),Comparativo!$R$6:$R$15,0)),"")</f>
         <v/>
       </c>
       <c r="F21" s="29">
-        <f>IFERROR(-IFERROR(INDEX(Comparativo!$K$6:$K$14,MATCH(LARGE(Comparativo!$R$6:$R$14,A21),Comparativo!$R$6:$R$14,0)),""),"")</f>
+        <f>IFERROR(-IFERROR(INDEX(Comparativo!$K$6:$K$15,MATCH(LARGE(Comparativo!$R$6:$R$15,A21),Comparativo!$R$6:$R$15,0)),""),"")</f>
         <v/>
       </c>
       <c r="G21" s="30">
@@ -1547,23 +1547,23 @@
         <v>2</v>
       </c>
       <c r="B22" s="27">
-        <f>IFERROR(INDEX(Comparativo!$D$6:$D$14,MATCH(LARGE(Comparativo!$R$6:$R$14,A22),Comparativo!$R$6:$R$14,0)),"")</f>
+        <f>IFERROR(INDEX(Comparativo!$D$6:$D$15,MATCH(LARGE(Comparativo!$R$6:$R$15,A22),Comparativo!$R$6:$R$15,0)),"")</f>
         <v/>
       </c>
       <c r="C22" s="27">
-        <f>IFERROR(INDEX(Comparativo!$B$6:$B$14,MATCH(LARGE(Comparativo!$R$6:$R$14,A22),Comparativo!$R$6:$R$14,0)),"")</f>
+        <f>IFERROR(INDEX(Comparativo!$B$6:$B$15,MATCH(LARGE(Comparativo!$R$6:$R$15,A22),Comparativo!$R$6:$R$15,0)),"")</f>
         <v/>
       </c>
       <c r="D22" s="28">
-        <f>IFERROR(INDEX(Comparativo!$I$6:$I$14,MATCH(LARGE(Comparativo!$R$6:$R$14,A22),Comparativo!$R$6:$R$14,0)),"")</f>
+        <f>IFERROR(INDEX(Comparativo!$I$6:$I$15,MATCH(LARGE(Comparativo!$R$6:$R$15,A22),Comparativo!$R$6:$R$15,0)),"")</f>
         <v/>
       </c>
       <c r="E22" s="28">
-        <f>IFERROR(INDEX(Comparativo!$J$6:$J$14,MATCH(LARGE(Comparativo!$R$6:$R$14,A22),Comparativo!$R$6:$R$14,0)),"")</f>
+        <f>IFERROR(INDEX(Comparativo!$J$6:$J$15,MATCH(LARGE(Comparativo!$R$6:$R$15,A22),Comparativo!$R$6:$R$15,0)),"")</f>
         <v/>
       </c>
       <c r="F22" s="29">
-        <f>IFERROR(-IFERROR(INDEX(Comparativo!$K$6:$K$14,MATCH(LARGE(Comparativo!$R$6:$R$14,A22),Comparativo!$R$6:$R$14,0)),""),"")</f>
+        <f>IFERROR(-IFERROR(INDEX(Comparativo!$K$6:$K$15,MATCH(LARGE(Comparativo!$R$6:$R$15,A22),Comparativo!$R$6:$R$15,0)),""),"")</f>
         <v/>
       </c>
       <c r="G22" s="30">
@@ -1576,23 +1576,23 @@
         <v>3</v>
       </c>
       <c r="B23" s="27">
-        <f>IFERROR(INDEX(Comparativo!$D$6:$D$14,MATCH(LARGE(Comparativo!$R$6:$R$14,A23),Comparativo!$R$6:$R$14,0)),"")</f>
+        <f>IFERROR(INDEX(Comparativo!$D$6:$D$15,MATCH(LARGE(Comparativo!$R$6:$R$15,A23),Comparativo!$R$6:$R$15,0)),"")</f>
         <v/>
       </c>
       <c r="C23" s="27">
-        <f>IFERROR(INDEX(Comparativo!$B$6:$B$14,MATCH(LARGE(Comparativo!$R$6:$R$14,A23),Comparativo!$R$6:$R$14,0)),"")</f>
+        <f>IFERROR(INDEX(Comparativo!$B$6:$B$15,MATCH(LARGE(Comparativo!$R$6:$R$15,A23),Comparativo!$R$6:$R$15,0)),"")</f>
         <v/>
       </c>
       <c r="D23" s="28">
-        <f>IFERROR(INDEX(Comparativo!$I$6:$I$14,MATCH(LARGE(Comparativo!$R$6:$R$14,A23),Comparativo!$R$6:$R$14,0)),"")</f>
+        <f>IFERROR(INDEX(Comparativo!$I$6:$I$15,MATCH(LARGE(Comparativo!$R$6:$R$15,A23),Comparativo!$R$6:$R$15,0)),"")</f>
         <v/>
       </c>
       <c r="E23" s="28">
-        <f>IFERROR(INDEX(Comparativo!$J$6:$J$14,MATCH(LARGE(Comparativo!$R$6:$R$14,A23),Comparativo!$R$6:$R$14,0)),"")</f>
+        <f>IFERROR(INDEX(Comparativo!$J$6:$J$15,MATCH(LARGE(Comparativo!$R$6:$R$15,A23),Comparativo!$R$6:$R$15,0)),"")</f>
         <v/>
       </c>
       <c r="F23" s="29">
-        <f>IFERROR(-IFERROR(INDEX(Comparativo!$K$6:$K$14,MATCH(LARGE(Comparativo!$R$6:$R$14,A23),Comparativo!$R$6:$R$14,0)),""),"")</f>
+        <f>IFERROR(-IFERROR(INDEX(Comparativo!$K$6:$K$15,MATCH(LARGE(Comparativo!$R$6:$R$15,A23),Comparativo!$R$6:$R$15,0)),""),"")</f>
         <v/>
       </c>
       <c r="G23" s="30">
@@ -1605,23 +1605,23 @@
         <v>4</v>
       </c>
       <c r="B24" s="27">
-        <f>IFERROR(INDEX(Comparativo!$D$6:$D$14,MATCH(LARGE(Comparativo!$R$6:$R$14,A24),Comparativo!$R$6:$R$14,0)),"")</f>
+        <f>IFERROR(INDEX(Comparativo!$D$6:$D$15,MATCH(LARGE(Comparativo!$R$6:$R$15,A24),Comparativo!$R$6:$R$15,0)),"")</f>
         <v/>
       </c>
       <c r="C24" s="27">
-        <f>IFERROR(INDEX(Comparativo!$B$6:$B$14,MATCH(LARGE(Comparativo!$R$6:$R$14,A24),Comparativo!$R$6:$R$14,0)),"")</f>
+        <f>IFERROR(INDEX(Comparativo!$B$6:$B$15,MATCH(LARGE(Comparativo!$R$6:$R$15,A24),Comparativo!$R$6:$R$15,0)),"")</f>
         <v/>
       </c>
       <c r="D24" s="28">
-        <f>IFERROR(INDEX(Comparativo!$I$6:$I$14,MATCH(LARGE(Comparativo!$R$6:$R$14,A24),Comparativo!$R$6:$R$14,0)),"")</f>
+        <f>IFERROR(INDEX(Comparativo!$I$6:$I$15,MATCH(LARGE(Comparativo!$R$6:$R$15,A24),Comparativo!$R$6:$R$15,0)),"")</f>
         <v/>
       </c>
       <c r="E24" s="28">
-        <f>IFERROR(INDEX(Comparativo!$J$6:$J$14,MATCH(LARGE(Comparativo!$R$6:$R$14,A24),Comparativo!$R$6:$R$14,0)),"")</f>
+        <f>IFERROR(INDEX(Comparativo!$J$6:$J$15,MATCH(LARGE(Comparativo!$R$6:$R$15,A24),Comparativo!$R$6:$R$15,0)),"")</f>
         <v/>
       </c>
       <c r="F24" s="29">
-        <f>IFERROR(-IFERROR(INDEX(Comparativo!$K$6:$K$14,MATCH(LARGE(Comparativo!$R$6:$R$14,A24),Comparativo!$R$6:$R$14,0)),""),"")</f>
+        <f>IFERROR(-IFERROR(INDEX(Comparativo!$K$6:$K$15,MATCH(LARGE(Comparativo!$R$6:$R$15,A24),Comparativo!$R$6:$R$15,0)),""),"")</f>
         <v/>
       </c>
       <c r="G24" s="30">
@@ -1634,23 +1634,23 @@
         <v>5</v>
       </c>
       <c r="B25" s="27">
-        <f>IFERROR(INDEX(Comparativo!$D$6:$D$14,MATCH(LARGE(Comparativo!$R$6:$R$14,A25),Comparativo!$R$6:$R$14,0)),"")</f>
+        <f>IFERROR(INDEX(Comparativo!$D$6:$D$15,MATCH(LARGE(Comparativo!$R$6:$R$15,A25),Comparativo!$R$6:$R$15,0)),"")</f>
         <v/>
       </c>
       <c r="C25" s="27">
-        <f>IFERROR(INDEX(Comparativo!$B$6:$B$14,MATCH(LARGE(Comparativo!$R$6:$R$14,A25),Comparativo!$R$6:$R$14,0)),"")</f>
+        <f>IFERROR(INDEX(Comparativo!$B$6:$B$15,MATCH(LARGE(Comparativo!$R$6:$R$15,A25),Comparativo!$R$6:$R$15,0)),"")</f>
         <v/>
       </c>
       <c r="D25" s="28">
-        <f>IFERROR(INDEX(Comparativo!$I$6:$I$14,MATCH(LARGE(Comparativo!$R$6:$R$14,A25),Comparativo!$R$6:$R$14,0)),"")</f>
+        <f>IFERROR(INDEX(Comparativo!$I$6:$I$15,MATCH(LARGE(Comparativo!$R$6:$R$15,A25),Comparativo!$R$6:$R$15,0)),"")</f>
         <v/>
       </c>
       <c r="E25" s="28">
-        <f>IFERROR(INDEX(Comparativo!$J$6:$J$14,MATCH(LARGE(Comparativo!$R$6:$R$14,A25),Comparativo!$R$6:$R$14,0)),"")</f>
+        <f>IFERROR(INDEX(Comparativo!$J$6:$J$15,MATCH(LARGE(Comparativo!$R$6:$R$15,A25),Comparativo!$R$6:$R$15,0)),"")</f>
         <v/>
       </c>
       <c r="F25" s="29">
-        <f>IFERROR(-IFERROR(INDEX(Comparativo!$K$6:$K$14,MATCH(LARGE(Comparativo!$R$6:$R$14,A25),Comparativo!$R$6:$R$14,0)),""),"")</f>
+        <f>IFERROR(-IFERROR(INDEX(Comparativo!$K$6:$K$15,MATCH(LARGE(Comparativo!$R$6:$R$15,A25),Comparativo!$R$6:$R$15,0)),""),"")</f>
         <v/>
       </c>
       <c r="G25" s="30">
@@ -1708,23 +1708,23 @@
         <v>1</v>
       </c>
       <c r="B30" s="27">
-        <f>IFERROR(INDEX(Comparativo!$D$6:$D$14,MATCH(LARGE(Comparativo!$O$6:$O$14,A30),Comparativo!$O$6:$O$14,0)),"")</f>
+        <f>IFERROR(INDEX(Comparativo!$D$6:$D$15,MATCH(LARGE(Comparativo!$O$6:$O$15,A30),Comparativo!$O$6:$O$15,0)),"")</f>
         <v/>
       </c>
       <c r="C30" s="27">
-        <f>IFERROR(INDEX(Comparativo!$B$6:$B$14,MATCH(LARGE(Comparativo!$O$6:$O$14,A30),Comparativo!$O$6:$O$14,0)),"")</f>
+        <f>IFERROR(INDEX(Comparativo!$B$6:$B$15,MATCH(LARGE(Comparativo!$O$6:$O$15,A30),Comparativo!$O$6:$O$15,0)),"")</f>
         <v/>
       </c>
       <c r="D30" s="28">
-        <f>IFERROR(INDEX(Comparativo!$I$6:$I$14,MATCH(LARGE(Comparativo!$O$6:$O$14,A30),Comparativo!$O$6:$O$14,0)),"")</f>
+        <f>IFERROR(INDEX(Comparativo!$I$6:$I$15,MATCH(LARGE(Comparativo!$O$6:$O$15,A30),Comparativo!$O$6:$O$15,0)),"")</f>
         <v/>
       </c>
       <c r="E30" s="28">
-        <f>IFERROR(INDEX(Comparativo!$J$6:$J$14,MATCH(LARGE(Comparativo!$O$6:$O$14,A30),Comparativo!$O$6:$O$14,0)),"")</f>
+        <f>IFERROR(INDEX(Comparativo!$J$6:$J$15,MATCH(LARGE(Comparativo!$O$6:$O$15,A30),Comparativo!$O$6:$O$15,0)),"")</f>
         <v/>
       </c>
       <c r="F30" s="28">
-        <f>IFERROR(INDEX(Comparativo!$K$6:$K$14,MATCH(LARGE(Comparativo!$O$6:$O$14,A30),Comparativo!$O$6:$O$14,0)),"")</f>
+        <f>IFERROR(INDEX(Comparativo!$K$6:$K$15,MATCH(LARGE(Comparativo!$O$6:$O$15,A30),Comparativo!$O$6:$O$15,0)),"")</f>
         <v/>
       </c>
       <c r="G30" s="30">
@@ -1737,23 +1737,23 @@
         <v>2</v>
       </c>
       <c r="B31" s="27">
-        <f>IFERROR(INDEX(Comparativo!$D$6:$D$14,MATCH(LARGE(Comparativo!$O$6:$O$14,A31),Comparativo!$O$6:$O$14,0)),"")</f>
+        <f>IFERROR(INDEX(Comparativo!$D$6:$D$15,MATCH(LARGE(Comparativo!$O$6:$O$15,A31),Comparativo!$O$6:$O$15,0)),"")</f>
         <v/>
       </c>
       <c r="C31" s="27">
-        <f>IFERROR(INDEX(Comparativo!$B$6:$B$14,MATCH(LARGE(Comparativo!$O$6:$O$14,A31),Comparativo!$O$6:$O$14,0)),"")</f>
+        <f>IFERROR(INDEX(Comparativo!$B$6:$B$15,MATCH(LARGE(Comparativo!$O$6:$O$15,A31),Comparativo!$O$6:$O$15,0)),"")</f>
         <v/>
       </c>
       <c r="D31" s="28">
-        <f>IFERROR(INDEX(Comparativo!$I$6:$I$14,MATCH(LARGE(Comparativo!$O$6:$O$14,A31),Comparativo!$O$6:$O$14,0)),"")</f>
+        <f>IFERROR(INDEX(Comparativo!$I$6:$I$15,MATCH(LARGE(Comparativo!$O$6:$O$15,A31),Comparativo!$O$6:$O$15,0)),"")</f>
         <v/>
       </c>
       <c r="E31" s="28">
-        <f>IFERROR(INDEX(Comparativo!$J$6:$J$14,MATCH(LARGE(Comparativo!$O$6:$O$14,A31),Comparativo!$O$6:$O$14,0)),"")</f>
+        <f>IFERROR(INDEX(Comparativo!$J$6:$J$15,MATCH(LARGE(Comparativo!$O$6:$O$15,A31),Comparativo!$O$6:$O$15,0)),"")</f>
         <v/>
       </c>
       <c r="F31" s="28">
-        <f>IFERROR(INDEX(Comparativo!$K$6:$K$14,MATCH(LARGE(Comparativo!$O$6:$O$14,A31),Comparativo!$O$6:$O$14,0)),"")</f>
+        <f>IFERROR(INDEX(Comparativo!$K$6:$K$15,MATCH(LARGE(Comparativo!$O$6:$O$15,A31),Comparativo!$O$6:$O$15,0)),"")</f>
         <v/>
       </c>
       <c r="G31" s="30">
@@ -1766,23 +1766,23 @@
         <v>3</v>
       </c>
       <c r="B32" s="27">
-        <f>IFERROR(INDEX(Comparativo!$D$6:$D$14,MATCH(LARGE(Comparativo!$O$6:$O$14,A32),Comparativo!$O$6:$O$14,0)),"")</f>
+        <f>IFERROR(INDEX(Comparativo!$D$6:$D$15,MATCH(LARGE(Comparativo!$O$6:$O$15,A32),Comparativo!$O$6:$O$15,0)),"")</f>
         <v/>
       </c>
       <c r="C32" s="27">
-        <f>IFERROR(INDEX(Comparativo!$B$6:$B$14,MATCH(LARGE(Comparativo!$O$6:$O$14,A32),Comparativo!$O$6:$O$14,0)),"")</f>
+        <f>IFERROR(INDEX(Comparativo!$B$6:$B$15,MATCH(LARGE(Comparativo!$O$6:$O$15,A32),Comparativo!$O$6:$O$15,0)),"")</f>
         <v/>
       </c>
       <c r="D32" s="28">
-        <f>IFERROR(INDEX(Comparativo!$I$6:$I$14,MATCH(LARGE(Comparativo!$O$6:$O$14,A32),Comparativo!$O$6:$O$14,0)),"")</f>
+        <f>IFERROR(INDEX(Comparativo!$I$6:$I$15,MATCH(LARGE(Comparativo!$O$6:$O$15,A32),Comparativo!$O$6:$O$15,0)),"")</f>
         <v/>
       </c>
       <c r="E32" s="28">
-        <f>IFERROR(INDEX(Comparativo!$J$6:$J$14,MATCH(LARGE(Comparativo!$O$6:$O$14,A32),Comparativo!$O$6:$O$14,0)),"")</f>
+        <f>IFERROR(INDEX(Comparativo!$J$6:$J$15,MATCH(LARGE(Comparativo!$O$6:$O$15,A32),Comparativo!$O$6:$O$15,0)),"")</f>
         <v/>
       </c>
       <c r="F32" s="28">
-        <f>IFERROR(INDEX(Comparativo!$K$6:$K$14,MATCH(LARGE(Comparativo!$O$6:$O$14,A32),Comparativo!$O$6:$O$14,0)),"")</f>
+        <f>IFERROR(INDEX(Comparativo!$K$6:$K$15,MATCH(LARGE(Comparativo!$O$6:$O$15,A32),Comparativo!$O$6:$O$15,0)),"")</f>
         <v/>
       </c>
       <c r="G32" s="30">
@@ -1795,23 +1795,23 @@
         <v>4</v>
       </c>
       <c r="B33" s="27">
-        <f>IFERROR(INDEX(Comparativo!$D$6:$D$14,MATCH(LARGE(Comparativo!$O$6:$O$14,A33),Comparativo!$O$6:$O$14,0)),"")</f>
+        <f>IFERROR(INDEX(Comparativo!$D$6:$D$15,MATCH(LARGE(Comparativo!$O$6:$O$15,A33),Comparativo!$O$6:$O$15,0)),"")</f>
         <v/>
       </c>
       <c r="C33" s="27">
-        <f>IFERROR(INDEX(Comparativo!$B$6:$B$14,MATCH(LARGE(Comparativo!$O$6:$O$14,A33),Comparativo!$O$6:$O$14,0)),"")</f>
+        <f>IFERROR(INDEX(Comparativo!$B$6:$B$15,MATCH(LARGE(Comparativo!$O$6:$O$15,A33),Comparativo!$O$6:$O$15,0)),"")</f>
         <v/>
       </c>
       <c r="D33" s="28">
-        <f>IFERROR(INDEX(Comparativo!$I$6:$I$14,MATCH(LARGE(Comparativo!$O$6:$O$14,A33),Comparativo!$O$6:$O$14,0)),"")</f>
+        <f>IFERROR(INDEX(Comparativo!$I$6:$I$15,MATCH(LARGE(Comparativo!$O$6:$O$15,A33),Comparativo!$O$6:$O$15,0)),"")</f>
         <v/>
       </c>
       <c r="E33" s="28">
-        <f>IFERROR(INDEX(Comparativo!$J$6:$J$14,MATCH(LARGE(Comparativo!$O$6:$O$14,A33),Comparativo!$O$6:$O$14,0)),"")</f>
+        <f>IFERROR(INDEX(Comparativo!$J$6:$J$15,MATCH(LARGE(Comparativo!$O$6:$O$15,A33),Comparativo!$O$6:$O$15,0)),"")</f>
         <v/>
       </c>
       <c r="F33" s="28">
-        <f>IFERROR(INDEX(Comparativo!$K$6:$K$14,MATCH(LARGE(Comparativo!$O$6:$O$14,A33),Comparativo!$O$6:$O$14,0)),"")</f>
+        <f>IFERROR(INDEX(Comparativo!$K$6:$K$15,MATCH(LARGE(Comparativo!$O$6:$O$15,A33),Comparativo!$O$6:$O$15,0)),"")</f>
         <v/>
       </c>
       <c r="G33" s="30">
@@ -1824,23 +1824,23 @@
         <v>5</v>
       </c>
       <c r="B34" s="27">
-        <f>IFERROR(INDEX(Comparativo!$D$6:$D$14,MATCH(LARGE(Comparativo!$O$6:$O$14,A34),Comparativo!$O$6:$O$14,0)),"")</f>
+        <f>IFERROR(INDEX(Comparativo!$D$6:$D$15,MATCH(LARGE(Comparativo!$O$6:$O$15,A34),Comparativo!$O$6:$O$15,0)),"")</f>
         <v/>
       </c>
       <c r="C34" s="27">
-        <f>IFERROR(INDEX(Comparativo!$B$6:$B$14,MATCH(LARGE(Comparativo!$O$6:$O$14,A34),Comparativo!$O$6:$O$14,0)),"")</f>
+        <f>IFERROR(INDEX(Comparativo!$B$6:$B$15,MATCH(LARGE(Comparativo!$O$6:$O$15,A34),Comparativo!$O$6:$O$15,0)),"")</f>
         <v/>
       </c>
       <c r="D34" s="28">
-        <f>IFERROR(INDEX(Comparativo!$I$6:$I$14,MATCH(LARGE(Comparativo!$O$6:$O$14,A34),Comparativo!$O$6:$O$14,0)),"")</f>
+        <f>IFERROR(INDEX(Comparativo!$I$6:$I$15,MATCH(LARGE(Comparativo!$O$6:$O$15,A34),Comparativo!$O$6:$O$15,0)),"")</f>
         <v/>
       </c>
       <c r="E34" s="28">
-        <f>IFERROR(INDEX(Comparativo!$J$6:$J$14,MATCH(LARGE(Comparativo!$O$6:$O$14,A34),Comparativo!$O$6:$O$14,0)),"")</f>
+        <f>IFERROR(INDEX(Comparativo!$J$6:$J$15,MATCH(LARGE(Comparativo!$O$6:$O$15,A34),Comparativo!$O$6:$O$15,0)),"")</f>
         <v/>
       </c>
       <c r="F34" s="28">
-        <f>IFERROR(INDEX(Comparativo!$K$6:$K$14,MATCH(LARGE(Comparativo!$O$6:$O$14,A34),Comparativo!$O$6:$O$14,0)),"")</f>
+        <f>IFERROR(INDEX(Comparativo!$K$6:$K$15,MATCH(LARGE(Comparativo!$O$6:$O$15,A34),Comparativo!$O$6:$O$15,0)),"")</f>
         <v/>
       </c>
       <c r="G34" s="30">
@@ -14734,7 +14734,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S31"/>
+  <dimension ref="A1:S32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -15590,57 +15590,135 @@
         <v/>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" s="43" t="inlineStr">
+    <row r="15" ht="24" customHeight="1">
+      <c r="A15" s="36">
+        <f>Planejado!A14</f>
+        <v/>
+      </c>
+      <c r="B15" s="36">
+        <f>Planejado!B14</f>
+        <v/>
+      </c>
+      <c r="C15" s="36">
+        <f>Planejado!C14</f>
+        <v/>
+      </c>
+      <c r="D15" s="37">
+        <f>Planejado!D14</f>
+        <v/>
+      </c>
+      <c r="E15" s="36">
+        <f>Planejado!G14</f>
+        <v/>
+      </c>
+      <c r="F15" s="38">
+        <f>INDEX(Planejado!$H14:$S14,$D$3)</f>
+        <v/>
+      </c>
+      <c r="G15" s="38">
+        <f>INDEX(Realizado!$H14:$S14,$D$3)</f>
+        <v/>
+      </c>
+      <c r="H15" s="38">
+        <f>G15-F15</f>
+        <v/>
+      </c>
+      <c r="I15" s="38">
+        <f>SUMPRODUCT((COLUMN(Planejado!$H$4:$S$4)-COLUMN(Planejado!$H$4)+1&lt;=$D$3)*Planejado!$H14:$S14)</f>
+        <v/>
+      </c>
+      <c r="J15" s="38">
+        <f>SUMPRODUCT((COLUMN(Realizado!$H$4:$S$4)-COLUMN(Realizado!$H$4)+1&lt;=$D$3)*Realizado!$H14:$S14)</f>
+        <v/>
+      </c>
+      <c r="K15" s="38">
+        <f>J15-I15</f>
+        <v/>
+      </c>
+      <c r="L15" s="39">
+        <f>IFERROR(K15/I15,"")</f>
+        <v/>
+      </c>
+      <c r="M15" s="39">
+        <f>IFERROR(J15/I15,"")</f>
+        <v/>
+      </c>
+      <c r="N15" s="40">
+        <f>IF(P15=0,"Sem lançamento",IF(AND(I15=0,J15=0),"—",IF(I15=0,"Não orçado",IF(K15&gt;0.05*I15,"Acima do orçado",IF(K15&lt;-0.05*I15,"Abaixo do orçado","Dentro do orçado")))))</f>
+        <v/>
+      </c>
+      <c r="O15" s="35">
+        <f>IF(K15&gt;1,K15+ROW()/1000000,"")</f>
+        <v/>
+      </c>
+      <c r="P15" s="41">
+        <f>SUMPRODUCT((COLUMN(Realizado!$H$4:$S$4)-COLUMN(Realizado!$H$4)+1&lt;=$D$3)*(Realizado!$H14:$S14&lt;&gt;""))</f>
+        <v/>
+      </c>
+      <c r="Q15" s="42">
+        <f>IF(P15=0,"",K15)</f>
+        <v/>
+      </c>
+      <c r="R15" s="42">
+        <f>IF(AND(Q15&lt;&gt;"",Q15&lt;-1),-Q15+ROW()/1000000,"")</f>
+        <v/>
+      </c>
+      <c r="S15" s="42">
+        <f>IF(Q15="","",I15)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="43" t="inlineStr">
         <is>
           <t>TOTAL GERAL</t>
         </is>
       </c>
-      <c r="B31" s="43" t="n"/>
-      <c r="C31" s="43" t="n"/>
-      <c r="D31" s="43" t="n"/>
-      <c r="E31" s="43" t="n"/>
-      <c r="F31" s="44">
-        <f>SUM(F6:F14)</f>
-        <v/>
-      </c>
-      <c r="G31" s="44">
-        <f>SUM(G6:G14)</f>
-        <v/>
-      </c>
-      <c r="H31" s="44">
-        <f>SUM(H6:H14)</f>
-        <v/>
-      </c>
-      <c r="I31" s="44">
-        <f>SUM(I6:I14)</f>
-        <v/>
-      </c>
-      <c r="J31" s="44">
-        <f>SUM(J6:J14)</f>
-        <v/>
-      </c>
-      <c r="K31" s="44">
-        <f>SUM(K6:K14)</f>
-        <v/>
-      </c>
-      <c r="L31" s="45">
-        <f>IFERROR(K31/I31,"")</f>
-        <v/>
-      </c>
-      <c r="M31" s="45">
-        <f>IFERROR(J31/I31,"")</f>
-        <v/>
-      </c>
-      <c r="N31" s="43" t="n"/>
+      <c r="B32" s="43" t="n"/>
+      <c r="C32" s="43" t="n"/>
+      <c r="D32" s="43" t="n"/>
+      <c r="E32" s="43" t="n"/>
+      <c r="F32" s="44">
+        <f>SUM(F6:F15)</f>
+        <v/>
+      </c>
+      <c r="G32" s="44">
+        <f>SUM(G6:G15)</f>
+        <v/>
+      </c>
+      <c r="H32" s="44">
+        <f>SUM(H6:H15)</f>
+        <v/>
+      </c>
+      <c r="I32" s="44">
+        <f>SUM(I6:I15)</f>
+        <v/>
+      </c>
+      <c r="J32" s="44">
+        <f>SUM(J6:J15)</f>
+        <v/>
+      </c>
+      <c r="K32" s="44">
+        <f>SUM(K6:K15)</f>
+        <v/>
+      </c>
+      <c r="L32" s="45">
+        <f>IFERROR(K32/I32,"")</f>
+        <v/>
+      </c>
+      <c r="M32" s="45">
+        <f>IFERROR(J32/I32,"")</f>
+        <v/>
+      </c>
+      <c r="N32" s="43" t="n"/>
     </row>
   </sheetData>
-  <autoFilter ref="A5:N14"/>
+  <autoFilter ref="A5:N15"/>
   <mergeCells count="2">
     <mergeCell ref="A2:N2"/>
     <mergeCell ref="A1:N1"/>
   </mergeCells>
-  <conditionalFormatting sqref="H6:H14">
+  <conditionalFormatting sqref="H6:H15">
     <cfRule type="cellIs" priority="1" operator="greaterThan" dxfId="0">
       <formula>0</formula>
     </cfRule>
@@ -15648,7 +15726,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K6:K14">
+  <conditionalFormatting sqref="K6:K15">
     <cfRule type="cellIs" priority="3" operator="greaterThan" dxfId="0">
       <formula>0</formula>
     </cfRule>
@@ -15671,7 +15749,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T14"/>
+  <dimension ref="A1:T15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -16046,7 +16124,7 @@
     <row r="8" ht="26" customHeight="1">
       <c r="A8" s="36" t="inlineStr">
         <is>
-          <t>JUR-D01</t>
+          <t>JUR-E04</t>
         </is>
       </c>
       <c r="B8" s="36" t="inlineStr">
@@ -16056,60 +16134,64 @@
       </c>
       <c r="C8" s="36" t="inlineStr">
         <is>
-          <t>Despesas</t>
+          <t>Equipe</t>
         </is>
       </c>
       <c r="D8" s="37" t="inlineStr">
         <is>
-          <t>JUSFY</t>
+          <t>Dra. Michele de Oliveira Silva</t>
         </is>
       </c>
       <c r="E8" s="37" t="inlineStr">
         <is>
-          <t>Fase de teste com objetivo de eliminar o Astrea</t>
-        </is>
-      </c>
-      <c r="F8" s="36" t="inlineStr"/>
+          <t>Advogada — NÃO CONSTAVA NA FICHA. R$ 2.750/mês fixos desde jul/26. Planejado a definir com a diretoria</t>
+        </is>
+      </c>
+      <c r="F8" s="36" t="inlineStr">
+        <is>
+          <t>PJ</t>
+        </is>
+      </c>
       <c r="G8" s="36" t="inlineStr">
         <is>
-          <t>Licenças de Softwares</t>
+          <t>Pessoal - PJ</t>
         </is>
       </c>
       <c r="H8" s="38" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I8" s="38" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="J8" s="38" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="K8" s="38" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="L8" s="38" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M8" s="38" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N8" s="38" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="O8" s="38" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="P8" s="38" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Q8" s="38" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="R8" s="38" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="S8" s="38" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="T8" s="46">
         <f>SUM(H8:S8)</f>
@@ -16119,7 +16201,7 @@
     <row r="9" ht="26" customHeight="1">
       <c r="A9" s="36" t="inlineStr">
         <is>
-          <t>JUR-D02</t>
+          <t>JUR-D01</t>
         </is>
       </c>
       <c r="B9" s="36" t="inlineStr">
@@ -16134,12 +16216,12 @@
       </c>
       <c r="D9" s="37" t="inlineStr">
         <is>
-          <t>JUSBRASIL</t>
+          <t>JUSFY</t>
         </is>
       </c>
       <c r="E9" s="37" t="inlineStr">
         <is>
-          <t>ORÇAMENTO VEIO ERRADO: orçado R$ 104,90/mês, custo real R$ 136,00/mês. Corrigir na revisão orçamentária</t>
+          <t>Fase de teste com objetivo de eliminar o Astrea</t>
         </is>
       </c>
       <c r="F9" s="36" t="inlineStr"/>
@@ -16149,40 +16231,40 @@
         </is>
       </c>
       <c r="H9" s="38" t="n">
-        <v>104.9</v>
+        <v>100</v>
       </c>
       <c r="I9" s="38" t="n">
-        <v>104.9</v>
+        <v>100</v>
       </c>
       <c r="J9" s="38" t="n">
-        <v>104.9</v>
+        <v>100</v>
       </c>
       <c r="K9" s="38" t="n">
-        <v>104.9</v>
+        <v>100</v>
       </c>
       <c r="L9" s="38" t="n">
-        <v>104.9</v>
+        <v>100</v>
       </c>
       <c r="M9" s="38" t="n">
-        <v>104.9</v>
+        <v>100</v>
       </c>
       <c r="N9" s="38" t="n">
-        <v>104.9</v>
+        <v>100</v>
       </c>
       <c r="O9" s="38" t="n">
-        <v>104.9</v>
+        <v>100</v>
       </c>
       <c r="P9" s="38" t="n">
-        <v>104.9</v>
+        <v>100</v>
       </c>
       <c r="Q9" s="38" t="n">
-        <v>104.9</v>
+        <v>100</v>
       </c>
       <c r="R9" s="38" t="n">
-        <v>104.9</v>
+        <v>100</v>
       </c>
       <c r="S9" s="38" t="n">
-        <v>104.9</v>
+        <v>100</v>
       </c>
       <c r="T9" s="46">
         <f>SUM(H9:S9)</f>
@@ -16192,7 +16274,7 @@
     <row r="10" ht="26" customHeight="1">
       <c r="A10" s="36" t="inlineStr">
         <is>
-          <t>JUR-D03</t>
+          <t>JUR-D02</t>
         </is>
       </c>
       <c r="B10" s="36" t="inlineStr">
@@ -16207,12 +16289,12 @@
       </c>
       <c r="D10" s="37" t="inlineStr">
         <is>
-          <t>ASTREA</t>
+          <t>JUSBRASIL</t>
         </is>
       </c>
       <c r="E10" s="37" t="inlineStr">
         <is>
-          <t>ORÇAMENTO VEIO ERRADO: orçado R$ 112,07/mês, custo real R$ 346,00/mês. Corrigir na revisão orçamentária</t>
+          <t>ORÇAMENTO VEIO ERRADO: orçado R$ 104,90/mês, custo real R$ 136,00/mês. Corrigir na revisão orçamentária</t>
         </is>
       </c>
       <c r="F10" s="36" t="inlineStr"/>
@@ -16222,40 +16304,40 @@
         </is>
       </c>
       <c r="H10" s="38" t="n">
-        <v>112.07</v>
+        <v>104.9</v>
       </c>
       <c r="I10" s="38" t="n">
-        <v>112.07</v>
+        <v>104.9</v>
       </c>
       <c r="J10" s="38" t="n">
-        <v>112.07</v>
+        <v>104.9</v>
       </c>
       <c r="K10" s="38" t="n">
-        <v>112.07</v>
+        <v>104.9</v>
       </c>
       <c r="L10" s="38" t="n">
-        <v>112.07</v>
+        <v>104.9</v>
       </c>
       <c r="M10" s="38" t="n">
-        <v>112.07</v>
+        <v>104.9</v>
       </c>
       <c r="N10" s="38" t="n">
-        <v>112.07</v>
+        <v>104.9</v>
       </c>
       <c r="O10" s="38" t="n">
-        <v>112.07</v>
+        <v>104.9</v>
       </c>
       <c r="P10" s="38" t="n">
-        <v>112.07</v>
+        <v>104.9</v>
       </c>
       <c r="Q10" s="38" t="n">
-        <v>112.07</v>
+        <v>104.9</v>
       </c>
       <c r="R10" s="38" t="n">
-        <v>112.07</v>
+        <v>104.9</v>
       </c>
       <c r="S10" s="38" t="n">
-        <v>112.07</v>
+        <v>104.9</v>
       </c>
       <c r="T10" s="46">
         <f>SUM(H10:S10)</f>
@@ -16265,7 +16347,7 @@
     <row r="11" ht="26" customHeight="1">
       <c r="A11" s="36" t="inlineStr">
         <is>
-          <t>JUR-D04</t>
+          <t>JUR-D03</t>
         </is>
       </c>
       <c r="B11" s="36" t="inlineStr">
@@ -16280,10 +16362,14 @@
       </c>
       <c r="D11" s="37" t="inlineStr">
         <is>
-          <t>LEME</t>
-        </is>
-      </c>
-      <c r="E11" s="37" t="inlineStr"/>
+          <t>ASTREA</t>
+        </is>
+      </c>
+      <c r="E11" s="37" t="inlineStr">
+        <is>
+          <t>ORÇAMENTO VEIO ERRADO: orçado R$ 112,07/mês, custo real R$ 346,00/mês. Corrigir na revisão orçamentária</t>
+        </is>
+      </c>
       <c r="F11" s="36" t="inlineStr"/>
       <c r="G11" s="36" t="inlineStr">
         <is>
@@ -16291,40 +16377,40 @@
         </is>
       </c>
       <c r="H11" s="38" t="n">
-        <v>1030</v>
+        <v>112.07</v>
       </c>
       <c r="I11" s="38" t="n">
-        <v>1030</v>
+        <v>112.07</v>
       </c>
       <c r="J11" s="38" t="n">
-        <v>1030</v>
+        <v>112.07</v>
       </c>
       <c r="K11" s="38" t="n">
-        <v>1030</v>
+        <v>112.07</v>
       </c>
       <c r="L11" s="38" t="n">
-        <v>1030</v>
+        <v>112.07</v>
       </c>
       <c r="M11" s="38" t="n">
-        <v>1030</v>
+        <v>112.07</v>
       </c>
       <c r="N11" s="38" t="n">
-        <v>1030</v>
+        <v>112.07</v>
       </c>
       <c r="O11" s="38" t="n">
-        <v>1030</v>
+        <v>112.07</v>
       </c>
       <c r="P11" s="38" t="n">
-        <v>1030</v>
+        <v>112.07</v>
       </c>
       <c r="Q11" s="38" t="n">
-        <v>1030</v>
+        <v>112.07</v>
       </c>
       <c r="R11" s="38" t="n">
-        <v>1030</v>
+        <v>112.07</v>
       </c>
       <c r="S11" s="38" t="n">
-        <v>1030</v>
+        <v>112.07</v>
       </c>
       <c r="T11" s="46">
         <f>SUM(H11:S11)</f>
@@ -16334,7 +16420,7 @@
     <row r="12" ht="26" customHeight="1">
       <c r="A12" s="36" t="inlineStr">
         <is>
-          <t>JUR-D05</t>
+          <t>JUR-D04</t>
         </is>
       </c>
       <c r="B12" s="36" t="inlineStr">
@@ -16349,51 +16435,51 @@
       </c>
       <c r="D12" s="37" t="inlineStr">
         <is>
-          <t>Cursos / Eventos / Network</t>
+          <t>LEME</t>
         </is>
       </c>
       <c r="E12" s="37" t="inlineStr"/>
       <c r="F12" s="36" t="inlineStr"/>
       <c r="G12" s="36" t="inlineStr">
         <is>
-          <t>Custeio de Treinamento</t>
+          <t>Licenças de Softwares</t>
         </is>
       </c>
       <c r="H12" s="38" t="n">
-        <v>1000</v>
+        <v>1030</v>
       </c>
       <c r="I12" s="38" t="n">
-        <v>1000</v>
+        <v>1030</v>
       </c>
       <c r="J12" s="38" t="n">
-        <v>1000</v>
+        <v>1030</v>
       </c>
       <c r="K12" s="38" t="n">
-        <v>1000</v>
+        <v>1030</v>
       </c>
       <c r="L12" s="38" t="n">
-        <v>1000</v>
+        <v>1030</v>
       </c>
       <c r="M12" s="38" t="n">
-        <v>1000</v>
+        <v>1030</v>
       </c>
       <c r="N12" s="38" t="n">
-        <v>1000</v>
+        <v>1030</v>
       </c>
       <c r="O12" s="38" t="n">
-        <v>1000</v>
+        <v>1030</v>
       </c>
       <c r="P12" s="38" t="n">
-        <v>1000</v>
+        <v>1030</v>
       </c>
       <c r="Q12" s="38" t="n">
-        <v>1000</v>
+        <v>1030</v>
       </c>
       <c r="R12" s="38" t="n">
-        <v>1000</v>
+        <v>1030</v>
       </c>
       <c r="S12" s="38" t="n">
-        <v>1000</v>
+        <v>1030</v>
       </c>
       <c r="T12" s="46">
         <f>SUM(H12:S12)</f>
@@ -16403,7 +16489,7 @@
     <row r="13" ht="26" customHeight="1">
       <c r="A13" s="36" t="inlineStr">
         <is>
-          <t>JUR-D06</t>
+          <t>JUR-D05</t>
         </is>
       </c>
       <c r="B13" s="36" t="inlineStr">
@@ -16418,128 +16504,197 @@
       </c>
       <c r="D13" s="37" t="inlineStr">
         <is>
-          <t>Bonificações trimestrais/semestrais do time</t>
-        </is>
-      </c>
-      <c r="E13" s="37" t="inlineStr">
-        <is>
-          <t>Participação em projetos e atingimento de resultados — CONFIRMAR se houve parcela no 1º quadrimestre</t>
-        </is>
-      </c>
+          <t>Cursos / Eventos / Network</t>
+        </is>
+      </c>
+      <c r="E13" s="37" t="inlineStr"/>
       <c r="F13" s="36" t="inlineStr"/>
       <c r="G13" s="36" t="inlineStr">
         <is>
-          <t>Prêmios</t>
+          <t>Custeio de Treinamento</t>
         </is>
       </c>
       <c r="H13" s="38" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="I13" s="38" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="J13" s="38" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="K13" s="38" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="L13" s="38" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="M13" s="38" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="N13" s="38" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="O13" s="38" t="n">
-        <v>10293.6</v>
+        <v>1000</v>
       </c>
       <c r="P13" s="38" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Q13" s="38" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="R13" s="38" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="S13" s="38" t="n">
-        <v>12867</v>
+        <v>1000</v>
       </c>
       <c r="T13" s="46">
         <f>SUM(H13:S13)</f>
         <v/>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="43" t="inlineStr">
+    <row r="14" ht="26" customHeight="1">
+      <c r="A14" s="36" t="inlineStr">
+        <is>
+          <t>JUR-D06</t>
+        </is>
+      </c>
+      <c r="B14" s="36" t="inlineStr">
+        <is>
+          <t>Jurídico</t>
+        </is>
+      </c>
+      <c r="C14" s="36" t="inlineStr">
+        <is>
+          <t>Despesas</t>
+        </is>
+      </c>
+      <c r="D14" s="37" t="inlineStr">
+        <is>
+          <t>Bonificações trimestrais/semestrais do time</t>
+        </is>
+      </c>
+      <c r="E14" s="37" t="inlineStr">
+        <is>
+          <t>Participação em projetos e atingimento de resultados — CONFIRMAR se houve parcela no 1º quadrimestre</t>
+        </is>
+      </c>
+      <c r="F14" s="36" t="inlineStr"/>
+      <c r="G14" s="36" t="inlineStr">
+        <is>
+          <t>Prêmios</t>
+        </is>
+      </c>
+      <c r="H14" s="38" t="n">
+        <v>0</v>
+      </c>
+      <c r="I14" s="38" t="n">
+        <v>0</v>
+      </c>
+      <c r="J14" s="38" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" s="38" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" s="38" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" s="38" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" s="38" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" s="38" t="n">
+        <v>10293.6</v>
+      </c>
+      <c r="P14" s="38" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" s="38" t="n">
+        <v>0</v>
+      </c>
+      <c r="R14" s="38" t="n">
+        <v>0</v>
+      </c>
+      <c r="S14" s="38" t="n">
+        <v>12867</v>
+      </c>
+      <c r="T14" s="46">
+        <f>SUM(H14:S14)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="43" t="inlineStr">
         <is>
           <t>TOTAL GERAL</t>
         </is>
       </c>
-      <c r="B14" s="43" t="n"/>
-      <c r="C14" s="43" t="n"/>
-      <c r="D14" s="43" t="n"/>
-      <c r="E14" s="43" t="n"/>
-      <c r="F14" s="43" t="n"/>
-      <c r="G14" s="43" t="n"/>
-      <c r="H14" s="44">
-        <f>SUM(H5:H13)</f>
-        <v/>
-      </c>
-      <c r="I14" s="44">
-        <f>SUM(I5:I13)</f>
-        <v/>
-      </c>
-      <c r="J14" s="44">
-        <f>SUM(J5:J13)</f>
-        <v/>
-      </c>
-      <c r="K14" s="44">
-        <f>SUM(K5:K13)</f>
-        <v/>
-      </c>
-      <c r="L14" s="44">
-        <f>SUM(L5:L13)</f>
-        <v/>
-      </c>
-      <c r="M14" s="44">
-        <f>SUM(M5:M13)</f>
-        <v/>
-      </c>
-      <c r="N14" s="44">
-        <f>SUM(N5:N13)</f>
-        <v/>
-      </c>
-      <c r="O14" s="44">
-        <f>SUM(O5:O13)</f>
-        <v/>
-      </c>
-      <c r="P14" s="44">
-        <f>SUM(P5:P13)</f>
-        <v/>
-      </c>
-      <c r="Q14" s="44">
-        <f>SUM(Q5:Q13)</f>
-        <v/>
-      </c>
-      <c r="R14" s="44">
-        <f>SUM(R5:R13)</f>
-        <v/>
-      </c>
-      <c r="S14" s="44">
-        <f>SUM(S5:S13)</f>
-        <v/>
-      </c>
-      <c r="T14" s="44">
-        <f>SUM(T5:T13)</f>
+      <c r="B15" s="43" t="n"/>
+      <c r="C15" s="43" t="n"/>
+      <c r="D15" s="43" t="n"/>
+      <c r="E15" s="43" t="n"/>
+      <c r="F15" s="43" t="n"/>
+      <c r="G15" s="43" t="n"/>
+      <c r="H15" s="44">
+        <f>SUM(H5:H14)</f>
+        <v/>
+      </c>
+      <c r="I15" s="44">
+        <f>SUM(I5:I14)</f>
+        <v/>
+      </c>
+      <c r="J15" s="44">
+        <f>SUM(J5:J14)</f>
+        <v/>
+      </c>
+      <c r="K15" s="44">
+        <f>SUM(K5:K14)</f>
+        <v/>
+      </c>
+      <c r="L15" s="44">
+        <f>SUM(L5:L14)</f>
+        <v/>
+      </c>
+      <c r="M15" s="44">
+        <f>SUM(M5:M14)</f>
+        <v/>
+      </c>
+      <c r="N15" s="44">
+        <f>SUM(N5:N14)</f>
+        <v/>
+      </c>
+      <c r="O15" s="44">
+        <f>SUM(O5:O14)</f>
+        <v/>
+      </c>
+      <c r="P15" s="44">
+        <f>SUM(P5:P14)</f>
+        <v/>
+      </c>
+      <c r="Q15" s="44">
+        <f>SUM(Q5:Q14)</f>
+        <v/>
+      </c>
+      <c r="R15" s="44">
+        <f>SUM(R5:R14)</f>
+        <v/>
+      </c>
+      <c r="S15" s="44">
+        <f>SUM(S5:S14)</f>
+        <v/>
+      </c>
+      <c r="T15" s="44">
+        <f>SUM(T5:T14)</f>
         <v/>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:T13"/>
+  <autoFilter ref="A4:T14"/>
   <mergeCells count="2">
     <mergeCell ref="A1:T1"/>
     <mergeCell ref="A2:T2"/>
@@ -16554,7 +16709,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V14"/>
+  <dimension ref="A1:V15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -16967,35 +17122,25 @@
         <v>0</v>
       </c>
       <c r="N8" s="50" t="n">
-        <v>0</v>
-      </c>
-      <c r="O8" s="50" t="n">
-        <v>0</v>
-      </c>
-      <c r="P8" s="50" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q8" s="50" t="n">
-        <v>0</v>
-      </c>
-      <c r="R8" s="50" t="n">
-        <v>0</v>
-      </c>
-      <c r="S8" s="50" t="n">
-        <v>0</v>
-      </c>
+        <v>2750</v>
+      </c>
+      <c r="O8" s="50" t="n"/>
+      <c r="P8" s="50" t="n"/>
+      <c r="Q8" s="50" t="n"/>
+      <c r="R8" s="50" t="n"/>
+      <c r="S8" s="50" t="n"/>
       <c r="T8" s="46">
         <f>SUM(H8:S8)</f>
         <v/>
       </c>
       <c r="U8" s="51" t="inlineStr">
         <is>
-          <t>Gestora, 05/08/26</t>
+          <t>Extrato do financeiro</t>
         </is>
       </c>
       <c r="V8" s="51" t="inlineStr">
         <is>
-          <t>Nunca iniciado. Cancelado em jan/26 na fase de experimento e não será contratado: zero o ano todo</t>
+          <t>R$ 2.750/mês fixos a partir de jul/26. Os demais lançamentos em nome dela no extrato são REPASSE de honorários pagos pelo cliente — não são custo do departamento</t>
         </is>
       </c>
     </row>
@@ -17029,31 +17174,41 @@
         <v/>
       </c>
       <c r="H9" s="50" t="n">
-        <v>136</v>
+        <v>0</v>
       </c>
       <c r="I9" s="50" t="n">
-        <v>136</v>
+        <v>0</v>
       </c>
       <c r="J9" s="50" t="n">
-        <v>136</v>
+        <v>0</v>
       </c>
       <c r="K9" s="50" t="n">
-        <v>136</v>
+        <v>0</v>
       </c>
       <c r="L9" s="50" t="n">
-        <v>136</v>
+        <v>0</v>
       </c>
       <c r="M9" s="50" t="n">
-        <v>136</v>
+        <v>0</v>
       </c>
       <c r="N9" s="50" t="n">
-        <v>136</v>
-      </c>
-      <c r="O9" s="50" t="n"/>
-      <c r="P9" s="50" t="n"/>
-      <c r="Q9" s="50" t="n"/>
-      <c r="R9" s="50" t="n"/>
-      <c r="S9" s="50" t="n"/>
+        <v>0</v>
+      </c>
+      <c r="O9" s="50" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" s="50" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" s="50" t="n">
+        <v>0</v>
+      </c>
+      <c r="R9" s="50" t="n">
+        <v>0</v>
+      </c>
+      <c r="S9" s="50" t="n">
+        <v>0</v>
+      </c>
       <c r="T9" s="46">
         <f>SUM(H9:S9)</f>
         <v/>
@@ -17065,7 +17220,7 @@
       </c>
       <c r="V9" s="51" t="inlineStr">
         <is>
-          <t>R$ 136,00/mês contra R$ 104,90 orçados. Erro no orçamento original</t>
+          <t>Nunca iniciado. Cancelado em jan/26 na fase de experimento e não será contratado: zero o ano todo</t>
         </is>
       </c>
     </row>
@@ -17099,53 +17254,43 @@
         <v/>
       </c>
       <c r="H10" s="50" t="n">
-        <v>1346.28</v>
+        <v>136</v>
       </c>
       <c r="I10" s="50" t="n">
-        <v>5385.12</v>
+        <v>136</v>
       </c>
       <c r="J10" s="50" t="n">
-        <v>0</v>
+        <v>136</v>
       </c>
       <c r="K10" s="50" t="n">
-        <v>0</v>
+        <v>136</v>
       </c>
       <c r="L10" s="50" t="n">
-        <v>0</v>
+        <v>136</v>
       </c>
       <c r="M10" s="50" t="n">
-        <v>0</v>
+        <v>136</v>
       </c>
       <c r="N10" s="50" t="n">
-        <v>0</v>
-      </c>
-      <c r="O10" s="50" t="n">
-        <v>0</v>
-      </c>
-      <c r="P10" s="50" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q10" s="50" t="n">
-        <v>0</v>
-      </c>
-      <c r="R10" s="50" t="n">
-        <v>0</v>
-      </c>
-      <c r="S10" s="50" t="n">
-        <v>0</v>
-      </c>
+        <v>136</v>
+      </c>
+      <c r="O10" s="50" t="n"/>
+      <c r="P10" s="50" t="n"/>
+      <c r="Q10" s="50" t="n"/>
+      <c r="R10" s="50" t="n"/>
+      <c r="S10" s="50" t="n"/>
       <c r="T10" s="46">
         <f>SUM(H10:S10)</f>
         <v/>
       </c>
       <c r="U10" s="51" t="inlineStr">
         <is>
-          <t>Extrato do financeiro + portal Astrea</t>
+          <t>Gestora, 05/08/26</t>
         </is>
       </c>
       <c r="V10" s="51" t="inlineStr">
         <is>
-          <t>Anuidade 2025/26 = R$ 6.731,40 em 5x de R$ 1.346,28 (venc. 01/11/25 a 01/03/26), quitada em 10/02/26. Cancelamento em ago/26, sem renovação e sem substituto: zero de mar a dez</t>
+          <t>R$ 136,00/mês contra R$ 104,90 orçados. Erro no orçamento original</t>
         </is>
       </c>
     </row>
@@ -17179,41 +17324,55 @@
         <v/>
       </c>
       <c r="H11" s="50" t="n">
-        <v>970</v>
+        <v>1346.28</v>
       </c>
       <c r="I11" s="50" t="n">
-        <v>970</v>
+        <v>5385.12</v>
       </c>
       <c r="J11" s="50" t="n">
-        <v>970</v>
+        <v>0</v>
       </c>
       <c r="K11" s="50" t="n">
-        <v>970</v>
+        <v>0</v>
       </c>
       <c r="L11" s="50" t="n">
-        <v>970</v>
+        <v>0</v>
       </c>
       <c r="M11" s="50" t="n">
-        <v>970</v>
+        <v>0</v>
       </c>
       <c r="N11" s="50" t="n">
-        <v>970</v>
-      </c>
-      <c r="O11" s="50" t="n"/>
-      <c r="P11" s="50" t="n"/>
-      <c r="Q11" s="50" t="n"/>
-      <c r="R11" s="50" t="n"/>
-      <c r="S11" s="50" t="n"/>
+        <v>0</v>
+      </c>
+      <c r="O11" s="50" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" s="50" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" s="50" t="n">
+        <v>0</v>
+      </c>
+      <c r="R11" s="50" t="n">
+        <v>0</v>
+      </c>
+      <c r="S11" s="50" t="n">
+        <v>0</v>
+      </c>
       <c r="T11" s="46">
         <f>SUM(H11:S11)</f>
         <v/>
       </c>
       <c r="U11" s="51" t="inlineStr">
         <is>
-          <t>Gestora, 05/08/26</t>
-        </is>
-      </c>
-      <c r="V11" s="51" t="n"/>
+          <t>Extrato do financeiro + portal Astrea</t>
+        </is>
+      </c>
+      <c r="V11" s="51" t="inlineStr">
+        <is>
+          <t>Anuidade 2025/26 = R$ 6.731,40 em 5x de R$ 1.346,28 (venc. 01/11/25 a 01/03/26), quitada em 10/02/26. Cancelamento em ago/26, sem renovação e sem substituto: zero de mar a dez</t>
+        </is>
+      </c>
     </row>
     <row r="12" ht="26" customHeight="1">
       <c r="A12" s="48">
@@ -17245,25 +17404,25 @@
         <v/>
       </c>
       <c r="H12" s="50" t="n">
-        <v>0</v>
+        <v>970</v>
       </c>
       <c r="I12" s="50" t="n">
-        <v>0</v>
+        <v>970</v>
       </c>
       <c r="J12" s="50" t="n">
-        <v>0</v>
+        <v>970</v>
       </c>
       <c r="K12" s="50" t="n">
-        <v>0</v>
+        <v>970</v>
       </c>
       <c r="L12" s="50" t="n">
-        <v>0</v>
+        <v>970</v>
       </c>
       <c r="M12" s="50" t="n">
-        <v>0</v>
+        <v>970</v>
       </c>
       <c r="N12" s="50" t="n">
-        <v>0</v>
+        <v>970</v>
       </c>
       <c r="O12" s="50" t="n"/>
       <c r="P12" s="50" t="n"/>
@@ -17279,11 +17438,7 @@
           <t>Gestora, 05/08/26</t>
         </is>
       </c>
-      <c r="V12" s="51" t="inlineStr">
-        <is>
-          <t>Sem gasto no período</t>
-        </is>
-      </c>
+      <c r="V12" s="51" t="n"/>
     </row>
     <row r="13" ht="26" customHeight="1">
       <c r="A13" s="48">
@@ -17351,76 +17506,146 @@
       </c>
       <c r="V13" s="51" t="inlineStr">
         <is>
+          <t>Sem gasto no período</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="26" customHeight="1">
+      <c r="A14" s="48">
+        <f>Planejado!A14</f>
+        <v/>
+      </c>
+      <c r="B14" s="48">
+        <f>Planejado!B14</f>
+        <v/>
+      </c>
+      <c r="C14" s="48">
+        <f>Planejado!C14</f>
+        <v/>
+      </c>
+      <c r="D14" s="49">
+        <f>Planejado!D14</f>
+        <v/>
+      </c>
+      <c r="E14" s="49">
+        <f>Planejado!E14</f>
+        <v/>
+      </c>
+      <c r="F14" s="48">
+        <f>Planejado!F14</f>
+        <v/>
+      </c>
+      <c r="G14" s="48">
+        <f>Planejado!G14</f>
+        <v/>
+      </c>
+      <c r="H14" s="50" t="n">
+        <v>0</v>
+      </c>
+      <c r="I14" s="50" t="n">
+        <v>0</v>
+      </c>
+      <c r="J14" s="50" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" s="50" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" s="50" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" s="50" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" s="50" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" s="50" t="n"/>
+      <c r="P14" s="50" t="n"/>
+      <c r="Q14" s="50" t="n"/>
+      <c r="R14" s="50" t="n"/>
+      <c r="S14" s="50" t="n"/>
+      <c r="T14" s="46">
+        <f>SUM(H14:S14)</f>
+        <v/>
+      </c>
+      <c r="U14" s="51" t="inlineStr">
+        <is>
+          <t>Gestora, 05/08/26</t>
+        </is>
+      </c>
+      <c r="V14" s="51" t="inlineStr">
+        <is>
           <t>Sem parcela no 1º semestre; bonificação de ago/26 a confirmar</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="52" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="52" t="inlineStr">
         <is>
           <t>TOTAL GERAL</t>
         </is>
       </c>
-      <c r="B14" s="52" t="n"/>
-      <c r="C14" s="52" t="n"/>
-      <c r="D14" s="52" t="n"/>
-      <c r="E14" s="52" t="n"/>
-      <c r="F14" s="52" t="n"/>
-      <c r="G14" s="52" t="n"/>
-      <c r="H14" s="53">
-        <f>SUM(H5:H13)</f>
-        <v/>
-      </c>
-      <c r="I14" s="53">
-        <f>SUM(I5:I13)</f>
-        <v/>
-      </c>
-      <c r="J14" s="53">
-        <f>SUM(J5:J13)</f>
-        <v/>
-      </c>
-      <c r="K14" s="53">
-        <f>SUM(K5:K13)</f>
-        <v/>
-      </c>
-      <c r="L14" s="53">
-        <f>SUM(L5:L13)</f>
-        <v/>
-      </c>
-      <c r="M14" s="53">
-        <f>SUM(M5:M13)</f>
-        <v/>
-      </c>
-      <c r="N14" s="53">
-        <f>SUM(N5:N13)</f>
-        <v/>
-      </c>
-      <c r="O14" s="53">
-        <f>SUM(O5:O13)</f>
-        <v/>
-      </c>
-      <c r="P14" s="53">
-        <f>SUM(P5:P13)</f>
-        <v/>
-      </c>
-      <c r="Q14" s="53">
-        <f>SUM(Q5:Q13)</f>
-        <v/>
-      </c>
-      <c r="R14" s="53">
-        <f>SUM(R5:R13)</f>
-        <v/>
-      </c>
-      <c r="S14" s="53">
-        <f>SUM(S5:S13)</f>
-        <v/>
-      </c>
-      <c r="T14" s="53">
-        <f>SUM(T5:T13)</f>
-        <v/>
-      </c>
-      <c r="U14" s="52" t="n"/>
-      <c r="V14" s="52" t="n"/>
+      <c r="B15" s="52" t="n"/>
+      <c r="C15" s="52" t="n"/>
+      <c r="D15" s="52" t="n"/>
+      <c r="E15" s="52" t="n"/>
+      <c r="F15" s="52" t="n"/>
+      <c r="G15" s="52" t="n"/>
+      <c r="H15" s="53">
+        <f>SUM(H5:H14)</f>
+        <v/>
+      </c>
+      <c r="I15" s="53">
+        <f>SUM(I5:I14)</f>
+        <v/>
+      </c>
+      <c r="J15" s="53">
+        <f>SUM(J5:J14)</f>
+        <v/>
+      </c>
+      <c r="K15" s="53">
+        <f>SUM(K5:K14)</f>
+        <v/>
+      </c>
+      <c r="L15" s="53">
+        <f>SUM(L5:L14)</f>
+        <v/>
+      </c>
+      <c r="M15" s="53">
+        <f>SUM(M5:M14)</f>
+        <v/>
+      </c>
+      <c r="N15" s="53">
+        <f>SUM(N5:N14)</f>
+        <v/>
+      </c>
+      <c r="O15" s="53">
+        <f>SUM(O5:O14)</f>
+        <v/>
+      </c>
+      <c r="P15" s="53">
+        <f>SUM(P5:P14)</f>
+        <v/>
+      </c>
+      <c r="Q15" s="53">
+        <f>SUM(Q5:Q14)</f>
+        <v/>
+      </c>
+      <c r="R15" s="53">
+        <f>SUM(R5:R14)</f>
+        <v/>
+      </c>
+      <c r="S15" s="53">
+        <f>SUM(S5:S14)</f>
+        <v/>
+      </c>
+      <c r="T15" s="53">
+        <f>SUM(T5:T14)</f>
+        <v/>
+      </c>
+      <c r="U15" s="52" t="n"/>
+      <c r="V15" s="52" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -17513,11 +17738,11 @@
         </is>
       </c>
       <c r="B5" s="38">
-        <f>SUMIFS(Planejado!$H$5:$H$13,Planejado!$B$5:$B$13,"Jurídico")</f>
+        <f>SUMIFS(Planejado!$H$5:$H$14,Planejado!$B$5:$B$14,"Jurídico")</f>
         <v/>
       </c>
       <c r="C5" s="38">
-        <f>SUMIFS(Realizado!$H$5:$H$13,Realizado!$B$5:$B$13,"Jurídico")</f>
+        <f>SUMIFS(Realizado!$H$5:$H$14,Realizado!$B$5:$B$14,"Jurídico")</f>
         <v/>
       </c>
       <c r="D5" s="38">
@@ -17548,11 +17773,11 @@
         </is>
       </c>
       <c r="B6" s="56">
-        <f>SUMIFS(Planejado!$I$5:$I$13,Planejado!$B$5:$B$13,"Jurídico")</f>
+        <f>SUMIFS(Planejado!$I$5:$I$14,Planejado!$B$5:$B$14,"Jurídico")</f>
         <v/>
       </c>
       <c r="C6" s="56">
-        <f>SUMIFS(Realizado!$I$5:$I$13,Realizado!$B$5:$B$13,"Jurídico")</f>
+        <f>SUMIFS(Realizado!$I$5:$I$14,Realizado!$B$5:$B$14,"Jurídico")</f>
         <v/>
       </c>
       <c r="D6" s="56">
@@ -17583,11 +17808,11 @@
         </is>
       </c>
       <c r="B7" s="38">
-        <f>SUMIFS(Planejado!$J$5:$J$13,Planejado!$B$5:$B$13,"Jurídico")</f>
+        <f>SUMIFS(Planejado!$J$5:$J$14,Planejado!$B$5:$B$14,"Jurídico")</f>
         <v/>
       </c>
       <c r="C7" s="38">
-        <f>SUMIFS(Realizado!$J$5:$J$13,Realizado!$B$5:$B$13,"Jurídico")</f>
+        <f>SUMIFS(Realizado!$J$5:$J$14,Realizado!$B$5:$B$14,"Jurídico")</f>
         <v/>
       </c>
       <c r="D7" s="38">
@@ -17618,11 +17843,11 @@
         </is>
       </c>
       <c r="B8" s="56">
-        <f>SUMIFS(Planejado!$K$5:$K$13,Planejado!$B$5:$B$13,"Jurídico")</f>
+        <f>SUMIFS(Planejado!$K$5:$K$14,Planejado!$B$5:$B$14,"Jurídico")</f>
         <v/>
       </c>
       <c r="C8" s="56">
-        <f>SUMIFS(Realizado!$K$5:$K$13,Realizado!$B$5:$B$13,"Jurídico")</f>
+        <f>SUMIFS(Realizado!$K$5:$K$14,Realizado!$B$5:$B$14,"Jurídico")</f>
         <v/>
       </c>
       <c r="D8" s="56">
@@ -17653,11 +17878,11 @@
         </is>
       </c>
       <c r="B9" s="38">
-        <f>SUMIFS(Planejado!$L$5:$L$13,Planejado!$B$5:$B$13,"Jurídico")</f>
+        <f>SUMIFS(Planejado!$L$5:$L$14,Planejado!$B$5:$B$14,"Jurídico")</f>
         <v/>
       </c>
       <c r="C9" s="38">
-        <f>SUMIFS(Realizado!$L$5:$L$13,Realizado!$B$5:$B$13,"Jurídico")</f>
+        <f>SUMIFS(Realizado!$L$5:$L$14,Realizado!$B$5:$B$14,"Jurídico")</f>
         <v/>
       </c>
       <c r="D9" s="38">
@@ -17688,11 +17913,11 @@
         </is>
       </c>
       <c r="B10" s="56">
-        <f>SUMIFS(Planejado!$M$5:$M$13,Planejado!$B$5:$B$13,"Jurídico")</f>
+        <f>SUMIFS(Planejado!$M$5:$M$14,Planejado!$B$5:$B$14,"Jurídico")</f>
         <v/>
       </c>
       <c r="C10" s="56">
-        <f>SUMIFS(Realizado!$M$5:$M$13,Realizado!$B$5:$B$13,"Jurídico")</f>
+        <f>SUMIFS(Realizado!$M$5:$M$14,Realizado!$B$5:$B$14,"Jurídico")</f>
         <v/>
       </c>
       <c r="D10" s="56">
@@ -17723,11 +17948,11 @@
         </is>
       </c>
       <c r="B11" s="38">
-        <f>SUMIFS(Planejado!$N$5:$N$13,Planejado!$B$5:$B$13,"Jurídico")</f>
+        <f>SUMIFS(Planejado!$N$5:$N$14,Planejado!$B$5:$B$14,"Jurídico")</f>
         <v/>
       </c>
       <c r="C11" s="38">
-        <f>SUMIFS(Realizado!$N$5:$N$13,Realizado!$B$5:$B$13,"Jurídico")</f>
+        <f>SUMIFS(Realizado!$N$5:$N$14,Realizado!$B$5:$B$14,"Jurídico")</f>
         <v/>
       </c>
       <c r="D11" s="38">
@@ -17758,11 +17983,11 @@
         </is>
       </c>
       <c r="B12" s="56">
-        <f>SUMIFS(Planejado!$O$5:$O$13,Planejado!$B$5:$B$13,"Jurídico")</f>
+        <f>SUMIFS(Planejado!$O$5:$O$14,Planejado!$B$5:$B$14,"Jurídico")</f>
         <v/>
       </c>
       <c r="C12" s="56">
-        <f>SUMIFS(Realizado!$O$5:$O$13,Realizado!$B$5:$B$13,"Jurídico")</f>
+        <f>SUMIFS(Realizado!$O$5:$O$14,Realizado!$B$5:$B$14,"Jurídico")</f>
         <v/>
       </c>
       <c r="D12" s="56">
@@ -17793,11 +18018,11 @@
         </is>
       </c>
       <c r="B13" s="38">
-        <f>SUMIFS(Planejado!$P$5:$P$13,Planejado!$B$5:$B$13,"Jurídico")</f>
+        <f>SUMIFS(Planejado!$P$5:$P$14,Planejado!$B$5:$B$14,"Jurídico")</f>
         <v/>
       </c>
       <c r="C13" s="38">
-        <f>SUMIFS(Realizado!$P$5:$P$13,Realizado!$B$5:$B$13,"Jurídico")</f>
+        <f>SUMIFS(Realizado!$P$5:$P$14,Realizado!$B$5:$B$14,"Jurídico")</f>
         <v/>
       </c>
       <c r="D13" s="38">
@@ -17828,11 +18053,11 @@
         </is>
       </c>
       <c r="B14" s="56">
-        <f>SUMIFS(Planejado!$Q$5:$Q$13,Planejado!$B$5:$B$13,"Jurídico")</f>
+        <f>SUMIFS(Planejado!$Q$5:$Q$14,Planejado!$B$5:$B$14,"Jurídico")</f>
         <v/>
       </c>
       <c r="C14" s="56">
-        <f>SUMIFS(Realizado!$Q$5:$Q$13,Realizado!$B$5:$B$13,"Jurídico")</f>
+        <f>SUMIFS(Realizado!$Q$5:$Q$14,Realizado!$B$5:$B$14,"Jurídico")</f>
         <v/>
       </c>
       <c r="D14" s="56">
@@ -17863,11 +18088,11 @@
         </is>
       </c>
       <c r="B15" s="38">
-        <f>SUMIFS(Planejado!$R$5:$R$13,Planejado!$B$5:$B$13,"Jurídico")</f>
+        <f>SUMIFS(Planejado!$R$5:$R$14,Planejado!$B$5:$B$14,"Jurídico")</f>
         <v/>
       </c>
       <c r="C15" s="38">
-        <f>SUMIFS(Realizado!$R$5:$R$13,Realizado!$B$5:$B$13,"Jurídico")</f>
+        <f>SUMIFS(Realizado!$R$5:$R$14,Realizado!$B$5:$B$14,"Jurídico")</f>
         <v/>
       </c>
       <c r="D15" s="38">
@@ -17898,11 +18123,11 @@
         </is>
       </c>
       <c r="B16" s="56">
-        <f>SUMIFS(Planejado!$S$5:$S$13,Planejado!$B$5:$B$13,"Jurídico")</f>
+        <f>SUMIFS(Planejado!$S$5:$S$14,Planejado!$B$5:$B$14,"Jurídico")</f>
         <v/>
       </c>
       <c r="C16" s="56">
-        <f>SUMIFS(Realizado!$S$5:$S$13,Realizado!$B$5:$B$13,"Jurídico")</f>
+        <f>SUMIFS(Realizado!$S$5:$S$14,Realizado!$B$5:$B$14,"Jurídico")</f>
         <v/>
       </c>
       <c r="D16" s="56">
@@ -18055,11 +18280,11 @@
         </is>
       </c>
       <c r="B5" s="38">
-        <f>SUMIFS(Comparativo!$I$6:$I$14,Comparativo!$E$6:$E$14,$A5,Comparativo!$B$6:$B$14,"Jurídico")</f>
+        <f>SUMIFS(Comparativo!$I$6:$I$15,Comparativo!$E$6:$E$15,$A5,Comparativo!$B$6:$B$15,"Jurídico")</f>
         <v/>
       </c>
       <c r="C5" s="38">
-        <f>SUMIFS(Comparativo!$J$6:$J$14,Comparativo!$E$6:$E$14,$A5,Comparativo!$B$6:$B$14,"Jurídico")</f>
+        <f>SUMIFS(Comparativo!$J$6:$J$15,Comparativo!$E$6:$E$15,$A5,Comparativo!$B$6:$B$15,"Jurídico")</f>
         <v/>
       </c>
       <c r="D5" s="38">
@@ -18079,7 +18304,7 @@
         <v/>
       </c>
       <c r="H5" s="38">
-        <f>SUMIFS(Planejado!$T$5:$T$13,Planejado!$G$5:$G$13,$A5)</f>
+        <f>SUMIFS(Planejado!$T$5:$T$14,Planejado!$G$5:$G$14,$A5)</f>
         <v/>
       </c>
     </row>
@@ -18090,11 +18315,11 @@
         </is>
       </c>
       <c r="B6" s="56">
-        <f>SUMIFS(Comparativo!$I$6:$I$14,Comparativo!$E$6:$E$14,$A6,Comparativo!$B$6:$B$14,"Jurídico")</f>
+        <f>SUMIFS(Comparativo!$I$6:$I$15,Comparativo!$E$6:$E$15,$A6,Comparativo!$B$6:$B$15,"Jurídico")</f>
         <v/>
       </c>
       <c r="C6" s="56">
-        <f>SUMIFS(Comparativo!$J$6:$J$14,Comparativo!$E$6:$E$14,$A6,Comparativo!$B$6:$B$14,"Jurídico")</f>
+        <f>SUMIFS(Comparativo!$J$6:$J$15,Comparativo!$E$6:$E$15,$A6,Comparativo!$B$6:$B$15,"Jurídico")</f>
         <v/>
       </c>
       <c r="D6" s="56">
@@ -18114,7 +18339,7 @@
         <v/>
       </c>
       <c r="H6" s="56">
-        <f>SUMIFS(Planejado!$T$5:$T$13,Planejado!$G$5:$G$13,$A6)</f>
+        <f>SUMIFS(Planejado!$T$5:$T$14,Planejado!$G$5:$G$14,$A6)</f>
         <v/>
       </c>
     </row>
@@ -18125,11 +18350,11 @@
         </is>
       </c>
       <c r="B7" s="38">
-        <f>SUMIFS(Comparativo!$I$6:$I$14,Comparativo!$E$6:$E$14,$A7,Comparativo!$B$6:$B$14,"Jurídico")</f>
+        <f>SUMIFS(Comparativo!$I$6:$I$15,Comparativo!$E$6:$E$15,$A7,Comparativo!$B$6:$B$15,"Jurídico")</f>
         <v/>
       </c>
       <c r="C7" s="38">
-        <f>SUMIFS(Comparativo!$J$6:$J$14,Comparativo!$E$6:$E$14,$A7,Comparativo!$B$6:$B$14,"Jurídico")</f>
+        <f>SUMIFS(Comparativo!$J$6:$J$15,Comparativo!$E$6:$E$15,$A7,Comparativo!$B$6:$B$15,"Jurídico")</f>
         <v/>
       </c>
       <c r="D7" s="38">
@@ -18149,7 +18374,7 @@
         <v/>
       </c>
       <c r="H7" s="38">
-        <f>SUMIFS(Planejado!$T$5:$T$13,Planejado!$G$5:$G$13,$A7)</f>
+        <f>SUMIFS(Planejado!$T$5:$T$14,Planejado!$G$5:$G$14,$A7)</f>
         <v/>
       </c>
     </row>
@@ -18160,11 +18385,11 @@
         </is>
       </c>
       <c r="B8" s="56">
-        <f>SUMIFS(Comparativo!$I$6:$I$14,Comparativo!$E$6:$E$14,$A8,Comparativo!$B$6:$B$14,"Jurídico")</f>
+        <f>SUMIFS(Comparativo!$I$6:$I$15,Comparativo!$E$6:$E$15,$A8,Comparativo!$B$6:$B$15,"Jurídico")</f>
         <v/>
       </c>
       <c r="C8" s="56">
-        <f>SUMIFS(Comparativo!$J$6:$J$14,Comparativo!$E$6:$E$14,$A8,Comparativo!$B$6:$B$14,"Jurídico")</f>
+        <f>SUMIFS(Comparativo!$J$6:$J$15,Comparativo!$E$6:$E$15,$A8,Comparativo!$B$6:$B$15,"Jurídico")</f>
         <v/>
       </c>
       <c r="D8" s="56">
@@ -18184,7 +18409,7 @@
         <v/>
       </c>
       <c r="H8" s="56">
-        <f>SUMIFS(Planejado!$T$5:$T$13,Planejado!$G$5:$G$13,$A8)</f>
+        <f>SUMIFS(Planejado!$T$5:$T$14,Planejado!$G$5:$G$14,$A8)</f>
         <v/>
       </c>
     </row>
@@ -18195,11 +18420,11 @@
         </is>
       </c>
       <c r="B9" s="38">
-        <f>SUMIFS(Comparativo!$I$6:$I$14,Comparativo!$E$6:$E$14,$A9,Comparativo!$B$6:$B$14,"Jurídico")</f>
+        <f>SUMIFS(Comparativo!$I$6:$I$15,Comparativo!$E$6:$E$15,$A9,Comparativo!$B$6:$B$15,"Jurídico")</f>
         <v/>
       </c>
       <c r="C9" s="38">
-        <f>SUMIFS(Comparativo!$J$6:$J$14,Comparativo!$E$6:$E$14,$A9,Comparativo!$B$6:$B$14,"Jurídico")</f>
+        <f>SUMIFS(Comparativo!$J$6:$J$15,Comparativo!$E$6:$E$15,$A9,Comparativo!$B$6:$B$15,"Jurídico")</f>
         <v/>
       </c>
       <c r="D9" s="38">
@@ -18219,7 +18444,7 @@
         <v/>
       </c>
       <c r="H9" s="38">
-        <f>SUMIFS(Planejado!$T$5:$T$13,Planejado!$G$5:$G$13,$A9)</f>
+        <f>SUMIFS(Planejado!$T$5:$T$14,Planejado!$G$5:$G$14,$A9)</f>
         <v/>
       </c>
     </row>
@@ -18281,7 +18506,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F16"/>
+  <dimension ref="A1:F18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -18548,7 +18773,7 @@
       </c>
       <c r="D11" s="63" t="inlineStr">
         <is>
-          <t>Só os dois primeiros credores do Jurídico superam o orçamento anual inteiro do departamento. Decidir na reunião quais entram no centro de custo da área — e, para os que entrarem, criar linha no orçamento, senão aparecerão como 'Não orçado' e distorcerão o comparativo.</t>
+          <t>Só os dois primeiros credores do Jurídico superam o orçamento anual inteiro do departamento. ATENÇÃO: parte desses valores pode ser repasse ou custa reembolsável pelo cliente, e não custo da área — foi o caso da Dra. Michele (ver item P). Separar o que é custo antes de decidir. Para os que entrarem no centro de custo, criar linha no orçamento, senão aparecerão como 'Não orçado' e distorcerão o comparativo.</t>
         </is>
       </c>
       <c r="E11" s="63" t="inlineStr">
@@ -18661,22 +18886,22 @@
     <row r="15" ht="58" customHeight="1">
       <c r="A15" s="62" t="inlineStr">
         <is>
-          <t>K</t>
+          <t>O</t>
         </is>
       </c>
       <c r="B15" s="63" t="inlineStr">
         <is>
-          <t>ORÇAMENTO VEIO ERRADO — Astrea e Jusbrasil</t>
+          <t>Dra. Michele fora do orçamento — INCLUIR</t>
         </is>
       </c>
       <c r="C15" s="63" t="inlineStr">
         <is>
-          <t>ASTREA: orçado R$ 112,07/mês, o que dá R$ 1.344,84 no ano — praticamente o valor de UMA das cinco parcelas (R$ 1.346,28). Quem montou a ficha tomou uma parcela pelo custo total do ano. O custo real da anuidade foi R$ 6.731,40, 5x o orçado. JUSBRASIL: orçado R$ 104,90/mês contra R$ 136,00 reais (1,3x), R$ 373,20 no ano. PAUTA PARA A REUNIÃO COM A DIRETORIA.</t>
+          <t>Advogada que presta serviço ao departamento e não foi incluída na ficha. Recebe R$ 2.750/mês fixos desde jul/26. A linha foi criada com planejado zerado, à espera da definição.</t>
         </is>
       </c>
       <c r="D15" s="63" t="inlineStr">
         <is>
-          <t>Subdimensionamento de R$ 5.759,76 no ano (R$ 5.386,56 do Astrea + R$ 373,20 do Jusbrasil). O planejado das duas linhas foi mantido como veio na ficha, de propósito, para o erro aparecer no comparativo em vez de ser corrigido em silêncio. Não é estouro de gestão: é erro na origem. Como o Astrea será cancelado, o efeito prático é só de 2026 — mas o método de orçar serviços parcelados precisa ser revisto para o ano que vem.</t>
+          <t>A R$ 2.750/mês são R$ 33.000/ano, que hoje não têm previsão. Enquanto o planejado for zero, a linha aparece como 'Não orçado' e o valor entra inteiro como estouro. Definir o valor a orçar e a partir de quando.</t>
         </is>
       </c>
       <c r="E15" s="63" t="inlineStr">
@@ -18693,30 +18918,94 @@
     <row r="16" ht="58" customHeight="1">
       <c r="A16" s="65" t="inlineStr">
         <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="B16" s="66" t="inlineStr">
+        <is>
+          <t>Extrato contém REPASSES, não só custo</t>
+        </is>
+      </c>
+      <c r="C16" s="66" t="inlineStr">
+        <is>
+          <t>Os lançamentos em nome da Dra. Michele até jun/26 (R$ 20.821,53) são repasse: o cliente paga à empresa e a empresa repassa a ela. Não são custo do departamento e por isso não foram lançados no realizado.</t>
+        </is>
+      </c>
+      <c r="D16" s="66" t="inlineStr">
+        <is>
+          <t>Vale a mesma checagem nos outros credores das abas 'Contas Pagas' antes de usá-los como custo — em especial custas processuais e honorários de terceiros, que podem ser reembolsados pelo cliente. O total de R$ 446.577,92 do centro de custo Jurídico no extrato NÃO é despesa líquida do departamento.</t>
+        </is>
+      </c>
+      <c r="E16" s="66" t="inlineStr">
+        <is>
+          <t>Cristiane + Financeiro</t>
+        </is>
+      </c>
+      <c r="F16" s="70" t="inlineStr">
+        <is>
+          <t>CONFERIR</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="58" customHeight="1">
+      <c r="A17" s="62" t="inlineStr">
+        <is>
+          <t>K</t>
+        </is>
+      </c>
+      <c r="B17" s="63" t="inlineStr">
+        <is>
+          <t>ORÇAMENTO VEIO ERRADO — Astrea e Jusbrasil</t>
+        </is>
+      </c>
+      <c r="C17" s="63" t="inlineStr">
+        <is>
+          <t>ASTREA: orçado R$ 112,07/mês, o que dá R$ 1.344,84 no ano — praticamente o valor de UMA das cinco parcelas (R$ 1.346,28). Quem montou a ficha tomou uma parcela pelo custo total do ano. O custo real da anuidade foi R$ 6.731,40, 5x o orçado. JUSBRASIL: orçado R$ 104,90/mês contra R$ 136,00 reais (1,3x), R$ 373,20 no ano. PAUTA PARA A REUNIÃO COM A DIRETORIA.</t>
+        </is>
+      </c>
+      <c r="D17" s="63" t="inlineStr">
+        <is>
+          <t>Subdimensionamento de R$ 5.759,76 no ano (R$ 5.386,56 do Astrea + R$ 373,20 do Jusbrasil). O planejado das duas linhas foi mantido como veio na ficha, de propósito, para o erro aparecer no comparativo em vez de ser corrigido em silêncio. Não é estouro de gestão: é erro na origem. Como o Astrea será cancelado, o efeito prático é só de 2026 — mas o método de orçar serviços parcelados precisa ser revisto para o ano que vem.</t>
+        </is>
+      </c>
+      <c r="E17" s="63" t="inlineStr">
+        <is>
+          <t>Cristiane + Diretoria</t>
+        </is>
+      </c>
+      <c r="F17" s="69" t="inlineStr">
+        <is>
+          <t>PAUTA REUNIÃO</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="58" customHeight="1">
+      <c r="A18" s="65" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="B16" s="66" t="inlineStr">
+      <c r="B18" s="66" t="inlineStr">
         <is>
           <t>Competência x caixa — DEFASAGEM CONFIRMADA</t>
         </is>
       </c>
-      <c r="C16" s="66" t="inlineStr">
+      <c r="C18" s="66" t="inlineStr">
         <is>
           <t>O pagamento do Miguel de 01/08/26 refere-se a julho, então há pelo menos um prestador cujo pagamento cai no mês seguinte ao da prestação. Todo o realizado está lançado por CAIXA (mês em que o pagamento saiu), que é como os valores foram informados.</t>
         </is>
       </c>
-      <c r="D16" s="66" t="inlineStr">
+      <c r="D18" s="66" t="inlineStr">
         <is>
           <t>Consequência: o valor lançado em jan/26 pode ser referente a dez/2025, e o serviço de dez/26 só aparecerá em jan/2027 — o ano fecha com 12 pagamentos, mas defasados em relação ao orçamento, que é de competência. Com a extração vindo do SIENGE, basta escolher o regime na hora de gerar o relatório: definir isso UMA vez e manter, para o histórico não misturar critérios.</t>
         </is>
       </c>
-      <c r="E16" s="66" t="inlineStr">
+      <c r="E18" s="66" t="inlineStr">
         <is>
           <t>Cristiane + Financeiro</t>
         </is>
       </c>
-      <c r="F16" s="70" t="inlineStr">
+      <c r="F18" s="70" t="inlineStr">
         <is>
           <t>DECIDIR</t>
         </is>

--- a/orcamento/Orcamento_JURIDICO_2026.xlsx
+++ b/orcamento/Orcamento_JURIDICO_2026.xlsx
@@ -16144,7 +16144,7 @@
       </c>
       <c r="E8" s="37" t="inlineStr">
         <is>
-          <t>Advogada — NÃO CONSTAVA NA FICHA. R$ 2.750/mês fixos desde jul/26. Planejado a definir com a diretoria</t>
+          <t>Advogada — R$ 2.750/mês fixos desde jan/26. Não constava na ficha por esquecimento na montagem do orçamento; incluída na revisão</t>
         </is>
       </c>
       <c r="F8" s="36" t="inlineStr">
@@ -16158,40 +16158,40 @@
         </is>
       </c>
       <c r="H8" s="38" t="n">
-        <v>0</v>
+        <v>2750</v>
       </c>
       <c r="I8" s="38" t="n">
-        <v>0</v>
+        <v>2750</v>
       </c>
       <c r="J8" s="38" t="n">
-        <v>0</v>
+        <v>2750</v>
       </c>
       <c r="K8" s="38" t="n">
-        <v>0</v>
+        <v>2750</v>
       </c>
       <c r="L8" s="38" t="n">
-        <v>0</v>
+        <v>2750</v>
       </c>
       <c r="M8" s="38" t="n">
-        <v>0</v>
+        <v>2750</v>
       </c>
       <c r="N8" s="38" t="n">
-        <v>0</v>
+        <v>2750</v>
       </c>
       <c r="O8" s="38" t="n">
-        <v>0</v>
+        <v>2750</v>
       </c>
       <c r="P8" s="38" t="n">
-        <v>0</v>
+        <v>2750</v>
       </c>
       <c r="Q8" s="38" t="n">
-        <v>0</v>
+        <v>2750</v>
       </c>
       <c r="R8" s="38" t="n">
-        <v>0</v>
+        <v>2750</v>
       </c>
       <c r="S8" s="38" t="n">
-        <v>0</v>
+        <v>2750</v>
       </c>
       <c r="T8" s="46">
         <f>SUM(H8:S8)</f>
@@ -17104,22 +17104,22 @@
         <v/>
       </c>
       <c r="H8" s="50" t="n">
-        <v>0</v>
+        <v>2750</v>
       </c>
       <c r="I8" s="50" t="n">
-        <v>0</v>
+        <v>2750</v>
       </c>
       <c r="J8" s="50" t="n">
-        <v>0</v>
+        <v>2750</v>
       </c>
       <c r="K8" s="50" t="n">
-        <v>0</v>
+        <v>2750</v>
       </c>
       <c r="L8" s="50" t="n">
-        <v>0</v>
+        <v>2750</v>
       </c>
       <c r="M8" s="50" t="n">
-        <v>0</v>
+        <v>2750</v>
       </c>
       <c r="N8" s="50" t="n">
         <v>2750</v>
@@ -17135,12 +17135,12 @@
       </c>
       <c r="U8" s="51" t="inlineStr">
         <is>
-          <t>Extrato do financeiro</t>
+          <t>Gestora, 05/08/26</t>
         </is>
       </c>
       <c r="V8" s="51" t="inlineStr">
         <is>
-          <t>R$ 2.750/mês fixos a partir de jul/26. Os demais lançamentos em nome dela no extrato são REPASSE de honorários pagos pelo cliente — não são custo do departamento</t>
+          <t>R$ 2.750/mês fixos desde jan/26. Os demais lançamentos em nome dela no extrato são REPASSE de honorários pagos pelo cliente — não são custo do departamento</t>
         </is>
       </c>
     </row>
@@ -18891,27 +18891,27 @@
       </c>
       <c r="B15" s="63" t="inlineStr">
         <is>
-          <t>Dra. Michele fora do orçamento — INCLUIR</t>
+          <t>Dra. Michele incluída no orçamento</t>
         </is>
       </c>
       <c r="C15" s="63" t="inlineStr">
         <is>
-          <t>Advogada que presta serviço ao departamento e não foi incluída na ficha. Recebe R$ 2.750/mês fixos desde jul/26. A linha foi criada com planejado zerado, à espera da definição.</t>
+          <t>Mão de obra que ficou de fora da ficha por esquecimento na montagem do orçamento. Orçada em R$ 2.750/mês pelo ano inteiro, valor fixo em vigor desde jan/26.</t>
         </is>
       </c>
       <c r="D15" s="63" t="inlineStr">
         <is>
-          <t>A R$ 2.750/mês são R$ 33.000/ano, que hoje não têm previsão. Enquanto o planejado for zero, a linha aparece como 'Não orçado' e o valor entra inteiro como estouro. Definir o valor a orçar e a partir de quando.</t>
+          <t>Acréscimo de R$ 33.000 ao orçamento do Jurídico, que passa a R$ 324.730,42. CONFERIR NO SIENGE: no extrato de contas pagas, o único lançamento isolado de R$ 2.750 é o de jul/26 — de jan a jun aparecem apenas honorários por processo, que são repasse (item P). Ou os pagamentos do fixo de jan a jun saíram por outro centro de custo, ou estão embutidos naqueles lançamentos. Vale localizar antes da reunião. A justificativa da inclusão é pauta.</t>
         </is>
       </c>
       <c r="E15" s="63" t="inlineStr">
         <is>
-          <t>Cristiane + Diretoria</t>
-        </is>
-      </c>
-      <c r="F15" s="69" t="inlineStr">
-        <is>
-          <t>PAUTA REUNIÃO</t>
+          <t>Cristiane + Financeiro</t>
+        </is>
+      </c>
+      <c r="F15" s="70" t="inlineStr">
+        <is>
+          <t>CONFERIR</t>
         </is>
       </c>
     </row>

--- a/orcamento/Orcamento_JURIDICO_2026.xlsx
+++ b/orcamento/Orcamento_JURIDICO_2026.xlsx
@@ -18901,17 +18901,17 @@
       </c>
       <c r="D15" s="63" t="inlineStr">
         <is>
-          <t>Acréscimo de R$ 33.000 ao orçamento do Jurídico, que passa a R$ 324.730,42. CONFERIR NO SIENGE: no extrato de contas pagas, o único lançamento isolado de R$ 2.750 é o de jul/26 — de jan a jun aparecem apenas honorários por processo, que são repasse (item P). Ou os pagamentos do fixo de jan a jun saíram por outro centro de custo, ou estão embutidos naqueles lançamentos. Vale localizar antes da reunião. A justificativa da inclusão é pauta.</t>
+          <t>Acréscimo de R$ 33.000 ao orçamento do Jurídico, que passa a R$ 324.730,42. No extrato, o fixo de jan a jun vem somado aos honorários de repasse no mesmo credor: o total mensal (R$ 3.739 a R$ 4.326) é o fixo de R$ 2.750 mais o repasse, que o cliente paga e a empresa apenas transfere. Só jun/26 fica abaixo do fixo (R$ 1.036,92), provavelmente porque o pagamento daquele mês caiu em jul — é o lançamento isolado de R$ 2.750 que aparece lá. A justificativa da inclusão é pauta da reunião.</t>
         </is>
       </c>
       <c r="E15" s="63" t="inlineStr">
         <is>
-          <t>Cristiane + Financeiro</t>
-        </is>
-      </c>
-      <c r="F15" s="70" t="inlineStr">
-        <is>
-          <t>CONFERIR</t>
+          <t>Cristiane + Diretoria</t>
+        </is>
+      </c>
+      <c r="F15" s="67" t="inlineStr">
+        <is>
+          <t>APLICADO</t>
         </is>
       </c>
     </row>

--- a/orcamento/Orcamento_JURIDICO_2026.xlsx
+++ b/orcamento/Orcamento_JURIDICO_2026.xlsx
@@ -20341,12 +20341,12 @@
       </c>
       <c r="C18" s="66" t="inlineStr">
         <is>
-          <t>Confirmado pela gestora: TODOS os PJs prestam o serviço e recebem no mês seguinte. O que foi pago em jan/26 é serviço de dez/2025, e o serviço de dez/26 só será pago em jan/2027. Hoje o realizado está lançado por CAIXA (mês do pagamento), que é como os valores foram informados, enquanto o orçamento foi montado por COMPETÊNCIA (mês do serviço). São bases diferentes no mesmo comparativo.</t>
+          <t>Confirmado pela gestora: TODOS os PJs das duas áreas prestam o serviço e recebem no mês seguinte — no Jurídico, Miguel, Thamar e Dra. Michele; no TI, Elias e Jonathan. O que foi pago em jan/26 é serviço de dez/2025, e o serviço de dez/26 só será pago em jan/2027. Hoje o realizado está lançado por CAIXA (mês do pagamento), que é como os valores foram informados, enquanto o orçamento foi montado por COMPETÊNCIA (mês do serviço). São bases diferentes no mesmo comparativo.</t>
         </is>
       </c>
       <c r="D18" s="66" t="inlineStr">
         <is>
-          <t>RECOMENDAÇÃO: migrar para competência, deslocando os PJs um mês para trás. Motivos: (1) o orçamento já é de competência, então acaba a comparação de bases diferentes; (2) por caixa, o ano de 2026 carrega um mês de 2025 e perde dez/26, o que distorce sempre que o valor muda no meio do ano — no Miguel, R$ 47.250 por caixa contra R$ 49.318 por competência em jan–jul, R$ 2.068 de diferença; (3) o SIENGE gera os dois regimes, então é escolha de configuração. Contra: caixa é mais fácil de bater com o extrato bancário. Decidir UMA vez e manter, senão o histórico mistura critérios.</t>
+          <t>RECOMENDAÇÃO: migrar para competência, deslocando os PJs um mês para trás. Motivos: (1) o orçamento já é de competência, então acaba a comparação de bases diferentes; (2) por caixa, o ano de 2026 carrega um mês de 2025 e perde dez/26, o que distorce sempre que o valor muda no meio do ano — no Miguel, R$ 47.250 por caixa contra R$ 49.318 por competência em jan–jul, R$ 2.068 de diferença; (3) o SIENGE gera os dois regimes, então é escolha de configuração. Contra: caixa é mais fácil de bater com o extrato bancário. Decidir UMA vez e manter, senão o histórico mistura critérios. ATENÇÃO NO JONATHAN: o planejado dele começa em abr/26 (competência) e o realizado também foi lançado a partir de abr (caixa) — se ele recebe no mês seguinte, o pagamento de abril é serviço de março, e ou a entrada dele foi em março, ou o realizado de abril deveria ser zero. Conferir junto com a decisão do regime.</t>
         </is>
       </c>
       <c r="E18" s="66" t="inlineStr">

--- a/orcamento/Orcamento_JURIDICO_2026.xlsx
+++ b/orcamento/Orcamento_JURIDICO_2026.xlsx
@@ -19855,7 +19855,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F18"/>
+  <dimension ref="A1:F19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -20267,22 +20267,22 @@
     <row r="16" ht="58" customHeight="1">
       <c r="A16" s="65" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>Q</t>
         </is>
       </c>
       <c r="B16" s="66" t="inlineStr">
         <is>
-          <t>Extrato contém REPASSES, não só custo</t>
+          <t>Adapta lançado no centro de custo errado — RECLASSIFICAR</t>
         </is>
       </c>
       <c r="C16" s="66" t="inlineStr">
         <is>
-          <t>Os lançamentos em nome da Dra. Michele até jun/26 (R$ 20.821,53) são repasse: o cliente paga à empresa e a empresa repassa a ela. Não são custo do departamento e por isso não foram lançados no realizado.</t>
+          <t>Os pagamentos do Adapta (ADAPTA EDUCACAO LTDA, contrato 4134643529) estão no centro de custo Jurídico no SIENGE: R$ 575,00/mês de jan a mai e R$ 476,00 em jun, todos com vencimento dia 15. Total de R$ 3.351,00 em seis meses. Não é despesa do Jurídico — é ferramenta de IA, de uso transversal.</t>
         </is>
       </c>
       <c r="D16" s="66" t="inlineStr">
         <is>
-          <t>Vale a mesma checagem nos outros credores das abas 'Contas Pagas' antes de usá-los como custo — em especial custas processuais e honorários de terceiros, que podem ser reembolsados pelo cliente. O total de R$ 446.577,92 do centro de custo Jurídico no extrato NÃO é despesa líquida do departamento.</t>
+          <t>Reclassificar no SIENGE para o centro de custo correto e aplicar o rateio do item L. Enquanto não for corrigido, o Jurídico carrega R$ 3.351 que não são dele e o TI aparece sem um gasto que é seu — as duas áreas ficam com o comparativo errado. Aproveitar a abertura do novo centro de custo para acertar a classificação desde a origem.</t>
         </is>
       </c>
       <c r="E16" s="66" t="inlineStr">
@@ -20290,71 +20290,103 @@
           <t>Cristiane + Financeiro</t>
         </is>
       </c>
-      <c r="F16" s="70" t="inlineStr">
-        <is>
-          <t>CONFERIR</t>
+      <c r="F16" s="64" t="inlineStr">
+        <is>
+          <t>RECLASSIFICAR</t>
         </is>
       </c>
     </row>
     <row r="17" ht="58" customHeight="1">
       <c r="A17" s="62" t="inlineStr">
         <is>
-          <t>K</t>
+          <t>P</t>
         </is>
       </c>
       <c r="B17" s="63" t="inlineStr">
         <is>
-          <t>ORÇAMENTO VEIO ERRADO — Astrea e Jusbrasil</t>
+          <t>Extrato contém REPASSES, não só custo</t>
         </is>
       </c>
       <c r="C17" s="63" t="inlineStr">
         <is>
-          <t>ASTREA: orçado R$ 112,07/mês, o que dá R$ 1.344,84 no ano — praticamente o valor de UMA das cinco parcelas (R$ 1.346,28). Quem montou a ficha tomou uma parcela pelo custo total do ano. O custo real da anuidade foi R$ 6.731,40, 5x o orçado. JUSBRASIL: orçado R$ 104,90/mês contra R$ 136,00 reais (1,3x), R$ 373,20 no ano. PAUTA PARA A REUNIÃO COM A DIRETORIA.</t>
+          <t>Os lançamentos em nome da Dra. Michele até jun/26 (R$ 20.821,53) são repasse: o cliente paga à empresa e a empresa repassa a ela. Não são custo do departamento e por isso não foram lançados no realizado.</t>
         </is>
       </c>
       <c r="D17" s="63" t="inlineStr">
         <is>
-          <t>Subdimensionamento de R$ 5.759,76 no ano (R$ 5.386,56 do Astrea + R$ 373,20 do Jusbrasil). O planejado das duas linhas foi mantido como veio na ficha, de propósito, para o erro aparecer no comparativo em vez de ser corrigido em silêncio. Não é estouro de gestão: é erro na origem. Como o Astrea será cancelado, o efeito prático é só de 2026 — mas o método de orçar serviços parcelados precisa ser revisto para o ano que vem.</t>
+          <t>Vale a mesma checagem nos outros credores das abas 'Contas Pagas' antes de usá-los como custo — em especial custas processuais e honorários de terceiros, que podem ser reembolsados pelo cliente. O total de R$ 446.577,92 do centro de custo Jurídico no extrato NÃO é despesa líquida do departamento.</t>
         </is>
       </c>
       <c r="E17" s="63" t="inlineStr">
         <is>
-          <t>Cristiane + Diretoria</t>
-        </is>
-      </c>
-      <c r="F17" s="69" t="inlineStr">
-        <is>
-          <t>PAUTA REUNIÃO</t>
+          <t>Cristiane + Financeiro</t>
+        </is>
+      </c>
+      <c r="F17" s="70" t="inlineStr">
+        <is>
+          <t>CONFERIR</t>
         </is>
       </c>
     </row>
     <row r="18" ht="58" customHeight="1">
       <c r="A18" s="65" t="inlineStr">
         <is>
+          <t>K</t>
+        </is>
+      </c>
+      <c r="B18" s="66" t="inlineStr">
+        <is>
+          <t>ORÇAMENTO VEIO ERRADO — Astrea e Jusbrasil</t>
+        </is>
+      </c>
+      <c r="C18" s="66" t="inlineStr">
+        <is>
+          <t>ASTREA: orçado R$ 112,07/mês, o que dá R$ 1.344,84 no ano — praticamente o valor de UMA das cinco parcelas (R$ 1.346,28). Quem montou a ficha tomou uma parcela pelo custo total do ano. O custo real da anuidade foi R$ 6.731,40, 5x o orçado. JUSBRASIL: orçado R$ 104,90/mês contra R$ 136,00 reais (1,3x), R$ 373,20 no ano. PAUTA PARA A REUNIÃO COM A DIRETORIA.</t>
+        </is>
+      </c>
+      <c r="D18" s="66" t="inlineStr">
+        <is>
+          <t>Subdimensionamento de R$ 5.759,76 no ano (R$ 5.386,56 do Astrea + R$ 373,20 do Jusbrasil). O planejado das duas linhas foi mantido como veio na ficha, de propósito, para o erro aparecer no comparativo em vez de ser corrigido em silêncio. Não é estouro de gestão: é erro na origem. Como o Astrea será cancelado, o efeito prático é só de 2026 — mas o método de orçar serviços parcelados precisa ser revisto para o ano que vem.</t>
+        </is>
+      </c>
+      <c r="E18" s="66" t="inlineStr">
+        <is>
+          <t>Cristiane + Diretoria</t>
+        </is>
+      </c>
+      <c r="F18" s="69" t="inlineStr">
+        <is>
+          <t>PAUTA REUNIÃO</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="58" customHeight="1">
+      <c r="A19" s="62" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="B18" s="66" t="inlineStr">
+      <c r="B19" s="63" t="inlineStr">
         <is>
           <t>Competência x caixa — DECIDIR O REGIME</t>
         </is>
       </c>
-      <c r="C18" s="66" t="inlineStr">
+      <c r="C19" s="63" t="inlineStr">
         <is>
           <t>Confirmado pela gestora: TODOS os PJs das duas áreas prestam o serviço e recebem no mês seguinte — no Jurídico, Miguel, Thamar e Dra. Michele; no TI, Elias e Jonathan. O que foi pago em jan/26 é serviço de dez/2025, e o serviço de dez/26 só será pago em jan/2027. Hoje o realizado está lançado por CAIXA (mês do pagamento), que é como os valores foram informados, enquanto o orçamento foi montado por COMPETÊNCIA (mês do serviço). São bases diferentes no mesmo comparativo.</t>
         </is>
       </c>
-      <c r="D18" s="66" t="inlineStr">
+      <c r="D19" s="63" t="inlineStr">
         <is>
           <t>RECOMENDAÇÃO: migrar para competência, deslocando os PJs um mês para trás. Motivos: (1) o orçamento já é de competência, então acaba a comparação de bases diferentes; (2) por caixa, o ano de 2026 carrega um mês de 2025 e perde dez/26, o que distorce sempre que o valor muda no meio do ano — no Miguel, R$ 47.250 por caixa contra R$ 49.318 por competência em jan–jul, R$ 2.068 de diferença; (3) o SIENGE gera os dois regimes, então é escolha de configuração. Contra: caixa é mais fácil de bater com o extrato bancário. Decidir UMA vez e manter, senão o histórico mistura critérios. ATENÇÃO NO JONATHAN: o planejado dele começa em abr/26 (competência) e o realizado também foi lançado a partir de abr (caixa) — se ele recebe no mês seguinte, o pagamento de abril é serviço de março, e ou a entrada dele foi em março, ou o realizado de abril deveria ser zero. Conferir junto com a decisão do regime.</t>
         </is>
       </c>
-      <c r="E18" s="66" t="inlineStr">
+      <c r="E19" s="63" t="inlineStr">
         <is>
           <t>Cristiane + Financeiro</t>
         </is>
       </c>
-      <c r="F18" s="70" t="inlineStr">
+      <c r="F19" s="70" t="inlineStr">
         <is>
           <t>DECIDIR</t>
         </is>

--- a/orcamento/Orcamento_JURIDICO_2026.xlsx
+++ b/orcamento/Orcamento_JURIDICO_2026.xlsx
@@ -20407,7 +20407,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C21"/>
+  <dimension ref="A1:C24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -20500,134 +20500,156 @@
     <row r="11" ht="22" customHeight="1">
       <c r="A11" s="31" t="inlineStr">
         <is>
-          <t>COMO LER OS NÚMEROS</t>
+          <t>PADRÃO DE DESCRIÇÃO</t>
         </is>
       </c>
     </row>
     <row r="12" ht="34" customHeight="1">
       <c r="A12" s="71" t="inlineStr">
         <is>
-          <t>Desvio positivo (vermelho)</t>
+          <t>Rubricas genéricas</t>
         </is>
       </c>
       <c r="B12" s="72" t="inlineStr">
         <is>
-          <t>Gastou ACIMA do orçado.</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="34" customHeight="1">
-      <c r="A13" s="71" t="inlineStr">
-        <is>
-          <t>Desvio negativo (verde)</t>
-        </is>
-      </c>
-      <c r="B13" s="72" t="inlineStr">
-        <is>
-          <t>Gastou ABAIXO do orçado — economia ou despesa ainda não realizada.</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="34" customHeight="1">
-      <c r="A14" s="71" t="inlineStr">
-        <is>
-          <t>Planejado acum.</t>
-        </is>
-      </c>
-      <c r="B14" s="72" t="inlineStr">
-        <is>
-          <t>Soma de maio até o mês selecionado.</t>
+          <t>Em linhas que agrupam itens variados (peças de manutenção, equipamentos diversos), detalhe o item na descrição do lançamento no SIENGE, sempre no mesmo padrão: 'Peças – mouse', 'Peças – tela'. O orçamento fica numa linha só e o detalhe sai por filtro quando precisar.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="8" customHeight="1"/>
+    <row r="14" ht="22" customHeight="1">
+      <c r="A14" s="31" t="inlineStr">
+        <is>
+          <t>COMO LER OS NÚMEROS</t>
         </is>
       </c>
     </row>
     <row r="15" ht="34" customHeight="1">
       <c r="A15" s="71" t="inlineStr">
         <is>
-          <t>% Executado</t>
+          <t>Desvio positivo (vermelho)</t>
         </is>
       </c>
       <c r="B15" s="72" t="inlineStr">
         <is>
-          <t>Realizado acumulado ÷ Planejado acumulado. Perto de 100% = no ritmo.</t>
+          <t>Gastou ACIMA do orçado.</t>
         </is>
       </c>
     </row>
     <row r="16" ht="34" customHeight="1">
       <c r="A16" s="71" t="inlineStr">
         <is>
-          <t>Sem lançamento</t>
+          <t>Desvio negativo (verde)</t>
         </is>
       </c>
       <c r="B16" s="72" t="inlineStr">
         <is>
-          <t>Nada foi lançado no realizado ainda — não confunda com economia.</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="8" customHeight="1"/>
-    <row r="18" ht="22" customHeight="1">
-      <c r="A18" s="31" t="inlineStr">
-        <is>
-          <t>REGRAS DA PLANILHA</t>
+          <t>Gastou ABAIXO do orçado — economia ou despesa ainda não realizada.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="34" customHeight="1">
+      <c r="A17" s="71" t="inlineStr">
+        <is>
+          <t>Planejado acum.</t>
+        </is>
+      </c>
+      <c r="B17" s="72" t="inlineStr">
+        <is>
+          <t>Soma de maio até o mês selecionado.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="34" customHeight="1">
+      <c r="A18" s="71" t="inlineStr">
+        <is>
+          <t>% Executado</t>
+        </is>
+      </c>
+      <c r="B18" s="72" t="inlineStr">
+        <is>
+          <t>Realizado acumulado ÷ Planejado acumulado. Perto de 100% = no ritmo.</t>
         </is>
       </c>
     </row>
     <row r="19" ht="34" customHeight="1">
       <c r="A19" s="71" t="inlineStr">
         <is>
+          <t>Sem lançamento</t>
+        </is>
+      </c>
+      <c r="B19" s="72" t="inlineStr">
+        <is>
+          <t>Nada foi lançado no realizado ainda — não confunda com economia.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="8" customHeight="1"/>
+    <row r="21" ht="22" customHeight="1">
+      <c r="A21" s="31" t="inlineStr">
+        <is>
+          <t>REGRAS DA PLANILHA</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="34" customHeight="1">
+      <c r="A22" s="71" t="inlineStr">
+        <is>
           <t>Não altere</t>
         </is>
       </c>
-      <c r="B19" s="72" t="inlineStr">
+      <c r="B22" s="72" t="inlineStr">
         <is>
           <t>As colunas de identificação da aba Realizado (A a G) são fórmulas que espelham a aba Planejado. Alterar quebra o comparativo.</t>
         </is>
       </c>
     </row>
-    <row r="20" ht="34" customHeight="1">
-      <c r="A20" s="71" t="inlineStr">
+    <row r="23" ht="34" customHeight="1">
+      <c r="A23" s="71" t="inlineStr">
         <is>
           <t>Nova linha de orçamento</t>
         </is>
       </c>
-      <c r="B20" s="72" t="inlineStr">
+      <c r="B23" s="72" t="inlineStr">
         <is>
           <t>Insira na aba Planejado e replique a mesma linha na aba Realizado e na aba Comparativo, mantendo o mesmo ID.</t>
         </is>
       </c>
     </row>
-    <row r="21" ht="34" customHeight="1">
-      <c r="A21" s="71" t="inlineStr">
+    <row r="24" ht="34" customHeight="1">
+      <c r="A24" s="71" t="inlineStr">
         <is>
           <t>Revisão de orçamento</t>
         </is>
       </c>
-      <c r="B21" s="72" t="inlineStr">
+      <c r="B24" s="72" t="inlineStr">
         <is>
           <t>Se a diretoria aprovar um valor novo, altere na aba Planejado e registre o motivo na aba Pendências.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="18">
-    <mergeCell ref="B13:C13"/>
+  <mergeCells count="20">
+    <mergeCell ref="B16:C16"/>
+    <mergeCell ref="B7:C7"/>
+    <mergeCell ref="B22:C22"/>
+    <mergeCell ref="A21:C21"/>
+    <mergeCell ref="B18:C18"/>
+    <mergeCell ref="A2:C2"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="A14:C14"/>
+    <mergeCell ref="B23:C23"/>
+    <mergeCell ref="B17:C17"/>
+    <mergeCell ref="A4:C4"/>
+    <mergeCell ref="B8:C8"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="B9:C9"/>
     <mergeCell ref="B6:C6"/>
-    <mergeCell ref="B21:C21"/>
-    <mergeCell ref="B16:C16"/>
+    <mergeCell ref="B24:C24"/>
     <mergeCell ref="A11:C11"/>
     <mergeCell ref="B15:C15"/>
-    <mergeCell ref="B7:C7"/>
     <mergeCell ref="A1:C1"/>
     <mergeCell ref="B5:C5"/>
-    <mergeCell ref="B19:C19"/>
-    <mergeCell ref="B20:C20"/>
-    <mergeCell ref="A18:C18"/>
-    <mergeCell ref="B14:C14"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="A4:C4"/>
-    <mergeCell ref="B8:C8"/>
-    <mergeCell ref="A2:C2"/>
-    <mergeCell ref="B12:C12"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/orcamento/Orcamento_JURIDICO_2026.xlsx
+++ b/orcamento/Orcamento_JURIDICO_2026.xlsx
@@ -16083,7 +16083,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S32"/>
+  <dimension ref="A1:S33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -17017,49 +17017,49 @@
         <v/>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="43" t="inlineStr">
+    <row r="33">
+      <c r="A33" s="43" t="inlineStr">
         <is>
           <t>TOTAL GERAL</t>
         </is>
       </c>
-      <c r="B32" s="43" t="n"/>
-      <c r="C32" s="43" t="n"/>
-      <c r="D32" s="43" t="n"/>
-      <c r="E32" s="43" t="n"/>
-      <c r="F32" s="44">
+      <c r="B33" s="43" t="n"/>
+      <c r="C33" s="43" t="n"/>
+      <c r="D33" s="43" t="n"/>
+      <c r="E33" s="43" t="n"/>
+      <c r="F33" s="44">
         <f>SUM(F6:F15)</f>
         <v/>
       </c>
-      <c r="G32" s="44">
+      <c r="G33" s="44">
         <f>SUM(G6:G15)</f>
         <v/>
       </c>
-      <c r="H32" s="44">
+      <c r="H33" s="44">
         <f>SUM(H6:H15)</f>
         <v/>
       </c>
-      <c r="I32" s="44">
+      <c r="I33" s="44">
         <f>SUM(I6:I15)</f>
         <v/>
       </c>
-      <c r="J32" s="44">
+      <c r="J33" s="44">
         <f>SUM(J6:J15)</f>
         <v/>
       </c>
-      <c r="K32" s="44">
+      <c r="K33" s="44">
         <f>SUM(K6:K15)</f>
         <v/>
       </c>
-      <c r="L32" s="45">
-        <f>IFERROR(K32/I32,"")</f>
-        <v/>
-      </c>
-      <c r="M32" s="45">
-        <f>IFERROR(J32/I32,"")</f>
-        <v/>
-      </c>
-      <c r="N32" s="43" t="n"/>
+      <c r="L33" s="45">
+        <f>IFERROR(K33/I33,"")</f>
+        <v/>
+      </c>
+      <c r="M33" s="45">
+        <f>IFERROR(J33/I33,"")</f>
+        <v/>
+      </c>
+      <c r="N33" s="43" t="n"/>
     </row>
   </sheetData>
   <autoFilter ref="A5:N15"/>

--- a/orcamento/Orcamento_JURIDICO_2026.xlsx
+++ b/orcamento/Orcamento_JURIDICO_2026.xlsx
@@ -20117,7 +20117,7 @@
       </c>
       <c r="C11" s="63" t="inlineStr">
         <is>
-          <t>O extrato do financeiro traz gastos relevantes sem linha na ficha. Jurídico: Carneiro Rabelo (R$ 107.742) e Cristiane Carneiro Rabelo (R$ 94.825), somando R$ 202.567 em sete meses; mais Tribunal de Justiça (R$ 49.244), Michele de Oliveira (R$ 23.572) e ONR (R$ 22.576). TI: J H Alves / Monitor Remoto (R$ 20.509) e um bloco de telefonia e infraestrutura de cerca de R$ 15.700 (Claro, TIM, Telefônica, Locaweb, Web Mobile, Sabha, Intelbras, VC1, Alfama).</t>
+          <t>O extrato do financeiro traz gastos relevantes sem linha na ficha. Jurídico: Carneiro Rabelo (R$ 107.742) e Cristiane Carneiro Rabelo (R$ 94.825), somando R$ 202.567 em sete meses; mais Tribunal de Justiça (R$ 49.244), Michele de Oliveira (R$ 23.572) e ONR (R$ 22.576). TI: um bloco de telefonia e infraestrutura de cerca de R$ 15.700 (Claro, TIM, Telefônica, Locaweb, Web Mobile, Sabha, Intelbras, VC1, Alfama). O 'J H Alves — Monitor Remoto' NÃO entra nesta lista: é o Jonathan, que já tem linha no orçamento (TI-E03).</t>
         </is>
       </c>
       <c r="D11" s="63" t="inlineStr">

--- a/orcamento/Orcamento_JURIDICO_2026.xlsx
+++ b/orcamento/Orcamento_JURIDICO_2026.xlsx
@@ -16083,7 +16083,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S33"/>
+  <dimension ref="A1:S34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -17017,49 +17017,49 @@
         <v/>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" s="43" t="inlineStr">
+    <row r="34">
+      <c r="A34" s="43" t="inlineStr">
         <is>
           <t>TOTAL GERAL</t>
         </is>
       </c>
-      <c r="B33" s="43" t="n"/>
-      <c r="C33" s="43" t="n"/>
-      <c r="D33" s="43" t="n"/>
-      <c r="E33" s="43" t="n"/>
-      <c r="F33" s="44">
+      <c r="B34" s="43" t="n"/>
+      <c r="C34" s="43" t="n"/>
+      <c r="D34" s="43" t="n"/>
+      <c r="E34" s="43" t="n"/>
+      <c r="F34" s="44">
         <f>SUM(F6:F15)</f>
         <v/>
       </c>
-      <c r="G33" s="44">
+      <c r="G34" s="44">
         <f>SUM(G6:G15)</f>
         <v/>
       </c>
-      <c r="H33" s="44">
+      <c r="H34" s="44">
         <f>SUM(H6:H15)</f>
         <v/>
       </c>
-      <c r="I33" s="44">
+      <c r="I34" s="44">
         <f>SUM(I6:I15)</f>
         <v/>
       </c>
-      <c r="J33" s="44">
+      <c r="J34" s="44">
         <f>SUM(J6:J15)</f>
         <v/>
       </c>
-      <c r="K33" s="44">
+      <c r="K34" s="44">
         <f>SUM(K6:K15)</f>
         <v/>
       </c>
-      <c r="L33" s="45">
-        <f>IFERROR(K33/I33,"")</f>
-        <v/>
-      </c>
-      <c r="M33" s="45">
-        <f>IFERROR(J33/I33,"")</f>
-        <v/>
-      </c>
-      <c r="N33" s="43" t="n"/>
+      <c r="L34" s="45">
+        <f>IFERROR(K34/I34,"")</f>
+        <v/>
+      </c>
+      <c r="M34" s="45">
+        <f>IFERROR(J34/I34,"")</f>
+        <v/>
+      </c>
+      <c r="N34" s="43" t="n"/>
     </row>
   </sheetData>
   <autoFilter ref="A5:N15"/>

--- a/orcamento/Orcamento_JURIDICO_2026.xlsx
+++ b/orcamento/Orcamento_JURIDICO_2026.xlsx
@@ -20282,7 +20282,7 @@
       </c>
       <c r="D16" s="66" t="inlineStr">
         <is>
-          <t>Reclassificar no SIENGE para o centro de custo correto e aplicar o rateio do item L. Enquanto não for corrigido, o Jurídico carrega R$ 3.351 que não são dele e o TI aparece sem um gasto que é seu — as duas áreas ficam com o comparativo errado. Aproveitar a abertura do novo centro de custo para acertar a classificação desde a origem.</t>
+          <t>DECIDIDO: solicitar a reclassificação contábil ao financeiro agora, sem esperar a abertura do centro de custo novo. Enquanto não for corrigido, o Jurídico carrega R$ 3.351 que não são dele e o TI aparece sem um gasto que é seu — as duas áreas ficam com o comparativo errado ao mesmo tempo. O que pedir ao financeiro: reclassificar os seis lançamentos do contrato 4134643529 (jan a jun/26) do centro de custo Jurídico para o de TI, e ajustar a classificação dos próximos para não repetir. Depois de reclassificado, aplicar o rateio do item L, já que é ferramenta de uso transversal. Quando o centro de custo novo abrir, conferir se a classificação nasceu certa.</t>
         </is>
       </c>
       <c r="E16" s="66" t="inlineStr">
@@ -20290,9 +20290,9 @@
           <t>Cristiane + Financeiro</t>
         </is>
       </c>
-      <c r="F16" s="64" t="inlineStr">
-        <is>
-          <t>RECLASSIFICAR</t>
+      <c r="F16" s="68" t="inlineStr">
+        <is>
+          <t>SOLICITADA</t>
         </is>
       </c>
     </row>

--- a/orcamento/Orcamento_JURIDICO_2026.xlsx
+++ b/orcamento/Orcamento_JURIDICO_2026.xlsx
@@ -16129,7 +16129,7 @@
       </c>
       <c r="B3" s="32" t="inlineStr">
         <is>
-          <t>Jul/26</t>
+          <t>Jun/26</t>
         </is>
       </c>
       <c r="C3" s="33" t="inlineStr">
@@ -18259,11 +18259,9 @@
         <v>6750</v>
       </c>
       <c r="N5" s="50" t="n">
-        <v>6750</v>
-      </c>
-      <c r="O5" s="50" t="n">
         <v>8818</v>
       </c>
+      <c r="O5" s="50" t="n"/>
       <c r="P5" s="50" t="n"/>
       <c r="Q5" s="50" t="n"/>
       <c r="R5" s="50" t="n"/>
@@ -18274,12 +18272,12 @@
       </c>
       <c r="U5" s="51" t="inlineStr">
         <is>
-          <t>Gestora, 05/08/26</t>
+          <t>Gestora, 05/08/26 — competência</t>
         </is>
       </c>
       <c r="V5" s="51" t="inlineStr">
         <is>
-          <t>R$ 6.750/mês de jan a jul; R$ 8.818 pagos em 01/08 (ref. julho). Lançado por caixa</t>
+          <t>R$ 6.750/mês de jan a jun e R$ 8.818 em jul (pago em 01/08). O pagamento de jan/26 era serviço de dez/25 e saiu do exercício</t>
         </is>
       </c>
     </row>
@@ -18344,7 +18342,7 @@
       </c>
       <c r="U6" s="51" t="inlineStr">
         <is>
-          <t>Gestora, 05/08/26</t>
+          <t>Gestora, 05/08/26 — competência</t>
         </is>
       </c>
       <c r="V6" s="51" t="inlineStr">
@@ -18389,7 +18387,7 @@
         <v>4500</v>
       </c>
       <c r="J7" s="50" t="n">
-        <v>4500</v>
+        <v>5500</v>
       </c>
       <c r="K7" s="50" t="n">
         <v>5500</v>
@@ -18400,9 +18398,7 @@
       <c r="M7" s="50" t="n">
         <v>5500</v>
       </c>
-      <c r="N7" s="50" t="n">
-        <v>5500</v>
-      </c>
+      <c r="N7" s="50" t="n"/>
       <c r="O7" s="50" t="n"/>
       <c r="P7" s="50" t="n"/>
       <c r="Q7" s="50" t="n"/>
@@ -18414,12 +18410,12 @@
       </c>
       <c r="U7" s="51" t="inlineStr">
         <is>
-          <t>Gestora, 05/08/26</t>
+          <t>Gestora, 05/08/26 — competência</t>
         </is>
       </c>
       <c r="V7" s="51" t="inlineStr">
         <is>
-          <t>R$ 4.500/mês em jan–mar; aumento de R$ 1.000 a partir de abr/26</t>
+          <t>R$ 4.500 em jan–fev e R$ 5.500 de mar a jun, por competência. CONFERIR: o aumento foi no serviço de mar ou de abr?</t>
         </is>
       </c>
     </row>
@@ -18470,9 +18466,7 @@
       <c r="M8" s="50" t="n">
         <v>2750</v>
       </c>
-      <c r="N8" s="50" t="n">
-        <v>2750</v>
-      </c>
+      <c r="N8" s="50" t="n"/>
       <c r="O8" s="50" t="n"/>
       <c r="P8" s="50" t="n"/>
       <c r="Q8" s="50" t="n"/>
@@ -18484,7 +18478,7 @@
       </c>
       <c r="U8" s="51" t="inlineStr">
         <is>
-          <t>Gestora, 05/08/26</t>
+          <t>Gestora, 05/08/26 — competência</t>
         </is>
       </c>
       <c r="V8" s="51" t="inlineStr">
@@ -18564,7 +18558,7 @@
       </c>
       <c r="U9" s="51" t="inlineStr">
         <is>
-          <t>Gestora, 05/08/26</t>
+          <t>Gestora, 05/08/26 — competência</t>
         </is>
       </c>
       <c r="V9" s="51" t="inlineStr">
@@ -18634,7 +18628,7 @@
       </c>
       <c r="U10" s="51" t="inlineStr">
         <is>
-          <t>Gestora, 05/08/26</t>
+          <t>Gestora, 05/08/26 — competência</t>
         </is>
       </c>
       <c r="V10" s="51" t="inlineStr">
@@ -18784,7 +18778,7 @@
       </c>
       <c r="U12" s="51" t="inlineStr">
         <is>
-          <t>Gestora, 05/08/26</t>
+          <t>Gestora, 05/08/26 — competência</t>
         </is>
       </c>
       <c r="V12" s="51" t="n"/>
@@ -18850,7 +18844,7 @@
       </c>
       <c r="U13" s="51" t="inlineStr">
         <is>
-          <t>Gestora, 05/08/26</t>
+          <t>Gestora, 05/08/26 — competência</t>
         </is>
       </c>
       <c r="V13" s="51" t="inlineStr">
@@ -18920,7 +18914,7 @@
       </c>
       <c r="U14" s="51" t="inlineStr">
         <is>
-          <t>Gestora, 05/08/26</t>
+          <t>Gestora, 05/08/26 — competência</t>
         </is>
       </c>
       <c r="V14" s="51" t="inlineStr">
@@ -20368,17 +20362,17 @@
       </c>
       <c r="B19" s="63" t="inlineStr">
         <is>
-          <t>Competência x caixa — DECIDIR O REGIME</t>
+          <t>Competência x caixa — DECIDIDO: COMPETÊNCIA</t>
         </is>
       </c>
       <c r="C19" s="63" t="inlineStr">
         <is>
-          <t>Confirmado pela gestora: TODOS os PJs das duas áreas prestam o serviço e recebem no mês seguinte — no Jurídico, Miguel, Thamar e Dra. Michele; no TI, Elias e Jonathan. O que foi pago em jan/26 é serviço de dez/2025, e o serviço de dez/26 só será pago em jan/2027. Hoje o realizado está lançado por CAIXA (mês do pagamento), que é como os valores foram informados, enquanto o orçamento foi montado por COMPETÊNCIA (mês do serviço). São bases diferentes no mesmo comparativo.</t>
+          <t>Todos os PJs prestam no mês e recebem no seguinte — Miguel, Thamar e Dra. Michele no Jurídico; Elias e Jonathan no TI. O realizado foi convertido para COMPETÊNCIA: os valores dos PJs foram deslocados um mês para trás em relação à data de pagamento. O que foi pago em jan/26 era serviço de dez/25 e saiu do exercício.</t>
         </is>
       </c>
       <c r="D19" s="63" t="inlineStr">
         <is>
-          <t>RECOMENDAÇÃO: migrar para competência, deslocando os PJs um mês para trás. Motivos: (1) o orçamento já é de competência, então acaba a comparação de bases diferentes; (2) por caixa, o ano de 2026 carrega um mês de 2025 e perde dez/26, o que distorce sempre que o valor muda no meio do ano — no Miguel, R$ 47.250 por caixa contra R$ 49.318 por competência em jan–jul, R$ 2.068 de diferença; (3) o SIENGE gera os dois regimes, então é escolha de configuração. Contra: caixa é mais fácil de bater com o extrato bancário. Decidir UMA vez e manter, senão o histórico mistura critérios. ATENÇÃO NO JONATHAN: o planejado dele começa em abr/26 (competência) e o realizado também foi lançado a partir de abr (caixa) — se ele recebe no mês seguinte, o pagamento de abril é serviço de março, e ou a entrada dele foi em março, ou o realizado de abril deveria ser zero. Conferir junto com a decisão do regime.</t>
+          <t>Três efeitos. (1) O último mês completo passa a ser JUNHO, não julho: o serviço de jul só fecha quando sair o pagamento de ago — o mês de referência do Comparativo foi ajustado. (2) A conversão validou a entrada do Jonathan: por competência, o primeiro mês de serviço dele cai em abr, exatamente como informado. (3) O Monitor Remoto zerou no exercício — aquele pagamento de jan era serviço de dez/25. A CONFERIR: os CLT (Geovanna e Vinicius) NÃO foram deslocados. Se a folha for paga no mês seguinte, como é usual, eles também precisam deslocar. E na Thamar, confirmar se o aumento valeu para o serviço de mar ou de abr. Ao configurar a extração no SIENGE, travar o regime de competência e manter — trocar no meio do ano mistura critérios no histórico.</t>
         </is>
       </c>
       <c r="E19" s="63" t="inlineStr">
@@ -20386,9 +20380,9 @@
           <t>Cristiane + Financeiro</t>
         </is>
       </c>
-      <c r="F19" s="70" t="inlineStr">
-        <is>
-          <t>DECIDIR</t>
+      <c r="F19" s="67" t="inlineStr">
+        <is>
+          <t>APLICADO</t>
         </is>
       </c>
     </row>

--- a/orcamento/Orcamento_JURIDICO_2026.xlsx
+++ b/orcamento/Orcamento_JURIDICO_2026.xlsx
@@ -18328,9 +18328,7 @@
       <c r="M6" s="50" t="n">
         <v>2886.91</v>
       </c>
-      <c r="N6" s="50" t="n">
-        <v>2886.91</v>
-      </c>
+      <c r="N6" s="50" t="n"/>
       <c r="O6" s="50" t="n"/>
       <c r="P6" s="50" t="n"/>
       <c r="Q6" s="50" t="n"/>
@@ -18614,9 +18612,7 @@
       <c r="M10" s="50" t="n">
         <v>136</v>
       </c>
-      <c r="N10" s="50" t="n">
-        <v>136</v>
-      </c>
+      <c r="N10" s="50" t="n"/>
       <c r="O10" s="50" t="n"/>
       <c r="P10" s="50" t="n"/>
       <c r="Q10" s="50" t="n"/>
@@ -18764,9 +18760,7 @@
       <c r="M12" s="50" t="n">
         <v>970</v>
       </c>
-      <c r="N12" s="50" t="n">
-        <v>970</v>
-      </c>
+      <c r="N12" s="50" t="n"/>
       <c r="O12" s="50" t="n"/>
       <c r="P12" s="50" t="n"/>
       <c r="Q12" s="50" t="n"/>
@@ -18830,9 +18824,7 @@
       <c r="M13" s="50" t="n">
         <v>0</v>
       </c>
-      <c r="N13" s="50" t="n">
-        <v>0</v>
-      </c>
+      <c r="N13" s="50" t="n"/>
       <c r="O13" s="50" t="n"/>
       <c r="P13" s="50" t="n"/>
       <c r="Q13" s="50" t="n"/>
@@ -18900,9 +18892,7 @@
       <c r="M14" s="50" t="n">
         <v>0</v>
       </c>
-      <c r="N14" s="50" t="n">
-        <v>0</v>
-      </c>
+      <c r="N14" s="50" t="n"/>
       <c r="O14" s="50" t="n"/>
       <c r="P14" s="50" t="n"/>
       <c r="Q14" s="50" t="n"/>
@@ -20372,7 +20362,7 @@
       </c>
       <c r="D19" s="63" t="inlineStr">
         <is>
-          <t>Três efeitos. (1) O último mês completo passa a ser JUNHO, não julho: o serviço de jul só fecha quando sair o pagamento de ago — o mês de referência do Comparativo foi ajustado. (2) A conversão validou a entrada do Jonathan: por competência, o primeiro mês de serviço dele cai em abr, exatamente como informado. (3) O Monitor Remoto zerou no exercício — aquele pagamento de jan era serviço de dez/25. A CONFERIR: os CLT (Geovanna e Vinicius) NÃO foram deslocados. Se a folha for paga no mês seguinte, como é usual, eles também precisam deslocar. E na Thamar, confirmar se o aumento valeu para o serviço de mar ou de abr. Ao configurar a extração no SIENGE, travar o regime de competência e manter — trocar no meio do ano mistura critérios no histórico.</t>
+          <t>Três efeitos. (1) O último mês completo passa a ser JUNHO, não julho: o serviço de jul só fecha quando sair o pagamento de ago — o mês de referência do Comparativo foi ajustado. (2) A conversão validou a entrada do Jonathan: por competência, o primeiro mês de serviço dele cai em abr, exatamente como informado. (3) O Monitor Remoto zerou no exercício — aquele pagamento de jan era serviço de dez/25. Os CLT (Geovanna e Vinicius) seguem a mesma regra, confirmado pela gestora: folha paga no mês seguinte, também deslocados. A CONFERIR apenas na Thamar: se o aumento valeu para o serviço de mar ou de abr. Ao configurar a extração no SIENGE, travar o regime de competência e manter — trocar no meio do ano mistura critérios no histórico.</t>
         </is>
       </c>
       <c r="E19" s="63" t="inlineStr">
